--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -5,21 +5,22 @@
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\VEDA_Models\PhD_Kristopher\EE-TIMES-New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931DAE3A-F577-4556-849B-139BED96B5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B380FF01-0887-4980-AA73-9EA63544559A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
-    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId2"/>
-    <sheet name="ELC" sheetId="143" r:id="rId3"/>
-    <sheet name="Emi" sheetId="149" r:id="rId4"/>
+    <sheet name="Intra_areas" sheetId="150" r:id="rId2"/>
+    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId3"/>
+    <sheet name="ELC" sheetId="143" r:id="rId4"/>
+    <sheet name="Emi" sheetId="149" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -1512,7 +1513,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="183">
   <si>
     <t>CommName</t>
   </si>
@@ -1937,9 +1938,6 @@
     <t>Share-I~UP</t>
   </si>
   <si>
-    <t>M€2005</t>
-  </si>
-  <si>
     <t>Data used in the template to buld the model</t>
   </si>
   <si>
@@ -2010,6 +2008,60 @@
   </si>
   <si>
     <t>ELCC</t>
+  </si>
+  <si>
+    <t>PARNU</t>
+  </si>
+  <si>
+    <t>TARTU</t>
+  </si>
+  <si>
+    <t>LVIRU</t>
+  </si>
+  <si>
+    <t>IVIRU</t>
+  </si>
+  <si>
+    <t>JARVA</t>
+  </si>
+  <si>
+    <t>JOGEVA</t>
+  </si>
+  <si>
+    <t>POLVA</t>
+  </si>
+  <si>
+    <t>VALGA</t>
+  </si>
+  <si>
+    <t>VILJANDI</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>VORU</t>
+  </si>
+  <si>
+    <t>SAARE</t>
+  </si>
+  <si>
+    <t>RAPLA</t>
+  </si>
+  <si>
+    <t>LAANE</t>
+  </si>
+  <si>
+    <t>HIIU</t>
+  </si>
+  <si>
+    <t>HARJU</t>
+  </si>
+  <si>
+    <t>M€2025</t>
+  </si>
+  <si>
+    <t>TWh</t>
   </si>
 </sst>
 </file>
@@ -2560,7 +2612,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2765,6 +2817,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="30">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -2817,14 +2873,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>3810</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>407670</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2839,7 +2895,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6537960" y="4933949"/>
+          <a:off x="6537960" y="8058149"/>
           <a:ext cx="6376035" cy="981075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2974,16 +3030,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>24974</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>8678</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>109641</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>146261</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>137563</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1090</xdr:rowOff>
+      <xdr:colOff>74063</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>138673</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2998,8 +3054,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10692974" y="4231428"/>
-          <a:ext cx="6483756" cy="1262412"/>
+          <a:off x="12904891" y="9618344"/>
+          <a:ext cx="7097589" cy="1262412"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3703,24 +3759,24 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="B1:AA17"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" customWidth="1"/>
-    <col min="9" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.83203125" customWidth="1"/>
-    <col min="22" max="22" width="7.27734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.71875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.27734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
       <c r="X1" s="19" t="s">
         <v>78</v>
       </c>
@@ -3734,7 +3790,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D2" s="40" t="s">
         <v>42</v>
       </c>
@@ -3769,16 +3825,16 @@
         <v>45</v>
       </c>
       <c r="O2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="P2" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q2" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="P2" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q2" s="40" t="s">
+      <c r="R2" s="40" t="s">
         <v>154</v>
-      </c>
-      <c r="R2" s="40" t="s">
-        <v>155</v>
       </c>
       <c r="S2" s="40" t="s">
         <v>46</v>
@@ -3790,10 +3846,10 @@
         <v>48</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y2" s="39" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="Z2" s="10" t="s">
         <v>68</v>
@@ -3802,7 +3858,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="24.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C3" s="59" t="s">
         <v>121</v>
       </c>
@@ -3840,16 +3896,16 @@
         <v>51</v>
       </c>
       <c r="O3" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P3" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q3" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="Q3" s="41" t="s">
+      <c r="R3" s="41" t="s">
         <v>151</v>
-      </c>
-      <c r="R3" s="41" t="s">
-        <v>152</v>
       </c>
       <c r="S3" s="41" t="s">
         <v>52</v>
@@ -3864,7 +3920,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B4" s="38"/>
       <c r="C4" s="72" t="s">
         <v>55</v>
@@ -3889,7 +3945,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="73"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B5" s="42" t="s">
         <v>56</v>
       </c>
@@ -3954,7 +4010,7 @@
         <v>-1274.6994499999998</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="42" t="s">
         <v>48</v>
       </c>
@@ -4020,7 +4076,7 @@
       </c>
       <c r="X6" s="80"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B7" s="42" t="s">
         <v>59</v>
       </c>
@@ -4085,7 +4141,7 @@
         <v>-26.820549999999912</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B8" s="42" t="s">
         <v>61</v>
       </c>
@@ -4150,7 +4206,7 @@
         <v>-200.86150000000021</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="38"/>
       <c r="C9" s="47" t="s">
         <v>63</v>
@@ -4232,7 +4288,7 @@
         <v>-9781.6922875000037</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -4243,7 +4299,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -4259,9 +4315,9 @@
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
     </row>
-    <row r="12" spans="2:27" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="C12" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="45"/>
       <c r="E12" s="45"/>
@@ -4274,7 +4330,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C15" s="56" t="s">
         <v>89</v>
       </c>
@@ -4285,7 +4341,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B16" s="19" t="s">
         <v>98</v>
       </c>
@@ -4299,7 +4355,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="42" t="s">
         <v>48</v>
       </c>
@@ -4316,31 +4372,121 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6423A684-055B-484D-8A1E-47060250CBEB}">
+  <dimension ref="B2:B17"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R33"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.27734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.1640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.71875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.1640625" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.1640625" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>65</v>
       </c>
@@ -4361,7 +4507,7 @@
       </c>
       <c r="H1" s="31"/>
     </row>
-    <row r="2" spans="2:18" ht="31.2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -4379,7 +4525,7 @@
       </c>
       <c r="F2" s="10" t="str">
         <f>'EB1'!Y2</f>
-        <v>M€2005</v>
+        <v>M€2025</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>84</v>
@@ -4397,7 +4543,7 @@
       <c r="Q2" s="90"/>
       <c r="R2" s="90"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="91" t="s">
         <v>7</v>
       </c>
@@ -4426,7 +4572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -4460,7 +4606,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="68"/>
@@ -4486,7 +4632,7 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="94"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="68"/>
@@ -4512,7 +4658,7 @@
       <c r="Q6" s="94"/>
       <c r="R6" s="94"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="68"/>
@@ -4538,7 +4684,7 @@
       <c r="Q7" s="94"/>
       <c r="R7" s="94"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="68"/>
@@ -4564,7 +4710,7 @@
       <c r="Q8" s="94"/>
       <c r="R8" s="94"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="68"/>
@@ -4590,7 +4736,7 @@
       <c r="Q9" s="94"/>
       <c r="R9" s="94"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="68"/>
@@ -4616,7 +4762,7 @@
       <c r="Q10" s="94"/>
       <c r="R10" s="94"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="68"/>
@@ -4642,7 +4788,7 @@
       <c r="Q11" s="94"/>
       <c r="R11" s="94"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="68"/>
@@ -4668,11 +4814,11 @@
       <c r="Q12" s="94"/>
       <c r="R12" s="94"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L13" s="21"/>
       <c r="M13" s="22"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
@@ -4690,7 +4836,7 @@
       <c r="Q14" s="94"/>
       <c r="R14" s="94"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
         <v>1</v>
       </c>
@@ -4740,7 +4886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>37</v>
       </c>
@@ -4760,7 +4906,7 @@
         <v>75</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J16" s="93" t="s">
         <v>36</v>
@@ -4790,7 +4936,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>76</v>
       </c>
@@ -4799,7 +4945,7 @@
       <c r="E17" s="13"/>
       <c r="F17" s="13" t="str">
         <f>F2&amp;"a"</f>
-        <v>M€2005a</v>
+        <v>M€2025a</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
@@ -4817,7 +4963,7 @@
       <c r="Q17" s="96"/>
       <c r="R17" s="96"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="21" t="str">
         <f>Sector_Fuels_ELC!L18</f>
         <v>FTE-ELCCOA</v>
@@ -4862,7 +5008,7 @@
       <c r="Q18" s="94"/>
       <c r="R18" s="94"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="21" t="str">
         <f>Sector_Fuels_ELC!L19</f>
         <v>FTE-ELCGAS</v>
@@ -4907,7 +5053,7 @@
       <c r="Q19" s="94"/>
       <c r="R19" s="94"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="21" t="str">
         <f>Sector_Fuels_ELC!L20</f>
         <v>FTE-ELCOIL</v>
@@ -4955,7 +5101,7 @@
       <c r="Q20" s="94"/>
       <c r="R20" s="94"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="21"/>
       <c r="C21" t="str">
         <f>'EB1'!I$2</f>
@@ -4993,7 +5139,7 @@
       <c r="Q21" s="94"/>
       <c r="R21" s="94"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="21"/>
       <c r="C22" t="str">
         <f>'EB1'!L$2</f>
@@ -5031,7 +5177,7 @@
       <c r="Q22" s="94"/>
       <c r="R22" s="94"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="21"/>
       <c r="C23" t="str">
         <f>'EB1'!M$2</f>
@@ -5069,7 +5215,7 @@
       <c r="Q23" s="94"/>
       <c r="R23" s="94"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
         <f>Sector_Fuels_ELC!L21</f>
         <v>FTE-ELCNUC</v>
@@ -5114,7 +5260,7 @@
       <c r="Q24" s="94"/>
       <c r="R24" s="94"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="21" t="str">
         <f>Sector_Fuels_ELC!L22</f>
         <v>FTE-ELCBIO</v>
@@ -5159,7 +5305,7 @@
       <c r="Q25" s="94"/>
       <c r="R25" s="94"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
         <f>Sector_Fuels_ELC!L23</f>
         <v>FTE-ELCHYD</v>
@@ -5181,7 +5327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
         <f>Sector_Fuels_ELC!L24</f>
         <v>FTE-ELCWIN</v>
@@ -5203,7 +5349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f>Sector_Fuels_ELC!L25</f>
         <v>FTE-ELCSOL</v>
@@ -5225,16 +5371,16 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="44"/>
       <c r="C32" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="60"/>
       <c r="C33" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5245,40 +5391,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:AB65536"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AB65536"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.27734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="21" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.27734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="2" style="21" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="43.27734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.27734375" customWidth="1"/>
-    <col min="25" max="25" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="45" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.83203125" style="21"/>
+    <col min="28" max="28" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.85546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>65</v>
       </c>
@@ -5301,7 +5447,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="31.2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -5322,7 +5468,7 @@
       </c>
       <c r="G2" s="10" t="str">
         <f>'EB1'!Y2</f>
-        <v>M€2005</v>
+        <v>M€2025</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>84</v>
@@ -5339,7 +5485,7 @@
       <c r="AA2" s="90"/>
       <c r="AB2" s="90"/>
     </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T3" s="91" t="s">
         <v>7</v>
       </c>
@@ -5368,7 +5514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="22.2" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="2:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>107</v>
       </c>
@@ -5414,7 +5560,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
@@ -5437,7 +5583,7 @@
       </c>
       <c r="U5" s="94"/>
       <c r="V5" s="90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W5" s="90" t="str">
         <f>'EB1'!$U$3</f>
@@ -5456,7 +5602,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T6" s="94" t="s">
         <v>88</v>
       </c>
@@ -5478,11 +5624,11 @@
       <c r="AA6" s="94"/>
       <c r="AB6" s="94"/>
     </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -5506,7 +5652,7 @@
       <c r="AA8" s="90"/>
       <c r="AB8" s="90"/>
     </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -5517,25 +5663,25 @@
         <v>6</v>
       </c>
       <c r="E9" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>161</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>162</v>
       </c>
       <c r="G9" s="69" t="s">
         <v>123</v>
       </c>
       <c r="H9" s="69" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I9" s="69" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K9" s="69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L9" s="69" t="s">
         <v>72</v>
@@ -5547,7 +5693,7 @@
         <v>70</v>
       </c>
       <c r="O9" s="69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P9" s="69" t="s">
         <v>118</v>
@@ -5585,7 +5731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -5596,10 +5742,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>34</v>
@@ -5614,7 +5760,7 @@
         <v>82</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>81</v>
@@ -5623,7 +5769,7 @@
         <v>105</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O10" s="15" t="s">
         <v>106</v>
@@ -5663,7 +5809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -5689,15 +5835,15 @@
       <c r="J11" s="70"/>
       <c r="K11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
-        <v>M€2005/GW</v>
+        <v>M€2025/GW</v>
       </c>
       <c r="L11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
-        <v>M€2005/GW</v>
+        <v>M€2025/GW</v>
       </c>
       <c r="M11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
-        <v>M€2005/PJ</v>
+        <v>M€2025/PJ</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>77</v>
@@ -5723,9 +5869,9 @@
       <c r="AA11" s="93"/>
       <c r="AB11" s="93"/>
     </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B12" s="21" t="str">
-        <f t="shared" ref="B12:B19" si="0">V12</f>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B12" s="97" t="str">
+        <f>V12</f>
         <v>ELCTECOA00</v>
       </c>
       <c r="C12" s="21" t="str">
@@ -5733,7 +5879,7 @@
         <v>ELCCOA</v>
       </c>
       <c r="D12" s="21" t="str">
-        <f t="shared" ref="D12:D19" si="1">$V$5</f>
+        <f t="shared" ref="D12:D34" si="0">$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="G12" s="83">
@@ -5764,7 +5910,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="26">
-        <f t="shared" ref="R12:R19" si="2">G12*$J12*$O12</f>
+        <f>G12*$J12*$O12</f>
         <v>2395.6907520000004</v>
       </c>
       <c r="S12" s="84"/>
@@ -5781,11 +5927,11 @@
         <v>Power Plants Existing00 - Solid Fuels</v>
       </c>
       <c r="X12" s="94" t="str">
-        <f t="shared" ref="X12:X19" si="3">$E$2</f>
+        <f t="shared" ref="X12:X19" si="1">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y12" s="94" t="str">
-        <f t="shared" ref="Y12:Y19" si="4">$F$2</f>
+        <f t="shared" ref="Y12:Y19" si="2">$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z12" s="90" t="s">
@@ -5794,9 +5940,9 @@
       <c r="AA12" s="94"/>
       <c r="AB12" s="94"/>
     </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V13</f>
         <v>ELCTEGAS00</v>
       </c>
       <c r="C13" s="21" t="str">
@@ -5804,7 +5950,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D13" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G13" s="83">
@@ -5835,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="26">
-        <f t="shared" si="2"/>
+        <f>G13*$J13*$O13</f>
         <v>1111.1038550399999</v>
       </c>
       <c r="S13" s="29"/>
@@ -5852,20 +5998,20 @@
         <v>Power Plants Existing00 - Natural Gas</v>
       </c>
       <c r="X13" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
       <c r="Y13" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z13" s="94"/>
       <c r="AA13" s="94"/>
       <c r="AB13" s="94"/>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B14" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V14</f>
         <v>ELCTEOIL00</v>
       </c>
       <c r="C14" s="21" t="str">
@@ -5873,7 +6019,7 @@
         <v>ELCOIL</v>
       </c>
       <c r="D14" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G14" s="83">
@@ -5904,7 +6050,7 @@
         <v>1</v>
       </c>
       <c r="R14" s="26">
-        <f t="shared" si="2"/>
+        <f>G14*$J14*$O14</f>
         <v>153.07612499999996</v>
       </c>
       <c r="S14" s="29"/>
@@ -5921,20 +6067,20 @@
         <v>Power Plants Existing00 - Crude oil</v>
       </c>
       <c r="X14" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
       <c r="Y14" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z14" s="94"/>
       <c r="AA14" s="94"/>
       <c r="AB14" s="94"/>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B15" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V15</f>
         <v>ELCNENUC00</v>
       </c>
       <c r="C15" s="21" t="str">
@@ -5942,7 +6088,7 @@
         <v>ELCNUC</v>
       </c>
       <c r="D15" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G15" s="83">
@@ -5974,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="R15" s="26">
-        <f t="shared" si="2"/>
+        <f>G15*$J15*$O15</f>
         <v>1470.1500000000003</v>
       </c>
       <c r="S15" s="29"/>
@@ -5991,11 +6137,11 @@
         <v>Power Plants Existing00 - Nuclear Energy</v>
       </c>
       <c r="X15" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
       <c r="Y15" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z15" s="90" t="s">
@@ -6004,9 +6150,9 @@
       <c r="AA15" s="94"/>
       <c r="AB15" s="94"/>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B16" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V16</f>
         <v>ELCREBIO00</v>
       </c>
       <c r="C16" s="21" t="str">
@@ -6014,7 +6160,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D16" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G16" s="83">
@@ -6045,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="R16" s="26">
-        <f t="shared" si="2"/>
+        <f>G16*$J16*$O16</f>
         <v>147.63257250000001</v>
       </c>
       <c r="S16" s="29"/>
@@ -6062,20 +6208,20 @@
         <v>Power Plants Existing00 - Biomass</v>
       </c>
       <c r="X16" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
       <c r="Y16" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z16" s="90"/>
       <c r="AA16" s="94"/>
       <c r="AB16" s="94"/>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B17" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V17</f>
         <v>ELCREHYD00</v>
       </c>
       <c r="C17" s="21" t="str">
@@ -6083,7 +6229,7 @@
         <v>ELCHYD</v>
       </c>
       <c r="D17" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="E17" s="43">
@@ -6134,20 +6280,20 @@
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
       <c r="X17" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
       <c r="Y17" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z17" s="94"/>
       <c r="AA17" s="94"/>
       <c r="AB17" s="94"/>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B18" s="21" t="str">
-        <f t="shared" si="0"/>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B18" s="97" t="str">
+        <f>V18</f>
         <v>ELCREWIN00</v>
       </c>
       <c r="C18" s="21" t="str">
@@ -6155,7 +6301,7 @@
         <v>ELCWIN</v>
       </c>
       <c r="D18" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G18" s="83">
@@ -6186,37 +6332,37 @@
         <v>0.3</v>
       </c>
       <c r="R18" s="26">
-        <f t="shared" si="2"/>
+        <f>G18*$J18*$O18</f>
         <v>263.8965</v>
       </c>
       <c r="S18" s="29"/>
-      <c r="T18" s="94" t="s">
+      <c r="T18" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="U18" s="94"/>
-      <c r="V18" s="94" t="str">
+      <c r="U18" s="99"/>
+      <c r="V18" s="99" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$11,3)&amp;"00"</f>
         <v>ELCREWIN00</v>
       </c>
-      <c r="W18" s="94" t="str">
+      <c r="W18" s="99" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" - "&amp;'EB1'!Q3</f>
         <v>Power Plants Existing00 - Wind energy</v>
       </c>
-      <c r="X18" s="94" t="str">
-        <f t="shared" si="3"/>
+      <c r="X18" s="99" t="str">
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="Y18" s="94" t="str">
-        <f t="shared" si="4"/>
+      <c r="Y18" s="99" t="str">
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z18" s="94"/>
       <c r="AA18" s="94"/>
       <c r="AB18" s="94"/>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f>V19</f>
         <v>ELCRESOL00</v>
       </c>
       <c r="C19" s="21" t="str">
@@ -6224,7 +6370,7 @@
         <v>ELCSOL</v>
       </c>
       <c r="D19" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G19" s="83">
@@ -6253,58 +6399,914 @@
         <v>0.2</v>
       </c>
       <c r="R19" s="26">
-        <f t="shared" si="2"/>
+        <f>G19*$J19*$O19</f>
         <v>68</v>
       </c>
       <c r="S19" s="29"/>
-      <c r="T19" s="94" t="s">
+      <c r="T19" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94" t="str">
+      <c r="U19" s="98"/>
+      <c r="V19" s="98" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"00"</f>
         <v>ELCRESOL00</v>
       </c>
-      <c r="W19" s="94" t="str">
+      <c r="W19" s="98" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" - "&amp;'EB1'!R3</f>
         <v>Power Plants Existing00 - Solar energy</v>
       </c>
-      <c r="X19" s="94" t="str">
-        <f t="shared" si="3"/>
+      <c r="X19" s="98" t="str">
+        <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="Y19" s="94" t="str">
-        <f t="shared" si="4"/>
+      <c r="Y19" s="98" t="str">
+        <f t="shared" si="2"/>
         <v>GW</v>
       </c>
       <c r="Z19" s="94"/>
       <c r="AA19" s="94"/>
       <c r="AB19" s="94"/>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="str">
+        <f>V20</f>
+        <v>ELCRESOL_PARNU00</v>
+      </c>
+      <c r="C20" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D20" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G20">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="I20" s="101">
+        <v>1</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L20" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M20" s="88">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21">
+        <v>35</v>
+      </c>
+      <c r="O20" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P20" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T20" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V20" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
+        <v>ELCRESOL_PARNU00</v>
+      </c>
+      <c r="W20" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in PARNU - Solar energy</v>
+      </c>
+      <c r="X20" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B21" s="21" t="str">
+        <f t="shared" ref="B21:B34" si="3">V21</f>
+        <v>ELCRESOL_TARTU00</v>
+      </c>
+      <c r="C21" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D21" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G21">
+        <v>0.108</v>
+      </c>
+      <c r="I21" s="101">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L21" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M21" s="88">
+        <v>0</v>
+      </c>
+      <c r="N21" s="21">
+        <v>35</v>
+      </c>
+      <c r="O21" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P21" s="21">
+        <v>0.2</v>
+      </c>
       <c r="R21" s="82"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="T21" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V21" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
+        <v>ELCRESOL_TARTU00</v>
+      </c>
+      <c r="W21" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in TARTU - Solar energy</v>
+      </c>
+      <c r="X21" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A22" s="100"/>
+      <c r="B22" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="C22" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D22" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G22">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="I22" s="101">
+        <v>1</v>
+      </c>
+      <c r="K22" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L22" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M22" s="88">
+        <v>0</v>
+      </c>
+      <c r="N22" s="21">
+        <v>35</v>
+      </c>
+      <c r="O22" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P22" s="21">
+        <v>0.2</v>
+      </c>
       <c r="R22" s="82"/>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B23" s="44"/>
-      <c r="C23" s="1" t="s">
-        <v>144</v>
+      <c r="T22" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V22" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="W22" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LVIRU - Solar energy</v>
+      </c>
+      <c r="X22" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A23" s="100"/>
+      <c r="B23" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_IVIRU00</v>
+      </c>
+      <c r="C23" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D23" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G23">
+        <v>7.8E-2</v>
+      </c>
+      <c r="I23" s="101">
+        <v>1</v>
+      </c>
+      <c r="K23" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L23" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M23" s="88">
+        <v>0</v>
+      </c>
+      <c r="N23" s="21">
+        <v>35</v>
+      </c>
+      <c r="O23" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P23" s="21">
+        <v>0.2</v>
       </c>
       <c r="R23" s="82"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B24" s="60"/>
-      <c r="C24" s="1" t="s">
-        <v>145</v>
+      <c r="T23" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V23" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
+        <v>ELCRESOL_IVIRU00</v>
+      </c>
+      <c r="W23" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in IVIRU - Solar energy</v>
+      </c>
+      <c r="X23" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A24" s="100"/>
+      <c r="B24" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_JARVA00</v>
+      </c>
+      <c r="C24" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D24" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G24">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="I24" s="101">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L24" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M24" s="88">
+        <v>0</v>
+      </c>
+      <c r="N24" s="21">
+        <v>35</v>
+      </c>
+      <c r="O24" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P24" s="21">
+        <v>0.2</v>
       </c>
       <c r="R24" s="82"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.4">
+      <c r="T24" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V24" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
+        <v>ELCRESOL_JARVA00</v>
+      </c>
+      <c r="W24" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in JARVA - Solar energy</v>
+      </c>
+      <c r="X24" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A25" s="100"/>
+      <c r="B25" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_JOGEVA00</v>
+      </c>
+      <c r="C25" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D25" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G25">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I25" s="101">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L25" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M25" s="88">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21">
+        <v>35</v>
+      </c>
+      <c r="O25" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P25" s="21">
+        <v>0.2</v>
+      </c>
       <c r="R25" s="82"/>
-    </row>
-    <row r="65536" spans="19:19" x14ac:dyDescent="0.4">
+      <c r="T25" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V25" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
+        <v>ELCRESOL_JOGEVA00</v>
+      </c>
+      <c r="W25" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
+      </c>
+      <c r="X25" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B26" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="C26" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D26" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G26">
+        <v>0.04</v>
+      </c>
+      <c r="I26" s="101">
+        <v>1</v>
+      </c>
+      <c r="K26" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L26" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M26" s="88">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21">
+        <v>35</v>
+      </c>
+      <c r="O26" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P26" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T26" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V26" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="W26" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in HARJU - Solar energy</v>
+      </c>
+      <c r="X26" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B27" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_POLVA00</v>
+      </c>
+      <c r="C27" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D27" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G27">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="I27" s="101">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L27" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M27" s="88">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21">
+        <v>35</v>
+      </c>
+      <c r="O27" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P27" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T27" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V27" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
+        <v>ELCRESOL_POLVA00</v>
+      </c>
+      <c r="W27" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in POLVA - Solar energy</v>
+      </c>
+      <c r="X27" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B28" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_VALGA00</v>
+      </c>
+      <c r="C28" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="D28" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G28">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I28" s="101">
+        <v>1</v>
+      </c>
+      <c r="K28" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L28" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M28" s="88">
+        <v>0</v>
+      </c>
+      <c r="N28" s="21">
+        <v>35</v>
+      </c>
+      <c r="O28" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P28" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T28" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V28" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
+        <v>ELCRESOL_VALGA00</v>
+      </c>
+      <c r="W28" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in VALGA - Solar energy</v>
+      </c>
+      <c r="X28" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B29" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_VILJANDI00</v>
+      </c>
+      <c r="C29" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L13,3)</f>
+        <v>ELC</v>
+      </c>
+      <c r="D29" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G29">
+        <v>0.08</v>
+      </c>
+      <c r="I29" s="101">
+        <v>1</v>
+      </c>
+      <c r="K29" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L29" s="88">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M29" s="88">
+        <v>0</v>
+      </c>
+      <c r="N29" s="21">
+        <v>35</v>
+      </c>
+      <c r="O29" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P29" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T29" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V29" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
+        <v>ELCRESOL_VILJANDI00</v>
+      </c>
+      <c r="W29" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
+      </c>
+      <c r="X29" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B30" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_VORU00</v>
+      </c>
+      <c r="C30" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELC</v>
+      </c>
+      <c r="D30" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G30">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I30" s="101">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7">
+        <v>1019</v>
+      </c>
+      <c r="L30" s="88">
+        <v>16.079820000000002</v>
+      </c>
+      <c r="M30" s="88">
+        <v>0</v>
+      </c>
+      <c r="N30" s="21">
+        <v>35</v>
+      </c>
+      <c r="O30" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P30" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T30" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V30" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
+        <v>ELCRESOL_VORU00</v>
+      </c>
+      <c r="W30" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in VORU - Solar energy</v>
+      </c>
+      <c r="X30" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B31" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_SAARE00</v>
+      </c>
+      <c r="C31" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)</f>
+        <v>ELCame</v>
+      </c>
+      <c r="D31" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G31">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I31" s="101">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7">
+        <v>1020</v>
+      </c>
+      <c r="L31" s="88">
+        <v>16.095600000000001</v>
+      </c>
+      <c r="M31" s="88">
+        <v>0</v>
+      </c>
+      <c r="N31" s="21">
+        <v>35</v>
+      </c>
+      <c r="O31" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P31" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T31" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V31" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
+        <v>ELCRESOL_SAARE00</v>
+      </c>
+      <c r="W31" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SAARE - Solar energy</v>
+      </c>
+      <c r="X31" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B32" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_RAPLA00</v>
+      </c>
+      <c r="C32" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L16,3)</f>
+        <v>ELCame</v>
+      </c>
+      <c r="D32" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G32">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I32" s="101">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7">
+        <v>1021</v>
+      </c>
+      <c r="L32" s="88">
+        <v>16.111380000000004</v>
+      </c>
+      <c r="M32" s="88">
+        <v>0</v>
+      </c>
+      <c r="N32" s="21">
+        <v>35</v>
+      </c>
+      <c r="O32" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P32" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T32" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V32" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
+        <v>ELCRESOL_RAPLA00</v>
+      </c>
+      <c r="W32" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in RAPLA - Solar energy</v>
+      </c>
+      <c r="X32" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="C33" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L17,3)</f>
+        <v>ELC</v>
+      </c>
+      <c r="D33" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G33">
+        <v>0.01</v>
+      </c>
+      <c r="I33" s="101">
+        <v>1</v>
+      </c>
+      <c r="K33" s="7">
+        <v>1022</v>
+      </c>
+      <c r="L33" s="88">
+        <v>16.127160000000003</v>
+      </c>
+      <c r="M33" s="88">
+        <v>0</v>
+      </c>
+      <c r="N33" s="21">
+        <v>35</v>
+      </c>
+      <c r="O33" s="66">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="P33" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T33" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V33" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="W33" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LAANE - Solar energy</v>
+      </c>
+      <c r="X33" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B34" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_HIIU00</v>
+      </c>
+      <c r="C34" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L18,3)</f>
+        <v>ELCCOA</v>
+      </c>
+      <c r="D34" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G34">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I34" s="101">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7">
+        <v>1023</v>
+      </c>
+      <c r="L34" s="88">
+        <v>16.142940000000003</v>
+      </c>
+      <c r="M34" s="88">
+        <v>0</v>
+      </c>
+      <c r="N34" s="21">
+        <v>35</v>
+      </c>
+      <c r="O34" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P34" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="T34" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V34" s="94" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
+        <v>ELCRESOL_HIIU00</v>
+      </c>
+      <c r="W34" s="94" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in HIIU - Solar energy</v>
+      </c>
+      <c r="X34" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65536" spans="19:19" x14ac:dyDescent="0.2">
       <c r="S65536" s="29"/>
     </row>
   </sheetData>
@@ -6315,17 +7317,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:J24"/>
-  <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
@@ -6336,7 +7338,7 @@
       <c r="I3" s="34"/>
       <c r="J3" s="34"/>
     </row>
-    <row r="4" spans="2:10" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -6344,13 +7346,13 @@
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
     </row>
-    <row r="5" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>138</v>
       </c>
       <c r="C5" s="33"/>
     </row>
-    <row r="6" spans="2:10" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
         <v>0</v>
       </c>
@@ -6370,24 +7372,24 @@
       <c r="G6" s="36"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="2:10" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F7" s="76"/>
       <c r="G7" s="76"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="21" t="str">
         <f>ELC!$V$6</f>
         <v>ELCCO2</v>
@@ -6405,16 +7407,16 @@
       <c r="G8" s="77"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="60"/>
       <c r="C24" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B380FF01-0887-4980-AA73-9EA63544559A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48489F3D-34C0-42E2-BF33-7E3EA11F39B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6964,8 +6964,8 @@
         <v>ELCRESOL_VILJANDI00</v>
       </c>
       <c r="C29" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L13,3)</f>
-        <v>ELC</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D29" s="21" t="str">
         <f t="shared" si="0"/>
@@ -7022,8 +7022,8 @@
         <v>ELCRESOL_VORU00</v>
       </c>
       <c r="C30" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELC</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D30" s="21" t="str">
         <f t="shared" si="0"/>
@@ -7080,8 +7080,8 @@
         <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="C31" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)</f>
-        <v>ELCame</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D31" s="21" t="str">
         <f t="shared" si="0"/>
@@ -7138,8 +7138,8 @@
         <v>ELCRESOL_RAPLA00</v>
       </c>
       <c r="C32" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L16,3)</f>
-        <v>ELCame</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D32" s="21" t="str">
         <f t="shared" si="0"/>
@@ -7196,8 +7196,8 @@
         <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="C33" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L17,3)</f>
-        <v>ELC</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D33" s="21" t="str">
         <f t="shared" si="0"/>
@@ -7254,8 +7254,8 @@
         <v>ELCRESOL_HIIU00</v>
       </c>
       <c r="C34" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L18,3)</f>
-        <v>ELCCOA</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D34" s="21" t="str">
         <f t="shared" si="0"/>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48489F3D-34C0-42E2-BF33-7E3EA11F39B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5EA78E-ADC3-4ECF-97F6-B4A16E229781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="P17" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -442,7 +442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="Q17" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -467,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="R17" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -530,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="J18" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1513,7 +1513,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="193">
   <si>
     <t>CommName</t>
   </si>
@@ -2062,6 +2062,36 @@
   </si>
   <si>
     <t>TWh</t>
+  </si>
+  <si>
+    <t>Windon</t>
+  </si>
+  <si>
+    <t>SOPIPURTSE</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>SOPITOOTSI</t>
+  </si>
+  <si>
+    <t>ELCWON</t>
+  </si>
+  <si>
+    <t>Electricity Plants Wind Offshore energy</t>
+  </si>
+  <si>
+    <t>Electricity Plants Wind Onshore energy</t>
+  </si>
+  <si>
+    <t>ELCWOF</t>
+  </si>
+  <si>
+    <t>Wind onshore energy</t>
+  </si>
+  <si>
+    <t>Wind offshore energy</t>
   </si>
 </sst>
 </file>
@@ -2873,13 +2903,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>3810</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>407670</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3758,7 +3788,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="B1:AA17"/>
+  <dimension ref="B1:AC17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3768,29 +3798,29 @@
     <col min="8" max="8" width="12.140625" customWidth="1"/>
     <col min="9" max="12" width="10.85546875" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="10.85546875" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="X1" s="19" t="s">
+    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="Z1" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D2" s="40" t="s">
         <v>42</v>
       </c>
@@ -3834,31 +3864,37 @@
         <v>153</v>
       </c>
       <c r="R2" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="S2" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="T2" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="U2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="T2" s="40" t="s">
+      <c r="V2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="W2" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="X2" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="AA2" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="AB2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AC2" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:29" ht="38.25" x14ac:dyDescent="0.2">
       <c r="C3" s="59" t="s">
         <v>121</v>
       </c>
@@ -3905,22 +3941,28 @@
         <v>150</v>
       </c>
       <c r="R3" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="S3" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="T3" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="S3" s="41" t="s">
+      <c r="U3" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="41" t="s">
+      <c r="V3" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="41" t="s">
+      <c r="W3" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="V3" s="41" t="s">
+      <c r="X3" s="41" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B4" s="38"/>
       <c r="C4" s="72" t="s">
         <v>55</v>
@@ -3943,9 +3985,11 @@
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
-      <c r="V4" s="73"/>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="73"/>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B5" s="42" t="s">
         <v>56</v>
       </c>
@@ -3994,23 +4038,25 @@
       <c r="Q5" s="43">
         <v>0</v>
       </c>
-      <c r="R5" s="43">
-        <v>0</v>
-      </c>
-      <c r="S5" s="43">
-        <v>-0.76</v>
-      </c>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
       <c r="T5" s="43">
         <v>0</v>
       </c>
       <c r="U5" s="43">
+        <v>-0.76</v>
+      </c>
+      <c r="V5" s="43">
         <v>0</v>
       </c>
-      <c r="V5" s="74">
+      <c r="W5" s="43">
+        <v>0</v>
+      </c>
+      <c r="X5" s="74">
         <v>-1274.6994499999998</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:29" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="42" t="s">
         <v>48</v>
       </c>
@@ -4059,24 +4105,26 @@
       <c r="Q6" s="45">
         <v>-263.8965</v>
       </c>
-      <c r="R6" s="45">
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="45">
         <v>-68</v>
       </c>
-      <c r="S6" s="43">
+      <c r="U6" s="43">
         <v>-16.474499999999999</v>
       </c>
-      <c r="T6" s="43">
+      <c r="V6" s="43">
         <v>868.77949999999998</v>
       </c>
-      <c r="U6" s="45">
+      <c r="W6" s="45">
         <v>5790.5</v>
       </c>
-      <c r="V6" s="74">
+      <c r="X6" s="74">
         <v>-8279.3107875000023</v>
       </c>
-      <c r="X6" s="80"/>
-    </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="Z6" s="80"/>
+    </row>
+    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B7" s="42" t="s">
         <v>59</v>
       </c>
@@ -4125,23 +4173,25 @@
       <c r="Q7" s="43">
         <v>0</v>
       </c>
-      <c r="R7" s="43">
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43">
         <v>0</v>
       </c>
-      <c r="S7" s="43">
+      <c r="U7" s="43">
         <v>-0.78449999999999998</v>
       </c>
-      <c r="T7" s="43">
+      <c r="V7" s="43">
         <v>329.37150000000003</v>
       </c>
-      <c r="U7" s="43">
+      <c r="W7" s="43">
         <v>0</v>
       </c>
-      <c r="V7" s="74">
+      <c r="X7" s="74">
         <v>-26.820549999999912</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B8" s="42" t="s">
         <v>61</v>
       </c>
@@ -4190,23 +4240,25 @@
       <c r="Q8" s="43">
         <v>0</v>
       </c>
-      <c r="R8" s="43">
-        <v>0</v>
-      </c>
-      <c r="S8" s="43">
-        <v>0</v>
-      </c>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
       <c r="T8" s="43">
         <v>0</v>
       </c>
       <c r="U8" s="43">
         <v>0</v>
       </c>
-      <c r="V8" s="74">
+      <c r="V8" s="43">
+        <v>0</v>
+      </c>
+      <c r="W8" s="43">
+        <v>0</v>
+      </c>
+      <c r="X8" s="74">
         <v>-200.86150000000021</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:29" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="38"/>
       <c r="C9" s="47" t="s">
         <v>63</v>
@@ -4216,7 +4268,7 @@
         <v>-6381.1501000000017</v>
       </c>
       <c r="E9" s="48">
-        <f t="shared" ref="E9:U9" si="0">SUM(E5:E8)</f>
+        <f t="shared" ref="E9:W9" si="0">SUM(E5:E8)</f>
         <v>-2691.93</v>
       </c>
       <c r="F9" s="48">
@@ -4267,28 +4319,30 @@
         <f t="shared" si="0"/>
         <v>-263.8965</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48">
         <f t="shared" si="0"/>
         <v>-68</v>
       </c>
-      <c r="S9" s="48">
+      <c r="U9" s="48">
         <f t="shared" si="0"/>
         <v>-18.019000000000002</v>
       </c>
-      <c r="T9" s="48">
+      <c r="V9" s="48">
         <f t="shared" si="0"/>
         <v>1198.1510000000001</v>
       </c>
-      <c r="U9" s="48">
+      <c r="W9" s="48">
         <f t="shared" si="0"/>
         <v>5790.5</v>
       </c>
-      <c r="V9" s="49">
-        <f>SUM(V5:V8)</f>
+      <c r="X9" s="49">
+        <f>SUM(X5:X8)</f>
         <v>-9781.6922875000037</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -4299,7 +4353,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -4314,8 +4368,10 @@
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
-    </row>
-    <row r="12" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+    </row>
+    <row r="12" spans="2:29" ht="15" x14ac:dyDescent="0.25">
       <c r="C12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4330,7 +4386,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C15" s="56" t="s">
         <v>89</v>
       </c>
@@ -4341,7 +4397,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B16" s="19" t="s">
         <v>98</v>
       </c>
@@ -4373,80 +4429,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6423A684-055B-484D-8A1E-47060250CBEB}">
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>178</v>
       </c>
@@ -4463,7 +4552,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:R33"/>
+  <dimension ref="B1:R35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4520,11 +4609,11 @@
         <v>94</v>
       </c>
       <c r="E2" s="10" t="str">
-        <f>'EB1'!Z2</f>
+        <f>'EB1'!AB2</f>
         <v>PJ</v>
       </c>
       <c r="F2" s="10" t="str">
-        <f>'EB1'!Y2</f>
+        <f>'EB1'!AA2</f>
         <v>M€2025</v>
       </c>
       <c r="G2" s="10" t="s">
@@ -4624,7 +4713,7 @@
         <v>Electricity Plants Solid Fuels</v>
       </c>
       <c r="N5" s="94" t="str">
-        <f t="shared" ref="N5:N12" si="0">$E$2</f>
+        <f t="shared" ref="N5:N14" si="0">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O5" s="94"/>
@@ -4797,17 +4886,14 @@
         <v>64</v>
       </c>
       <c r="K12" s="94"/>
-      <c r="L12" s="94" t="str">
-        <f>$B$2&amp;'EB1'!$R$2</f>
-        <v>ELCSOL</v>
-      </c>
-      <c r="M12" s="95" t="str">
-        <f>$C$2&amp;" "&amp;'EB1'!$R$3</f>
-        <v>Electricity Plants Solar energy</v>
-      </c>
-      <c r="N12" s="94" t="str">
-        <f t="shared" si="0"/>
-        <v>PJ</v>
+      <c r="L12" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="M12" s="95" t="s">
+        <v>189</v>
+      </c>
+      <c r="N12" s="94" t="s">
+        <v>68</v>
       </c>
       <c r="O12" s="94"/>
       <c r="P12" s="94"/>
@@ -4815,261 +4901,217 @@
       <c r="R12" s="94"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L13" s="21"/>
-      <c r="M13" s="22"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="11"/>
+      <c r="J13" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94" t="s">
+        <v>190</v>
+      </c>
+      <c r="M13" s="95" t="s">
+        <v>188</v>
+      </c>
+      <c r="N13" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="J14" s="89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="89"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="94"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="11"/>
+      <c r="J14" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="94"/>
+      <c r="L14" s="94" t="str">
+        <f>$B$2&amp;'EB1'!$T$2</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="M14" s="95" t="str">
+        <f>$C$2&amp;" "&amp;'EB1'!$T$3</f>
+        <v>Electricity Plants Solar energy</v>
+      </c>
+      <c r="N14" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="O14" s="94"/>
       <c r="P14" s="94"/>
       <c r="Q14" s="94"/>
       <c r="R14" s="94"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="16" t="s">
+      <c r="L15" s="21"/>
+      <c r="M15" s="22"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="J16" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="89"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E17" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="69" t="s">
+      <c r="F17" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G17" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="69" t="s">
+      <c r="H17" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="91" t="s">
+      <c r="J17" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="92" t="s">
+      <c r="K17" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="91" t="s">
+      <c r="L17" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="91" t="s">
+      <c r="M17" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="N15" s="91" t="s">
+      <c r="N17" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="91" t="s">
+      <c r="O17" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="91" t="s">
+      <c r="P17" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="Q15" s="91" t="s">
+      <c r="Q17" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="R15" s="91" t="s">
+      <c r="R17" s="91" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+    <row r="18" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F18" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G18" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H18" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J16" s="93" t="s">
+      <c r="J18" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="K16" s="93" t="s">
+      <c r="K18" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="93" t="s">
+      <c r="L18" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="93" t="s">
+      <c r="M18" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="93" t="s">
+      <c r="N18" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="O16" s="93" t="s">
+      <c r="O18" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="P16" s="93" t="s">
+      <c r="P18" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="Q16" s="93" t="s">
+      <c r="Q18" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="R16" s="93" t="s">
+      <c r="R18" s="93" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
+    <row r="19" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="str">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13" t="str">
         <f>F2&amp;"a"</f>
         <v>M€2025a</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13" t="s">
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="93" t="s">
+      <c r="J19" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B18" s="21" t="str">
-        <f>Sector_Fuels_ELC!L18</f>
-        <v>FTE-ELCCOA</v>
-      </c>
-      <c r="C18" t="str">
-        <f>RIGHT(D18,3)</f>
-        <v>COA</v>
-      </c>
-      <c r="D18" s="21" t="str">
-        <f>L5</f>
-        <v>ELCCOA</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="63">
-        <v>1</v>
-      </c>
-      <c r="H18" s="64">
-        <v>30</v>
-      </c>
-      <c r="J18" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K18" s="97"/>
-      <c r="L18" s="94" t="str">
-        <f t="shared" ref="L18:L25" si="1">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
-        <v>FTE-ELCCOA</v>
-      </c>
-      <c r="M18" s="95" t="str">
-        <f t="shared" ref="M18:M25" si="2">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
-      </c>
-      <c r="N18" s="94" t="str">
-        <f t="shared" ref="N18:N25" si="3">$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="O18" s="94" t="str">
-        <f t="shared" ref="O18:O25" si="4">$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="21" t="str">
-        <f>Sector_Fuels_ELC!L19</f>
-        <v>FTE-ELCGAS</v>
-      </c>
-      <c r="C19" t="str">
-        <f>RIGHT(D19,3)</f>
-        <v>GAS</v>
-      </c>
-      <c r="D19" s="21" t="str">
-        <f>L6</f>
-        <v>ELCGAS</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="63">
-        <v>1</v>
-      </c>
-      <c r="H19" s="64">
-        <v>30</v>
-      </c>
-      <c r="J19" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" s="97"/>
-      <c r="L19" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>FTE-ELCGAS</v>
-      </c>
-      <c r="M19" s="95" t="str">
-        <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
-      </c>
-      <c r="N19" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O19" s="94" t="str">
-        <f t="shared" si="4"/>
-        <v>PJa</v>
-      </c>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="21" t="str">
         <f>Sector_Fuels_ELC!L20</f>
-        <v>FTE-ELCOIL</v>
+        <v>FTE-ELCCOA</v>
       </c>
       <c r="C20" t="str">
-        <f>'EB1'!G$2</f>
-        <v>DSL</v>
+        <f>RIGHT(D20,3)</f>
+        <v>COA</v>
       </c>
       <c r="D20" s="21" t="str">
-        <f>L7</f>
-        <v>ELCOIL</v>
-      </c>
-      <c r="E20" s="62">
-        <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>4.9257354796510562E-2</v>
-      </c>
+        <f>L5</f>
+        <v>ELCCOA</v>
+      </c>
+      <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="63">
         <v>1</v>
@@ -5082,19 +5124,19 @@
       </c>
       <c r="K20" s="97"/>
       <c r="L20" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>FTE-ELCOIL</v>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <v>FTE-ELCCOA</v>
       </c>
       <c r="M20" s="95" t="str">
-        <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants oil</v>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
       <c r="N20" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="N20:N29" si="1">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O20" s="94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="O20:O29" si="2">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P20" s="94"/>
@@ -5102,37 +5144,44 @@
       <c r="R20" s="94"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="21"/>
+      <c r="B21" s="21" t="str">
+        <f>Sector_Fuels_ELC!L21</f>
+        <v>FTE-ELCGAS</v>
+      </c>
       <c r="C21" t="str">
-        <f>'EB1'!I$2</f>
-        <v>LPG</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="62">
-        <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>3.8926710484734312E-2</v>
-      </c>
+        <f>RIGHT(D21,3)</f>
+        <v>GAS</v>
+      </c>
+      <c r="D21" s="21" t="str">
+        <f>L6</f>
+        <v>ELCGAS</v>
+      </c>
+      <c r="E21" s="12"/>
       <c r="F21" s="12"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="64"/>
+      <c r="G21" s="63">
+        <v>1</v>
+      </c>
+      <c r="H21" s="64">
+        <v>30</v>
+      </c>
       <c r="J21" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="K21" s="94"/>
+      <c r="K21" s="97"/>
       <c r="L21" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
+        <v>FTE-ELCGAS</v>
+      </c>
+      <c r="M21" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
+      </c>
+      <c r="N21" s="94" t="str">
         <f t="shared" si="1"/>
-        <v>FTE-ELCNUC</v>
-      </c>
-      <c r="M21" s="95" t="str">
+        <v>PJ</v>
+      </c>
+      <c r="O21" s="94" t="str">
         <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
-      </c>
-      <c r="N21" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O21" s="94" t="str">
-        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P21" s="94"/>
@@ -5140,37 +5189,47 @@
       <c r="R21" s="94"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="21"/>
+      <c r="B22" s="21" t="str">
+        <f>Sector_Fuels_ELC!L22</f>
+        <v>FTE-ELCOIL</v>
+      </c>
       <c r="C22" t="str">
-        <f>'EB1'!L$2</f>
-        <v>HFO</v>
-      </c>
-      <c r="D22" s="21"/>
+        <f>'EB1'!G$2</f>
+        <v>DSL</v>
+      </c>
+      <c r="D22" s="21" t="str">
+        <f>L7</f>
+        <v>ELCOIL</v>
+      </c>
       <c r="E22" s="62">
-        <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>0.85705723214511731</v>
+        <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>4.9257354796510562E-2</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="64"/>
+      <c r="G22" s="63">
+        <v>1</v>
+      </c>
+      <c r="H22" s="64">
+        <v>30</v>
+      </c>
       <c r="J22" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="94"/>
+      <c r="K22" s="97"/>
       <c r="L22" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
+        <v>FTE-ELCOIL</v>
+      </c>
+      <c r="M22" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
+        <v>Sector Fuel Technology Existing Electricity Plants oil</v>
+      </c>
+      <c r="N22" s="94" t="str">
         <f t="shared" si="1"/>
-        <v>FTE-ELCBIO</v>
-      </c>
-      <c r="M22" s="95" t="str">
+        <v>PJ</v>
+      </c>
+      <c r="O22" s="94" t="str">
         <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
-      </c>
-      <c r="N22" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O22" s="94" t="str">
-        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P22" s="94"/>
@@ -5180,13 +5239,13 @@
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="21"/>
       <c r="C23" t="str">
-        <f>'EB1'!M$2</f>
-        <v>OPP</v>
+        <f>'EB1'!I$2</f>
+        <v>LPG</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="62">
-        <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>5.4758702573637796E-2</v>
+        <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>3.8926710484734312E-2</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="63"/>
@@ -5196,19 +5255,19 @@
       </c>
       <c r="K23" s="94"/>
       <c r="L23" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
+        <v>FTE-ELCNUC</v>
+      </c>
+      <c r="M23" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
+      </c>
+      <c r="N23" s="94" t="str">
         <f t="shared" si="1"/>
-        <v>FTE-ELCHYD</v>
-      </c>
-      <c r="M23" s="95" t="str">
+        <v>PJ</v>
+      </c>
+      <c r="O23" s="94" t="str">
         <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
-      </c>
-      <c r="N23" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O23" s="94" t="str">
-        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P23" s="94"/>
@@ -5216,44 +5275,37 @@
       <c r="R23" s="94"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="21" t="str">
-        <f>Sector_Fuels_ELC!L21</f>
-        <v>FTE-ELCNUC</v>
-      </c>
+      <c r="B24" s="21"/>
       <c r="C24" t="str">
-        <f>RIGHT(D24,3)</f>
-        <v>NUC</v>
-      </c>
-      <c r="D24" s="21" t="str">
-        <f>L8</f>
-        <v>ELCNUC</v>
-      </c>
-      <c r="E24" s="12"/>
+        <f>'EB1'!L$2</f>
+        <v>HFO</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="62">
+        <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>0.85705723214511731</v>
+      </c>
       <c r="F24" s="12"/>
-      <c r="G24" s="63">
-        <v>1</v>
-      </c>
-      <c r="H24" s="64">
-        <v>30</v>
-      </c>
+      <c r="G24" s="63"/>
+      <c r="H24" s="64"/>
       <c r="J24" s="90" t="s">
         <v>95</v>
       </c>
       <c r="K24" s="94"/>
       <c r="L24" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
+        <v>FTE-ELCBIO</v>
+      </c>
+      <c r="M24" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
+      </c>
+      <c r="N24" s="94" t="str">
         <f t="shared" si="1"/>
-        <v>FTE-ELCWIN</v>
-      </c>
-      <c r="M24" s="95" t="str">
+        <v>PJ</v>
+      </c>
+      <c r="O24" s="94" t="str">
         <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
-      </c>
-      <c r="N24" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O24" s="94" t="str">
-        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P24" s="94"/>
@@ -5261,44 +5313,37 @@
       <c r="R24" s="94"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B25" s="21" t="str">
-        <f>Sector_Fuels_ELC!L22</f>
-        <v>FTE-ELCBIO</v>
-      </c>
+      <c r="B25" s="21"/>
       <c r="C25" t="str">
-        <f>RIGHT(D25,3)</f>
-        <v>BIO</v>
-      </c>
-      <c r="D25" s="21" t="str">
-        <f>L9</f>
-        <v>ELCBIO</v>
-      </c>
-      <c r="E25" s="12"/>
+        <f>'EB1'!M$2</f>
+        <v>OPP</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="62">
+        <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>5.4758702573637796E-2</v>
+      </c>
       <c r="F25" s="12"/>
-      <c r="G25" s="63">
-        <v>1</v>
-      </c>
-      <c r="H25" s="64">
-        <v>30</v>
-      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="64"/>
       <c r="J25" s="90" t="s">
         <v>95</v>
       </c>
       <c r="K25" s="94"/>
       <c r="L25" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
+        <v>FTE-ELCHYD</v>
+      </c>
+      <c r="M25" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
+      </c>
+      <c r="N25" s="94" t="str">
         <f t="shared" si="1"/>
-        <v>FTE-ELCSOL</v>
-      </c>
-      <c r="M25" s="95" t="str">
+        <v>PJ</v>
+      </c>
+      <c r="O25" s="94" t="str">
         <f t="shared" si="2"/>
-        <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
-      </c>
-      <c r="N25" s="94" t="str">
-        <f t="shared" si="3"/>
-        <v>PJ</v>
-      </c>
-      <c r="O25" s="94" t="str">
-        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P25" s="94"/>
@@ -5308,15 +5353,15 @@
     <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
         <f>Sector_Fuels_ELC!L23</f>
-        <v>FTE-ELCHYD</v>
+        <v>FTE-ELCNUC</v>
       </c>
       <c r="C26" t="str">
         <f>RIGHT(D26,3)</f>
-        <v>HYD</v>
+        <v>NUC</v>
       </c>
       <c r="D26" s="21" t="str">
-        <f>L10</f>
-        <v>ELCHYD</v>
+        <f>L8</f>
+        <v>ELCNUC</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -5326,19 +5371,42 @@
       <c r="H26" s="64">
         <v>30</v>
       </c>
+      <c r="J26" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="K26" s="94"/>
+      <c r="L26" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
+        <v>FTE-ELCWIN</v>
+      </c>
+      <c r="M26" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
+      </c>
+      <c r="N26" s="94" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O26" s="94" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="94"/>
+      <c r="R26" s="94"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
         <f>Sector_Fuels_ELC!L24</f>
-        <v>FTE-ELCWIN</v>
+        <v>FTE-ELCBIO</v>
       </c>
       <c r="C27" t="str">
         <f>RIGHT(D27,3)</f>
-        <v>WIN</v>
+        <v>BIO</v>
       </c>
       <c r="D27" s="21" t="str">
-        <f>L11</f>
-        <v>ELCWIN</v>
+        <f>L9</f>
+        <v>ELCBIO</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -5348,19 +5416,42 @@
       <c r="H27" s="64">
         <v>30</v>
       </c>
+      <c r="J27" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="94"/>
+      <c r="L27" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
+        <v>FTE-ELCWON</v>
+      </c>
+      <c r="M27" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind Onshore energy</v>
+      </c>
+      <c r="N27" s="94" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O27" s="94" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f>Sector_Fuels_ELC!L25</f>
-        <v>FTE-ELCSOL</v>
+        <v>FTE-ELCHYD</v>
       </c>
       <c r="C28" t="str">
         <f>RIGHT(D28,3)</f>
-        <v>SOL</v>
+        <v>HYD</v>
       </c>
       <c r="D28" s="21" t="str">
-        <f>L12</f>
-        <v>ELCSOL</v>
+        <f>L10</f>
+        <v>ELCHYD</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -5370,16 +5461,142 @@
       <c r="H28" s="64">
         <v>30</v>
       </c>
+      <c r="J28" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="K28" s="94"/>
+      <c r="L28" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L13</f>
+        <v>FTE-ELCWOF</v>
+      </c>
+      <c r="M28" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M13</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind Offshore energy</v>
+      </c>
+      <c r="N28" s="94" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O28" s="94" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B29" s="21" t="str">
+        <f>Sector_Fuels_ELC!L26</f>
+        <v>FTE-ELCWIN</v>
+      </c>
+      <c r="C29" t="str">
+        <f>RIGHT(D29,3)</f>
+        <v>WIN</v>
+      </c>
+      <c r="D29" s="21" t="str">
+        <f>L11</f>
+        <v>ELCWIN</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="63">
+        <v>1</v>
+      </c>
+      <c r="H29" s="64">
+        <v>30</v>
+      </c>
+      <c r="J29" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="94"/>
+      <c r="L29" s="94" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L14</f>
+        <v>FTE-ELCSOL</v>
+      </c>
+      <c r="M29" s="95" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M14</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
+      </c>
+      <c r="N29" s="94" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O29" s="94" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B30" s="21" t="str">
+        <f>Sector_Fuels_ELC!L27</f>
+        <v>FTE-ELCWON</v>
+      </c>
+      <c r="C30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="21" t="str">
+        <f>L12</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="63">
+        <v>1</v>
+      </c>
+      <c r="H30" s="64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B31" s="21" t="str">
+        <f>Sector_Fuels_ELC!L28</f>
+        <v>FTE-ELCWOF</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="21" t="str">
+        <f>L13</f>
+        <v>ELCWOF</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="63">
+        <v>1</v>
+      </c>
+      <c r="H31" s="64">
+        <v>30</v>
+      </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B32" s="44"/>
-      <c r="C32" s="1" t="s">
+      <c r="B32" s="21" t="str">
+        <f>Sector_Fuels_ELC!L29</f>
+        <v>FTE-ELCSOL</v>
+      </c>
+      <c r="C32" t="str">
+        <f>RIGHT(D32,3)</f>
+        <v>SOL</v>
+      </c>
+      <c r="D32" s="21" t="str">
+        <f>L14</f>
+        <v>ELCSOL</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="63">
+        <v>1</v>
+      </c>
+      <c r="H32" s="64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="44"/>
+      <c r="C34" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="60"/>
-      <c r="C33" s="1" t="s">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="60"/>
+      <c r="C35" s="1" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5397,7 +5614,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="21" bestFit="1" customWidth="1"/>
@@ -5414,8 +5631,8 @@
     <col min="19" max="19" width="2.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="45" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="57.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6.28515625" customWidth="1"/>
     <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5460,14 +5677,14 @@
         <v>100</v>
       </c>
       <c r="E2" s="10" t="str">
-        <f>'EB1'!Z2</f>
+        <f>'EB1'!AB2</f>
         <v>PJ</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>101</v>
       </c>
       <c r="G2" s="10" t="str">
-        <f>'EB1'!Y2</f>
+        <f>'EB1'!AA2</f>
         <v>M€2025</v>
       </c>
       <c r="H2" s="10" t="s">
@@ -5586,7 +5803,7 @@
         <v>164</v>
       </c>
       <c r="W5" s="90" t="str">
-        <f>'EB1'!$U$3</f>
+        <f>'EB1'!$W$3</f>
         <v>Electricity</v>
       </c>
       <c r="X5" s="90" t="str">
@@ -5616,7 +5833,7 @@
         <v>Electricity Plants Carbon dioxide</v>
       </c>
       <c r="X6" s="94" t="str">
-        <f>'EB1'!$AA$2</f>
+        <f>'EB1'!$AC$2</f>
         <v>kt</v>
       </c>
       <c r="Y6" s="94"/>
@@ -5879,7 +6096,7 @@
         <v>ELCCOA</v>
       </c>
       <c r="D12" s="21" t="str">
-        <f t="shared" ref="D12:D34" si="0">$V$5</f>
+        <f t="shared" ref="D12:D43" si="0">$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="G12" s="83">
@@ -6366,7 +6583,7 @@
         <v>ELCRESOL00</v>
       </c>
       <c r="C19" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D19" s="21" t="str">
@@ -6374,7 +6591,7 @@
         <v>ELCC</v>
       </c>
       <c r="G19" s="83">
-        <f>(-'EB1'!$R$6*$I$19)/($J$19*$O$19)</f>
+        <f>(-'EB1'!$T$6*$I$19)/($J$19*$O$19)</f>
         <v>7.1875528496533061</v>
       </c>
       <c r="H19" s="61"/>
@@ -6408,11 +6625,11 @@
       </c>
       <c r="U19" s="98"/>
       <c r="V19" s="98" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"00"</f>
         <v>ELCRESOL00</v>
       </c>
       <c r="W19" s="98" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" - "&amp;'EB1'!R3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" - "&amp;'EB1'!T3</f>
         <v>Power Plants Existing00 - Solar energy</v>
       </c>
       <c r="X19" s="98" t="str">
@@ -6433,7 +6650,7 @@
         <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="C20" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D20" s="21" t="str">
@@ -6461,18 +6678,18 @@
       <c r="O20" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P20" s="21">
-        <v>0.2</v>
+      <c r="P20" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T20" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V20" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="W20" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in PARNU - Solar energy</v>
       </c>
       <c r="X20" t="s">
@@ -6487,11 +6704,11 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B21" s="21" t="str">
-        <f t="shared" ref="B21:B34" si="3">V21</f>
+        <f t="shared" ref="B21:B43" si="3">V21</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
       <c r="C21" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D21" s="21" t="str">
@@ -6519,19 +6736,19 @@
       <c r="O21" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P21" s="21">
-        <v>0.2</v>
+      <c r="P21" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="R21" s="82"/>
       <c r="T21" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V21" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
       <c r="W21" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in TARTU - Solar energy</v>
       </c>
       <c r="X21" t="s">
@@ -6551,7 +6768,7 @@
         <v>ELCRESOL_LVIRU00</v>
       </c>
       <c r="C22" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D22" s="21" t="str">
@@ -6579,19 +6796,19 @@
       <c r="O22" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P22" s="21">
-        <v>0.2</v>
+      <c r="P22" s="77">
+        <v>0.14867925344692126</v>
       </c>
       <c r="R22" s="82"/>
       <c r="T22" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V22" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
         <v>ELCRESOL_LVIRU00</v>
       </c>
       <c r="W22" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LVIRU - Solar energy</v>
       </c>
       <c r="X22" t="s">
@@ -6611,7 +6828,7 @@
         <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="C23" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D23" s="21" t="str">
@@ -6639,19 +6856,19 @@
       <c r="O23" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P23" s="21">
-        <v>0.2</v>
+      <c r="P23" s="77">
+        <v>0.14701259708091721</v>
       </c>
       <c r="R23" s="82"/>
       <c r="T23" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V23" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
         <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="W23" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in IVIRU - Solar energy</v>
       </c>
       <c r="X23" t="s">
@@ -6671,7 +6888,7 @@
         <v>ELCRESOL_JARVA00</v>
       </c>
       <c r="C24" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D24" s="21" t="str">
@@ -6699,19 +6916,19 @@
       <c r="O24" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P24" s="21">
-        <v>0.2</v>
+      <c r="P24" s="77">
+        <v>0.15309859852159369</v>
       </c>
       <c r="R24" s="82"/>
       <c r="T24" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V24" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
         <v>ELCRESOL_JARVA00</v>
       </c>
       <c r="W24" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JARVA - Solar energy</v>
       </c>
       <c r="X24" t="s">
@@ -6731,7 +6948,7 @@
         <v>ELCRESOL_JOGEVA00</v>
       </c>
       <c r="C25" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D25" s="21" t="str">
@@ -6759,19 +6976,19 @@
       <c r="O25" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P25" s="21">
-        <v>0.2</v>
+      <c r="P25" s="77">
+        <v>0.15309859852159369</v>
       </c>
       <c r="R25" s="82"/>
       <c r="T25" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V25" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
         <v>ELCRESOL_JOGEVA00</v>
       </c>
       <c r="W25" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
       </c>
       <c r="X25" t="s">
@@ -6790,7 +7007,7 @@
         <v>ELCRESOL_HARJU00</v>
       </c>
       <c r="C26" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D26" s="21" t="str">
@@ -6818,18 +7035,18 @@
       <c r="O26" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P26" s="21">
-        <v>0.2</v>
+      <c r="P26" s="77">
+        <v>0.15619560585976827</v>
       </c>
       <c r="T26" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V26" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
         <v>ELCRESOL_HARJU00</v>
       </c>
       <c r="W26" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HARJU - Solar energy</v>
       </c>
       <c r="X26" t="s">
@@ -6848,7 +7065,7 @@
         <v>ELCRESOL_POLVA00</v>
       </c>
       <c r="C27" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D27" s="21" t="str">
@@ -6876,18 +7093,18 @@
       <c r="O27" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P27" s="21">
-        <v>0.2</v>
+      <c r="P27" s="77">
+        <v>0.14537310453496291</v>
       </c>
       <c r="T27" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V27" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
         <v>ELCRESOL_POLVA00</v>
       </c>
       <c r="W27" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
       <c r="X27" t="s">
@@ -6906,7 +7123,7 @@
         <v>ELCRESOL_VALGA00</v>
       </c>
       <c r="C28" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D28" s="21" t="str">
@@ -6934,18 +7151,18 @@
       <c r="O28" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P28" s="21">
-        <v>0.2</v>
+      <c r="P28" s="77">
+        <v>0.14763873655681015</v>
       </c>
       <c r="T28" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V28" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
         <v>ELCRESOL_VALGA00</v>
       </c>
       <c r="W28" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
       <c r="X28" t="s">
@@ -6964,7 +7181,7 @@
         <v>ELCRESOL_VILJANDI00</v>
       </c>
       <c r="C29" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D29" s="21" t="str">
@@ -6992,18 +7209,18 @@
       <c r="O29" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P29" s="21">
-        <v>0.2</v>
+      <c r="P29" s="77">
+        <v>0.1532628310027955</v>
       </c>
       <c r="T29" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V29" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
         <v>ELCRESOL_VILJANDI00</v>
       </c>
       <c r="W29" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
       <c r="X29" t="s">
@@ -7022,7 +7239,7 @@
         <v>ELCRESOL_VORU00</v>
       </c>
       <c r="C30" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D30" s="21" t="str">
@@ -7050,18 +7267,18 @@
       <c r="O30" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P30" s="21">
-        <v>0.2</v>
+      <c r="P30" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T30" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V30" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
         <v>ELCRESOL_VORU00</v>
       </c>
       <c r="W30" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
       <c r="X30" t="s">
@@ -7080,7 +7297,7 @@
         <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="C31" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D31" s="21" t="str">
@@ -7108,18 +7325,18 @@
       <c r="O31" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P31" s="21">
-        <v>0.2</v>
+      <c r="P31" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T31" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V31" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
         <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="W31" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
       <c r="X31" t="s">
@@ -7138,7 +7355,7 @@
         <v>ELCRESOL_RAPLA00</v>
       </c>
       <c r="C32" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D32" s="21" t="str">
@@ -7166,18 +7383,18 @@
       <c r="O32" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P32" s="21">
-        <v>0.2</v>
+      <c r="P32" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T32" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V32" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
         <v>ELCRESOL_RAPLA00</v>
       </c>
       <c r="W32" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
       <c r="X32" t="s">
@@ -7196,7 +7413,7 @@
         <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="C33" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D33" s="21" t="str">
@@ -7224,18 +7441,18 @@
       <c r="O33" s="66">
         <v>31.536000000000001</v>
       </c>
-      <c r="P33" s="21">
-        <v>0.2</v>
+      <c r="P33" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T33" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V33" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
         <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="W33" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
       <c r="X33" t="s">
@@ -7254,7 +7471,7 @@
         <v>ELCRESOL_HIIU00</v>
       </c>
       <c r="C34" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L12,3)</f>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
         <v>ELCSOL</v>
       </c>
       <c r="D34" s="21" t="str">
@@ -7282,18 +7499,18 @@
       <c r="O34" s="21">
         <v>8.76</v>
       </c>
-      <c r="P34" s="21">
-        <v>0.2</v>
+      <c r="P34" s="77">
+        <v>0.1461854238754417</v>
       </c>
       <c r="T34" s="94" t="s">
         <v>102</v>
       </c>
       <c r="V34" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
         <v>ELCRESOL_HIIU00</v>
       </c>
       <c r="W34" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$R$3</f>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V34,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
       <c r="X34" t="s">
@@ -7303,6 +7520,528 @@
         <v>101</v>
       </c>
       <c r="Z34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B35" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_SOPITOOTSI00</v>
+      </c>
+      <c r="C35" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D35" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G35">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="I35" s="101">
+        <v>1</v>
+      </c>
+      <c r="K35" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L35" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M35" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N35">
+        <v>27</v>
+      </c>
+      <c r="O35" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P35">
+        <v>0.4</v>
+      </c>
+      <c r="T35" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V35" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
+        <v>ELCRESOL_SOPITOOTSI00</v>
+      </c>
+      <c r="W35" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V35,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
+      </c>
+      <c r="X35" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B36" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_SOPIPURTSE00</v>
+      </c>
+      <c r="C36" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D36" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G36">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I36" s="101">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L36" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M36" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N36">
+        <v>27</v>
+      </c>
+      <c r="O36" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P36">
+        <v>0.4</v>
+      </c>
+      <c r="T36" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V36" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
+        <v>ELCRESOL_SOPIPURTSE00</v>
+      </c>
+      <c r="W36" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V36,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
+      </c>
+      <c r="X36" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B37" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_OTHER00</v>
+      </c>
+      <c r="C37" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D37" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G37">
+        <v>8.130000000000015E-2</v>
+      </c>
+      <c r="I37" s="101">
+        <v>1</v>
+      </c>
+      <c r="K37" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L37" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M37" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N37">
+        <v>27</v>
+      </c>
+      <c r="O37" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P37">
+        <v>0.4</v>
+      </c>
+      <c r="T37" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V37" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
+        <v>ELCRESOL_OTHER00</v>
+      </c>
+      <c r="W37" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V37,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
+      </c>
+      <c r="X37" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B38" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_SAARE00</v>
+      </c>
+      <c r="C38" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D38" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G38">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I38" s="101">
+        <v>1</v>
+      </c>
+      <c r="K38" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L38" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M38" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N38">
+        <v>27</v>
+      </c>
+      <c r="O38" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P38">
+        <v>0.4</v>
+      </c>
+      <c r="T38" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V38" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
+        <v>ELCRESOL_SAARE00</v>
+      </c>
+      <c r="W38" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V38,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
+      </c>
+      <c r="X38" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B39" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="C39" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D39" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G39">
+        <v>3.27E-2</v>
+      </c>
+      <c r="I39" s="101">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L39" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M39" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N39">
+        <v>27</v>
+      </c>
+      <c r="O39" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P39">
+        <v>0.4</v>
+      </c>
+      <c r="T39" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V39" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="W39" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V39,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
+      </c>
+      <c r="X39" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B40" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="C40" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D40" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G40">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="I40" s="101">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L40" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M40" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N40">
+        <v>27</v>
+      </c>
+      <c r="O40" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P40">
+        <v>0.4</v>
+      </c>
+      <c r="T40" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V40" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="W40" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V40,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
+      </c>
+      <c r="X40" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B41" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="C41" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D41" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G41">
+        <v>0.06</v>
+      </c>
+      <c r="I41" s="101">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L41" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M41" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N41">
+        <v>27</v>
+      </c>
+      <c r="O41" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P41">
+        <v>0.4</v>
+      </c>
+      <c r="T41" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V41" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="W41" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V41,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
+      </c>
+      <c r="X41" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B42" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_IVIRU00</v>
+      </c>
+      <c r="C42" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D42" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G42">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="I42" s="101">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L42" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M42" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N42">
+        <v>27</v>
+      </c>
+      <c r="O42" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P42">
+        <v>0.4</v>
+      </c>
+      <c r="T42" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V42" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
+        <v>ELCRESOL_IVIRU00</v>
+      </c>
+      <c r="W42" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V42,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
+      </c>
+      <c r="X42" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B43" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCRESOL_PARNU00</v>
+      </c>
+      <c r="C43" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="D43" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G43">
+        <v>0.1036</v>
+      </c>
+      <c r="I43" s="101">
+        <v>1</v>
+      </c>
+      <c r="K43" s="7">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L43" s="88">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M43" s="88">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N43">
+        <v>27</v>
+      </c>
+      <c r="O43" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P43">
+        <v>0.4</v>
+      </c>
+      <c r="T43" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="V43" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
+        <v>ELCRESOL_PARNU00</v>
+      </c>
+      <c r="W43" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V43,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
+      </c>
+      <c r="X43" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z43" t="s">
         <v>116</v>
       </c>
     </row>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5EA78E-ADC3-4ECF-97F6-B4A16E229781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D5CBE5-9EAF-4A21-AC28-12BE82A69724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
     <sheet name="Intra_areas" sheetId="150" r:id="rId2"/>
     <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId3"/>
     <sheet name="ELC" sheetId="143" r:id="rId4"/>
-    <sheet name="Emi" sheetId="149" r:id="rId5"/>
+    <sheet name="CHP" sheetId="151" r:id="rId5"/>
+    <sheet name="Emi" sheetId="149" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -349,7 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P17" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="P19" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -442,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="Q19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -467,7 +468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R17" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="R19" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -530,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="J20" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1512,8 +1513,443 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Maurizio Gargiulo</author>
+    <author>Amit Kanudia</author>
+  </authors>
+  <commentList>
+    <comment ref="W9" authorId="0" shapeId="0" xr:uid="{8D31B832-0A34-455E-8E68-4081B61E92A5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed TsLvl
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ANNUAL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Annual level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X9" authorId="1" shapeId="0" xr:uid="{5C55A955-88D5-4297-B97A-C5CCA6A69957}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Needed only when one wants to override the VEDA default assignment
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y9" authorId="0" shapeId="0" xr:uid="{B59FE625-F08C-45E7-A39D-3E0EAFD7A7B5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed Vintage</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (if empty by default mean </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+YES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q10" authorId="0" shapeId="0" xr:uid="{89AF1D2E-C150-43C7-A482-2EB853D30173}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sets declarations are </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>inherited. 
+Allowed Process Sets</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ELE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Thermal Electric Power Plant)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CHP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Combined Heat and Power)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGTSS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pump Storage)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGIPS</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Pump Storage IP)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+PRE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Genric Process/Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DMD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand Device)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+IMP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Import)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EXP</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Export)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+MIN </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Mining Process)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RNW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Renewable Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+HPL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Heating Plant)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="197">
   <si>
     <t>CommName</t>
   </si>
@@ -1866,9 +2302,6 @@
     <t>DAYNITE</t>
   </si>
   <si>
-    <t>SEASON</t>
-  </si>
-  <si>
     <t>Peak</t>
   </si>
   <si>
@@ -2092,6 +2525,21 @@
   </si>
   <si>
     <t>Wind offshore energy</t>
+  </si>
+  <si>
+    <t>ELCMSW</t>
+  </si>
+  <si>
+    <t>Electricity Plants Municipal Waste</t>
+  </si>
+  <si>
+    <t>TWh/GW</t>
+  </si>
+  <si>
+    <t>ELCSHL</t>
+  </si>
+  <si>
+    <t>Electricity Plants Oil Shale</t>
   </si>
 </sst>
 </file>
@@ -2642,7 +3090,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2778,7 +3226,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="4" fillId="16" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
@@ -2816,10 +3263,6 @@
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2847,10 +3290,33 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="30">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -2903,13 +3369,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>3810</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>407670</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3060,16 +3526,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>109641</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>146261</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>871640</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>120128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>74063</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>138673</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>692699</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>115715</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3084,8 +3550,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12904891" y="9618344"/>
-          <a:ext cx="7097589" cy="1262412"/>
+          <a:off x="13473948" y="12614974"/>
+          <a:ext cx="8242136" cy="1324203"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3195,6 +3661,144 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>109641</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>146261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>74063</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>138673</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21CF7748-CB74-4FE8-B3BC-39E21B0439C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13628791" y="9928436"/>
+          <a:ext cx="8232122" cy="1313212"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Declare  electricity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> an energy commodity and  electricity plants carbon dioxide</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> an environmental commodity (FI_COMM table) and define power plant options (FI_Process table).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Construct a power plant option for each fuel commodity.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3831,46 +4435,46 @@
         <v>44</v>
       </c>
       <c r="G2" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="K2" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="L2" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="M2" s="40" t="s">
         <v>130</v>
-      </c>
-      <c r="M2" s="40" t="s">
-        <v>131</v>
       </c>
       <c r="N2" s="40" t="s">
         <v>45</v>
       </c>
       <c r="O2" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="P2" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q2" s="40" t="s">
+      <c r="R2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="S2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="T2" s="40" t="s">
         <v>153</v>
-      </c>
-      <c r="R2" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="S2" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="T2" s="40" t="s">
-        <v>154</v>
       </c>
       <c r="U2" s="40" t="s">
         <v>46</v>
@@ -3882,10 +4486,10 @@
         <v>48</v>
       </c>
       <c r="X2" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA2" s="39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB2" s="10" t="s">
         <v>68</v>
@@ -3896,7 +4500,7 @@
     </row>
     <row r="3" spans="2:29" ht="38.25" x14ac:dyDescent="0.2">
       <c r="C3" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="41" t="s">
         <v>49</v>
@@ -3905,49 +4509,49 @@
         <v>50</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H3" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="J3" s="41" t="s">
+      <c r="K3" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="K3" s="41" t="s">
-        <v>136</v>
-      </c>
       <c r="L3" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" s="41" t="s">
         <v>132</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>133</v>
       </c>
       <c r="N3" s="41" t="s">
         <v>51</v>
       </c>
       <c r="O3" s="41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P3" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="Q3" s="41" t="s">
+      <c r="R3" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="S3" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="T3" s="41" t="s">
         <v>150</v>
-      </c>
-      <c r="R3" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="S3" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="T3" s="41" t="s">
-        <v>151</v>
       </c>
       <c r="U3" s="41" t="s">
         <v>52</v>
@@ -3964,7 +4568,7 @@
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B4" s="38"/>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="71" t="s">
         <v>55</v>
       </c>
       <c r="D4" s="6"/>
@@ -3987,7 +4591,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="73"/>
+      <c r="X4" s="72"/>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B5" s="42" t="s">
@@ -4052,7 +4656,7 @@
       <c r="W5" s="43">
         <v>0</v>
       </c>
-      <c r="X5" s="74">
+      <c r="X5" s="73">
         <v>-1274.6994499999998</v>
       </c>
     </row>
@@ -4119,10 +4723,10 @@
       <c r="W6" s="45">
         <v>5790.5</v>
       </c>
-      <c r="X6" s="74">
+      <c r="X6" s="73">
         <v>-8279.3107875000023</v>
       </c>
-      <c r="Z6" s="80"/>
+      <c r="Z6" s="79"/>
     </row>
     <row r="7" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B7" s="42" t="s">
@@ -4187,7 +4791,7 @@
       <c r="W7" s="43">
         <v>0</v>
       </c>
-      <c r="X7" s="74">
+      <c r="X7" s="73">
         <v>-26.820549999999912</v>
       </c>
     </row>
@@ -4254,7 +4858,7 @@
       <c r="W8" s="43">
         <v>0</v>
       </c>
-      <c r="X8" s="74">
+      <c r="X8" s="73">
         <v>-200.86150000000021</v>
       </c>
     </row>
@@ -4365,15 +4969,15 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
     </row>
     <row r="12" spans="2:29" ht="15" x14ac:dyDescent="0.25">
       <c r="C12" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" s="45"/>
       <c r="E12" s="45"/>
@@ -4415,11 +5019,11 @@
       <c r="B17" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="77">
         <v>1</v>
       </c>
       <c r="D17" s="55"/>
-      <c r="E17" s="79"/>
+      <c r="E17" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4437,112 +5041,112 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +5156,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:R35"/>
+  <dimension ref="B1:R41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4620,44 +5224,44 @@
         <v>84</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="89"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="J3" s="91" t="s">
+      <c r="J3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="92" t="s">
+      <c r="K3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="91" t="s">
+      <c r="L3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="91" t="s">
+      <c r="M3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="91" t="s">
+      <c r="N3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="91" t="s">
+      <c r="O3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="91" t="s">
+      <c r="P3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="91" t="s">
+      <c r="Q3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="91" t="s">
+      <c r="R3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4667,937 +5271,1041 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="93" t="s">
+      <c r="K4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="93" t="s">
+      <c r="L4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="93" t="s">
+      <c r="M4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="93" t="s">
+      <c r="N4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="93" t="s">
+      <c r="O4" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="93" t="s">
+      <c r="P4" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="93" t="s">
+      <c r="Q4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="93" t="s">
+      <c r="R4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="68"/>
+      <c r="G5" s="67"/>
       <c r="H5" s="11"/>
-      <c r="J5" s="94" t="s">
+      <c r="J5" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94" t="str">
+      <c r="K5" s="91"/>
+      <c r="L5" s="91" t="str">
         <f>$B$2&amp;'EB1'!$D$2</f>
         <v>ELCCOA</v>
       </c>
-      <c r="M5" s="95" t="str">
+      <c r="M5" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$D$3</f>
         <v>Electricity Plants Solid Fuels</v>
       </c>
-      <c r="N5" s="94" t="str">
+      <c r="N5" s="91" t="str">
         <f t="shared" ref="N5:N14" si="0">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="68"/>
+      <c r="G6" s="67"/>
       <c r="H6" s="11"/>
-      <c r="J6" s="94" t="s">
+      <c r="J6" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94" t="str">
+      <c r="K6" s="91"/>
+      <c r="L6" s="91" t="str">
         <f>$B$2&amp;'EB1'!$E$2</f>
         <v>ELCGAS</v>
       </c>
-      <c r="M6" s="95" t="str">
+      <c r="M6" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$E$3</f>
         <v>Electricity Plants Natural Gas</v>
       </c>
-      <c r="N6" s="94" t="str">
+      <c r="N6" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="68"/>
+      <c r="G7" s="67"/>
       <c r="H7" s="11"/>
-      <c r="J7" s="94" t="s">
+      <c r="J7" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94" t="str">
+      <c r="K7" s="91"/>
+      <c r="L7" s="91" t="str">
         <f>$B$2&amp;'EB1'!$F$2</f>
         <v>ELCOIL</v>
       </c>
-      <c r="M7" s="95" t="str">
+      <c r="M7" s="92" t="str">
         <f>$C$2&amp;" "&amp;RIGHT('EB1'!$F$3,3)</f>
         <v>Electricity Plants oil</v>
       </c>
-      <c r="N7" s="94" t="str">
+      <c r="N7" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="68"/>
+      <c r="G8" s="67"/>
       <c r="H8" s="11"/>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94" t="str">
+      <c r="K8" s="91"/>
+      <c r="L8" s="91" t="str">
         <f>$B$2&amp;'EB1'!$N$2</f>
         <v>ELCNUC</v>
       </c>
-      <c r="M8" s="95" t="str">
+      <c r="M8" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$N$3</f>
         <v>Electricity Plants Nuclear Energy</v>
       </c>
-      <c r="N8" s="94" t="str">
+      <c r="N8" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="91"/>
+      <c r="R8" s="91"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="68"/>
+      <c r="G9" s="67"/>
       <c r="H9" s="11"/>
-      <c r="J9" s="94" t="s">
+      <c r="J9" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94" t="str">
+      <c r="K9" s="91"/>
+      <c r="L9" s="91" t="str">
         <f>$B$2&amp;'EB1'!$O$2</f>
         <v>ELCBIO</v>
       </c>
-      <c r="M9" s="95" t="str">
+      <c r="M9" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$O$3</f>
         <v>Electricity Plants Biomass</v>
       </c>
-      <c r="N9" s="94" t="str">
+      <c r="N9" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
+      <c r="O9" s="91"/>
+      <c r="P9" s="91"/>
+      <c r="Q9" s="91"/>
+      <c r="R9" s="91"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="68"/>
+      <c r="G10" s="67"/>
       <c r="H10" s="11"/>
-      <c r="J10" s="94" t="s">
+      <c r="J10" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94" t="str">
+      <c r="K10" s="91"/>
+      <c r="L10" s="91" t="str">
         <f>$B$2&amp;'EB1'!$P$2</f>
         <v>ELCHYD</v>
       </c>
-      <c r="M10" s="95" t="str">
+      <c r="M10" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$P$3</f>
         <v>Electricity Plants Hydro power</v>
       </c>
-      <c r="N10" s="94" t="str">
+      <c r="N10" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
+      <c r="Q10" s="91"/>
+      <c r="R10" s="91"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="68"/>
+      <c r="G11" s="67"/>
       <c r="H11" s="11"/>
-      <c r="J11" s="94" t="s">
+      <c r="J11" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94" t="str">
+      <c r="K11" s="91"/>
+      <c r="L11" s="91" t="str">
         <f>$B$2&amp;'EB1'!$Q$2</f>
         <v>ELCWIN</v>
       </c>
-      <c r="M11" s="95" t="str">
+      <c r="M11" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$Q$3</f>
         <v>Electricity Plants Wind energy</v>
       </c>
-      <c r="N11" s="94" t="str">
+      <c r="N11" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="68"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="11"/>
-      <c r="J12" s="94" t="s">
+      <c r="J12" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94" t="s">
-        <v>187</v>
-      </c>
-      <c r="M12" s="95" t="s">
-        <v>189</v>
-      </c>
-      <c r="N12" s="94" t="s">
+      <c r="K12" s="91"/>
+      <c r="L12" s="91" t="s">
+        <v>186</v>
+      </c>
+      <c r="M12" s="92" t="s">
+        <v>188</v>
+      </c>
+      <c r="N12" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
+      <c r="R12" s="91"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="68"/>
+      <c r="G13" s="67"/>
       <c r="H13" s="11"/>
-      <c r="J13" s="94" t="s">
+      <c r="J13" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94" t="s">
-        <v>190</v>
-      </c>
-      <c r="M13" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="N13" s="94" t="s">
+      <c r="K13" s="91"/>
+      <c r="L13" s="91" t="s">
+        <v>189</v>
+      </c>
+      <c r="M13" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="N13" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
+      <c r="R13" s="91"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="68"/>
+      <c r="G14" s="67"/>
       <c r="H14" s="11"/>
-      <c r="J14" s="94" t="s">
+      <c r="J14" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94" t="str">
+      <c r="K14" s="91"/>
+      <c r="L14" s="91" t="str">
         <f>$B$2&amp;'EB1'!$T$2</f>
         <v>ELCSOL</v>
       </c>
-      <c r="M14" s="95" t="str">
+      <c r="M14" s="92" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$T$3</f>
         <v>Electricity Plants Solar energy</v>
       </c>
-      <c r="N14" s="94" t="str">
+      <c r="N14" s="91" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O14" s="94"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="94"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L15" s="21"/>
-      <c r="M15" s="22"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="11"/>
+      <c r="J15" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91" t="s">
+        <v>192</v>
+      </c>
+      <c r="M15" s="92" t="s">
+        <v>193</v>
+      </c>
+      <c r="N15" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="11"/>
+      <c r="J16" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="91"/>
+      <c r="L16" s="91" t="s">
+        <v>195</v>
+      </c>
+      <c r="M16" s="92" t="s">
+        <v>196</v>
+      </c>
+      <c r="N16" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
+      <c r="Q16" s="91"/>
+      <c r="R16" s="91"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="L17" s="21"/>
+      <c r="M17" s="22"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="D18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="J16" s="89" t="s">
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="J18" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="89"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="16" t="s">
+      <c r="K18" s="86"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="91"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C19" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="69" t="s">
+      <c r="E19" s="70" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="69" t="s">
+      <c r="H19" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="91" t="s">
+      <c r="J19" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="92" t="s">
+      <c r="K19" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L17" s="91" t="s">
+      <c r="L19" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="91" t="s">
+      <c r="M19" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="N17" s="91" t="s">
+      <c r="N19" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="91" t="s">
+      <c r="O19" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P17" s="91" t="s">
+      <c r="P19" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="Q17" s="91" t="s">
+      <c r="Q19" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="R17" s="91" t="s">
+      <c r="R19" s="88" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+    <row r="20" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="E20" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G20" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18" s="93" t="s">
+      <c r="H20" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="93" t="s">
+      <c r="K20" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="93" t="s">
+      <c r="L20" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="93" t="s">
+      <c r="M20" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="N18" s="93" t="s">
+      <c r="N20" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="O18" s="93" t="s">
+      <c r="O20" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="P18" s="93" t="s">
+      <c r="P20" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="Q18" s="93" t="s">
+      <c r="Q20" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="R18" s="93" t="s">
+      <c r="R20" s="90" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+    <row r="21" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13" t="str">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13" t="str">
         <f>F2&amp;"a"</f>
         <v>M€2025a</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13" t="s">
+      <c r="G21" s="13"/>
+      <c r="H21" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="J19" s="93" t="s">
+      <c r="J21" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="96"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="21" t="str">
-        <f>Sector_Fuels_ELC!L20</f>
-        <v>FTE-ELCCOA</v>
-      </c>
-      <c r="C20" t="str">
-        <f>RIGHT(D20,3)</f>
-        <v>COA</v>
-      </c>
-      <c r="D20" s="21" t="str">
-        <f>L5</f>
-        <v>ELCCOA</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="63">
-        <v>1</v>
-      </c>
-      <c r="H20" s="64">
-        <v>30</v>
-      </c>
-      <c r="J20" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K20" s="97"/>
-      <c r="L20" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
-        <v>FTE-ELCCOA</v>
-      </c>
-      <c r="M20" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
-      </c>
-      <c r="N20" s="94" t="str">
-        <f t="shared" ref="N20:N29" si="1">$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="O20" s="94" t="str">
-        <f t="shared" ref="O20:O29" si="2">$E$2&amp;"a"</f>
-        <v>PJa</v>
-      </c>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="21" t="str">
-        <f>Sector_Fuels_ELC!L21</f>
-        <v>FTE-ELCGAS</v>
-      </c>
-      <c r="C21" t="str">
-        <f>RIGHT(D21,3)</f>
-        <v>GAS</v>
-      </c>
-      <c r="D21" s="21" t="str">
-        <f>L6</f>
-        <v>ELCGAS</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="63">
-        <v>1</v>
-      </c>
-      <c r="H21" s="64">
-        <v>30</v>
-      </c>
-      <c r="J21" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K21" s="97"/>
-      <c r="L21" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
-        <v>FTE-ELCGAS</v>
-      </c>
-      <c r="M21" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
-      </c>
-      <c r="N21" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="O21" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>PJa</v>
-      </c>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="94"/>
-      <c r="R21" s="94"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="93"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="93"/>
+      <c r="Q21" s="93"/>
+      <c r="R21" s="93"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
         <f>Sector_Fuels_ELC!L22</f>
+        <v>FTE-ELCCOA</v>
+      </c>
+      <c r="C22" t="str">
+        <f>RIGHT(D22,3)</f>
+        <v>COA</v>
+      </c>
+      <c r="D22" s="21" t="str">
+        <f>L5</f>
+        <v>ELCCOA</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="62">
+        <v>1</v>
+      </c>
+      <c r="H22" s="63">
+        <v>30</v>
+      </c>
+      <c r="J22" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="94"/>
+      <c r="L22" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <v>FTE-ELCCOA</v>
+      </c>
+      <c r="M22" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
+      </c>
+      <c r="N22" s="91" t="str">
+        <f t="shared" ref="N22:N33" si="1">$E$2</f>
+        <v>PJ</v>
+      </c>
+      <c r="O22" s="91" t="str">
+        <f t="shared" ref="O22:O33" si="2">$E$2&amp;"a"</f>
+        <v>PJa</v>
+      </c>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="91"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="str">
+        <f>Sector_Fuels_ELC!L23</f>
+        <v>FTE-ELCGAS</v>
+      </c>
+      <c r="C23" t="str">
+        <f>RIGHT(D23,3)</f>
+        <v>GAS</v>
+      </c>
+      <c r="D23" s="21" t="str">
+        <f>L6</f>
+        <v>ELCGAS</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="62">
+        <v>1</v>
+      </c>
+      <c r="H23" s="63">
+        <v>30</v>
+      </c>
+      <c r="J23" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" s="94"/>
+      <c r="L23" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
+        <v>FTE-ELCGAS</v>
+      </c>
+      <c r="M23" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
+      </c>
+      <c r="N23" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O23" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="91"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="21" t="str">
+        <f>Sector_Fuels_ELC!L24</f>
         <v>FTE-ELCOIL</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C24" t="str">
         <f>'EB1'!G$2</f>
         <v>DSL</v>
       </c>
-      <c r="D22" s="21" t="str">
+      <c r="D24" s="21" t="str">
         <f>L7</f>
         <v>ELCOIL</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E24" s="61">
         <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>4.9257354796510562E-2</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="63">
+      <c r="F24" s="12"/>
+      <c r="G24" s="62">
         <v>1</v>
       </c>
-      <c r="H22" s="64">
+      <c r="H24" s="63">
         <v>30</v>
       </c>
-      <c r="J22" s="90" t="s">
+      <c r="J24" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="97"/>
-      <c r="L22" s="94" t="str">
+      <c r="K24" s="94"/>
+      <c r="L24" s="91" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-ELCOIL</v>
       </c>
-      <c r="M22" s="95" t="str">
+      <c r="M24" s="92" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Electricity Plants oil</v>
       </c>
-      <c r="N22" s="94" t="str">
+      <c r="N24" s="91" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O22" s="94" t="str">
+      <c r="O24" s="91" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="21"/>
-      <c r="C23" t="str">
-        <f>'EB1'!I$2</f>
-        <v>LPG</v>
-      </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="62">
-        <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>3.8926710484734312E-2</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="J23" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
-        <v>FTE-ELCNUC</v>
-      </c>
-      <c r="M23" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
-      </c>
-      <c r="N23" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="O23" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>PJa</v>
-      </c>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="94"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="21"/>
-      <c r="C24" t="str">
-        <f>'EB1'!L$2</f>
-        <v>HFO</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="62">
-        <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>0.85705723214511731</v>
-      </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="64"/>
-      <c r="J24" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
-        <v>FTE-ELCBIO</v>
-      </c>
-      <c r="M24" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
-      </c>
-      <c r="N24" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="O24" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>PJa</v>
-      </c>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="91"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="21"/>
       <c r="C25" t="str">
+        <f>'EB1'!I$2</f>
+        <v>LPG</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="61">
+        <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>3.8926710484734312E-2</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="63"/>
+      <c r="J25" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
+        <v>FTE-ELCNUC</v>
+      </c>
+      <c r="M25" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
+      </c>
+      <c r="N25" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O25" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="91"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" s="21"/>
+      <c r="C26" t="str">
+        <f>'EB1'!L$2</f>
+        <v>HFO</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="61">
+        <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
+        <v>0.85705723214511731</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="63"/>
+      <c r="J26" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
+        <v>FTE-ELCBIO</v>
+      </c>
+      <c r="M26" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
+      </c>
+      <c r="N26" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O26" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="91"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B27" s="21"/>
+      <c r="C27" t="str">
         <f>'EB1'!M$2</f>
         <v>OPP</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="62">
+      <c r="D27" s="21"/>
+      <c r="E27" s="61">
         <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>5.4758702573637796E-2</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="64"/>
-      <c r="J25" s="90" t="s">
+      <c r="F27" s="12"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="J27" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94" t="str">
+      <c r="K27" s="91"/>
+      <c r="L27" s="91" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
         <v>FTE-ELCHYD</v>
       </c>
-      <c r="M25" s="95" t="str">
+      <c r="M27" s="92" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
         <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
       </c>
-      <c r="N25" s="94" t="str">
+      <c r="N27" s="91" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O25" s="94" t="str">
+      <c r="O27" s="91" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P25" s="94"/>
-      <c r="Q25" s="94"/>
-      <c r="R25" s="94"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B26" s="21" t="str">
-        <f>Sector_Fuels_ELC!L23</f>
-        <v>FTE-ELCNUC</v>
-      </c>
-      <c r="C26" t="str">
-        <f>RIGHT(D26,3)</f>
-        <v>NUC</v>
-      </c>
-      <c r="D26" s="21" t="str">
-        <f>L8</f>
-        <v>ELCNUC</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="63">
-        <v>1</v>
-      </c>
-      <c r="H26" s="64">
-        <v>30</v>
-      </c>
-      <c r="J26" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K26" s="94"/>
-      <c r="L26" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
-        <v>FTE-ELCWIN</v>
-      </c>
-      <c r="M26" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
-      </c>
-      <c r="N26" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="O26" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>PJa</v>
-      </c>
-      <c r="P26" s="94"/>
-      <c r="Q26" s="94"/>
-      <c r="R26" s="94"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B27" s="21" t="str">
-        <f>Sector_Fuels_ELC!L24</f>
-        <v>FTE-ELCBIO</v>
-      </c>
-      <c r="C27" t="str">
-        <f>RIGHT(D27,3)</f>
-        <v>BIO</v>
-      </c>
-      <c r="D27" s="21" t="str">
-        <f>L9</f>
-        <v>ELCBIO</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="63">
-        <v>1</v>
-      </c>
-      <c r="H27" s="64">
-        <v>30</v>
-      </c>
-      <c r="J27" s="90" t="s">
-        <v>95</v>
-      </c>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
-        <v>FTE-ELCWON</v>
-      </c>
-      <c r="M27" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Wind Onshore energy</v>
-      </c>
-      <c r="N27" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="O27" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>PJa</v>
-      </c>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="94"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="91"/>
+      <c r="R27" s="91"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f>Sector_Fuels_ELC!L25</f>
-        <v>FTE-ELCHYD</v>
+        <v>FTE-ELCNUC</v>
       </c>
       <c r="C28" t="str">
         <f>RIGHT(D28,3)</f>
-        <v>HYD</v>
+        <v>NUC</v>
       </c>
       <c r="D28" s="21" t="str">
-        <f>L10</f>
-        <v>ELCHYD</v>
+        <f>L8</f>
+        <v>ELCNUC</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="63">
+      <c r="G28" s="62">
         <v>1</v>
       </c>
-      <c r="H28" s="64">
+      <c r="H28" s="63">
         <v>30</v>
       </c>
-      <c r="J28" s="90" t="s">
+      <c r="J28" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="K28" s="94"/>
-      <c r="L28" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L13</f>
-        <v>FTE-ELCWOF</v>
-      </c>
-      <c r="M28" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M13</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Wind Offshore energy</v>
-      </c>
-      <c r="N28" s="94" t="str">
+      <c r="K28" s="91"/>
+      <c r="L28" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
+        <v>FTE-ELCWIN</v>
+      </c>
+      <c r="M28" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
+      </c>
+      <c r="N28" s="91" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O28" s="94" t="str">
+      <c r="O28" s="91" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
+      <c r="P28" s="91"/>
+      <c r="Q28" s="91"/>
+      <c r="R28" s="91"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
         <f>Sector_Fuels_ELC!L26</f>
-        <v>FTE-ELCWIN</v>
+        <v>FTE-ELCBIO</v>
       </c>
       <c r="C29" t="str">
         <f>RIGHT(D29,3)</f>
-        <v>WIN</v>
+        <v>BIO</v>
       </c>
       <c r="D29" s="21" t="str">
-        <f>L11</f>
-        <v>ELCWIN</v>
+        <f>L9</f>
+        <v>ELCBIO</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="63">
+      <c r="G29" s="62">
         <v>1</v>
       </c>
-      <c r="H29" s="64">
+      <c r="H29" s="63">
         <v>30</v>
       </c>
-      <c r="J29" s="90" t="s">
+      <c r="J29" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L14</f>
-        <v>FTE-ELCSOL</v>
-      </c>
-      <c r="M29" s="95" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M14</f>
-        <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
-      </c>
-      <c r="N29" s="94" t="str">
+      <c r="K29" s="91"/>
+      <c r="L29" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
+        <v>FTE-ELCWON</v>
+      </c>
+      <c r="M29" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind Onshore energy</v>
+      </c>
+      <c r="N29" s="91" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O29" s="94" t="str">
+      <c r="O29" s="91" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
+      <c r="P29" s="91"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="91"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
         <f>Sector_Fuels_ELC!L27</f>
-        <v>FTE-ELCWON</v>
-      </c>
-      <c r="C30" t="s">
-        <v>153</v>
+        <v>FTE-ELCHYD</v>
+      </c>
+      <c r="C30" t="str">
+        <f>RIGHT(D30,3)</f>
+        <v>HYD</v>
       </c>
       <c r="D30" s="21" t="str">
-        <f>L12</f>
-        <v>ELCWON</v>
+        <f>L10</f>
+        <v>ELCHYD</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="63">
+      <c r="G30" s="62">
         <v>1</v>
       </c>
-      <c r="H30" s="64">
+      <c r="H30" s="63">
         <v>30</v>
+      </c>
+      <c r="J30" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K30" s="91"/>
+      <c r="L30" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L13</f>
+        <v>FTE-ELCWOF</v>
+      </c>
+      <c r="M30" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M13</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Wind Offshore energy</v>
+      </c>
+      <c r="N30" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O30" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
         <f>Sector_Fuels_ELC!L28</f>
-        <v>FTE-ELCWOF</v>
-      </c>
-      <c r="C31" t="s">
-        <v>153</v>
+        <v>FTE-ELCWIN</v>
+      </c>
+      <c r="C31" t="str">
+        <f>RIGHT(D31,3)</f>
+        <v>WIN</v>
       </c>
       <c r="D31" s="21" t="str">
-        <f>L13</f>
-        <v>ELCWOF</v>
+        <f>L11</f>
+        <v>ELCWIN</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
-      <c r="G31" s="63">
+      <c r="G31" s="62">
         <v>1</v>
       </c>
-      <c r="H31" s="64">
+      <c r="H31" s="63">
         <v>30</v>
+      </c>
+      <c r="J31" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="91"/>
+      <c r="L31" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L14</f>
+        <v>FTE-ELCSOL</v>
+      </c>
+      <c r="M31" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M14</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
+      </c>
+      <c r="N31" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O31" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
         <f>Sector_Fuels_ELC!L29</f>
+        <v>FTE-ELCWON</v>
+      </c>
+      <c r="C32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="21" t="str">
+        <f>L12</f>
+        <v>ELCWON</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="62">
+        <v>1</v>
+      </c>
+      <c r="H32" s="63">
+        <v>30</v>
+      </c>
+      <c r="J32" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="L32" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L15</f>
+        <v>FTE-ELCMSW</v>
+      </c>
+      <c r="M32" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M15</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Municipal Waste</v>
+      </c>
+      <c r="N32" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O32" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="str">
+        <f>Sector_Fuels_ELC!L30</f>
+        <v>FTE-ELCWOF</v>
+      </c>
+      <c r="C33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="21" t="str">
+        <f>L13</f>
+        <v>ELCWOF</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="62">
+        <v>1</v>
+      </c>
+      <c r="H33" s="63">
+        <v>30</v>
+      </c>
+      <c r="J33" s="87" t="s">
+        <v>95</v>
+      </c>
+      <c r="L33" s="91" t="str">
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L16</f>
+        <v>FTE-ELCSHL</v>
+      </c>
+      <c r="M33" s="92" t="str">
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M16</f>
+        <v>Sector Fuel Technology Existing Electricity Plants Oil Shale</v>
+      </c>
+      <c r="N33" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ</v>
+      </c>
+      <c r="O33" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v>PJa</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B34" s="21" t="str">
+        <f>Sector_Fuels_ELC!L31</f>
         <v>FTE-ELCSOL</v>
       </c>
-      <c r="C32" t="str">
-        <f>RIGHT(D32,3)</f>
+      <c r="C34" t="str">
+        <f>RIGHT(D34,3)</f>
         <v>SOL</v>
       </c>
-      <c r="D32" s="21" t="str">
+      <c r="D34" s="21" t="str">
         <f>L14</f>
         <v>ELCSOL</v>
       </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="63">
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="62">
         <v>1</v>
       </c>
-      <c r="H32" s="64">
+      <c r="H34" s="63">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="44"/>
-      <c r="C34" s="1" t="s">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B35" s="21" t="str">
+        <f>Sector_Fuels_ELC!L32</f>
+        <v>FTE-ELCMSW</v>
+      </c>
+      <c r="C35" t="str">
+        <f>RIGHT(D35,3)</f>
+        <v>MSW</v>
+      </c>
+      <c r="D35" s="21" t="str">
+        <f>L15</f>
+        <v>ELCMSW</v>
+      </c>
+      <c r="G35" s="62">
+        <v>1</v>
+      </c>
+      <c r="H35" s="63">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B40" s="44"/>
+      <c r="C40" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B41" s="60"/>
+      <c r="C41" s="1" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="60"/>
-      <c r="C35" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5610,7 +6318,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AB65536"/>
+  <dimension ref="A1:AB65529"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -5641,7 +6349,7 @@
     <col min="29" max="16384" width="8.85546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>65</v>
       </c>
@@ -5664,7 +6372,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -5690,48 +6398,48 @@
       <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="89" t="s">
+      <c r="T2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="89"/>
-      <c r="V2" s="90"/>
-      <c r="W2" s="90"/>
-      <c r="X2" s="90"/>
-      <c r="Y2" s="90"/>
-      <c r="Z2" s="90"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="90"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="T3" s="91" t="s">
+      <c r="U2" s="86"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="87"/>
+      <c r="Z2" s="87"/>
+      <c r="AA2" s="87"/>
+      <c r="AB2" s="87"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="T3" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="92" t="s">
+      <c r="U3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="91" t="s">
+      <c r="V3" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="W3" s="91" t="s">
+      <c r="W3" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="X3" s="91" t="s">
+      <c r="X3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="91" t="s">
+      <c r="Y3" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="91" t="s">
+      <c r="Z3" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="91" t="s">
+      <c r="AA3" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="91" t="s">
+      <c r="AB3" s="88" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>107</v>
       </c>
@@ -5745,39 +6453,39 @@
         <v>109</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="T4" s="93" t="s">
+      <c r="T4" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="93" t="s">
+      <c r="U4" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="93" t="s">
+      <c r="V4" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="93" t="s">
+      <c r="W4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="93" t="s">
+      <c r="X4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="93" t="s">
+      <c r="Y4" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" s="93" t="s">
+      <c r="Z4" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" s="93" t="s">
+      <c r="AA4" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="93" t="s">
+      <c r="AB4" s="90" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
@@ -5795,57 +6503,57 @@
       </c>
       <c r="H5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="T5" s="90" t="s">
+      <c r="T5" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="94"/>
-      <c r="V5" s="90" t="s">
-        <v>164</v>
-      </c>
-      <c r="W5" s="90" t="str">
+      <c r="U5" s="91"/>
+      <c r="V5" s="87" t="s">
+        <v>163</v>
+      </c>
+      <c r="W5" s="87" t="str">
         <f>'EB1'!$W$3</f>
         <v>Electricity</v>
       </c>
-      <c r="X5" s="90" t="str">
+      <c r="X5" s="87" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90" t="s">
+      <c r="Y5" s="87"/>
+      <c r="Z5" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="90" t="s">
+      <c r="AA5" s="87"/>
+      <c r="AB5" s="87" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="T6" s="94" t="s">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="T6" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="U6" s="94"/>
-      <c r="V6" s="94" t="str">
+      <c r="U6" s="91"/>
+      <c r="V6" s="91" t="str">
         <f>$B$2&amp;'EB1'!$C$15</f>
         <v>ELCCO2</v>
       </c>
-      <c r="W6" s="94" t="str">
+      <c r="W6" s="91" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$16</f>
         <v>Electricity Plants Carbon dioxide</v>
       </c>
-      <c r="X6" s="94" t="str">
+      <c r="X6" s="91" t="str">
         <f>'EB1'!$AC$2</f>
         <v>kt</v>
       </c>
-      <c r="Y6" s="94"/>
-      <c r="Z6" s="94"/>
-      <c r="AA6" s="94"/>
-      <c r="AB6" s="94"/>
-    </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -5857,19 +6565,19 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="3"/>
-      <c r="T8" s="89" t="s">
+      <c r="T8" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="89"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-    </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U8" s="86"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="87"/>
+      <c r="X8" s="87"/>
+      <c r="Y8" s="87"/>
+      <c r="Z8" s="87"/>
+      <c r="AA8" s="87"/>
+      <c r="AB8" s="87"/>
+    </row>
+    <row r="9" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -5880,75 +6588,75 @@
         <v>6</v>
       </c>
       <c r="E9" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="69" t="s">
-        <v>145</v>
-      </c>
-      <c r="I9" s="69" t="s">
+      <c r="G9" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="69" t="s">
-        <v>163</v>
-      </c>
-      <c r="K9" s="69" t="s">
-        <v>158</v>
-      </c>
-      <c r="L9" s="69" t="s">
+      <c r="J9" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="K9" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="69" t="s">
+      <c r="N9" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="69" t="s">
-        <v>157</v>
-      </c>
-      <c r="P9" s="69" t="s">
-        <v>118</v>
+      <c r="O9" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="P9" s="68" t="s">
+        <v>117</v>
       </c>
       <c r="Q9" s="23"/>
-      <c r="R9" s="85" t="s">
+      <c r="R9" s="82" t="s">
         <v>115</v>
       </c>
       <c r="S9" s="27"/>
-      <c r="T9" s="91" t="s">
+      <c r="T9" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="92" t="s">
+      <c r="U9" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="91" t="s">
+      <c r="V9" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="W9" s="91" t="s">
+      <c r="W9" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="X9" s="91" t="s">
+      <c r="X9" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="Y9" s="91" t="s">
+      <c r="Y9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="91" t="s">
+      <c r="Z9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="AA9" s="91" t="s">
+      <c r="AA9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" s="91" t="s">
+      <c r="AB9" s="88" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -5959,25 +6667,25 @@
         <v>33</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="75" t="s">
-        <v>120</v>
+      <c r="H10" s="74" t="s">
+        <v>119</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="75" t="s">
+      <c r="J10" s="74" t="s">
         <v>82</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>81</v>
@@ -5986,47 +6694,47 @@
         <v>105</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O10" s="15" t="s">
         <v>106</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>104</v>
       </c>
       <c r="S10" s="28"/>
-      <c r="T10" s="93" t="s">
+      <c r="T10" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="93" t="s">
+      <c r="U10" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="93" t="s">
+      <c r="V10" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="W10" s="93" t="s">
+      <c r="W10" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="X10" s="93" t="s">
+      <c r="X10" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="Y10" s="93" t="s">
+      <c r="Y10" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="93" t="s">
+      <c r="Z10" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="AA10" s="93" t="s">
+      <c r="AA10" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="AB10" s="93" t="s">
+      <c r="AB10" s="90" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -6044,12 +6752,12 @@
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="H11" s="70" t="str">
+      <c r="H11" s="69" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="I11" s="13"/>
-      <c r="J11" s="70"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
@@ -6065,522 +6773,470 @@
       <c r="N11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="13" t="str">
-        <f>$E$2&amp;"/"&amp;$F$2</f>
-        <v>PJ/GW</v>
+      <c r="O11" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="P11" s="13"/>
-      <c r="R11" s="86" t="s">
-        <v>121</v>
+      <c r="R11" s="83" t="s">
+        <v>120</v>
       </c>
       <c r="S11" s="28"/>
-      <c r="T11" s="93" t="s">
+      <c r="T11" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="93"/>
-      <c r="V11" s="93"/>
-      <c r="W11" s="93"/>
-      <c r="X11" s="93"/>
-      <c r="Y11" s="93"/>
-      <c r="Z11" s="93"/>
-      <c r="AA11" s="93"/>
-      <c r="AB11" s="93"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B12" s="97" t="str">
+      <c r="U11" s="90"/>
+      <c r="V11" s="90"/>
+      <c r="W11" s="90"/>
+      <c r="X11" s="90"/>
+      <c r="Y11" s="90"/>
+      <c r="Z11" s="90"/>
+      <c r="AA11" s="90"/>
+      <c r="AB11" s="90"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B12" s="21" t="str">
         <f>V12</f>
-        <v>ELCTECOA00</v>
+        <v>ELCREHYD00</v>
       </c>
       <c r="C12" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L5,3)</f>
-        <v>ELCCOA</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L10,3)</f>
+        <v>ELCHYD</v>
       </c>
       <c r="D12" s="21" t="str">
-        <f t="shared" ref="D12:D43" si="0">$V$5</f>
+        <f t="shared" ref="D12:D48" si="0">$V$5</f>
         <v>ELCC</v>
       </c>
-      <c r="G12" s="83">
-        <f>(-'EB1'!$D$6*$I$12)/($J$12*$O$12)</f>
-        <v>89.372771062763022</v>
-      </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="67">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="J12" s="67">
-        <v>0.85</v>
-      </c>
-      <c r="K12" s="66"/>
-      <c r="L12" s="67">
-        <v>40</v>
-      </c>
-      <c r="M12" s="67">
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="84">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H12" s="85"/>
+      <c r="I12" s="64">
+        <v>1</v>
+      </c>
+      <c r="J12" s="64">
         <v>0.5</v>
       </c>
-      <c r="N12" s="66">
-        <v>30</v>
-      </c>
-      <c r="O12" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P12" s="67">
-        <v>1</v>
+      <c r="K12" s="64"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P12" s="66">
+        <v>0.5</v>
       </c>
       <c r="R12" s="26">
-        <f>G12*$J12*$O12</f>
-        <v>2395.6907520000004</v>
-      </c>
-      <c r="S12" s="84"/>
-      <c r="T12" s="94" t="s">
+        <f>(E12+F12)*$J12*$O12</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="29"/>
+      <c r="T12" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94" t="str">
-        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$5,3)&amp;"00"</f>
-        <v>ELCTECOA00</v>
-      </c>
-      <c r="W12" s="95" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V12,2)&amp;" - "&amp;'EB1'!D3</f>
-        <v>Power Plants Existing00 - Solid Fuels</v>
-      </c>
-      <c r="X12" s="94" t="str">
-        <f t="shared" ref="X12:X19" si="1">$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="Y12" s="94" t="str">
-        <f t="shared" ref="Y12:Y19" si="2">$F$2</f>
+      <c r="U12" s="91"/>
+      <c r="V12" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
+        <v>ELCREHYD00</v>
+      </c>
+      <c r="W12" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V12,2)&amp;" - "&amp;'EB1'!P3</f>
+        <v>Power Plants Existing00 - Hydro power</v>
+      </c>
+      <c r="X12" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y12" s="91" t="str">
+        <f t="shared" ref="Y12" si="1">$F$2</f>
         <v>GW</v>
       </c>
-      <c r="Z12" s="90" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA12" s="94"/>
-      <c r="AB12" s="94"/>
-    </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="Z12" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA12" s="91"/>
+      <c r="AB12" s="91"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
         <f>V13</f>
-        <v>ELCTEGAS00</v>
+        <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="C13" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L6,3)</f>
-        <v>ELCGAS</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D13" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G13" s="83">
-        <f>(-'EB1'!$E$6*$I$13)/($J$13*$O$13)</f>
-        <v>41.450437783149788</v>
-      </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="67">
-        <v>0.4929</v>
-      </c>
-      <c r="J13" s="67">
-        <v>0.85</v>
-      </c>
-      <c r="K13" s="66"/>
-      <c r="L13" s="67">
+      <c r="G13">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="I13" s="96">
+        <v>1</v>
+      </c>
+      <c r="J13" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L13" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M13" s="85">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21">
         <v>35</v>
       </c>
-      <c r="M13" s="67">
-        <v>0.4</v>
-      </c>
-      <c r="N13" s="66">
-        <v>20</v>
-      </c>
-      <c r="O13" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P13" s="67">
-        <v>1</v>
-      </c>
-      <c r="R13" s="26">
-        <f>G13*$J13*$O13</f>
-        <v>1111.1038550399999</v>
-      </c>
-      <c r="S13" s="29"/>
-      <c r="T13" s="94" t="s">
+      <c r="O13" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P13" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T13" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U13" s="94"/>
-      <c r="V13" s="94" t="str">
-        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"00"</f>
-        <v>ELCTEGAS00</v>
-      </c>
-      <c r="W13" s="95" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V13,2)&amp;" - "&amp;'EB1'!E3</f>
-        <v>Power Plants Existing00 - Natural Gas</v>
-      </c>
-      <c r="X13" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y13" s="94" t="str">
-        <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z13" s="94"/>
-      <c r="AA13" s="94"/>
-      <c r="AB13" s="94"/>
-    </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="V13" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
+        <v>ELCRESOL_PARNU00</v>
+      </c>
+      <c r="W13" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in PARNU - Solar energy</v>
+      </c>
+      <c r="X13" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="21" t="str">
-        <f>V14</f>
-        <v>ELCTEOIL00</v>
+        <f t="shared" ref="B14:B37" si="2">V14</f>
+        <v>ELCRESOL_TARTU00</v>
       </c>
       <c r="C14" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L7,3)</f>
-        <v>ELCOIL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D14" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G14" s="83">
-        <f>((-SUM('EB1'!G6:M6)*$I$14)/($J$14*$O$14))</f>
-        <v>5.710602448742053</v>
-      </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="67">
-        <v>0.25</v>
-      </c>
-      <c r="J14" s="67">
-        <v>0.85</v>
-      </c>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67">
-        <v>20</v>
-      </c>
-      <c r="M14" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="N14" s="66">
-        <v>30</v>
-      </c>
-      <c r="O14" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P14" s="67">
+      <c r="G14">
+        <v>0.108</v>
+      </c>
+      <c r="I14" s="96">
         <v>1</v>
       </c>
-      <c r="R14" s="26">
-        <f>G14*$J14*$O14</f>
-        <v>153.07612499999996</v>
-      </c>
-      <c r="S14" s="29"/>
-      <c r="T14" s="94" t="s">
+      <c r="J14" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L14" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M14" s="85">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
+        <v>35</v>
+      </c>
+      <c r="O14" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P14" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="R14" s="81"/>
+      <c r="T14" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U14" s="94"/>
-      <c r="V14" s="94" t="str">
-        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$7,3)&amp;"00"</f>
-        <v>ELCTEOIL00</v>
-      </c>
-      <c r="W14" s="95" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V14,2)&amp;" - "&amp;'EB1'!F3</f>
-        <v>Power Plants Existing00 - Crude oil</v>
-      </c>
-      <c r="X14" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y14" s="94" t="str">
+      <c r="V14" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
+        <v>ELCRESOL_TARTU00</v>
+      </c>
+      <c r="W14" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in TARTU - Solar energy</v>
+      </c>
+      <c r="X14" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" s="95"/>
+      <c r="B15" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z14" s="94"/>
-      <c r="AA14" s="94"/>
-      <c r="AB14" s="94"/>
-    </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B15" s="21" t="str">
-        <f>V15</f>
-        <v>ELCNENUC00</v>
+        <v>ELCRESOL_LVIRU00</v>
       </c>
       <c r="C15" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L8,3)</f>
-        <v>ELCNUC</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D15" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G15" s="83">
-        <f>(-'EB1'!$N$6*$I$15)/($J$15*$O$15)</f>
-        <v>51.797945205479458</v>
-      </c>
-      <c r="H15" s="83">
-        <f>G15</f>
-        <v>51.797945205479458</v>
-      </c>
-      <c r="I15" s="66">
-        <v>0.33</v>
-      </c>
-      <c r="J15" s="67">
-        <v>0.9</v>
-      </c>
-      <c r="K15" s="66"/>
-      <c r="L15" s="67">
-        <v>38</v>
-      </c>
-      <c r="M15" s="66">
-        <v>0.27</v>
-      </c>
-      <c r="N15" s="43"/>
-      <c r="O15" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P15" s="67">
+      <c r="G15">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="I15" s="96">
         <v>1</v>
       </c>
-      <c r="R15" s="26">
-        <f>G15*$J15*$O15</f>
-        <v>1470.1500000000003</v>
-      </c>
-      <c r="S15" s="29"/>
-      <c r="T15" s="94" t="s">
+      <c r="J15" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K15" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L15" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M15" s="85">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21">
+        <v>35</v>
+      </c>
+      <c r="O15" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P15" s="76">
+        <v>0.14867925344692126</v>
+      </c>
+      <c r="R15" s="81"/>
+      <c r="T15" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="94"/>
-      <c r="V15" s="94" t="str">
-        <f>$B$2&amp;$F$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$8,3)&amp;"00"</f>
-        <v>ELCNENUC00</v>
-      </c>
-      <c r="W15" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V15,2)&amp;" - "&amp;'EB1'!N3</f>
-        <v>Power Plants Existing00 - Nuclear Energy</v>
-      </c>
-      <c r="X15" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y15" s="94" t="str">
+      <c r="V15" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="W15" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in LVIRU - Solar energy</v>
+      </c>
+      <c r="X15" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" s="95"/>
+      <c r="B16" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z15" s="90" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA15" s="94"/>
-      <c r="AB15" s="94"/>
-    </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B16" s="21" t="str">
-        <f>V16</f>
-        <v>ELCREBIO00</v>
+        <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="C16" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L9,3)</f>
-        <v>ELCBIO</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D16" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G16" s="83">
-        <f>(-'EB1'!$O$6*$I$16)/($J$16*$O$16)</f>
-        <v>7.8023302733384083</v>
-      </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="65">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J16" s="65">
-        <v>0.6</v>
-      </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="43">
-        <v>25</v>
-      </c>
-      <c r="M16" s="65">
-        <v>0.35</v>
-      </c>
-      <c r="N16" s="43">
-        <v>25</v>
-      </c>
-      <c r="O16" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P16" s="67">
+      <c r="G16">
+        <v>7.8E-2</v>
+      </c>
+      <c r="I16" s="96">
         <v>1</v>
       </c>
-      <c r="R16" s="26">
-        <f>G16*$J16*$O16</f>
-        <v>147.63257250000001</v>
-      </c>
-      <c r="S16" s="29"/>
-      <c r="T16" s="94" t="s">
+      <c r="J16" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L16" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M16" s="85">
+        <v>0</v>
+      </c>
+      <c r="N16" s="21">
+        <v>35</v>
+      </c>
+      <c r="O16" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P16" s="76">
+        <v>0.14701259708091721</v>
+      </c>
+      <c r="R16" s="81"/>
+      <c r="T16" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"00"</f>
-        <v>ELCREBIO00</v>
-      </c>
-      <c r="W16" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V16,2)&amp;" - "&amp;'EB1'!O3</f>
-        <v>Power Plants Existing00 - Biomass</v>
-      </c>
-      <c r="X16" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y16" s="94" t="str">
+      <c r="V16" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
+        <v>ELCRESOL_IVIRU00</v>
+      </c>
+      <c r="W16" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in IVIRU - Solar energy</v>
+      </c>
+      <c r="X16" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A17" s="95"/>
+      <c r="B17" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z16" s="90"/>
-      <c r="AA16" s="94"/>
-      <c r="AB16" s="94"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B17" s="21" t="str">
-        <f>V17</f>
-        <v>ELCREHYD00</v>
+        <v>ELCRESOL_JARVA00</v>
       </c>
       <c r="C17" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L10,3)</f>
-        <v>ELCHYD</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D17" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="E17" s="43">
-        <v>15</v>
-      </c>
-      <c r="F17" s="43">
-        <v>16</v>
-      </c>
-      <c r="G17" s="87"/>
-      <c r="H17" s="88"/>
-      <c r="I17" s="65">
+      <c r="G17">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="I17" s="96">
         <v>1</v>
       </c>
-      <c r="J17" s="65">
-        <v>0.5</v>
-      </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="43">
-        <v>50</v>
-      </c>
-      <c r="M17" s="65">
-        <v>2</v>
-      </c>
-      <c r="N17" s="43">
-        <v>50</v>
-      </c>
-      <c r="O17" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P17" s="67">
-        <v>0.5</v>
-      </c>
-      <c r="R17" s="26">
-        <f>(E17+F17)*$J17*$O17</f>
-        <v>488.80799999999999</v>
-      </c>
-      <c r="S17" s="29"/>
-      <c r="T17" s="94" t="s">
+      <c r="J17" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K17" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L17" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M17" s="85">
+        <v>0</v>
+      </c>
+      <c r="N17" s="21">
+        <v>35</v>
+      </c>
+      <c r="O17" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P17" s="76">
+        <v>0.15309859852159369</v>
+      </c>
+      <c r="R17" s="81"/>
+      <c r="T17" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U17" s="94"/>
-      <c r="V17" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
-        <v>ELCREHYD00</v>
-      </c>
-      <c r="W17" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V17,2)&amp;" - "&amp;'EB1'!P3</f>
-        <v>Power Plants Existing00 - Hydro power</v>
-      </c>
-      <c r="X17" s="94" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y17" s="94" t="str">
+      <c r="V17" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
+        <v>ELCRESOL_JARVA00</v>
+      </c>
+      <c r="W17" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in JARVA - Solar energy</v>
+      </c>
+      <c r="X17" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A18" s="95"/>
+      <c r="B18" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z17" s="94"/>
-      <c r="AA17" s="94"/>
-      <c r="AB17" s="94"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B18" s="97" t="str">
-        <f>V18</f>
-        <v>ELCREWIN00</v>
+        <v>ELCRESOL_JOGEVA00</v>
       </c>
       <c r="C18" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L11,3)</f>
-        <v>ELCWIN</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
+        <v>ELCSOL</v>
       </c>
       <c r="D18" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G18" s="83">
-        <f>(-'EB1'!$Q$6*$I$18)/($J$18*$O$18)</f>
-        <v>23.908866057838662</v>
-      </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="65">
+      <c r="G18">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I18" s="96">
         <v>1</v>
       </c>
-      <c r="J18" s="65">
-        <v>0.35</v>
-      </c>
-      <c r="K18" s="65"/>
-      <c r="L18" s="43">
+      <c r="J18" s="64">
+        <v>0.3</v>
+      </c>
+      <c r="K18" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L18" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M18" s="85">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21">
         <v>35</v>
       </c>
-      <c r="M18" s="65">
-        <v>0.5</v>
-      </c>
-      <c r="N18" s="43">
-        <v>20</v>
-      </c>
-      <c r="O18" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P18" s="67">
-        <v>0.3</v>
-      </c>
-      <c r="R18" s="26">
-        <f>G18*$J18*$O18</f>
-        <v>263.8965</v>
-      </c>
-      <c r="S18" s="29"/>
-      <c r="T18" s="99" t="s">
+      <c r="O18" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P18" s="76">
+        <v>0.15309859852159369</v>
+      </c>
+      <c r="R18" s="81"/>
+      <c r="T18" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U18" s="99"/>
-      <c r="V18" s="99" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$11,3)&amp;"00"</f>
-        <v>ELCREWIN00</v>
-      </c>
-      <c r="W18" s="99" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" - "&amp;'EB1'!Q3</f>
-        <v>Power Plants Existing00 - Wind energy</v>
-      </c>
-      <c r="X18" s="99" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y18" s="99" t="str">
+      <c r="V18" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
+        <v>ELCRESOL_JOGEVA00</v>
+      </c>
+      <c r="W18" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
+      </c>
+      <c r="X18" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B19" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z18" s="94"/>
-      <c r="AA18" s="94"/>
-      <c r="AB18" s="94"/>
-    </row>
-    <row r="19" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="str">
-        <f>V19</f>
-        <v>ELCRESOL00</v>
+        <v>ELCRESOL_HARJU00</v>
       </c>
       <c r="C19" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6590,64 +7246,58 @@
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G19" s="83">
-        <f>(-'EB1'!$T$6*$I$19)/($J$19*$O$19)</f>
-        <v>7.1875528496533061</v>
-      </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="65">
+      <c r="G19">
+        <v>0.04</v>
+      </c>
+      <c r="I19" s="96">
         <v>1</v>
       </c>
-      <c r="J19" s="65">
+      <c r="J19" s="64">
         <v>0.3</v>
       </c>
-      <c r="K19" s="65"/>
-      <c r="L19" s="43">
-        <v>60</v>
-      </c>
-      <c r="M19" s="65"/>
-      <c r="N19" s="43">
-        <v>15</v>
-      </c>
-      <c r="O19" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P19" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="R19" s="26">
-        <f>G19*$J19*$O19</f>
-        <v>68</v>
-      </c>
-      <c r="S19" s="29"/>
-      <c r="T19" s="98" t="s">
+      <c r="K19" s="7">
+        <v>1018</v>
+      </c>
+      <c r="L19" s="85">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="M19" s="85">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
+        <v>35</v>
+      </c>
+      <c r="O19" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P19" s="76">
+        <v>0.15619560585976827</v>
+      </c>
+      <c r="T19" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="U19" s="98"/>
-      <c r="V19" s="98" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"00"</f>
-        <v>ELCRESOL00</v>
-      </c>
-      <c r="W19" s="98" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" - "&amp;'EB1'!T3</f>
-        <v>Power Plants Existing00 - Solar energy</v>
-      </c>
-      <c r="X19" s="98" t="str">
-        <f t="shared" si="1"/>
-        <v>PJ</v>
-      </c>
-      <c r="Y19" s="98" t="str">
+      <c r="V19" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="W19" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in HARJU - Solar energy</v>
+      </c>
+      <c r="X19" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>GW</v>
-      </c>
-      <c r="Z19" s="94"/>
-      <c r="AA19" s="94"/>
-      <c r="AB19" s="94"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B20" s="21" t="str">
-        <f>V20</f>
-        <v>ELCRESOL_PARNU00</v>
+        <v>ELCRESOL_POLVA00</v>
       </c>
       <c r="C20" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6660,40 +7310,43 @@
       <c r="G20">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I20" s="101">
+      <c r="I20" s="96">
         <v>1</v>
+      </c>
+      <c r="J20" s="64">
+        <v>0.3</v>
       </c>
       <c r="K20" s="7">
         <v>1018</v>
       </c>
-      <c r="L20" s="88">
+      <c r="L20" s="85">
         <v>16.064040000000002</v>
       </c>
-      <c r="M20" s="88">
+      <c r="M20" s="85">
         <v>0</v>
       </c>
       <c r="N20" s="21">
         <v>35</v>
       </c>
-      <c r="O20" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P20" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T20" s="94" t="s">
+      <c r="O20" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P20" s="76">
+        <v>0.14537310453496291</v>
+      </c>
+      <c r="T20" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V20" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
-        <v>ELCRESOL_PARNU00</v>
-      </c>
-      <c r="W20" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in PARNU - Solar energy</v>
+      <c r="V20" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
+        <v>ELCRESOL_POLVA00</v>
+      </c>
+      <c r="W20" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
       <c r="X20" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y20" t="s">
         <v>101</v>
@@ -6702,10 +7355,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B21" s="21" t="str">
-        <f t="shared" ref="B21:B43" si="3">V21</f>
-        <v>ELCRESOL_TARTU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_VALGA00</v>
       </c>
       <c r="C21" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6716,43 +7369,45 @@
         <v>ELCC</v>
       </c>
       <c r="G21">
-        <v>0.108</v>
-      </c>
-      <c r="I21" s="101">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I21" s="96">
         <v>1</v>
+      </c>
+      <c r="J21" s="64">
+        <v>0.3</v>
       </c>
       <c r="K21" s="7">
         <v>1018</v>
       </c>
-      <c r="L21" s="88">
+      <c r="L21" s="85">
         <v>16.064040000000002</v>
       </c>
-      <c r="M21" s="88">
+      <c r="M21" s="85">
         <v>0</v>
       </c>
       <c r="N21" s="21">
         <v>35</v>
       </c>
-      <c r="O21" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P21" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="R21" s="82"/>
-      <c r="T21" s="94" t="s">
+      <c r="O21" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P21" s="76">
+        <v>0.14763873655681015</v>
+      </c>
+      <c r="T21" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V21" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
-        <v>ELCRESOL_TARTU00</v>
-      </c>
-      <c r="W21" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in TARTU - Solar energy</v>
+      <c r="V21" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
+        <v>ELCRESOL_VALGA00</v>
+      </c>
+      <c r="W21" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
       <c r="X21" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y21" t="s">
         <v>101</v>
@@ -6761,11 +7416,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A22" s="100"/>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_LVIRU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_VILJANDI00</v>
       </c>
       <c r="C22" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6776,43 +7430,45 @@
         <v>ELCC</v>
       </c>
       <c r="G22">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="I22" s="101">
+        <v>0.08</v>
+      </c>
+      <c r="I22" s="96">
         <v>1</v>
+      </c>
+      <c r="J22" s="64">
+        <v>0.3</v>
       </c>
       <c r="K22" s="7">
         <v>1018</v>
       </c>
-      <c r="L22" s="88">
+      <c r="L22" s="85">
         <v>16.064040000000002</v>
       </c>
-      <c r="M22" s="88">
+      <c r="M22" s="85">
         <v>0</v>
       </c>
       <c r="N22" s="21">
         <v>35</v>
       </c>
-      <c r="O22" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P22" s="77">
-        <v>0.14867925344692126</v>
-      </c>
-      <c r="R22" s="82"/>
-      <c r="T22" s="94" t="s">
+      <c r="O22" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P22" s="76">
+        <v>0.1532628310027955</v>
+      </c>
+      <c r="T22" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V22" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
-        <v>ELCRESOL_LVIRU00</v>
-      </c>
-      <c r="W22" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in LVIRU - Solar energy</v>
+      <c r="V22" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
+        <v>ELCRESOL_VILJANDI00</v>
+      </c>
+      <c r="W22" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
       <c r="X22" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y22" t="s">
         <v>101</v>
@@ -6821,11 +7477,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A23" s="100"/>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_IVIRU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_VORU00</v>
       </c>
       <c r="C23" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6836,43 +7491,45 @@
         <v>ELCC</v>
       </c>
       <c r="G23">
-        <v>7.8E-2</v>
-      </c>
-      <c r="I23" s="101">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I23" s="96">
         <v>1</v>
       </c>
+      <c r="J23" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K23" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L23" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M23" s="88">
+        <v>1019</v>
+      </c>
+      <c r="L23" s="85">
+        <v>16.079820000000002</v>
+      </c>
+      <c r="M23" s="85">
         <v>0</v>
       </c>
       <c r="N23" s="21">
         <v>35</v>
       </c>
-      <c r="O23" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P23" s="77">
-        <v>0.14701259708091721</v>
-      </c>
-      <c r="R23" s="82"/>
-      <c r="T23" s="94" t="s">
+      <c r="O23" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P23" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T23" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V23" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
-        <v>ELCRESOL_IVIRU00</v>
-      </c>
-      <c r="W23" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in IVIRU - Solar energy</v>
+      <c r="V23" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
+        <v>ELCRESOL_VORU00</v>
+      </c>
+      <c r="W23" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
       <c r="X23" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y23" t="s">
         <v>101</v>
@@ -6881,11 +7538,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A24" s="100"/>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_JARVA00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="C24" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6896,43 +7552,45 @@
         <v>ELCC</v>
       </c>
       <c r="G24">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="I24" s="101">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I24" s="96">
         <v>1</v>
       </c>
+      <c r="J24" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K24" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L24" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M24" s="88">
+        <v>1020</v>
+      </c>
+      <c r="L24" s="85">
+        <v>16.095600000000001</v>
+      </c>
+      <c r="M24" s="85">
         <v>0</v>
       </c>
       <c r="N24" s="21">
         <v>35</v>
       </c>
-      <c r="O24" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P24" s="77">
-        <v>0.15309859852159369</v>
-      </c>
-      <c r="R24" s="82"/>
-      <c r="T24" s="94" t="s">
+      <c r="O24" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P24" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T24" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V24" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
-        <v>ELCRESOL_JARVA00</v>
-      </c>
-      <c r="W24" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in JARVA - Solar energy</v>
+      <c r="V24" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
+        <v>ELCRESOL_SAARE00</v>
+      </c>
+      <c r="W24" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
       <c r="X24" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y24" t="s">
         <v>101</v>
@@ -6941,11 +7599,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A25" s="100"/>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B25" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_JOGEVA00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_RAPLA00</v>
       </c>
       <c r="C25" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -6956,43 +7613,45 @@
         <v>ELCC</v>
       </c>
       <c r="G25">
-        <v>4.7E-2</v>
-      </c>
-      <c r="I25" s="101">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I25" s="96">
         <v>1</v>
       </c>
+      <c r="J25" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K25" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L25" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M25" s="88">
+        <v>1021</v>
+      </c>
+      <c r="L25" s="85">
+        <v>16.111380000000004</v>
+      </c>
+      <c r="M25" s="85">
         <v>0</v>
       </c>
       <c r="N25" s="21">
         <v>35</v>
       </c>
-      <c r="O25" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P25" s="77">
-        <v>0.15309859852159369</v>
-      </c>
-      <c r="R25" s="82"/>
-      <c r="T25" s="94" t="s">
+      <c r="O25" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P25" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T25" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V25" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
-        <v>ELCRESOL_JOGEVA00</v>
-      </c>
-      <c r="W25" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
+      <c r="V25" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
+        <v>ELCRESOL_RAPLA00</v>
+      </c>
+      <c r="W25" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
       <c r="X25" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y25" t="s">
         <v>101</v>
@@ -7001,10 +7660,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_HARJU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="C26" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -7015,42 +7674,45 @@
         <v>ELCC</v>
       </c>
       <c r="G26">
-        <v>0.04</v>
-      </c>
-      <c r="I26" s="101">
+        <v>0.01</v>
+      </c>
+      <c r="I26" s="96">
         <v>1</v>
       </c>
+      <c r="J26" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K26" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L26" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M26" s="88">
+        <v>1022</v>
+      </c>
+      <c r="L26" s="85">
+        <v>16.127160000000003</v>
+      </c>
+      <c r="M26" s="85">
         <v>0</v>
       </c>
       <c r="N26" s="21">
         <v>35</v>
       </c>
-      <c r="O26" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P26" s="77">
-        <v>0.15619560585976827</v>
-      </c>
-      <c r="T26" s="94" t="s">
+      <c r="O26" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="P26" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T26" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V26" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
-        <v>ELCRESOL_HARJU00</v>
-      </c>
-      <c r="W26" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in HARJU - Solar energy</v>
+      <c r="V26" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="W26" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
       <c r="X26" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y26" t="s">
         <v>101</v>
@@ -7059,10 +7721,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_POLVA00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_HIIU00</v>
       </c>
       <c r="C27" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
@@ -7073,42 +7735,45 @@
         <v>ELCC</v>
       </c>
       <c r="G27">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="I27" s="101">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I27" s="96">
         <v>1</v>
       </c>
+      <c r="J27" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K27" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L27" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M27" s="88">
+        <v>1023</v>
+      </c>
+      <c r="L27" s="85">
+        <v>16.142940000000003</v>
+      </c>
+      <c r="M27" s="85">
         <v>0</v>
       </c>
       <c r="N27" s="21">
         <v>35</v>
       </c>
-      <c r="O27" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P27" s="77">
-        <v>0.14537310453496291</v>
-      </c>
-      <c r="T27" s="94" t="s">
+      <c r="O27" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P27" s="76">
+        <v>0.1461854238754417</v>
+      </c>
+      <c r="T27" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V27" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
-        <v>ELCRESOL_POLVA00</v>
-      </c>
-      <c r="W27" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in POLVA - Solar energy</v>
+      <c r="V27" s="91" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
+        <v>ELCRESOL_HIIU00</v>
+      </c>
+      <c r="W27" s="91" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
+        <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
       <c r="X27" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y27" t="s">
         <v>101</v>
@@ -7117,56 +7782,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_VALGA00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_SOPITOOTSI00</v>
       </c>
       <c r="C28" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D28" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G28">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="I28" s="101">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="I28" s="96">
         <v>1</v>
       </c>
+      <c r="J28" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K28" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L28" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M28" s="88">
-        <v>0</v>
-      </c>
-      <c r="N28" s="21">
-        <v>35</v>
-      </c>
-      <c r="O28" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P28" s="77">
-        <v>0.14763873655681015</v>
-      </c>
-      <c r="T28" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L28" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M28" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N28">
+        <v>27</v>
+      </c>
+      <c r="O28" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P28">
+        <v>0.4</v>
+      </c>
+      <c r="T28" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V28" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
-        <v>ELCRESOL_VALGA00</v>
-      </c>
-      <c r="W28" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in VALGA - Solar energy</v>
+      <c r="V28" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
+        <v>ELCRESOL_SOPITOOTSI00</v>
+      </c>
+      <c r="W28" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
       </c>
       <c r="X28" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y28" t="s">
         <v>101</v>
@@ -7175,56 +7843,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_VILJANDI00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_SOPIPURTSE00</v>
       </c>
       <c r="C29" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D29" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G29">
-        <v>0.08</v>
-      </c>
-      <c r="I29" s="101">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I29" s="96">
         <v>1</v>
       </c>
+      <c r="J29" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K29" s="7">
-        <v>1018</v>
-      </c>
-      <c r="L29" s="88">
-        <v>16.064040000000002</v>
-      </c>
-      <c r="M29" s="88">
-        <v>0</v>
-      </c>
-      <c r="N29" s="21">
-        <v>35</v>
-      </c>
-      <c r="O29" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P29" s="77">
-        <v>0.1532628310027955</v>
-      </c>
-      <c r="T29" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L29" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M29" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N29">
+        <v>27</v>
+      </c>
+      <c r="O29" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P29">
+        <v>0.4</v>
+      </c>
+      <c r="T29" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V29" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
-        <v>ELCRESOL_VILJANDI00</v>
-      </c>
-      <c r="W29" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
+      <c r="V29" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
+        <v>ELCRESOL_SOPIPURTSE00</v>
+      </c>
+      <c r="W29" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
       </c>
       <c r="X29" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y29" t="s">
         <v>101</v>
@@ -7233,56 +7904,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_VORU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_OTHER00</v>
       </c>
       <c r="C30" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D30" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G30">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="I30" s="101">
+        <v>8.130000000000015E-2</v>
+      </c>
+      <c r="I30" s="96">
         <v>1</v>
       </c>
+      <c r="J30" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K30" s="7">
-        <v>1019</v>
-      </c>
-      <c r="L30" s="88">
-        <v>16.079820000000002</v>
-      </c>
-      <c r="M30" s="88">
-        <v>0</v>
-      </c>
-      <c r="N30" s="21">
-        <v>35</v>
-      </c>
-      <c r="O30" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P30" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T30" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L30" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M30" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N30">
+        <v>27</v>
+      </c>
+      <c r="O30" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P30">
+        <v>0.4</v>
+      </c>
+      <c r="T30" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V30" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
-        <v>ELCRESOL_VORU00</v>
-      </c>
-      <c r="W30" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in VORU - Solar energy</v>
+      <c r="V30" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
+        <v>ELCRESOL_OTHER00</v>
+      </c>
+      <c r="W30" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
       </c>
       <c r="X30" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y30" t="s">
         <v>101</v>
@@ -7291,56 +7965,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="C31" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D31" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G31">
-        <v>3.1E-2</v>
-      </c>
-      <c r="I31" s="101">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I31" s="96">
         <v>1</v>
       </c>
+      <c r="J31" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K31" s="7">
-        <v>1020</v>
-      </c>
-      <c r="L31" s="88">
-        <v>16.095600000000001</v>
-      </c>
-      <c r="M31" s="88">
-        <v>0</v>
-      </c>
-      <c r="N31" s="21">
-        <v>35</v>
-      </c>
-      <c r="O31" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P31" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T31" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L31" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M31" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N31">
+        <v>27</v>
+      </c>
+      <c r="O31" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P31">
+        <v>0.4</v>
+      </c>
+      <c r="T31" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V31" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
+      <c r="V31" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
         <v>ELCRESOL_SAARE00</v>
       </c>
-      <c r="W31" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in SAARE - Solar energy</v>
+      <c r="W31" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
       </c>
       <c r="X31" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y31" t="s">
         <v>101</v>
@@ -7349,56 +8026,59 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_RAPLA00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_LVIRU00</v>
       </c>
       <c r="C32" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D32" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G32">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="I32" s="101">
+        <v>3.27E-2</v>
+      </c>
+      <c r="I32" s="96">
         <v>1</v>
       </c>
+      <c r="J32" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K32" s="7">
-        <v>1021</v>
-      </c>
-      <c r="L32" s="88">
-        <v>16.111380000000004</v>
-      </c>
-      <c r="M32" s="88">
-        <v>0</v>
-      </c>
-      <c r="N32" s="21">
-        <v>35</v>
-      </c>
-      <c r="O32" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P32" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T32" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L32" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M32" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N32">
+        <v>27</v>
+      </c>
+      <c r="O32" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P32">
+        <v>0.4</v>
+      </c>
+      <c r="T32" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V32" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
-        <v>ELCRESOL_RAPLA00</v>
-      </c>
-      <c r="W32" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in RAPLA - Solar energy</v>
+      <c r="V32" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
+        <v>ELCRESOL_LVIRU00</v>
+      </c>
+      <c r="W32" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
       </c>
       <c r="X32" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y32" t="s">
         <v>101</v>
@@ -7409,54 +8089,57 @@
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B33" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_LAANE00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_HARJU00</v>
       </c>
       <c r="C33" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D33" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G33">
-        <v>0.01</v>
-      </c>
-      <c r="I33" s="101">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="I33" s="96">
         <v>1</v>
       </c>
+      <c r="J33" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K33" s="7">
-        <v>1022</v>
-      </c>
-      <c r="L33" s="88">
-        <v>16.127160000000003</v>
-      </c>
-      <c r="M33" s="88">
-        <v>0</v>
-      </c>
-      <c r="N33" s="21">
-        <v>35</v>
-      </c>
-      <c r="O33" s="66">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P33" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T33" s="94" t="s">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L33" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M33" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N33">
+        <v>27</v>
+      </c>
+      <c r="O33" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P33">
+        <v>0.4</v>
+      </c>
+      <c r="T33" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V33" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
-        <v>ELCRESOL_LAANE00</v>
-      </c>
-      <c r="W33" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in LAANE - Solar energy</v>
+      <c r="V33" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
+        <v>ELCRESOL_HARJU00</v>
+      </c>
+      <c r="W33" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
       </c>
       <c r="X33" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y33" t="s">
         <v>101</v>
@@ -7467,54 +8150,57 @@
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B34" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_HIIU00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="C34" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L14,3)</f>
-        <v>ELCSOL</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
+        <v>ELCWON</v>
       </c>
       <c r="D34" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
       <c r="G34">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="I34" s="101">
+        <v>0.06</v>
+      </c>
+      <c r="I34" s="96">
         <v>1</v>
       </c>
+      <c r="J34" s="64">
+        <v>0.3</v>
+      </c>
       <c r="K34" s="7">
-        <v>1023</v>
-      </c>
-      <c r="L34" s="88">
-        <v>16.142940000000003</v>
-      </c>
-      <c r="M34" s="88">
-        <v>0</v>
-      </c>
-      <c r="N34" s="21">
-        <v>35</v>
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="L34" s="85">
+        <v>18.701711233400001</v>
+      </c>
+      <c r="M34" s="85">
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="N34">
+        <v>27</v>
       </c>
       <c r="O34" s="21">
         <v>8.76</v>
       </c>
-      <c r="P34" s="77">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="T34" s="94" t="s">
+      <c r="P34">
+        <v>0.4</v>
+      </c>
+      <c r="T34" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V34" s="94" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
-        <v>ELCRESOL_HIIU00</v>
-      </c>
-      <c r="W34" s="94" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V34,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
-        <v>Power Plants Existing00 in HIIU - Solar energy</v>
+      <c r="V34" t="str">
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
+        <v>ELCRESOL_LAANE00</v>
+      </c>
+      <c r="W34" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
       </c>
       <c r="X34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y34" t="s">
         <v>101</v>
@@ -7525,8 +8211,8 @@
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B35" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_SOPITOOTSI00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="C35" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -7537,18 +8223,21 @@
         <v>ELCC</v>
       </c>
       <c r="G35">
-        <v>7.9699999999999993E-2</v>
-      </c>
-      <c r="I35" s="101">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="I35" s="96">
         <v>1</v>
+      </c>
+      <c r="J35" s="64">
+        <v>0.3</v>
       </c>
       <c r="K35" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L35" s="88">
+      <c r="L35" s="85">
         <v>18.701711233400001</v>
       </c>
-      <c r="M35" s="88">
+      <c r="M35" s="85">
         <v>2.0036999999999998</v>
       </c>
       <c r="N35">
@@ -7560,19 +8249,19 @@
       <c r="P35">
         <v>0.4</v>
       </c>
-      <c r="T35" s="94" t="s">
+      <c r="T35" s="91" t="s">
         <v>102</v>
       </c>
       <c r="V35" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
-        <v>ELCRESOL_SOPITOOTSI00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
+        <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="W35" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V35,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
       </c>
       <c r="X35" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y35" t="s">
         <v>101</v>
@@ -7583,8 +8272,8 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B36" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_SOPIPURTSE00</v>
+        <f t="shared" si="2"/>
+        <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="C36" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -7595,18 +8284,21 @@
         <v>ELCC</v>
       </c>
       <c r="G36">
-        <v>0.17519999999999999</v>
-      </c>
-      <c r="I36" s="101">
+        <v>0.1036</v>
+      </c>
+      <c r="I36" s="96">
         <v>1</v>
+      </c>
+      <c r="J36" s="64">
+        <v>0.3</v>
       </c>
       <c r="K36" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L36" s="88">
+      <c r="L36" s="85">
         <v>18.701711233400001</v>
       </c>
-      <c r="M36" s="88">
+      <c r="M36" s="85">
         <v>2.0036999999999998</v>
       </c>
       <c r="N36">
@@ -7618,19 +8310,19 @@
       <c r="P36">
         <v>0.4</v>
       </c>
-      <c r="T36" s="94" t="s">
+      <c r="T36" s="91" t="s">
         <v>102</v>
       </c>
       <c r="V36" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
-        <v>ELCRESOL_SOPIPURTSE00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
+        <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="W36" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V36,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
+        <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
       </c>
       <c r="X36" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y36" t="s">
         <v>101</v>
@@ -7641,54 +8333,57 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_OTHER00</v>
+        <f t="shared" si="2"/>
+        <v>ELCREMSW_IRU00</v>
       </c>
       <c r="C37" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)</f>
+        <v>ELCMSW</v>
       </c>
       <c r="D37" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G37">
-        <v>8.130000000000015E-2</v>
-      </c>
-      <c r="I37" s="101">
-        <v>1</v>
-      </c>
-      <c r="K37" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L37" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M37" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N37">
-        <v>27</v>
+      <c r="G37" s="21">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I37" s="21">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J37" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="K37" s="81">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="L37" s="81">
+        <v>160.216352398</v>
+      </c>
+      <c r="M37" s="81">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="N37" s="81">
+        <v>53</v>
       </c>
       <c r="O37" s="21">
         <v>8.76</v>
       </c>
       <c r="P37">
-        <v>0.4</v>
-      </c>
-      <c r="T37" s="94" t="s">
+        <v>1</v>
+      </c>
+      <c r="T37" s="91" t="s">
         <v>102</v>
       </c>
       <c r="V37" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
-        <v>ELCRESOL_OTHER00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)&amp;"_IRU"&amp;"00"</f>
+        <v>ELCREMSW_IRU00</v>
       </c>
       <c r="W37" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V37,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V37,2)&amp;" Iru Power plant - Municipal waste"</f>
+        <v>Power Plants Existing00 Iru Power plant - Municipal waste</v>
       </c>
       <c r="X37" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y37" t="s">
         <v>101</v>
@@ -7699,54 +8394,58 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B38" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_SAARE00</v>
+        <f>V38</f>
+        <v>ELCTESHL_EESTI00</v>
       </c>
       <c r="C38" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)</f>
+        <v>ELCSHL</v>
       </c>
       <c r="D38" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G38">
-        <v>1.6E-2</v>
-      </c>
-      <c r="I38" s="101">
-        <v>1</v>
-      </c>
-      <c r="K38" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L38" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M38" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N38">
-        <v>27</v>
+      <c r="G38" s="21">
+        <v>0.77</v>
+      </c>
+      <c r="I38" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="J38" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K38" s="81">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="L38" s="81">
+        <v>63.037519640000006</v>
+      </c>
+      <c r="M38" s="81">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="N38" s="81">
+        <v>40</v>
       </c>
       <c r="O38" s="21">
         <v>8.76</v>
       </c>
-      <c r="P38">
-        <v>0.4</v>
-      </c>
-      <c r="T38" s="94" t="s">
+      <c r="P38" s="21">
+        <v>1</v>
+      </c>
+      <c r="T38" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V38" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
-        <v>ELCRESOL_SAARE00</v>
+      <c r="U38" s="91"/>
+      <c r="V38" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_EESTI00"</f>
+        <v>ELCTESHL_EESTI00</v>
       </c>
       <c r="W38" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V38,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V38,2)&amp;" Eesti Power plant - Oil Shale"</f>
+        <v>Power Plants Existing00 Eesti Power plant - Oil Shale</v>
       </c>
       <c r="X38" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y38" t="s">
         <v>101</v>
@@ -7757,54 +8456,58 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B39" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_LVIRU00</v>
+        <f>V39</f>
+        <v>ELCTESHL_AUVERE00</v>
       </c>
       <c r="C39" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)</f>
+        <v>ELCSHL</v>
       </c>
       <c r="D39" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G39">
-        <v>3.27E-2</v>
-      </c>
-      <c r="I39" s="101">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L39" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M39" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N39">
-        <v>27</v>
+      <c r="G39" s="21">
+        <v>0.26</v>
+      </c>
+      <c r="I39" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="J39" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K39" s="81">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="L39" s="81">
+        <v>63.037519640000006</v>
+      </c>
+      <c r="M39" s="81">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="N39" s="21">
+        <v>40</v>
       </c>
       <c r="O39" s="21">
         <v>8.76</v>
       </c>
-      <c r="P39">
-        <v>0.4</v>
-      </c>
-      <c r="T39" s="94" t="s">
+      <c r="P39" s="21">
+        <v>1</v>
+      </c>
+      <c r="T39" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V39" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
-        <v>ELCRESOL_LVIRU00</v>
+      <c r="U39" s="91"/>
+      <c r="V39" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_AUVERE00"</f>
+        <v>ELCTESHL_AUVERE00</v>
       </c>
       <c r="W39" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V39,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V39,2)&amp;" Auvere Power plant - Oil Shale"</f>
+        <v>Power Plants Existing00 Auvere Power plant - Oil Shale</v>
       </c>
       <c r="X39" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y39" t="s">
         <v>101</v>
@@ -7815,54 +8518,58 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B40" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_HARJU00</v>
+        <f>V40</f>
+        <v>ELCTESHL_ENEFIT00</v>
       </c>
       <c r="C40" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)</f>
+        <v>ELCSHL</v>
       </c>
       <c r="D40" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G40">
-        <v>6.3399999999999998E-2</v>
-      </c>
-      <c r="I40" s="101">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L40" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M40" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N40">
-        <v>27</v>
+      <c r="G40" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="I40" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="J40" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K40" s="81">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="L40" s="81">
+        <v>63.037519640000006</v>
+      </c>
+      <c r="M40" s="81">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="N40" s="21">
+        <v>40</v>
       </c>
       <c r="O40" s="21">
         <v>8.76</v>
       </c>
-      <c r="P40">
-        <v>0.4</v>
-      </c>
-      <c r="T40" s="94" t="s">
+      <c r="P40" s="21">
+        <v>1</v>
+      </c>
+      <c r="T40" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V40" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
-        <v>ELCRESOL_HARJU00</v>
+      <c r="U40" s="91"/>
+      <c r="V40" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_ENEFIT00"</f>
+        <v>ELCTESHL_ENEFIT00</v>
       </c>
       <c r="W40" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V40,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V40,2)&amp;" Eenefit Power plant - Oil Shale"</f>
+        <v>Power Plants Existing00 Eenefit Power plant - Oil Shale</v>
       </c>
       <c r="X40" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y40" t="s">
         <v>101</v>
@@ -7873,54 +8580,58 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B41" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_LAANE00</v>
+        <f>V41</f>
+        <v>ELCTESHL_BALTI00</v>
       </c>
       <c r="C41" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)</f>
+        <v>ELCSHL</v>
       </c>
       <c r="D41" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G41">
-        <v>0.06</v>
-      </c>
-      <c r="I41" s="101">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L41" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M41" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N41">
-        <v>27</v>
+      <c r="G41" s="21">
+        <v>0.185</v>
+      </c>
+      <c r="I41" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="J41" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K41" s="81">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="L41" s="81">
+        <v>63.037519640000006</v>
+      </c>
+      <c r="M41" s="81">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="N41" s="21">
+        <v>40</v>
       </c>
       <c r="O41" s="21">
         <v>8.76</v>
       </c>
-      <c r="P41">
-        <v>0.4</v>
-      </c>
-      <c r="T41" s="94" t="s">
+      <c r="P41" s="21">
+        <v>1</v>
+      </c>
+      <c r="T41" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V41" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
-        <v>ELCRESOL_LAANE00</v>
+      <c r="U41" s="91"/>
+      <c r="V41" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_BALTI00"</f>
+        <v>ELCTESHL_BALTI00</v>
       </c>
       <c r="W41" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V41,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V41,2)&amp;" Balti Power plant - Oil Shale"</f>
+        <v>Power Plants Existing00 Balti Power plant - Oil Shale</v>
       </c>
       <c r="X41" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y41" t="s">
         <v>101</v>
@@ -7931,54 +8642,57 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B42" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_IVIRU00</v>
+        <f>V42</f>
+        <v>ELCTESHL_SILLAMAE00</v>
       </c>
       <c r="C42" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)</f>
+        <v>ELCSHL</v>
       </c>
       <c r="D42" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G42">
-        <v>8.2000000000000003E-2</v>
-      </c>
-      <c r="I42" s="101">
-        <v>1</v>
-      </c>
-      <c r="K42" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L42" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M42" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N42">
-        <v>27</v>
+      <c r="G42" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="I42" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="J42" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K42" s="81">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="L42" s="81">
+        <v>63.037519640000006</v>
+      </c>
+      <c r="M42" s="81">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="N42" s="21">
+        <v>40</v>
       </c>
       <c r="O42" s="21">
         <v>8.76</v>
       </c>
-      <c r="P42">
-        <v>0.4</v>
-      </c>
-      <c r="T42" s="94" t="s">
+      <c r="P42" s="21">
+        <v>1</v>
+      </c>
+      <c r="T42" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V42" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
-        <v>ELCRESOL_IVIRU00</v>
+      <c r="V42" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_SILLAMAE00"</f>
+        <v>ELCTESHL_SILLAMAE00</v>
       </c>
       <c r="W42" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V42,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V42,2)&amp;" Sillamae Power plant - Oil Shale"</f>
+        <v>Power Plants Existing00 Sillamae Power plant - Oil Shale</v>
       </c>
       <c r="X42" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y42" t="s">
         <v>101</v>
@@ -7989,54 +8703,58 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B43" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>ELCRESOL_PARNU00</v>
+        <f t="shared" ref="B43:B45" si="3">V43</f>
+        <v>ELCTEGAS_POHJA00</v>
       </c>
       <c r="C43" s="21" t="str">
-        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
-        <v>ELCWON</v>
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
+        <v>ELCGAS</v>
       </c>
       <c r="D43" s="21" t="str">
         <f t="shared" si="0"/>
         <v>ELCC</v>
       </c>
-      <c r="G43">
-        <v>0.1036</v>
-      </c>
-      <c r="I43" s="101">
-        <v>1</v>
-      </c>
-      <c r="K43" s="7">
-        <v>1494.4630999999999</v>
-      </c>
-      <c r="L43" s="88">
-        <v>18.701711233400001</v>
-      </c>
-      <c r="M43" s="88">
-        <v>2.0036999999999998</v>
-      </c>
-      <c r="N43">
-        <v>27</v>
+      <c r="G43" s="21">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="I43" s="76">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J43" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K43" s="81">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="L43" s="81">
+        <v>39.138495576499992</v>
+      </c>
+      <c r="M43" s="81">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="N43" s="81">
+        <v>40</v>
       </c>
       <c r="O43" s="21">
         <v>8.76</v>
       </c>
-      <c r="P43">
-        <v>0.4</v>
-      </c>
-      <c r="T43" s="94" t="s">
+      <c r="P43" s="21">
+        <v>1</v>
+      </c>
+      <c r="T43" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="V43" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
-        <v>ELCRESOL_PARNU00</v>
+      <c r="U43" s="91"/>
+      <c r="V43" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_POHJA00"</f>
+        <v>ELCTEGAS_POHJA00</v>
       </c>
       <c r="W43" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V43,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
-        <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V43,2)&amp;" Pohja Power plant - "&amp;'EB1'!E3</f>
+        <v>Power Plants Existing00 Pohja Power plant - Natural Gas</v>
       </c>
       <c r="X43" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="Y43" t="s">
         <v>101</v>
@@ -8045,8 +8763,313 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65536" spans="19:19" x14ac:dyDescent="0.2">
-      <c r="S65536" s="29"/>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B44" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCTEBIO_TLNUTILITAS00</v>
+      </c>
+      <c r="C44" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D44" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G44" s="21">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I44" s="76">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="J44" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K44" s="81">
+        <v>2950.7891</v>
+      </c>
+      <c r="L44" s="81">
+        <v>133.5792717679</v>
+      </c>
+      <c r="M44" s="81">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="N44" s="81">
+        <v>40</v>
+      </c>
+      <c r="O44" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P44" s="21">
+        <v>1</v>
+      </c>
+      <c r="T44" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V44" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TLNUTILITAS00"</f>
+        <v>ELCTEBIO_TLNUTILITAS00</v>
+      </c>
+      <c r="W44" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V44,2)&amp;" Tallinn Utilitas Power plant - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Tallinn Utilitas Power plant - Biomass</v>
+      </c>
+      <c r="X44" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B45" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>ELCTEBIO_TARTU00</v>
+      </c>
+      <c r="C45" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D45" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G45" s="21">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="I45" s="76">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="J45" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K45" s="81">
+        <v>2950.7891</v>
+      </c>
+      <c r="L45" s="81">
+        <v>133.5792717679</v>
+      </c>
+      <c r="M45" s="81">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="N45" s="81">
+        <v>40</v>
+      </c>
+      <c r="O45" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P45" s="21">
+        <v>1</v>
+      </c>
+      <c r="T45" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V45" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TARTU00"</f>
+        <v>ELCTEBIO_TARTU00</v>
+      </c>
+      <c r="W45" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V45,2)&amp;" Tartu Power plant - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Tartu Power plant - Biomass</v>
+      </c>
+      <c r="X45" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B46" s="21" t="str">
+        <f>V46</f>
+        <v>ELCTEBIO_PARNU00</v>
+      </c>
+      <c r="C46" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D46" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G46" s="21">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="I46" s="76">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="J46" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K46" s="81">
+        <v>2950.7891</v>
+      </c>
+      <c r="L46" s="81">
+        <v>133.5792717679</v>
+      </c>
+      <c r="M46" s="81">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="N46" s="81">
+        <v>40</v>
+      </c>
+      <c r="O46" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P46" s="21">
+        <v>1</v>
+      </c>
+      <c r="T46" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V46" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PARNU00"</f>
+        <v>ELCTEBIO_PARNU00</v>
+      </c>
+      <c r="W46" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V46,2)&amp;" Parnu Power plant - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Parnu Power plant - Biomass</v>
+      </c>
+      <c r="X46" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B47" s="21" t="str">
+        <f>V47</f>
+        <v>ELCTEBIO_HORIZON00</v>
+      </c>
+      <c r="C47" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D47" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G47" s="21">
+        <v>1.3900000000000001E-2</v>
+      </c>
+      <c r="I47" s="76">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="J47" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K47" s="81">
+        <v>2950.7891</v>
+      </c>
+      <c r="L47" s="81">
+        <v>133.5792717679</v>
+      </c>
+      <c r="M47" s="81">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="N47" s="81">
+        <v>40</v>
+      </c>
+      <c r="O47" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P47" s="21">
+        <v>1</v>
+      </c>
+      <c r="T47" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V47" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HORIZON00"</f>
+        <v>ELCTEBIO_HORIZON00</v>
+      </c>
+      <c r="W47" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V47,2)&amp;" Horizon Power plant - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Horizon Power plant - Biomass</v>
+      </c>
+      <c r="X47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B48" s="21" t="str">
+        <f>V48</f>
+        <v>ELCTEGAS_GRUNE00</v>
+      </c>
+      <c r="C48" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D48" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCC</v>
+      </c>
+      <c r="G48" s="21">
+        <v>4.0999999999999995E-3</v>
+      </c>
+      <c r="I48">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J48" s="21">
+        <v>0.95</v>
+      </c>
+      <c r="K48" s="7">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="L48" s="85">
+        <v>39.138495576499992</v>
+      </c>
+      <c r="M48" s="85">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="N48">
+        <v>40</v>
+      </c>
+      <c r="O48" s="21">
+        <v>8.76</v>
+      </c>
+      <c r="P48" s="21">
+        <v>1</v>
+      </c>
+      <c r="T48" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="V48" s="91" t="str">
+        <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_GRUNE00"</f>
+        <v>ELCTEGAS_GRUNE00</v>
+      </c>
+      <c r="W48" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V48,2)&amp;" GRUNE Power plant - "&amp;'EB1'!$E$3</f>
+        <v>Power Plants Existing00 GRUNE Power plant - Natural Gas</v>
+      </c>
+      <c r="X48" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65529" spans="19:19" x14ac:dyDescent="0.2">
+      <c r="S65529" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8057,6 +9080,1625 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FE1B269-F8EB-45DA-B587-21CAA9EF4FB5}">
+  <dimension ref="B1:AD65535"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" style="21" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="21" bestFit="1"/>
+    <col min="10" max="10" width="8.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85546875" style="21" bestFit="1"/>
+    <col min="15" max="15" width="15" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.85546875" style="21"/>
+    <col min="29" max="29" width="27" style="21" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="27.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.85546875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="str">
+        <f>'EB1'!B6</f>
+        <v>ELC</v>
+      </c>
+      <c r="C2" s="18" t="str">
+        <f>'EB1'!C6</f>
+        <v>Electricity Plants</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="10" t="str">
+        <f>'EB1'!AB2</f>
+        <v>PJ</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="10" t="str">
+        <f>'EB1'!AA2</f>
+        <v>M€2025</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="98"/>
+      <c r="V2" s="98"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
+      <c r="AA2" s="98"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99"/>
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+    </row>
+    <row r="4" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="100"/>
+      <c r="W4" s="100"/>
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+    </row>
+    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="S5" s="98"/>
+      <c r="T5" s="101"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
+      <c r="W5" s="98"/>
+      <c r="X5" s="98"/>
+      <c r="Y5" s="98"/>
+      <c r="Z5" s="98"/>
+      <c r="AA5" s="98"/>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="101"/>
+      <c r="T6" s="101"/>
+      <c r="U6" s="101"/>
+      <c r="V6" s="101"/>
+      <c r="W6" s="101"/>
+      <c r="X6" s="101"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="101"/>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="3"/>
+      <c r="Q8" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="R8" s="86"/>
+      <c r="S8" s="87"/>
+      <c r="T8" s="87"/>
+      <c r="U8" s="87"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="87"/>
+      <c r="X8" s="87"/>
+      <c r="Y8" s="87"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+    </row>
+    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="J9" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="O9" s="23"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="R9" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="88" t="s">
+        <v>2</v>
+      </c>
+      <c r="U9" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="V9" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="W9" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+    </row>
+    <row r="10" spans="2:28" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="T10" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" s="90" t="s">
+        <v>23</v>
+      </c>
+      <c r="V10" s="90" t="s">
+        <v>24</v>
+      </c>
+      <c r="W10" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="X10" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y10" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+    </row>
+    <row r="11" spans="2:28" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="B11" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="103" t="str">
+        <f>$F$2</f>
+        <v>GW</v>
+      </c>
+      <c r="F11" s="104" t="str">
+        <f>$F$2</f>
+        <v>GW</v>
+      </c>
+      <c r="G11" s="103"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="103" t="str">
+        <f>$G$2&amp;"/"&amp;$F$2</f>
+        <v>M€2025/GW</v>
+      </c>
+      <c r="J11" s="103" t="str">
+        <f>$G$2&amp;"/"&amp;$F$2</f>
+        <v>M€2025/GW</v>
+      </c>
+      <c r="K11" s="103" t="str">
+        <f>$G$2&amp;"/"&amp;$E$2</f>
+        <v>M€2025/PJ</v>
+      </c>
+      <c r="L11" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="103" t="s">
+        <v>194</v>
+      </c>
+      <c r="N11" s="103"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="105"/>
+      <c r="U11" s="105"/>
+      <c r="V11" s="105"/>
+      <c r="W11" s="105"/>
+      <c r="X11" s="105"/>
+      <c r="Y11" s="105"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+    </row>
+    <row r="12" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="94" t="str">
+        <f>S12</f>
+        <v>ELCCEBIO_OSULA00</v>
+      </c>
+      <c r="C12" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D12" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E12">
+        <v>0.01</v>
+      </c>
+      <c r="F12" s="107"/>
+      <c r="G12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H12" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I12" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J12" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K12" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L12">
+        <v>40</v>
+      </c>
+      <c r="M12" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N12" s="66">
+        <v>1</v>
+      </c>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12" s="101"/>
+      <c r="S12" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OSULA00"</f>
+        <v>ELCCEBIO_OSULA00</v>
+      </c>
+      <c r="T12" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S12,2)&amp;" Osula CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Osula CHP - Biomass</v>
+      </c>
+      <c r="U12" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V12" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W12" t="s">
+        <v>116</v>
+      </c>
+      <c r="X12" s="101"/>
+      <c r="Y12" s="101"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
+    </row>
+    <row r="13" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="94" t="str">
+        <f t="shared" ref="B13:B24" si="0">S13</f>
+        <v>ELCCEBIO_MUSTAMAE00</v>
+      </c>
+      <c r="C13" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D13" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E13">
+        <v>9.300000000000001E-3</v>
+      </c>
+      <c r="F13" s="107"/>
+      <c r="G13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H13" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I13" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J13" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K13" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L13">
+        <v>40</v>
+      </c>
+      <c r="M13" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N13" s="66">
+        <v>1</v>
+      </c>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" s="101"/>
+      <c r="S13" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_MUSTAMAE00"</f>
+        <v>ELCCEBIO_MUSTAMAE00</v>
+      </c>
+      <c r="T13" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S13,2)&amp;" Mustamae CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Mustamae CHP - Biomass</v>
+      </c>
+      <c r="U13" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V13" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W13" t="s">
+        <v>116</v>
+      </c>
+      <c r="X13" s="101"/>
+      <c r="Y13" s="101"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
+    </row>
+    <row r="14" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_SILLAMAE100</v>
+      </c>
+      <c r="C14" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D14" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E14">
+        <v>7.0999999999999995E-3</v>
+      </c>
+      <c r="F14" s="106"/>
+      <c r="G14">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H14" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I14" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J14" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K14" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L14">
+        <v>72</v>
+      </c>
+      <c r="M14" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N14" s="66">
+        <v>1</v>
+      </c>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R14" s="101"/>
+      <c r="S14" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_SILLAMAE100"</f>
+        <v>ELCCEBIO_SILLAMAE100</v>
+      </c>
+      <c r="T14" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S14,2)&amp;" Sillamae 1 CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Sillamae 1 CHP - Biomass</v>
+      </c>
+      <c r="U14" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V14" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W14" t="s">
+        <v>116</v>
+      </c>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
+    </row>
+    <row r="15" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEGAS_SILLAMAE200</v>
+      </c>
+      <c r="C15" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
+        <v>ELCGAS</v>
+      </c>
+      <c r="D15" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E15">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="F15" s="107"/>
+      <c r="G15">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H15" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I15" s="7">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="J15" s="7">
+        <v>39.138495576499992</v>
+      </c>
+      <c r="K15" s="7">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="L15">
+        <v>40</v>
+      </c>
+      <c r="M15" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N15" s="66">
+        <v>1</v>
+      </c>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" s="101"/>
+      <c r="S15" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_SILLAMAE200"</f>
+        <v>ELCCEGAS_SILLAMAE200</v>
+      </c>
+      <c r="T15" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S15,2)&amp;" Sillamae 2 CHP - "&amp;'EB1'!$E$3</f>
+        <v>Power Plants Existing00 Sillamae 2 CHP - Natural Gas</v>
+      </c>
+      <c r="U15" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V15" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W15" t="s">
+        <v>116</v>
+      </c>
+      <c r="X15" s="101"/>
+      <c r="Y15" s="101"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+    </row>
+    <row r="16" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_HELME00</v>
+      </c>
+      <c r="C16" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D16" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E16">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="F16" s="107"/>
+      <c r="G16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H16" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I16" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J16" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K16" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L16">
+        <v>40</v>
+      </c>
+      <c r="M16" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N16" s="66">
+        <v>1</v>
+      </c>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R16" s="101"/>
+      <c r="S16" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HELME00"</f>
+        <v>ELCCEBIO_HELME00</v>
+      </c>
+      <c r="T16" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S16,2)&amp;" Helme CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Helme CHP - Biomass</v>
+      </c>
+      <c r="U16" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V16" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W16" t="s">
+        <v>116</v>
+      </c>
+      <c r="X16" s="101"/>
+      <c r="Y16" s="101"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+    </row>
+    <row r="17" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_KURESSAARE00</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D17" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E17">
+        <v>1.8E-3</v>
+      </c>
+      <c r="F17" s="107"/>
+      <c r="G17">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H17" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I17" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J17" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K17" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L17">
+        <v>40</v>
+      </c>
+      <c r="M17" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N17" s="66">
+        <v>1</v>
+      </c>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R17" s="101"/>
+      <c r="S17" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_KURESSAARE00"</f>
+        <v>ELCCEBIO_KURESSAARE00</v>
+      </c>
+      <c r="T17" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S17,2)&amp;" Kuressaare CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Kuressaare CHP - Biomass</v>
+      </c>
+      <c r="U17" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V17" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W17" t="s">
+        <v>116</v>
+      </c>
+      <c r="X17" s="101"/>
+      <c r="Y17" s="101"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
+    </row>
+    <row r="18" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_PAIDE00</v>
+      </c>
+      <c r="C18" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D18" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E18">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F18" s="107"/>
+      <c r="G18">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H18" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I18" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J18" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K18" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L18">
+        <v>40</v>
+      </c>
+      <c r="M18" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N18" s="66">
+        <v>1</v>
+      </c>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R18" s="101"/>
+      <c r="S18" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PAIDE00"</f>
+        <v>ELCCEBIO_PAIDE00</v>
+      </c>
+      <c r="T18" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S18,2)&amp;" Paide CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Paide CHP - Biomass</v>
+      </c>
+      <c r="U18" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V18" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W18" t="s">
+        <v>116</v>
+      </c>
+      <c r="X18" s="101"/>
+      <c r="Y18" s="101"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+    </row>
+    <row r="19" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEGAS_JAMEJALA00</v>
+      </c>
+      <c r="C19" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
+        <v>ELCGAS</v>
+      </c>
+      <c r="D19" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E19">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G19">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H19" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I19" s="7">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="J19" s="7">
+        <v>39.138495576499992</v>
+      </c>
+      <c r="K19" s="7">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="L19">
+        <v>40</v>
+      </c>
+      <c r="M19" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N19" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R19" s="101"/>
+      <c r="S19" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_JAMEJALA00"</f>
+        <v>ELCCEGAS_JAMEJALA00</v>
+      </c>
+      <c r="T19" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S19,2)&amp;" Jamejala CHP - "&amp;'EB1'!$E$3</f>
+        <v>Power Plants Existing00 Jamejala CHP - Natural Gas</v>
+      </c>
+      <c r="U19" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V19" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W19" t="s">
+        <v>116</v>
+      </c>
+      <c r="X19" s="110"/>
+      <c r="Y19" s="110"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+    </row>
+    <row r="20" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEGAS_PUSSI00</v>
+      </c>
+      <c r="C20" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
+        <v>ELCGAS</v>
+      </c>
+      <c r="D20" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E20">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G20">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H20" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="J20" s="7">
+        <v>39.138495576499992</v>
+      </c>
+      <c r="K20" s="7">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="L20">
+        <v>40</v>
+      </c>
+      <c r="M20" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N20" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R20" s="101"/>
+      <c r="S20" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_PUSSI00"</f>
+        <v>ELCCEGAS_PUSSI00</v>
+      </c>
+      <c r="T20" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S20,2)&amp;" Pussi CHP - "&amp;'EB1'!$E$3</f>
+        <v>Power Plants Existing00 Pussi CHP - Natural Gas</v>
+      </c>
+      <c r="U20" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V20" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W20" t="s">
+        <v>116</v>
+      </c>
+      <c r="X20" s="110"/>
+      <c r="Y20" s="110"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
+    </row>
+    <row r="21" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_ILMATSALU00</v>
+      </c>
+      <c r="C21" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D21" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E21">
+        <v>1.5E-3</v>
+      </c>
+      <c r="G21">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H21" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I21" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J21" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K21" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L21">
+        <v>40</v>
+      </c>
+      <c r="M21" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N21" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R21" s="101"/>
+      <c r="S21" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_ILMATSALU00"</f>
+        <v>ELCCEBIO_ILMATSALU00</v>
+      </c>
+      <c r="T21" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S21,2)&amp;" Ilmatsalu CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Ilmatsalu CHP - Biomass</v>
+      </c>
+      <c r="U21" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V21" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W21" t="s">
+        <v>116</v>
+      </c>
+      <c r="X21" s="110"/>
+      <c r="Y21" s="110"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
+    </row>
+    <row r="22" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_VINNI00</v>
+      </c>
+      <c r="C22" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D22" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E22">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G22">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H22" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I22" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J22" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K22" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L22">
+        <v>40</v>
+      </c>
+      <c r="M22" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N22" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R22" s="101"/>
+      <c r="S22" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_VINNI00"</f>
+        <v>ELCCEBIO_VINNI00</v>
+      </c>
+      <c r="T22" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S22,2)&amp;" Vinni CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Vinni CHP - Biomass</v>
+      </c>
+      <c r="U22" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V22" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W22" t="s">
+        <v>116</v>
+      </c>
+      <c r="X22" s="110"/>
+      <c r="Y22" s="110"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+    </row>
+    <row r="23" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="94" t="str">
+        <f>S23</f>
+        <v>ELCCEBIO_OISU00</v>
+      </c>
+      <c r="C23" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D23" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E23">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G23">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H23" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I23" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J23" s="7">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K23" s="7">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L23">
+        <v>40</v>
+      </c>
+      <c r="M23" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N23" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R23" s="101"/>
+      <c r="S23" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OISU00"</f>
+        <v>ELCCEBIO_OISU00</v>
+      </c>
+      <c r="T23" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S23,2)&amp;" Oisu CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Oisu CHP - Biomass</v>
+      </c>
+      <c r="U23" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V23" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W23" t="s">
+        <v>116</v>
+      </c>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="110"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+    </row>
+    <row r="24" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCCEBIO_RAKVERE00</v>
+      </c>
+      <c r="C24" s="21" t="str">
+        <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
+        <v>ELCBIO</v>
+      </c>
+      <c r="D24" s="94" t="str">
+        <f>ELC!$V$5</f>
+        <v>ELCC</v>
+      </c>
+      <c r="E24">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G24">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H24" s="108">
+        <v>0.95</v>
+      </c>
+      <c r="I24" s="7">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="J24" s="85">
+        <v>162.96753257730003</v>
+      </c>
+      <c r="K24" s="85">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="L24">
+        <v>40</v>
+      </c>
+      <c r="M24" s="65">
+        <v>8.76</v>
+      </c>
+      <c r="N24" s="66">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="R24" s="101"/>
+      <c r="S24" s="91" t="str">
+        <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_RAKVERE00"</f>
+        <v>ELCCEBIO_RAKVERE00</v>
+      </c>
+      <c r="T24" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S24,2)&amp;" Rakvere CHP - "&amp;'EB1'!$O$3</f>
+        <v>Power Plants Existing00 Rakvere CHP - Biomass</v>
+      </c>
+      <c r="U24" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="V24" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="W24" t="s">
+        <v>116</v>
+      </c>
+      <c r="X24" s="110"/>
+      <c r="Y24" s="110"/>
+      <c r="AA24"/>
+      <c r="AB24"/>
+    </row>
+    <row r="25" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="110"/>
+      <c r="G25" s="108"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="N25" s="109"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="101"/>
+      <c r="S25" s="91"/>
+      <c r="T25"/>
+      <c r="U25" s="101"/>
+      <c r="V25" s="101"/>
+      <c r="W25"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="110"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+    </row>
+    <row r="26" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="110"/>
+      <c r="G26" s="108"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="N26" s="109"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="101"/>
+      <c r="S26" s="91"/>
+      <c r="T26"/>
+      <c r="U26" s="101"/>
+      <c r="V26" s="101"/>
+      <c r="W26"/>
+      <c r="X26" s="110"/>
+      <c r="Y26" s="110"/>
+      <c r="AA26"/>
+      <c r="AB26"/>
+    </row>
+    <row r="27" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="110"/>
+      <c r="I27" s="108"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="107"/>
+      <c r="P27" s="109"/>
+      <c r="S27" s="101"/>
+      <c r="T27" s="110"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="110"/>
+      <c r="X27" s="110"/>
+      <c r="Y27" s="110"/>
+      <c r="Z27" s="110"/>
+      <c r="AA27" s="110"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+    </row>
+    <row r="28" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="110"/>
+      <c r="I28" s="108"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="107"/>
+      <c r="P28" s="109"/>
+      <c r="S28" s="101"/>
+      <c r="T28" s="110"/>
+      <c r="U28" s="101"/>
+      <c r="V28" s="101"/>
+      <c r="W28" s="110"/>
+      <c r="X28" s="110"/>
+      <c r="Y28" s="110"/>
+      <c r="Z28" s="110"/>
+      <c r="AA28" s="110"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+    </row>
+    <row r="29" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="110"/>
+      <c r="I29" s="108"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="107"/>
+      <c r="M29" s="107"/>
+      <c r="P29" s="109"/>
+      <c r="S29" s="101"/>
+      <c r="T29" s="110"/>
+      <c r="U29" s="101"/>
+      <c r="V29" s="101"/>
+      <c r="W29" s="110"/>
+      <c r="X29" s="110"/>
+      <c r="Y29" s="110"/>
+      <c r="Z29" s="110"/>
+      <c r="AA29" s="110"/>
+    </row>
+    <row r="30" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="110"/>
+      <c r="I30" s="108"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="107"/>
+      <c r="M30" s="107"/>
+      <c r="P30" s="109"/>
+      <c r="S30" s="101"/>
+      <c r="T30" s="110"/>
+      <c r="U30" s="101"/>
+      <c r="V30" s="101"/>
+      <c r="W30" s="110"/>
+      <c r="X30" s="110"/>
+      <c r="Y30" s="110"/>
+      <c r="Z30" s="110"/>
+      <c r="AA30" s="110"/>
+    </row>
+    <row r="31" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="110"/>
+      <c r="I31" s="108"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="107"/>
+      <c r="M31" s="107"/>
+      <c r="P31" s="109"/>
+      <c r="S31" s="101"/>
+      <c r="T31" s="110"/>
+      <c r="U31" s="101"/>
+      <c r="V31" s="101"/>
+      <c r="W31" s="110"/>
+      <c r="X31" s="110"/>
+      <c r="Y31" s="110"/>
+      <c r="Z31" s="110"/>
+      <c r="AA31" s="110"/>
+    </row>
+    <row r="32" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="110"/>
+      <c r="I32" s="108"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="107"/>
+      <c r="P32" s="109"/>
+      <c r="S32" s="101"/>
+      <c r="T32" s="110"/>
+      <c r="U32" s="101"/>
+      <c r="V32" s="101"/>
+      <c r="W32" s="110"/>
+      <c r="X32" s="110"/>
+      <c r="Y32" s="110"/>
+      <c r="Z32" s="110"/>
+      <c r="AA32" s="110"/>
+    </row>
+    <row r="33" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="110"/>
+      <c r="I33" s="108"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="107"/>
+      <c r="P33" s="109"/>
+      <c r="S33" s="101"/>
+      <c r="T33" s="110"/>
+      <c r="U33" s="101"/>
+      <c r="V33" s="101"/>
+      <c r="W33" s="110"/>
+      <c r="X33" s="110"/>
+      <c r="Y33" s="110"/>
+      <c r="Z33" s="110"/>
+      <c r="AA33" s="110"/>
+    </row>
+    <row r="34" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="110"/>
+      <c r="I34" s="108"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="107"/>
+      <c r="M34" s="107"/>
+      <c r="N34" s="110"/>
+      <c r="P34" s="110"/>
+      <c r="S34" s="101"/>
+      <c r="T34" s="110"/>
+      <c r="U34" s="110"/>
+      <c r="V34" s="110"/>
+      <c r="W34" s="110"/>
+      <c r="X34" s="110"/>
+      <c r="Y34" s="110"/>
+      <c r="Z34" s="110"/>
+      <c r="AA34" s="110"/>
+    </row>
+    <row r="35" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="110"/>
+      <c r="I35" s="108"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="107"/>
+      <c r="N35" s="110"/>
+      <c r="P35" s="110"/>
+      <c r="S35" s="101"/>
+      <c r="T35" s="110"/>
+      <c r="U35" s="110"/>
+      <c r="V35" s="110"/>
+      <c r="W35" s="110"/>
+      <c r="X35" s="110"/>
+      <c r="Y35" s="110"/>
+      <c r="Z35" s="110"/>
+      <c r="AA35" s="110"/>
+    </row>
+    <row r="36" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="110"/>
+      <c r="I36" s="108"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="107"/>
+      <c r="N36" s="110"/>
+      <c r="P36" s="110"/>
+      <c r="S36" s="101"/>
+      <c r="T36" s="110"/>
+      <c r="U36" s="110"/>
+      <c r="V36" s="110"/>
+      <c r="W36" s="110"/>
+      <c r="X36" s="110"/>
+      <c r="Y36" s="110"/>
+      <c r="Z36" s="110"/>
+      <c r="AA36" s="110"/>
+    </row>
+    <row r="37" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="110"/>
+      <c r="I37" s="108"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="107"/>
+      <c r="N37" s="110"/>
+      <c r="P37" s="110"/>
+      <c r="S37" s="101"/>
+      <c r="T37" s="110"/>
+      <c r="U37" s="110"/>
+      <c r="V37" s="110"/>
+      <c r="W37" s="110"/>
+      <c r="X37" s="110"/>
+      <c r="Y37" s="110"/>
+      <c r="Z37" s="110"/>
+      <c r="AA37" s="110"/>
+    </row>
+    <row r="38" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="110"/>
+      <c r="I38" s="108"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="110"/>
+      <c r="P38" s="110"/>
+      <c r="S38" s="101"/>
+      <c r="T38" s="110"/>
+      <c r="U38" s="110"/>
+      <c r="V38" s="110"/>
+      <c r="W38" s="110"/>
+      <c r="X38" s="110"/>
+      <c r="Y38" s="110"/>
+      <c r="Z38" s="110"/>
+      <c r="AA38" s="110"/>
+    </row>
+    <row r="39" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="110"/>
+      <c r="I39" s="108"/>
+      <c r="K39" s="106"/>
+      <c r="L39" s="107"/>
+      <c r="M39" s="107"/>
+      <c r="N39" s="110"/>
+      <c r="P39" s="110"/>
+      <c r="S39" s="101"/>
+      <c r="T39" s="110"/>
+      <c r="U39" s="110"/>
+      <c r="V39" s="110"/>
+      <c r="W39" s="110"/>
+      <c r="X39" s="110"/>
+      <c r="Y39" s="110"/>
+      <c r="Z39" s="110"/>
+      <c r="AA39" s="110"/>
+    </row>
+    <row r="40" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="110"/>
+      <c r="I40" s="108"/>
+      <c r="K40" s="106"/>
+      <c r="L40" s="107"/>
+      <c r="M40" s="107"/>
+      <c r="N40" s="110"/>
+      <c r="P40" s="110"/>
+      <c r="S40" s="101"/>
+      <c r="T40" s="110"/>
+      <c r="U40" s="110"/>
+      <c r="V40" s="110"/>
+      <c r="W40" s="110"/>
+      <c r="X40" s="110"/>
+      <c r="Y40" s="110"/>
+      <c r="Z40" s="110"/>
+      <c r="AA40" s="110"/>
+    </row>
+    <row r="41" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="110"/>
+      <c r="I41" s="108"/>
+      <c r="K41" s="106"/>
+      <c r="L41" s="107"/>
+      <c r="M41" s="107"/>
+      <c r="N41" s="110"/>
+      <c r="P41" s="110"/>
+      <c r="S41" s="101"/>
+      <c r="T41" s="110"/>
+      <c r="U41" s="110"/>
+      <c r="V41" s="110"/>
+      <c r="W41" s="110"/>
+      <c r="X41" s="110"/>
+      <c r="Y41" s="110"/>
+      <c r="Z41" s="110"/>
+      <c r="AA41" s="110"/>
+    </row>
+    <row r="42" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="110"/>
+      <c r="I42" s="108"/>
+      <c r="K42" s="106"/>
+      <c r="L42" s="107"/>
+      <c r="M42" s="107"/>
+      <c r="N42" s="110"/>
+      <c r="P42" s="110"/>
+      <c r="S42" s="101"/>
+      <c r="T42" s="110"/>
+      <c r="U42" s="110"/>
+      <c r="V42" s="110"/>
+      <c r="W42" s="110"/>
+      <c r="X42" s="110"/>
+      <c r="Y42" s="110"/>
+      <c r="Z42" s="110"/>
+      <c r="AA42" s="110"/>
+    </row>
+    <row r="43" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K43" s="111"/>
+      <c r="L43" s="111"/>
+      <c r="M43" s="111"/>
+      <c r="N43" s="111"/>
+      <c r="P43" s="110"/>
+      <c r="S43" s="101"/>
+      <c r="T43" s="110"/>
+      <c r="U43" s="110"/>
+      <c r="V43" s="110"/>
+      <c r="W43" s="110"/>
+      <c r="X43" s="110"/>
+      <c r="Y43" s="110"/>
+      <c r="Z43" s="110"/>
+      <c r="AA43" s="110"/>
+      <c r="AC43" s="21"/>
+      <c r="AD43" s="21"/>
+    </row>
+    <row r="65535" spans="18:18" x14ac:dyDescent="0.2">
+      <c r="R65535" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="S15:T15 C15" formula="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:J24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -8066,7 +10708,7 @@
   <sheetData>
     <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
@@ -8087,7 +10729,7 @@
     </row>
     <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5" s="33"/>
     </row>
@@ -8116,16 +10758,16 @@
         <v>76</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
+        <v>141</v>
+      </c>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -8133,29 +10775,29 @@
         <f>ELC!$V$6</f>
         <v>ELCCO2</v>
       </c>
-      <c r="C8" s="65">
+      <c r="C8" s="64">
         <v>95</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="64">
         <v>56.1</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="64">
         <v>76.400000000000006</v>
       </c>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
       <c r="H8" s="1"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="60"/>
       <c r="C24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D5CBE5-9EAF-4A21-AC28-12BE82A69724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44174599-D1CB-4906-88F2-EF4961911109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -7785,7 +7785,7 @@
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_SOPITOOTSI00</v>
+        <v>ELCREWON_SOPITOOTSI00</v>
       </c>
       <c r="C28" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -7826,8 +7826,8 @@
         <v>102</v>
       </c>
       <c r="V28" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
-        <v>ELCRESOL_SOPITOOTSI00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
+        <v>ELCREWON_SOPITOOTSI00</v>
       </c>
       <c r="W28" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
@@ -7846,7 +7846,7 @@
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_SOPIPURTSE00</v>
+        <v>ELCREWON_SOPIPURTSE00</v>
       </c>
       <c r="C29" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -7887,8 +7887,8 @@
         <v>102</v>
       </c>
       <c r="V29" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
-        <v>ELCRESOL_SOPIPURTSE00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
+        <v>ELCREWON_SOPIPURTSE00</v>
       </c>
       <c r="W29" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
@@ -7907,7 +7907,7 @@
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_OTHER00</v>
+        <v>ELCREWON_OTHER00</v>
       </c>
       <c r="C30" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -7948,8 +7948,8 @@
         <v>102</v>
       </c>
       <c r="V30" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
-        <v>ELCRESOL_OTHER00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
+        <v>ELCREWON_OTHER00</v>
       </c>
       <c r="W30" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
@@ -7968,7 +7968,7 @@
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_SAARE00</v>
+        <v>ELCREWON_SAARE00</v>
       </c>
       <c r="C31" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8009,8 +8009,8 @@
         <v>102</v>
       </c>
       <c r="V31" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
-        <v>ELCRESOL_SAARE00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
+        <v>ELCREWON_SAARE00</v>
       </c>
       <c r="W31" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
@@ -8029,7 +8029,7 @@
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_LVIRU00</v>
+        <v>ELCREWON_LVIRU00</v>
       </c>
       <c r="C32" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8070,8 +8070,8 @@
         <v>102</v>
       </c>
       <c r="V32" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
-        <v>ELCRESOL_LVIRU00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
+        <v>ELCREWON_LVIRU00</v>
       </c>
       <c r="W32" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
@@ -8090,7 +8090,7 @@
     <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B33" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_HARJU00</v>
+        <v>ELCREWON_HARJU00</v>
       </c>
       <c r="C33" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8131,8 +8131,8 @@
         <v>102</v>
       </c>
       <c r="V33" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
-        <v>ELCRESOL_HARJU00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
+        <v>ELCREWON_HARJU00</v>
       </c>
       <c r="W33" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
@@ -8151,7 +8151,7 @@
     <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B34" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_LAANE00</v>
+        <v>ELCREWON_LAANE00</v>
       </c>
       <c r="C34" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8192,8 +8192,8 @@
         <v>102</v>
       </c>
       <c r="V34" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
-        <v>ELCRESOL_LAANE00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
+        <v>ELCREWON_LAANE00</v>
       </c>
       <c r="W34" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
@@ -8212,7 +8212,7 @@
     <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B35" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_IVIRU00</v>
+        <v>ELCREWON_IVIRU00</v>
       </c>
       <c r="C35" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8253,8 +8253,8 @@
         <v>102</v>
       </c>
       <c r="V35" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
-        <v>ELCRESOL_IVIRU00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
+        <v>ELCREWON_IVIRU00</v>
       </c>
       <c r="W35" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
@@ -8273,7 +8273,7 @@
     <row r="36" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B36" s="21" t="str">
         <f t="shared" si="2"/>
-        <v>ELCRESOL_PARNU00</v>
+        <v>ELCREWON_PARNU00</v>
       </c>
       <c r="C36" s="21" t="str">
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)</f>
@@ -8314,8 +8314,8 @@
         <v>102</v>
       </c>
       <c r="V36" t="str">
-        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
-        <v>ELCRESOL_PARNU00</v>
+        <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
+        <v>ELCREWON_PARNU00</v>
       </c>
       <c r="W36" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44174599-D1CB-4906-88F2-EF4961911109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03520AE-64B2-4014-B4AF-177EAA8A7857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1948,8 +1948,26 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={93CDE302-2DCC-4595-B2D6-E3674F8196EC}</author>
+  </authors>
+  <commentList>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{93CDE302-2DCC-4595-B2D6-E3674F8196EC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kliimaarvestus 45% of ~92</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="197">
   <si>
     <t>CommName</t>
   </si>
@@ -2554,7 +2572,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2729,6 +2747,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="17">
@@ -3090,7 +3114,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3165,9 +3189,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3248,9 +3269,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4041,6 +4059,12 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kristopher Raik" id="{A1A5B81E-CD06-4628-8001-D7897AF02153}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4387,6 +4411,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G8" dT="2026-09-21T05:35:17.90" personId="{A1A5B81E-CD06-4628-8001-D7897AF02153}" id="{93CDE302-2DCC-4595-B2D6-E3674F8196EC}">
+    <text>Kliimaarvestus 45% of ~92</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -4425,70 +4457,70 @@
       </c>
     </row>
     <row r="2" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="R2" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="S2" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="T2" s="40" t="s">
+      <c r="T2" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="V2" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="AA2" s="39" t="s">
+      <c r="AA2" s="38" t="s">
         <v>180</v>
       </c>
       <c r="AB2" s="10" t="s">
@@ -4499,76 +4531,76 @@
       </c>
     </row>
     <row r="3" spans="2:29" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="M3" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="41" t="s">
+      <c r="O3" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="P3" s="41" t="s">
+      <c r="P3" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="Q3" s="41" t="s">
+      <c r="Q3" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="R3" s="41" t="s">
+      <c r="R3" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="S3" s="41" t="s">
+      <c r="S3" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="T3" s="41" t="s">
+      <c r="T3" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="U3" s="41" t="s">
+      <c r="U3" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="41" t="s">
+      <c r="V3" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="W3" s="41" t="s">
+      <c r="W3" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="X3" s="41" t="s">
+      <c r="X3" s="40" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B4" s="38"/>
-      <c r="C4" s="71" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="70" t="s">
         <v>55</v>
       </c>
       <c r="D4" s="6"/>
@@ -4591,357 +4623,357 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="72"/>
+      <c r="X4" s="71"/>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="42">
         <v>-37.464700000000001</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="42">
         <v>-317.19200000000001</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="42">
         <v>0</v>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="42">
         <v>-16.283999999999999</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="42">
         <v>-2.1499999999999998E-2</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="42">
         <v>-528.76099999999997</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="42">
         <v>-164.50800000000001</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="42">
         <v>-0.61599999999999999</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="42">
         <v>-205.88</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="42">
         <v>0</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="42">
         <v>0</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="42">
         <v>-3.21225</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="42">
         <v>0</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="42">
         <v>0</v>
       </c>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43">
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42">
         <v>0</v>
       </c>
-      <c r="U5" s="43">
+      <c r="U5" s="42">
         <v>-0.76</v>
       </c>
-      <c r="V5" s="43">
+      <c r="V5" s="42">
         <v>0</v>
       </c>
-      <c r="W5" s="43">
+      <c r="W5" s="42">
         <v>0</v>
       </c>
-      <c r="X5" s="73">
+      <c r="X5" s="72">
         <v>-1274.6994499999998</v>
       </c>
     </row>
     <row r="6" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="45">
         <v>-6238.7780000000012</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="44">
         <v>-2254.2175999999999</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="44">
         <v>0</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="44">
         <v>-30.160499999999999</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="44">
         <v>0</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="44">
         <v>-23.835000000000001</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <v>0</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="44">
         <v>0</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="44">
         <v>-524.78</v>
       </c>
-      <c r="M6" s="45">
+      <c r="M6" s="44">
         <v>-33.529000000000003</v>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="44">
         <v>-4455</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="44">
         <v>-527.25918750000005</v>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="44">
         <v>-502.66000000000008</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="44">
         <v>-263.8965</v>
       </c>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45">
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44">
         <v>-68</v>
       </c>
-      <c r="U6" s="43">
+      <c r="U6" s="42">
         <v>-16.474499999999999</v>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="42">
         <v>868.77949999999998</v>
       </c>
-      <c r="W6" s="45">
+      <c r="W6" s="44">
         <v>5790.5</v>
       </c>
-      <c r="X6" s="73">
+      <c r="X6" s="72">
         <v>-8279.3107875000023</v>
       </c>
-      <c r="Z6" s="79"/>
+      <c r="Z6" s="77"/>
     </row>
     <row r="7" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="42">
         <v>-104.9074</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="42">
         <v>-120.5204</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="42">
         <v>0</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="42">
         <v>-7.6189999999999998</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="42">
         <v>0</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="42">
         <v>-0.23350000000000001</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="42">
         <v>0</v>
       </c>
-      <c r="K7" s="43">
+      <c r="K7" s="42">
         <v>0</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="42">
         <v>-15.2</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="42">
         <v>-1.772</v>
       </c>
-      <c r="N7" s="43">
+      <c r="N7" s="42">
         <v>0</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="42">
         <v>-105.15525</v>
       </c>
-      <c r="P7" s="43">
+      <c r="P7" s="42">
         <v>0</v>
       </c>
-      <c r="Q7" s="43">
+      <c r="Q7" s="42">
         <v>0</v>
       </c>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43">
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42">
         <v>0</v>
       </c>
-      <c r="U7" s="43">
+      <c r="U7" s="42">
         <v>-0.78449999999999998</v>
       </c>
-      <c r="V7" s="43">
+      <c r="V7" s="42">
         <v>329.37150000000003</v>
       </c>
-      <c r="W7" s="43">
+      <c r="W7" s="42">
         <v>0</v>
       </c>
-      <c r="X7" s="73">
+      <c r="X7" s="72">
         <v>-26.820549999999912</v>
       </c>
     </row>
     <row r="8" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="42">
         <v>0</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="42">
         <v>0</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="42">
         <v>-15868.2305</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="42">
         <v>5701.34</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="42">
         <v>969.47799999999995</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="42">
         <v>1086.3040000000001</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="42">
         <v>3354.9119999999998</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="42">
         <v>970.28800000000001</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="42">
         <v>2285.1019999999999</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="42">
         <v>1299.9449999999999</v>
       </c>
-      <c r="N8" s="43">
+      <c r="N8" s="42">
         <v>0</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="42">
         <v>0</v>
       </c>
-      <c r="P8" s="43">
+      <c r="P8" s="42">
         <v>0</v>
       </c>
-      <c r="Q8" s="43">
+      <c r="Q8" s="42">
         <v>0</v>
       </c>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43">
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42">
         <v>0</v>
       </c>
-      <c r="U8" s="43">
+      <c r="U8" s="42">
         <v>0</v>
       </c>
-      <c r="V8" s="43">
+      <c r="V8" s="42">
         <v>0</v>
       </c>
-      <c r="W8" s="43">
+      <c r="W8" s="42">
         <v>0</v>
       </c>
-      <c r="X8" s="73">
+      <c r="X8" s="72">
         <v>-200.86150000000021</v>
       </c>
     </row>
     <row r="9" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="47" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="49">
         <f>SUM(D5:D8)</f>
         <v>-6381.1501000000017</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="47">
         <f t="shared" ref="E9:W9" si="0">SUM(E5:E8)</f>
         <v>-2691.93</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="47">
         <f t="shared" si="0"/>
         <v>-15868.2305</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="47">
         <f t="shared" si="0"/>
         <v>5647.2764999999999</v>
       </c>
-      <c r="H9" s="48">
+      <c r="H9" s="47">
         <f t="shared" si="0"/>
         <v>969.45650000000001</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9" s="47">
         <f t="shared" si="0"/>
         <v>533.47450000000003</v>
       </c>
-      <c r="J9" s="48">
+      <c r="J9" s="47">
         <f t="shared" si="0"/>
         <v>3190.404</v>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="47">
         <f t="shared" si="0"/>
         <v>969.67200000000003</v>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="47">
         <f t="shared" si="0"/>
         <v>1539.2419999999997</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="47">
         <f t="shared" si="0"/>
         <v>1264.644</v>
       </c>
-      <c r="N9" s="48">
+      <c r="N9" s="47">
         <f t="shared" si="0"/>
         <v>-4455</v>
       </c>
-      <c r="O9" s="48">
+      <c r="O9" s="47">
         <f t="shared" si="0"/>
         <v>-635.62668750000012</v>
       </c>
-      <c r="P9" s="48">
+      <c r="P9" s="47">
         <f t="shared" si="0"/>
         <v>-502.66000000000008</v>
       </c>
-      <c r="Q9" s="48">
+      <c r="Q9" s="47">
         <f t="shared" si="0"/>
         <v>-263.8965</v>
       </c>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48">
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47">
         <f t="shared" si="0"/>
         <v>-68</v>
       </c>
-      <c r="U9" s="48">
+      <c r="U9" s="47">
         <f t="shared" si="0"/>
         <v>-18.019000000000002</v>
       </c>
-      <c r="V9" s="48">
+      <c r="V9" s="47">
         <f t="shared" si="0"/>
         <v>1198.1510000000001</v>
       </c>
-      <c r="W9" s="48">
+      <c r="W9" s="47">
         <f t="shared" si="0"/>
         <v>5790.5</v>
       </c>
-      <c r="X9" s="49">
+      <c r="X9" s="48">
         <f>SUM(X5:X8)</f>
         <v>-9781.6922875000037</v>
       </c>
@@ -4969,18 +5001,18 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="80"/>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
     </row>
     <row r="12" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -4991,13 +5023,13 @@
       <c r="M12" s="7"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="56" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5005,25 +5037,25 @@
       <c r="B16" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="53" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="75">
         <v>1</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="78"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5224,44 +5256,44 @@
         <v>84</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="J2" s="86" t="s">
+      <c r="J2" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="87"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="J3" s="88" t="s">
+      <c r="J3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="89" t="s">
+      <c r="K3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="88" t="s">
+      <c r="L3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="88" t="s">
+      <c r="M3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="88" t="s">
+      <c r="N3" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="88" t="s">
+      <c r="O3" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="88" t="s">
+      <c r="P3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="88" t="s">
+      <c r="Q3" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="88" t="s">
+      <c r="R3" s="86" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5271,333 +5303,333 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="J4" s="90" t="s">
+      <c r="J4" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="90" t="s">
+      <c r="K4" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="90" t="s">
+      <c r="L4" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="90" t="s">
+      <c r="M4" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="90" t="s">
+      <c r="O4" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="90" t="s">
+      <c r="P4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="90" t="s">
+      <c r="Q4" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="90" t="s">
+      <c r="R4" s="88" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="67"/>
+      <c r="G5" s="66"/>
       <c r="H5" s="11"/>
-      <c r="J5" s="91" t="s">
+      <c r="J5" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91" t="str">
+      <c r="K5" s="89"/>
+      <c r="L5" s="89" t="str">
         <f>$B$2&amp;'EB1'!$D$2</f>
         <v>ELCCOA</v>
       </c>
-      <c r="M5" s="92" t="str">
+      <c r="M5" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$D$3</f>
         <v>Electricity Plants Solid Fuels</v>
       </c>
-      <c r="N5" s="91" t="str">
+      <c r="N5" s="89" t="str">
         <f t="shared" ref="N5:N14" si="0">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="91"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="91"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="67"/>
+      <c r="G6" s="66"/>
       <c r="H6" s="11"/>
-      <c r="J6" s="91" t="s">
+      <c r="J6" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91" t="str">
+      <c r="K6" s="89"/>
+      <c r="L6" s="89" t="str">
         <f>$B$2&amp;'EB1'!$E$2</f>
         <v>ELCGAS</v>
       </c>
-      <c r="M6" s="92" t="str">
+      <c r="M6" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$E$3</f>
         <v>Electricity Plants Natural Gas</v>
       </c>
-      <c r="N6" s="91" t="str">
+      <c r="N6" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89"/>
+      <c r="Q6" s="89"/>
+      <c r="R6" s="89"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="67"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="11"/>
-      <c r="J7" s="91" t="s">
+      <c r="J7" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91" t="str">
+      <c r="K7" s="89"/>
+      <c r="L7" s="89" t="str">
         <f>$B$2&amp;'EB1'!$F$2</f>
         <v>ELCOIL</v>
       </c>
-      <c r="M7" s="92" t="str">
+      <c r="M7" s="90" t="str">
         <f>$C$2&amp;" "&amp;RIGHT('EB1'!$F$3,3)</f>
         <v>Electricity Plants oil</v>
       </c>
-      <c r="N7" s="91" t="str">
+      <c r="N7" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
+      <c r="O7" s="89"/>
+      <c r="P7" s="89"/>
+      <c r="Q7" s="89"/>
+      <c r="R7" s="89"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="67"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="11"/>
-      <c r="J8" s="91" t="s">
+      <c r="J8" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91" t="str">
+      <c r="K8" s="89"/>
+      <c r="L8" s="89" t="str">
         <f>$B$2&amp;'EB1'!$N$2</f>
         <v>ELCNUC</v>
       </c>
-      <c r="M8" s="92" t="str">
+      <c r="M8" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$N$3</f>
         <v>Electricity Plants Nuclear Energy</v>
       </c>
-      <c r="N8" s="91" t="str">
+      <c r="N8" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O8" s="91"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="91"/>
-      <c r="R8" s="91"/>
+      <c r="O8" s="89"/>
+      <c r="P8" s="89"/>
+      <c r="Q8" s="89"/>
+      <c r="R8" s="89"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="67"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="11"/>
-      <c r="J9" s="91" t="s">
+      <c r="J9" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91" t="str">
+      <c r="K9" s="89"/>
+      <c r="L9" s="89" t="str">
         <f>$B$2&amp;'EB1'!$O$2</f>
         <v>ELCBIO</v>
       </c>
-      <c r="M9" s="92" t="str">
+      <c r="M9" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$O$3</f>
         <v>Electricity Plants Biomass</v>
       </c>
-      <c r="N9" s="91" t="str">
+      <c r="N9" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O9" s="91"/>
-      <c r="P9" s="91"/>
-      <c r="Q9" s="91"/>
-      <c r="R9" s="91"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="89"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="89"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="67"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="11"/>
-      <c r="J10" s="91" t="s">
+      <c r="J10" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91" t="str">
+      <c r="K10" s="89"/>
+      <c r="L10" s="89" t="str">
         <f>$B$2&amp;'EB1'!$P$2</f>
         <v>ELCHYD</v>
       </c>
-      <c r="M10" s="92" t="str">
+      <c r="M10" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$P$3</f>
         <v>Electricity Plants Hydro power</v>
       </c>
-      <c r="N10" s="91" t="str">
+      <c r="N10" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O10" s="91"/>
-      <c r="P10" s="91"/>
-      <c r="Q10" s="91"/>
-      <c r="R10" s="91"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="89"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="67"/>
+      <c r="G11" s="66"/>
       <c r="H11" s="11"/>
-      <c r="J11" s="91" t="s">
+      <c r="J11" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91" t="str">
+      <c r="K11" s="89"/>
+      <c r="L11" s="89" t="str">
         <f>$B$2&amp;'EB1'!$Q$2</f>
         <v>ELCWIN</v>
       </c>
-      <c r="M11" s="92" t="str">
+      <c r="M11" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$Q$3</f>
         <v>Electricity Plants Wind energy</v>
       </c>
-      <c r="N11" s="91" t="str">
+      <c r="N11" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O11" s="91"/>
-      <c r="P11" s="91"/>
-      <c r="Q11" s="91"/>
-      <c r="R11" s="91"/>
+      <c r="O11" s="89"/>
+      <c r="P11" s="89"/>
+      <c r="Q11" s="89"/>
+      <c r="R11" s="89"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="67"/>
+      <c r="G12" s="66"/>
       <c r="H12" s="11"/>
-      <c r="J12" s="91" t="s">
+      <c r="J12" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91" t="s">
+      <c r="K12" s="89"/>
+      <c r="L12" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="M12" s="92" t="s">
+      <c r="M12" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="N12" s="91" t="s">
+      <c r="N12" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="91"/>
-      <c r="R12" s="91"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="89"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="67"/>
+      <c r="G13" s="66"/>
       <c r="H13" s="11"/>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91" t="s">
+      <c r="K13" s="89"/>
+      <c r="L13" s="89" t="s">
         <v>189</v>
       </c>
-      <c r="M13" s="92" t="s">
+      <c r="M13" s="90" t="s">
         <v>187</v>
       </c>
-      <c r="N13" s="91" t="s">
+      <c r="N13" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="91"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="67"/>
+      <c r="G14" s="66"/>
       <c r="H14" s="11"/>
-      <c r="J14" s="91" t="s">
+      <c r="J14" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91" t="str">
+      <c r="K14" s="89"/>
+      <c r="L14" s="89" t="str">
         <f>$B$2&amp;'EB1'!$T$2</f>
         <v>ELCSOL</v>
       </c>
-      <c r="M14" s="92" t="str">
+      <c r="M14" s="90" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$T$3</f>
         <v>Electricity Plants Solar energy</v>
       </c>
-      <c r="N14" s="91" t="str">
+      <c r="N14" s="89" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
+      <c r="O14" s="89"/>
+      <c r="P14" s="89"/>
+      <c r="Q14" s="89"/>
+      <c r="R14" s="89"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="67"/>
+      <c r="G15" s="66"/>
       <c r="H15" s="11"/>
-      <c r="J15" s="91" t="s">
+      <c r="J15" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91" t="s">
+      <c r="K15" s="89"/>
+      <c r="L15" s="89" t="s">
         <v>192</v>
       </c>
-      <c r="M15" s="92" t="s">
+      <c r="M15" s="90" t="s">
         <v>193</v>
       </c>
-      <c r="N15" s="91" t="s">
+      <c r="N15" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="67"/>
+      <c r="G16" s="66"/>
       <c r="H16" s="11"/>
-      <c r="J16" s="91" t="s">
+      <c r="J16" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="91" t="s">
+      <c r="K16" s="89"/>
+      <c r="L16" s="89" t="s">
         <v>195</v>
       </c>
-      <c r="M16" s="92" t="s">
+      <c r="M16" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="N16" s="91" t="s">
+      <c r="N16" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
+      <c r="O16" s="89"/>
+      <c r="P16" s="89"/>
+      <c r="Q16" s="89"/>
+      <c r="R16" s="89"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L17" s="21"/>
@@ -5609,17 +5641,17 @@
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="J18" s="86" t="s">
+      <c r="J18" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="K18" s="86"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="89"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -5631,43 +5663,43 @@
       <c r="D19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="70" t="s">
+      <c r="E19" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="F19" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="68" t="s">
+      <c r="H19" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="88" t="s">
+      <c r="J19" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="K19" s="89" t="s">
+      <c r="K19" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="L19" s="88" t="s">
+      <c r="L19" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="88" t="s">
+      <c r="M19" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="88" t="s">
+      <c r="N19" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="88" t="s">
+      <c r="O19" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="P19" s="88" t="s">
+      <c r="P19" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="Q19" s="88" t="s">
+      <c r="Q19" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="R19" s="88" t="s">
+      <c r="R19" s="86" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5693,31 +5725,31 @@
       <c r="H20" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J20" s="90" t="s">
+      <c r="J20" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="K20" s="90" t="s">
+      <c r="K20" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="L20" s="90" t="s">
+      <c r="L20" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="90" t="s">
+      <c r="M20" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="90" t="s">
+      <c r="N20" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="O20" s="90" t="s">
+      <c r="O20" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="P20" s="90" t="s">
+      <c r="P20" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="Q20" s="90" t="s">
+      <c r="Q20" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="R20" s="90" t="s">
+      <c r="R20" s="88" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5736,17 +5768,17 @@
       <c r="H21" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="J21" s="90" t="s">
+      <c r="J21" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="91"/>
+      <c r="Q21" s="91"/>
+      <c r="R21" s="91"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
@@ -5763,35 +5795,35 @@
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="62">
+      <c r="G22" s="61">
         <v>1</v>
       </c>
-      <c r="H22" s="63">
+      <c r="H22" s="62">
         <v>30</v>
       </c>
-      <c r="J22" s="87" t="s">
+      <c r="J22" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="94"/>
-      <c r="L22" s="91" t="str">
+      <c r="K22" s="92"/>
+      <c r="L22" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-ELCCOA</v>
       </c>
-      <c r="M22" s="92" t="str">
+      <c r="M22" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
-      <c r="N22" s="91" t="str">
+      <c r="N22" s="89" t="str">
         <f t="shared" ref="N22:N33" si="1">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O22" s="91" t="str">
+      <c r="O22" s="89" t="str">
         <f t="shared" ref="O22:O33" si="2">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="91"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="89"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="str">
@@ -5808,35 +5840,35 @@
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
-      <c r="G23" s="62">
+      <c r="G23" s="61">
         <v>1</v>
       </c>
-      <c r="H23" s="63">
+      <c r="H23" s="62">
         <v>30</v>
       </c>
-      <c r="J23" s="87" t="s">
+      <c r="J23" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="91" t="str">
+      <c r="K23" s="92"/>
+      <c r="L23" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
         <v>FTE-ELCGAS</v>
       </c>
-      <c r="M23" s="92" t="str">
+      <c r="M23" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
         <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
       </c>
-      <c r="N23" s="91" t="str">
+      <c r="N23" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O23" s="91" t="str">
+      <c r="O23" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="89"/>
+      <c r="R23" s="89"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
@@ -5851,40 +5883,40 @@
         <f>L7</f>
         <v>ELCOIL</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="60">
         <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>4.9257354796510562E-2</v>
       </c>
       <c r="F24" s="12"/>
-      <c r="G24" s="62">
+      <c r="G24" s="61">
         <v>1</v>
       </c>
-      <c r="H24" s="63">
+      <c r="H24" s="62">
         <v>30</v>
       </c>
-      <c r="J24" s="87" t="s">
+      <c r="J24" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K24" s="94"/>
-      <c r="L24" s="91" t="str">
+      <c r="K24" s="92"/>
+      <c r="L24" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-ELCOIL</v>
       </c>
-      <c r="M24" s="92" t="str">
+      <c r="M24" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Electricity Plants oil</v>
       </c>
-      <c r="N24" s="91" t="str">
+      <c r="N24" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O24" s="91" t="str">
+      <c r="O24" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="91"/>
+      <c r="P24" s="89"/>
+      <c r="Q24" s="89"/>
+      <c r="R24" s="89"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="21"/>
@@ -5893,36 +5925,36 @@
         <v>LPG</v>
       </c>
       <c r="D25" s="21"/>
-      <c r="E25" s="61">
+      <c r="E25" s="60">
         <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>3.8926710484734312E-2</v>
       </c>
       <c r="F25" s="12"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="63"/>
-      <c r="J25" s="87" t="s">
+      <c r="G25" s="61"/>
+      <c r="H25" s="62"/>
+      <c r="J25" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91" t="str">
+      <c r="K25" s="89"/>
+      <c r="L25" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
         <v>FTE-ELCNUC</v>
       </c>
-      <c r="M25" s="92" t="str">
+      <c r="M25" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
         <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
       </c>
-      <c r="N25" s="91" t="str">
+      <c r="N25" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O25" s="91" t="str">
+      <c r="O25" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="91"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="21"/>
@@ -5931,36 +5963,36 @@
         <v>HFO</v>
       </c>
       <c r="D26" s="21"/>
-      <c r="E26" s="61">
+      <c r="E26" s="60">
         <f>-'EB1'!L$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>0.85705723214511731</v>
       </c>
       <c r="F26" s="12"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="63"/>
-      <c r="J26" s="87" t="s">
+      <c r="G26" s="61"/>
+      <c r="H26" s="62"/>
+      <c r="J26" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91" t="str">
+      <c r="K26" s="89"/>
+      <c r="L26" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
         <v>FTE-ELCBIO</v>
       </c>
-      <c r="M26" s="92" t="str">
+      <c r="M26" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
         <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
       </c>
-      <c r="N26" s="91" t="str">
+      <c r="N26" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O26" s="91" t="str">
+      <c r="O26" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P26" s="91"/>
-      <c r="Q26" s="91"/>
-      <c r="R26" s="91"/>
+      <c r="P26" s="89"/>
+      <c r="Q26" s="89"/>
+      <c r="R26" s="89"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="21"/>
@@ -5969,36 +6001,36 @@
         <v>OPP</v>
       </c>
       <c r="D27" s="21"/>
-      <c r="E27" s="61">
+      <c r="E27" s="60">
         <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
         <v>5.4758702573637796E-2</v>
       </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="63"/>
-      <c r="J27" s="87" t="s">
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="J27" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91" t="str">
+      <c r="K27" s="89"/>
+      <c r="L27" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
         <v>FTE-ELCHYD</v>
       </c>
-      <c r="M27" s="92" t="str">
+      <c r="M27" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
         <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
       </c>
-      <c r="N27" s="91" t="str">
+      <c r="N27" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O27" s="91" t="str">
+      <c r="O27" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
+      <c r="P27" s="89"/>
+      <c r="Q27" s="89"/>
+      <c r="R27" s="89"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
@@ -6015,35 +6047,35 @@
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="62">
+      <c r="G28" s="61">
         <v>1</v>
       </c>
-      <c r="H28" s="63">
+      <c r="H28" s="62">
         <v>30</v>
       </c>
-      <c r="J28" s="87" t="s">
+      <c r="J28" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91" t="str">
+      <c r="K28" s="89"/>
+      <c r="L28" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
         <v>FTE-ELCWIN</v>
       </c>
-      <c r="M28" s="92" t="str">
+      <c r="M28" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
         <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
       </c>
-      <c r="N28" s="91" t="str">
+      <c r="N28" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O28" s="91" t="str">
+      <c r="O28" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P28" s="91"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="91"/>
+      <c r="P28" s="89"/>
+      <c r="Q28" s="89"/>
+      <c r="R28" s="89"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
@@ -6060,35 +6092,35 @@
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="62">
+      <c r="G29" s="61">
         <v>1</v>
       </c>
-      <c r="H29" s="63">
+      <c r="H29" s="62">
         <v>30</v>
       </c>
-      <c r="J29" s="87" t="s">
+      <c r="J29" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="91"/>
-      <c r="L29" s="91" t="str">
+      <c r="K29" s="89"/>
+      <c r="L29" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
         <v>FTE-ELCWON</v>
       </c>
-      <c r="M29" s="92" t="str">
+      <c r="M29" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
         <v>Sector Fuel Technology Existing Electricity Plants Wind Onshore energy</v>
       </c>
-      <c r="N29" s="91" t="str">
+      <c r="N29" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O29" s="91" t="str">
+      <c r="O29" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
-      <c r="P29" s="91"/>
-      <c r="Q29" s="91"/>
-      <c r="R29" s="91"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
@@ -6105,29 +6137,29 @@
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="62">
+      <c r="G30" s="61">
         <v>1</v>
       </c>
-      <c r="H30" s="63">
+      <c r="H30" s="62">
         <v>30</v>
       </c>
-      <c r="J30" s="87" t="s">
+      <c r="J30" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91" t="str">
+      <c r="K30" s="89"/>
+      <c r="L30" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L13</f>
         <v>FTE-ELCWOF</v>
       </c>
-      <c r="M30" s="92" t="str">
+      <c r="M30" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M13</f>
         <v>Sector Fuel Technology Existing Electricity Plants Wind Offshore energy</v>
       </c>
-      <c r="N30" s="91" t="str">
+      <c r="N30" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O30" s="91" t="str">
+      <c r="O30" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
@@ -6147,29 +6179,29 @@
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
-      <c r="G31" s="62">
+      <c r="G31" s="61">
         <v>1</v>
       </c>
-      <c r="H31" s="63">
+      <c r="H31" s="62">
         <v>30</v>
       </c>
-      <c r="J31" s="87" t="s">
+      <c r="J31" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91" t="str">
+      <c r="K31" s="89"/>
+      <c r="L31" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L14</f>
         <v>FTE-ELCSOL</v>
       </c>
-      <c r="M31" s="92" t="str">
+      <c r="M31" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M14</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
       </c>
-      <c r="N31" s="91" t="str">
+      <c r="N31" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O31" s="91" t="str">
+      <c r="O31" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
@@ -6188,28 +6220,28 @@
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
-      <c r="G32" s="62">
+      <c r="G32" s="61">
         <v>1</v>
       </c>
-      <c r="H32" s="63">
+      <c r="H32" s="62">
         <v>30</v>
       </c>
-      <c r="J32" s="87" t="s">
+      <c r="J32" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="L32" s="91" t="str">
+      <c r="L32" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L15</f>
         <v>FTE-ELCMSW</v>
       </c>
-      <c r="M32" s="92" t="str">
+      <c r="M32" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M15</f>
         <v>Sector Fuel Technology Existing Electricity Plants Municipal Waste</v>
       </c>
-      <c r="N32" s="91" t="str">
+      <c r="N32" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O32" s="91" t="str">
+      <c r="O32" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
@@ -6228,28 +6260,28 @@
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="62">
+      <c r="G33" s="61">
         <v>1</v>
       </c>
-      <c r="H33" s="63">
+      <c r="H33" s="62">
         <v>30</v>
       </c>
-      <c r="J33" s="87" t="s">
+      <c r="J33" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="L33" s="91" t="str">
+      <c r="L33" s="89" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L16</f>
         <v>FTE-ELCSHL</v>
       </c>
-      <c r="M33" s="92" t="str">
+      <c r="M33" s="90" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M16</f>
         <v>Sector Fuel Technology Existing Electricity Plants Oil Shale</v>
       </c>
-      <c r="N33" s="91" t="str">
+      <c r="N33" s="89" t="str">
         <f t="shared" si="1"/>
         <v>PJ</v>
       </c>
-      <c r="O33" s="91" t="str">
+      <c r="O33" s="89" t="str">
         <f t="shared" si="2"/>
         <v>PJa</v>
       </c>
@@ -6269,10 +6301,10 @@
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
-      <c r="G34" s="62">
+      <c r="G34" s="61">
         <v>1</v>
       </c>
-      <c r="H34" s="63">
+      <c r="H34" s="62">
         <v>30</v>
       </c>
     </row>
@@ -6289,21 +6321,21 @@
         <f>L15</f>
         <v>ELCMSW</v>
       </c>
-      <c r="G35" s="62">
+      <c r="G35" s="61">
         <v>1</v>
       </c>
-      <c r="H35" s="63">
+      <c r="H35" s="62">
         <v>30</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B40" s="44"/>
+      <c r="B40" s="43"/>
       <c r="C40" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B41" s="60"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="1" t="s">
         <v>143</v>
       </c>
@@ -6398,44 +6430,44 @@
       <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="86" t="s">
+      <c r="T2" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="86"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="87"/>
-      <c r="Z2" s="87"/>
-      <c r="AA2" s="87"/>
-      <c r="AB2" s="87"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
+      <c r="AB2" s="85"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="T3" s="88" t="s">
+      <c r="T3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="89" t="s">
+      <c r="U3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="88" t="s">
+      <c r="V3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="W3" s="88" t="s">
+      <c r="W3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="X3" s="88" t="s">
+      <c r="X3" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="88" t="s">
+      <c r="Y3" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="88" t="s">
+      <c r="Z3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="88" t="s">
+      <c r="AA3" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="88" t="s">
+      <c r="AB3" s="86" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6457,31 +6489,31 @@
       </c>
       <c r="H4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="T4" s="90" t="s">
+      <c r="T4" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="90" t="s">
+      <c r="U4" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="90" t="s">
+      <c r="V4" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="90" t="s">
+      <c r="W4" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="90" t="s">
+      <c r="X4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="90" t="s">
+      <c r="Y4" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" s="90" t="s">
+      <c r="Z4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" s="90" t="s">
+      <c r="AA4" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="90" t="s">
+      <c r="AB4" s="88" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6503,51 +6535,51 @@
       </c>
       <c r="H5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="T5" s="87" t="s">
+      <c r="T5" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="91"/>
-      <c r="V5" s="87" t="s">
+      <c r="U5" s="89"/>
+      <c r="V5" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="W5" s="87" t="str">
+      <c r="W5" s="85" t="str">
         <f>'EB1'!$W$3</f>
         <v>Electricity</v>
       </c>
-      <c r="X5" s="87" t="str">
+      <c r="X5" s="85" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87" t="s">
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87" t="s">
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="T6" s="91" t="s">
+      <c r="T6" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91" t="str">
+      <c r="U6" s="89"/>
+      <c r="V6" s="89" t="str">
         <f>$B$2&amp;'EB1'!$C$15</f>
         <v>ELCCO2</v>
       </c>
-      <c r="W6" s="91" t="str">
+      <c r="W6" s="89" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$16</f>
         <v>Electricity Plants Carbon dioxide</v>
       </c>
-      <c r="X6" s="91" t="str">
+      <c r="X6" s="89" t="str">
         <f>'EB1'!$AC$2</f>
         <v>kt</v>
       </c>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
+      <c r="AB6" s="89"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="T7" s="2"/>
@@ -6565,17 +6597,17 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="3"/>
-      <c r="T8" s="86" t="s">
+      <c r="T8" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="86"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="85"/>
     </row>
     <row r="9" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
@@ -6593,66 +6625,66 @@
       <c r="F9" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="68" t="s">
+      <c r="J9" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="K9" s="68" t="s">
+      <c r="K9" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="68" t="s">
+      <c r="L9" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="68" t="s">
+      <c r="N9" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="68" t="s">
+      <c r="O9" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="P9" s="68" t="s">
+      <c r="P9" s="67" t="s">
         <v>117</v>
       </c>
       <c r="Q9" s="23"/>
-      <c r="R9" s="82" t="s">
+      <c r="R9" s="80" t="s">
         <v>115</v>
       </c>
       <c r="S9" s="27"/>
-      <c r="T9" s="88" t="s">
+      <c r="T9" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="89" t="s">
+      <c r="U9" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="88" t="s">
+      <c r="V9" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="W9" s="88" t="s">
+      <c r="W9" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="X9" s="88" t="s">
+      <c r="X9" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="Y9" s="88" t="s">
+      <c r="Y9" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="88" t="s">
+      <c r="Z9" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="AA9" s="88" t="s">
+      <c r="AA9" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" s="88" t="s">
+      <c r="AB9" s="86" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6675,13 +6707,13 @@
       <c r="G10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="73" t="s">
         <v>119</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="74" t="s">
+      <c r="J10" s="73" t="s">
         <v>82</v>
       </c>
       <c r="K10" s="15" t="s">
@@ -6706,31 +6738,31 @@
         <v>104</v>
       </c>
       <c r="S10" s="28"/>
-      <c r="T10" s="90" t="s">
+      <c r="T10" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="90" t="s">
+      <c r="U10" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="90" t="s">
+      <c r="V10" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="W10" s="90" t="s">
+      <c r="W10" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="X10" s="90" t="s">
+      <c r="X10" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="Y10" s="90" t="s">
+      <c r="Y10" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="90" t="s">
+      <c r="Z10" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="AA10" s="90" t="s">
+      <c r="AA10" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="AB10" s="90" t="s">
+      <c r="AB10" s="88" t="s">
         <v>25</v>
       </c>
     </row>
@@ -6752,12 +6784,12 @@
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="H11" s="69" t="str">
+      <c r="H11" s="68" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="I11" s="13"/>
-      <c r="J11" s="69"/>
+      <c r="J11" s="68"/>
       <c r="K11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
@@ -6777,21 +6809,21 @@
         <v>194</v>
       </c>
       <c r="P11" s="13"/>
-      <c r="R11" s="83" t="s">
+      <c r="R11" s="81" t="s">
         <v>120</v>
       </c>
       <c r="S11" s="28"/>
-      <c r="T11" s="90" t="s">
+      <c r="T11" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="90"/>
-      <c r="V11" s="90"/>
-      <c r="W11" s="90"/>
-      <c r="X11" s="90"/>
-      <c r="Y11" s="90"/>
-      <c r="Z11" s="90"/>
-      <c r="AA11" s="90"/>
-      <c r="AB11" s="90"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12" s="21" t="str">
@@ -6806,26 +6838,26 @@
         <f t="shared" ref="D12:D48" si="0">$V$5</f>
         <v>ELCC</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="84">
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="82">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="64">
+      <c r="H12" s="83"/>
+      <c r="I12" s="63">
         <v>1</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="63">
         <v>0.5</v>
       </c>
-      <c r="K12" s="64"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="65">
+      <c r="K12" s="63"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="64">
         <v>8.76</v>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="65">
         <v>0.5</v>
       </c>
       <c r="R12" s="26">
@@ -6833,30 +6865,30 @@
         <v>0</v>
       </c>
       <c r="S12" s="29"/>
-      <c r="T12" s="91" t="s">
+      <c r="T12" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91" t="str">
+      <c r="U12" s="89"/>
+      <c r="V12" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
         <v>ELCREHYD00</v>
       </c>
-      <c r="W12" s="91" t="str">
+      <c r="W12" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V12,2)&amp;" - "&amp;'EB1'!P3</f>
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
       <c r="X12" t="s">
         <v>181</v>
       </c>
-      <c r="Y12" s="91" t="str">
+      <c r="Y12" s="89" t="str">
         <f t="shared" ref="Y12" si="1">$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z12" t="s">
         <v>116</v>
       </c>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="91"/>
+      <c r="AA12" s="89"/>
+      <c r="AB12" s="89"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
@@ -6874,38 +6906,38 @@
       <c r="G13">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I13" s="96">
+      <c r="I13" s="94">
         <v>1</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="63">
         <v>0.3</v>
       </c>
       <c r="K13" s="7">
         <v>1018</v>
       </c>
-      <c r="L13" s="85">
+      <c r="L13" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M13" s="85">
+      <c r="M13" s="83">
         <v>0</v>
       </c>
       <c r="N13" s="21">
         <v>35</v>
       </c>
-      <c r="O13" s="65">
+      <c r="O13" s="64">
         <v>8.76</v>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T13" s="91" t="s">
+      <c r="T13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V13" s="91" t="str">
+      <c r="V13" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
-      <c r="W13" s="91" t="str">
+      <c r="W13" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in PARNU - Solar energy</v>
       </c>
@@ -6935,39 +6967,39 @@
       <c r="G14">
         <v>0.108</v>
       </c>
-      <c r="I14" s="96">
+      <c r="I14" s="94">
         <v>1</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="63">
         <v>0.3</v>
       </c>
       <c r="K14" s="7">
         <v>1018</v>
       </c>
-      <c r="L14" s="85">
+      <c r="L14" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M14" s="85">
+      <c r="M14" s="83">
         <v>0</v>
       </c>
       <c r="N14" s="21">
         <v>35</v>
       </c>
-      <c r="O14" s="65">
+      <c r="O14" s="64">
         <v>8.76</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="R14" s="81"/>
-      <c r="T14" s="91" t="s">
+      <c r="R14" s="79"/>
+      <c r="T14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V14" s="91" t="str">
+      <c r="V14" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
-      <c r="W14" s="91" t="str">
+      <c r="W14" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in TARTU - Solar energy</v>
       </c>
@@ -6982,7 +7014,7 @@
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="95"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_LVIRU00</v>
@@ -6998,39 +7030,39 @@
       <c r="G15">
         <v>0.13200000000000001</v>
       </c>
-      <c r="I15" s="96">
+      <c r="I15" s="94">
         <v>1</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J15" s="63">
         <v>0.3</v>
       </c>
       <c r="K15" s="7">
         <v>1018</v>
       </c>
-      <c r="L15" s="85">
+      <c r="L15" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M15" s="85">
+      <c r="M15" s="83">
         <v>0</v>
       </c>
       <c r="N15" s="21">
         <v>35</v>
       </c>
-      <c r="O15" s="65">
+      <c r="O15" s="64">
         <v>8.76</v>
       </c>
-      <c r="P15" s="76">
+      <c r="P15" s="74">
         <v>0.14867925344692126</v>
       </c>
-      <c r="R15" s="81"/>
-      <c r="T15" s="91" t="s">
+      <c r="R15" s="79"/>
+      <c r="T15" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V15" s="91" t="str">
+      <c r="V15" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
         <v>ELCRESOL_LVIRU00</v>
       </c>
-      <c r="W15" s="91" t="str">
+      <c r="W15" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LVIRU - Solar energy</v>
       </c>
@@ -7045,7 +7077,7 @@
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="95"/>
+      <c r="A16" s="93"/>
       <c r="B16" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_IVIRU00</v>
@@ -7061,39 +7093,39 @@
       <c r="G16">
         <v>7.8E-2</v>
       </c>
-      <c r="I16" s="96">
+      <c r="I16" s="94">
         <v>1</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J16" s="63">
         <v>0.3</v>
       </c>
       <c r="K16" s="7">
         <v>1018</v>
       </c>
-      <c r="L16" s="85">
+      <c r="L16" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M16" s="85">
+      <c r="M16" s="83">
         <v>0</v>
       </c>
       <c r="N16" s="21">
         <v>35</v>
       </c>
-      <c r="O16" s="65">
+      <c r="O16" s="64">
         <v>8.76</v>
       </c>
-      <c r="P16" s="76">
+      <c r="P16" s="74">
         <v>0.14701259708091721</v>
       </c>
-      <c r="R16" s="81"/>
-      <c r="T16" s="91" t="s">
+      <c r="R16" s="79"/>
+      <c r="T16" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V16" s="91" t="str">
+      <c r="V16" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
         <v>ELCRESOL_IVIRU00</v>
       </c>
-      <c r="W16" s="91" t="str">
+      <c r="W16" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in IVIRU - Solar energy</v>
       </c>
@@ -7108,7 +7140,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="95"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JARVA00</v>
@@ -7124,39 +7156,39 @@
       <c r="G17">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I17" s="96">
+      <c r="I17" s="94">
         <v>1</v>
       </c>
-      <c r="J17" s="64">
+      <c r="J17" s="63">
         <v>0.3</v>
       </c>
       <c r="K17" s="7">
         <v>1018</v>
       </c>
-      <c r="L17" s="85">
+      <c r="L17" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M17" s="85">
+      <c r="M17" s="83">
         <v>0</v>
       </c>
       <c r="N17" s="21">
         <v>35</v>
       </c>
-      <c r="O17" s="65">
+      <c r="O17" s="64">
         <v>8.76</v>
       </c>
-      <c r="P17" s="76">
+      <c r="P17" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="R17" s="81"/>
-      <c r="T17" s="91" t="s">
+      <c r="R17" s="79"/>
+      <c r="T17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V17" s="91" t="str">
+      <c r="V17" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
         <v>ELCRESOL_JARVA00</v>
       </c>
-      <c r="W17" s="91" t="str">
+      <c r="W17" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JARVA - Solar energy</v>
       </c>
@@ -7171,7 +7203,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="95"/>
+      <c r="A18" s="93"/>
       <c r="B18" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JOGEVA00</v>
@@ -7187,39 +7219,39 @@
       <c r="G18">
         <v>4.7E-2</v>
       </c>
-      <c r="I18" s="96">
+      <c r="I18" s="94">
         <v>1</v>
       </c>
-      <c r="J18" s="64">
+      <c r="J18" s="63">
         <v>0.3</v>
       </c>
       <c r="K18" s="7">
         <v>1018</v>
       </c>
-      <c r="L18" s="85">
+      <c r="L18" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M18" s="85">
+      <c r="M18" s="83">
         <v>0</v>
       </c>
       <c r="N18" s="21">
         <v>35</v>
       </c>
-      <c r="O18" s="65">
+      <c r="O18" s="64">
         <v>8.76</v>
       </c>
-      <c r="P18" s="76">
+      <c r="P18" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="R18" s="81"/>
-      <c r="T18" s="91" t="s">
+      <c r="R18" s="79"/>
+      <c r="T18" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V18" s="91" t="str">
+      <c r="V18" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
         <v>ELCRESOL_JOGEVA00</v>
       </c>
-      <c r="W18" s="91" t="str">
+      <c r="W18" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
       </c>
@@ -7249,38 +7281,38 @@
       <c r="G19">
         <v>0.04</v>
       </c>
-      <c r="I19" s="96">
+      <c r="I19" s="94">
         <v>1</v>
       </c>
-      <c r="J19" s="64">
+      <c r="J19" s="63">
         <v>0.3</v>
       </c>
       <c r="K19" s="7">
         <v>1018</v>
       </c>
-      <c r="L19" s="85">
+      <c r="L19" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M19" s="85">
+      <c r="M19" s="83">
         <v>0</v>
       </c>
       <c r="N19" s="21">
         <v>35</v>
       </c>
-      <c r="O19" s="65">
+      <c r="O19" s="64">
         <v>8.76</v>
       </c>
-      <c r="P19" s="76">
+      <c r="P19" s="74">
         <v>0.15619560585976827</v>
       </c>
-      <c r="T19" s="91" t="s">
+      <c r="T19" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V19" s="91" t="str">
+      <c r="V19" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
         <v>ELCRESOL_HARJU00</v>
       </c>
-      <c r="W19" s="91" t="str">
+      <c r="W19" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HARJU - Solar energy</v>
       </c>
@@ -7310,38 +7342,38 @@
       <c r="G20">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I20" s="96">
+      <c r="I20" s="94">
         <v>1</v>
       </c>
-      <c r="J20" s="64">
+      <c r="J20" s="63">
         <v>0.3</v>
       </c>
       <c r="K20" s="7">
         <v>1018</v>
       </c>
-      <c r="L20" s="85">
+      <c r="L20" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M20" s="85">
+      <c r="M20" s="83">
         <v>0</v>
       </c>
       <c r="N20" s="21">
         <v>35</v>
       </c>
-      <c r="O20" s="65">
+      <c r="O20" s="64">
         <v>8.76</v>
       </c>
-      <c r="P20" s="76">
+      <c r="P20" s="74">
         <v>0.14537310453496291</v>
       </c>
-      <c r="T20" s="91" t="s">
+      <c r="T20" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V20" s="91" t="str">
+      <c r="V20" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
         <v>ELCRESOL_POLVA00</v>
       </c>
-      <c r="W20" s="91" t="str">
+      <c r="W20" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
@@ -7371,38 +7403,38 @@
       <c r="G21">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I21" s="96">
+      <c r="I21" s="94">
         <v>1</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J21" s="63">
         <v>0.3</v>
       </c>
       <c r="K21" s="7">
         <v>1018</v>
       </c>
-      <c r="L21" s="85">
+      <c r="L21" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M21" s="85">
+      <c r="M21" s="83">
         <v>0</v>
       </c>
       <c r="N21" s="21">
         <v>35</v>
       </c>
-      <c r="O21" s="65">
+      <c r="O21" s="64">
         <v>8.76</v>
       </c>
-      <c r="P21" s="76">
+      <c r="P21" s="74">
         <v>0.14763873655681015</v>
       </c>
-      <c r="T21" s="91" t="s">
+      <c r="T21" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V21" s="91" t="str">
+      <c r="V21" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
         <v>ELCRESOL_VALGA00</v>
       </c>
-      <c r="W21" s="91" t="str">
+      <c r="W21" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
@@ -7432,38 +7464,38 @@
       <c r="G22">
         <v>0.08</v>
       </c>
-      <c r="I22" s="96">
+      <c r="I22" s="94">
         <v>1</v>
       </c>
-      <c r="J22" s="64">
+      <c r="J22" s="63">
         <v>0.3</v>
       </c>
       <c r="K22" s="7">
         <v>1018</v>
       </c>
-      <c r="L22" s="85">
+      <c r="L22" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M22" s="85">
+      <c r="M22" s="83">
         <v>0</v>
       </c>
       <c r="N22" s="21">
         <v>35</v>
       </c>
-      <c r="O22" s="65">
+      <c r="O22" s="64">
         <v>8.76</v>
       </c>
-      <c r="P22" s="76">
+      <c r="P22" s="74">
         <v>0.1532628310027955</v>
       </c>
-      <c r="T22" s="91" t="s">
+      <c r="T22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V22" s="91" t="str">
+      <c r="V22" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
         <v>ELCRESOL_VILJANDI00</v>
       </c>
-      <c r="W22" s="91" t="str">
+      <c r="W22" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
@@ -7493,38 +7525,38 @@
       <c r="G23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I23" s="96">
+      <c r="I23" s="94">
         <v>1</v>
       </c>
-      <c r="J23" s="64">
+      <c r="J23" s="63">
         <v>0.3</v>
       </c>
       <c r="K23" s="7">
         <v>1019</v>
       </c>
-      <c r="L23" s="85">
+      <c r="L23" s="83">
         <v>16.079820000000002</v>
       </c>
-      <c r="M23" s="85">
+      <c r="M23" s="83">
         <v>0</v>
       </c>
       <c r="N23" s="21">
         <v>35</v>
       </c>
-      <c r="O23" s="65">
+      <c r="O23" s="64">
         <v>8.76</v>
       </c>
-      <c r="P23" s="76">
+      <c r="P23" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T23" s="91" t="s">
+      <c r="T23" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V23" s="91" t="str">
+      <c r="V23" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
         <v>ELCRESOL_VORU00</v>
       </c>
-      <c r="W23" s="91" t="str">
+      <c r="W23" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
@@ -7554,38 +7586,38 @@
       <c r="G24">
         <v>3.1E-2</v>
       </c>
-      <c r="I24" s="96">
+      <c r="I24" s="94">
         <v>1</v>
       </c>
-      <c r="J24" s="64">
+      <c r="J24" s="63">
         <v>0.3</v>
       </c>
       <c r="K24" s="7">
         <v>1020</v>
       </c>
-      <c r="L24" s="85">
+      <c r="L24" s="83">
         <v>16.095600000000001</v>
       </c>
-      <c r="M24" s="85">
+      <c r="M24" s="83">
         <v>0</v>
       </c>
       <c r="N24" s="21">
         <v>35</v>
       </c>
-      <c r="O24" s="65">
+      <c r="O24" s="64">
         <v>8.76</v>
       </c>
-      <c r="P24" s="76">
+      <c r="P24" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T24" s="91" t="s">
+      <c r="T24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V24" s="91" t="str">
+      <c r="V24" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
         <v>ELCRESOL_SAARE00</v>
       </c>
-      <c r="W24" s="91" t="str">
+      <c r="W24" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
@@ -7615,38 +7647,38 @@
       <c r="G25">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I25" s="96">
+      <c r="I25" s="94">
         <v>1</v>
       </c>
-      <c r="J25" s="64">
+      <c r="J25" s="63">
         <v>0.3</v>
       </c>
       <c r="K25" s="7">
         <v>1021</v>
       </c>
-      <c r="L25" s="85">
+      <c r="L25" s="83">
         <v>16.111380000000004</v>
       </c>
-      <c r="M25" s="85">
+      <c r="M25" s="83">
         <v>0</v>
       </c>
       <c r="N25" s="21">
         <v>35</v>
       </c>
-      <c r="O25" s="65">
+      <c r="O25" s="64">
         <v>8.76</v>
       </c>
-      <c r="P25" s="76">
+      <c r="P25" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T25" s="91" t="s">
+      <c r="T25" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V25" s="91" t="str">
+      <c r="V25" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
         <v>ELCRESOL_RAPLA00</v>
       </c>
-      <c r="W25" s="91" t="str">
+      <c r="W25" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
@@ -7676,38 +7708,38 @@
       <c r="G26">
         <v>0.01</v>
       </c>
-      <c r="I26" s="96">
+      <c r="I26" s="94">
         <v>1</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="63">
         <v>0.3</v>
       </c>
       <c r="K26" s="7">
         <v>1022</v>
       </c>
-      <c r="L26" s="85">
+      <c r="L26" s="83">
         <v>16.127160000000003</v>
       </c>
-      <c r="M26" s="85">
+      <c r="M26" s="83">
         <v>0</v>
       </c>
       <c r="N26" s="21">
         <v>35</v>
       </c>
-      <c r="O26" s="65">
+      <c r="O26" s="64">
         <v>8.76</v>
       </c>
-      <c r="P26" s="76">
+      <c r="P26" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T26" s="91" t="s">
+      <c r="T26" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V26" s="91" t="str">
+      <c r="V26" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
         <v>ELCRESOL_LAANE00</v>
       </c>
-      <c r="W26" s="91" t="str">
+      <c r="W26" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
@@ -7737,19 +7769,19 @@
       <c r="G27">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="96">
+      <c r="I27" s="94">
         <v>1</v>
       </c>
-      <c r="J27" s="64">
+      <c r="J27" s="63">
         <v>0.3</v>
       </c>
       <c r="K27" s="7">
         <v>1023</v>
       </c>
-      <c r="L27" s="85">
+      <c r="L27" s="83">
         <v>16.142940000000003</v>
       </c>
-      <c r="M27" s="85">
+      <c r="M27" s="83">
         <v>0</v>
       </c>
       <c r="N27" s="21">
@@ -7758,17 +7790,17 @@
       <c r="O27" s="21">
         <v>8.76</v>
       </c>
-      <c r="P27" s="76">
+      <c r="P27" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T27" s="91" t="s">
+      <c r="T27" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V27" s="91" t="str">
+      <c r="V27" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
         <v>ELCRESOL_HIIU00</v>
       </c>
-      <c r="W27" s="91" t="str">
+      <c r="W27" s="89" t="str">
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
@@ -7798,19 +7830,19 @@
       <c r="G28">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="I28" s="96">
+      <c r="I28" s="94">
         <v>1</v>
       </c>
-      <c r="J28" s="64">
+      <c r="J28" s="63">
         <v>0.3</v>
       </c>
       <c r="K28" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L28" s="85">
+      <c r="L28" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M28" s="85">
+      <c r="M28" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N28">
@@ -7822,7 +7854,7 @@
       <c r="P28">
         <v>0.4</v>
       </c>
-      <c r="T28" s="91" t="s">
+      <c r="T28" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V28" t="str">
@@ -7859,19 +7891,19 @@
       <c r="G29">
         <v>0.17519999999999999</v>
       </c>
-      <c r="I29" s="96">
+      <c r="I29" s="94">
         <v>1</v>
       </c>
-      <c r="J29" s="64">
+      <c r="J29" s="63">
         <v>0.3</v>
       </c>
       <c r="K29" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L29" s="85">
+      <c r="L29" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M29" s="85">
+      <c r="M29" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N29">
@@ -7883,7 +7915,7 @@
       <c r="P29">
         <v>0.4</v>
       </c>
-      <c r="T29" s="91" t="s">
+      <c r="T29" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V29" t="str">
@@ -7920,19 +7952,19 @@
       <c r="G30">
         <v>8.130000000000015E-2</v>
       </c>
-      <c r="I30" s="96">
+      <c r="I30" s="94">
         <v>1</v>
       </c>
-      <c r="J30" s="64">
+      <c r="J30" s="63">
         <v>0.3</v>
       </c>
       <c r="K30" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L30" s="85">
+      <c r="L30" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M30" s="85">
+      <c r="M30" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N30">
@@ -7944,7 +7976,7 @@
       <c r="P30">
         <v>0.4</v>
       </c>
-      <c r="T30" s="91" t="s">
+      <c r="T30" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V30" t="str">
@@ -7981,19 +8013,19 @@
       <c r="G31">
         <v>1.6E-2</v>
       </c>
-      <c r="I31" s="96">
+      <c r="I31" s="94">
         <v>1</v>
       </c>
-      <c r="J31" s="64">
+      <c r="J31" s="63">
         <v>0.3</v>
       </c>
       <c r="K31" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L31" s="85">
+      <c r="L31" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M31" s="85">
+      <c r="M31" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N31">
@@ -8005,7 +8037,7 @@
       <c r="P31">
         <v>0.4</v>
       </c>
-      <c r="T31" s="91" t="s">
+      <c r="T31" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V31" t="str">
@@ -8042,19 +8074,19 @@
       <c r="G32">
         <v>3.27E-2</v>
       </c>
-      <c r="I32" s="96">
+      <c r="I32" s="94">
         <v>1</v>
       </c>
-      <c r="J32" s="64">
+      <c r="J32" s="63">
         <v>0.3</v>
       </c>
       <c r="K32" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L32" s="85">
+      <c r="L32" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M32" s="85">
+      <c r="M32" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N32">
@@ -8066,7 +8098,7 @@
       <c r="P32">
         <v>0.4</v>
       </c>
-      <c r="T32" s="91" t="s">
+      <c r="T32" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V32" t="str">
@@ -8103,19 +8135,19 @@
       <c r="G33">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="I33" s="96">
+      <c r="I33" s="94">
         <v>1</v>
       </c>
-      <c r="J33" s="64">
+      <c r="J33" s="63">
         <v>0.3</v>
       </c>
       <c r="K33" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L33" s="85">
+      <c r="L33" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M33" s="85">
+      <c r="M33" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N33">
@@ -8127,7 +8159,7 @@
       <c r="P33">
         <v>0.4</v>
       </c>
-      <c r="T33" s="91" t="s">
+      <c r="T33" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V33" t="str">
@@ -8164,19 +8196,19 @@
       <c r="G34">
         <v>0.06</v>
       </c>
-      <c r="I34" s="96">
+      <c r="I34" s="94">
         <v>1</v>
       </c>
-      <c r="J34" s="64">
+      <c r="J34" s="63">
         <v>0.3</v>
       </c>
       <c r="K34" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L34" s="85">
+      <c r="L34" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M34" s="85">
+      <c r="M34" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N34">
@@ -8188,7 +8220,7 @@
       <c r="P34">
         <v>0.4</v>
       </c>
-      <c r="T34" s="91" t="s">
+      <c r="T34" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V34" t="str">
@@ -8225,19 +8257,19 @@
       <c r="G35">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="I35" s="96">
+      <c r="I35" s="94">
         <v>1</v>
       </c>
-      <c r="J35" s="64">
+      <c r="J35" s="63">
         <v>0.3</v>
       </c>
       <c r="K35" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L35" s="85">
+      <c r="L35" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M35" s="85">
+      <c r="M35" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N35">
@@ -8249,7 +8281,7 @@
       <c r="P35">
         <v>0.4</v>
       </c>
-      <c r="T35" s="91" t="s">
+      <c r="T35" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V35" t="str">
@@ -8286,19 +8318,19 @@
       <c r="G36">
         <v>0.1036</v>
       </c>
-      <c r="I36" s="96">
+      <c r="I36" s="94">
         <v>1</v>
       </c>
-      <c r="J36" s="64">
+      <c r="J36" s="63">
         <v>0.3</v>
       </c>
       <c r="K36" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L36" s="85">
+      <c r="L36" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M36" s="85">
+      <c r="M36" s="83">
         <v>2.0036999999999998</v>
       </c>
       <c r="N36">
@@ -8310,7 +8342,7 @@
       <c r="P36">
         <v>0.4</v>
       </c>
-      <c r="T36" s="91" t="s">
+      <c r="T36" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V36" t="str">
@@ -8353,16 +8385,16 @@
       <c r="J37" s="21">
         <v>0.9</v>
       </c>
-      <c r="K37" s="81">
+      <c r="K37" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L37" s="81">
+      <c r="L37" s="79">
         <v>160.216352398</v>
       </c>
-      <c r="M37" s="81">
+      <c r="M37" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="N37" s="81">
+      <c r="N37" s="79">
         <v>53</v>
       </c>
       <c r="O37" s="21">
@@ -8371,7 +8403,7 @@
       <c r="P37">
         <v>1</v>
       </c>
-      <c r="T37" s="91" t="s">
+      <c r="T37" s="89" t="s">
         <v>102</v>
       </c>
       <c r="V37" t="str">
@@ -8414,16 +8446,16 @@
       <c r="J38" s="21">
         <v>0.95</v>
       </c>
-      <c r="K38" s="81">
+      <c r="K38" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L38" s="81">
+      <c r="L38" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M38" s="81">
+      <c r="M38" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N38" s="81">
+      <c r="N38" s="79">
         <v>40</v>
       </c>
       <c r="O38" s="21">
@@ -8432,11 +8464,11 @@
       <c r="P38" s="21">
         <v>1</v>
       </c>
-      <c r="T38" s="91" t="s">
+      <c r="T38" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U38" s="91"/>
-      <c r="V38" s="91" t="str">
+      <c r="U38" s="89"/>
+      <c r="V38" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_EESTI00"</f>
         <v>ELCTESHL_EESTI00</v>
       </c>
@@ -8476,13 +8508,13 @@
       <c r="J39" s="21">
         <v>0.95</v>
       </c>
-      <c r="K39" s="81">
+      <c r="K39" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L39" s="81">
+      <c r="L39" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M39" s="81">
+      <c r="M39" s="79">
         <v>4.1005000000000003</v>
       </c>
       <c r="N39" s="21">
@@ -8494,11 +8526,11 @@
       <c r="P39" s="21">
         <v>1</v>
       </c>
-      <c r="T39" s="91" t="s">
+      <c r="T39" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U39" s="91"/>
-      <c r="V39" s="91" t="str">
+      <c r="U39" s="89"/>
+      <c r="V39" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_AUVERE00"</f>
         <v>ELCTESHL_AUVERE00</v>
       </c>
@@ -8538,13 +8570,13 @@
       <c r="J40" s="21">
         <v>0.95</v>
       </c>
-      <c r="K40" s="81">
+      <c r="K40" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L40" s="81">
+      <c r="L40" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M40" s="81">
+      <c r="M40" s="79">
         <v>4.1005000000000003</v>
       </c>
       <c r="N40" s="21">
@@ -8556,11 +8588,11 @@
       <c r="P40" s="21">
         <v>1</v>
       </c>
-      <c r="T40" s="91" t="s">
+      <c r="T40" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U40" s="91"/>
-      <c r="V40" s="91" t="str">
+      <c r="U40" s="89"/>
+      <c r="V40" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_ENEFIT00"</f>
         <v>ELCTESHL_ENEFIT00</v>
       </c>
@@ -8600,13 +8632,13 @@
       <c r="J41" s="21">
         <v>0.95</v>
       </c>
-      <c r="K41" s="81">
+      <c r="K41" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L41" s="81">
+      <c r="L41" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M41" s="81">
+      <c r="M41" s="79">
         <v>4.1005000000000003</v>
       </c>
       <c r="N41" s="21">
@@ -8618,11 +8650,11 @@
       <c r="P41" s="21">
         <v>1</v>
       </c>
-      <c r="T41" s="91" t="s">
+      <c r="T41" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U41" s="91"/>
-      <c r="V41" s="91" t="str">
+      <c r="U41" s="89"/>
+      <c r="V41" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_BALTI00"</f>
         <v>ELCTESHL_BALTI00</v>
       </c>
@@ -8662,13 +8694,13 @@
       <c r="J42" s="21">
         <v>0.95</v>
       </c>
-      <c r="K42" s="81">
+      <c r="K42" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L42" s="81">
+      <c r="L42" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M42" s="81">
+      <c r="M42" s="79">
         <v>4.1005000000000003</v>
       </c>
       <c r="N42" s="21">
@@ -8680,10 +8712,10 @@
       <c r="P42" s="21">
         <v>1</v>
       </c>
-      <c r="T42" s="91" t="s">
+      <c r="T42" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V42" s="91" t="str">
+      <c r="V42" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_SILLAMAE00"</f>
         <v>ELCTESHL_SILLAMAE00</v>
       </c>
@@ -8717,22 +8749,22 @@
       <c r="G43" s="21">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I43" s="76">
+      <c r="I43" s="74">
         <v>0.56000000000000005</v>
       </c>
       <c r="J43" s="21">
         <v>0.95</v>
       </c>
-      <c r="K43" s="81">
+      <c r="K43" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L43" s="81">
+      <c r="L43" s="79">
         <v>39.138495576499992</v>
       </c>
-      <c r="M43" s="81">
+      <c r="M43" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="N43" s="81">
+      <c r="N43" s="79">
         <v>40</v>
       </c>
       <c r="O43" s="21">
@@ -8741,11 +8773,11 @@
       <c r="P43" s="21">
         <v>1</v>
       </c>
-      <c r="T43" s="91" t="s">
+      <c r="T43" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U43" s="91"/>
-      <c r="V43" s="91" t="str">
+      <c r="U43" s="89"/>
+      <c r="V43" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_POHJA00"</f>
         <v>ELCTEGAS_POHJA00</v>
       </c>
@@ -8779,22 +8811,22 @@
       <c r="G44" s="21">
         <v>3.9E-2</v>
       </c>
-      <c r="I44" s="76">
+      <c r="I44" s="74">
         <v>0.46800000000000003</v>
       </c>
       <c r="J44" s="21">
         <v>0.95</v>
       </c>
-      <c r="K44" s="81">
+      <c r="K44" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L44" s="81">
+      <c r="L44" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M44" s="81">
+      <c r="M44" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N44" s="81">
+      <c r="N44" s="79">
         <v>40</v>
       </c>
       <c r="O44" s="21">
@@ -8803,10 +8835,10 @@
       <c r="P44" s="21">
         <v>1</v>
       </c>
-      <c r="T44" s="91" t="s">
+      <c r="T44" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V44" s="91" t="str">
+      <c r="V44" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TLNUTILITAS00"</f>
         <v>ELCTEBIO_TLNUTILITAS00</v>
       </c>
@@ -8840,22 +8872,22 @@
       <c r="G45" s="21">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="I45" s="76">
+      <c r="I45" s="74">
         <v>0.46800000000000003</v>
       </c>
       <c r="J45" s="21">
         <v>0.95</v>
       </c>
-      <c r="K45" s="81">
+      <c r="K45" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L45" s="81">
+      <c r="L45" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M45" s="81">
+      <c r="M45" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N45" s="81">
+      <c r="N45" s="79">
         <v>40</v>
       </c>
       <c r="O45" s="21">
@@ -8864,10 +8896,10 @@
       <c r="P45" s="21">
         <v>1</v>
       </c>
-      <c r="T45" s="91" t="s">
+      <c r="T45" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V45" s="91" t="str">
+      <c r="V45" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TARTU00"</f>
         <v>ELCTEBIO_TARTU00</v>
       </c>
@@ -8901,22 +8933,22 @@
       <c r="G46" s="21">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="I46" s="76">
+      <c r="I46" s="74">
         <v>0.46800000000000003</v>
       </c>
       <c r="J46" s="21">
         <v>0.95</v>
       </c>
-      <c r="K46" s="81">
+      <c r="K46" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L46" s="81">
+      <c r="L46" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M46" s="81">
+      <c r="M46" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N46" s="81">
+      <c r="N46" s="79">
         <v>40</v>
       </c>
       <c r="O46" s="21">
@@ -8925,10 +8957,10 @@
       <c r="P46" s="21">
         <v>1</v>
       </c>
-      <c r="T46" s="91" t="s">
+      <c r="T46" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V46" s="91" t="str">
+      <c r="V46" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PARNU00"</f>
         <v>ELCTEBIO_PARNU00</v>
       </c>
@@ -8962,22 +8994,22 @@
       <c r="G47" s="21">
         <v>1.3900000000000001E-2</v>
       </c>
-      <c r="I47" s="76">
+      <c r="I47" s="74">
         <v>0.46800000000000003</v>
       </c>
       <c r="J47" s="21">
         <v>0.95</v>
       </c>
-      <c r="K47" s="81">
+      <c r="K47" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L47" s="81">
+      <c r="L47" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M47" s="81">
+      <c r="M47" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N47" s="81">
+      <c r="N47" s="79">
         <v>40</v>
       </c>
       <c r="O47" s="21">
@@ -8986,10 +9018,10 @@
       <c r="P47" s="21">
         <v>1</v>
       </c>
-      <c r="T47" s="91" t="s">
+      <c r="T47" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V47" s="91" t="str">
+      <c r="V47" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HORIZON00"</f>
         <v>ELCTEBIO_HORIZON00</v>
       </c>
@@ -9032,10 +9064,10 @@
       <c r="K48" s="7">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L48" s="85">
+      <c r="L48" s="83">
         <v>39.138495576499992</v>
       </c>
-      <c r="M48" s="85">
+      <c r="M48" s="83">
         <v>5.8775000000000004</v>
       </c>
       <c r="N48">
@@ -9047,10 +9079,10 @@
       <c r="P48" s="21">
         <v>1</v>
       </c>
-      <c r="T48" s="91" t="s">
+      <c r="T48" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V48" s="91" t="str">
+      <c r="V48" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_GRUNE00"</f>
         <v>ELCTEGAS_GRUNE00</v>
       </c>
@@ -9163,26 +9195,26 @@
       <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
+      <c r="S2" s="95"/>
+      <c r="T2" s="95"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="96"/>
+      <c r="X2" s="96"/>
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="96"/>
+      <c r="AA2" s="96"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
     </row>
     <row r="4" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
@@ -9202,15 +9234,15 @@
       </c>
       <c r="H4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
     </row>
     <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
@@ -9230,26 +9262,26 @@
       </c>
       <c r="H5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="S5" s="98"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-      <c r="Y5" s="98"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="98"/>
+      <c r="S5" s="96"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="96"/>
+      <c r="V5" s="96"/>
+      <c r="W5" s="96"/>
+      <c r="X5" s="96"/>
+      <c r="Y5" s="96"/>
+      <c r="Z5" s="96"/>
+      <c r="AA5" s="96"/>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="S6" s="101"/>
-      <c r="T6" s="101"/>
-      <c r="U6" s="101"/>
-      <c r="V6" s="101"/>
-      <c r="W6" s="101"/>
-      <c r="X6" s="101"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="101"/>
+      <c r="S6" s="99"/>
+      <c r="T6" s="99"/>
+      <c r="U6" s="99"/>
+      <c r="V6" s="99"/>
+      <c r="W6" s="99"/>
+      <c r="X6" s="99"/>
+      <c r="Y6" s="99"/>
+      <c r="Z6" s="99"/>
+      <c r="AA6" s="99"/>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.2">
       <c r="S7" s="2"/>
@@ -9265,17 +9297,17 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="3"/>
-      <c r="Q8" s="86" t="s">
+      <c r="Q8" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="R8" s="86"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
       <c r="Z8" s="21"/>
       <c r="AA8" s="21"/>
     </row>
@@ -9289,63 +9321,63 @@
       <c r="D9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="F9" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="J9" s="68" t="s">
+      <c r="J9" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="68" t="s">
+      <c r="K9" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="L9" s="68" t="s">
+      <c r="L9" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="N9" s="68" t="s">
+      <c r="N9" s="67" t="s">
         <v>117</v>
       </c>
       <c r="O9" s="23"/>
       <c r="P9" s="27"/>
-      <c r="Q9" s="88" t="s">
+      <c r="Q9" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="89" t="s">
+      <c r="R9" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="S9" s="88" t="s">
+      <c r="S9" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="T9" s="88" t="s">
+      <c r="T9" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="U9" s="88" t="s">
+      <c r="U9" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="V9" s="88" t="s">
+      <c r="V9" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="W9" s="88" t="s">
+      <c r="W9" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="X9" s="88" t="s">
+      <c r="X9" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="Y9" s="88" t="s">
+      <c r="Y9" s="86" t="s">
         <v>20</v>
       </c>
       <c r="Z9" s="21"/>
@@ -9364,13 +9396,13 @@
       <c r="E10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="73" t="s">
         <v>119</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="73" t="s">
         <v>82</v>
       </c>
       <c r="I10" s="15" t="s">
@@ -9392,31 +9424,31 @@
         <v>118</v>
       </c>
       <c r="P10" s="28"/>
-      <c r="Q10" s="90" t="s">
+      <c r="Q10" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="R10" s="90" t="s">
+      <c r="R10" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="S10" s="90" t="s">
+      <c r="S10" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="T10" s="90" t="s">
+      <c r="T10" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="U10" s="90" t="s">
+      <c r="U10" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="V10" s="90" t="s">
+      <c r="V10" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="W10" s="90" t="s">
+      <c r="W10" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="X10" s="90" t="s">
+      <c r="X10" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="Y10" s="90" t="s">
+      <c r="Y10" s="88" t="s">
         <v>25</v>
       </c>
       <c r="Z10" s="21"/>
@@ -9428,52 +9460,52 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="103" t="str">
+      <c r="E11" s="101" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="F11" s="104" t="str">
+      <c r="F11" s="102" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="103" t="str">
+      <c r="G11" s="101"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="101" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
-      <c r="J11" s="103" t="str">
+      <c r="J11" s="101" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
-      <c r="K11" s="103" t="str">
+      <c r="K11" s="101" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2025/PJ</v>
       </c>
-      <c r="L11" s="103" t="s">
+      <c r="L11" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="103" t="s">
+      <c r="M11" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="N11" s="103"/>
+      <c r="N11" s="101"/>
       <c r="P11" s="28"/>
-      <c r="Q11" s="105" t="s">
+      <c r="Q11" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="105"/>
-      <c r="U11" s="105"/>
-      <c r="V11" s="105"/>
-      <c r="W11" s="105"/>
-      <c r="X11" s="105"/>
-      <c r="Y11" s="105"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103"/>
       <c r="Z11" s="21"/>
       <c r="AA11" s="21"/>
     </row>
-    <row r="12" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="94" t="str">
+    <row r="12" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="92" t="str">
         <f>S12</f>
         <v>ELCCEBIO_OSULA00</v>
       </c>
@@ -9481,18 +9513,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D12" s="94" t="str">
+      <c r="D12" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E12">
         <v>0.01</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="105"/>
       <c r="G12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H12" s="108">
+      <c r="H12" s="106">
         <v>0.95</v>
       </c>
       <c r="I12" s="7">
@@ -9507,18 +9539,18 @@
       <c r="L12">
         <v>40</v>
       </c>
-      <c r="M12" s="65">
+      <c r="M12" s="64">
         <v>8.76</v>
       </c>
-      <c r="N12" s="66">
+      <c r="N12" s="65">
         <v>1</v>
       </c>
       <c r="P12" s="29"/>
-      <c r="Q12" s="91" t="s">
+      <c r="Q12" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R12" s="101"/>
-      <c r="S12" s="91" t="str">
+      <c r="R12" s="99"/>
+      <c r="S12" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OSULA00"</f>
         <v>ELCCEBIO_OSULA00</v>
       </c>
@@ -9526,22 +9558,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S12,2)&amp;" Osula CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Osula CHP - Biomass</v>
       </c>
-      <c r="U12" s="101" t="s">
+      <c r="U12" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V12" s="101" t="s">
+      <c r="V12" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W12" t="s">
         <v>116</v>
       </c>
-      <c r="X12" s="101"/>
-      <c r="Y12" s="101"/>
+      <c r="X12" s="99"/>
+      <c r="Y12" s="99"/>
       <c r="AA12"/>
       <c r="AB12"/>
     </row>
-    <row r="13" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="94" t="str">
+    <row r="13" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="92" t="str">
         <f t="shared" ref="B13:B24" si="0">S13</f>
         <v>ELCCEBIO_MUSTAMAE00</v>
       </c>
@@ -9549,18 +9581,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D13" s="94" t="str">
+      <c r="D13" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E13">
         <v>9.300000000000001E-3</v>
       </c>
-      <c r="F13" s="107"/>
+      <c r="F13" s="105"/>
       <c r="G13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H13" s="108">
+      <c r="H13" s="106">
         <v>0.95</v>
       </c>
       <c r="I13" s="7">
@@ -9575,18 +9607,18 @@
       <c r="L13">
         <v>40</v>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="64">
         <v>8.76</v>
       </c>
-      <c r="N13" s="66">
+      <c r="N13" s="65">
         <v>1</v>
       </c>
       <c r="P13" s="29"/>
-      <c r="Q13" s="91" t="s">
+      <c r="Q13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R13" s="101"/>
-      <c r="S13" s="91" t="str">
+      <c r="R13" s="99"/>
+      <c r="S13" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_MUSTAMAE00"</f>
         <v>ELCCEBIO_MUSTAMAE00</v>
       </c>
@@ -9594,22 +9626,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S13,2)&amp;" Mustamae CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Mustamae CHP - Biomass</v>
       </c>
-      <c r="U13" s="101" t="s">
+      <c r="U13" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V13" s="101" t="s">
+      <c r="V13" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W13" t="s">
         <v>116</v>
       </c>
-      <c r="X13" s="101"/>
-      <c r="Y13" s="101"/>
+      <c r="X13" s="99"/>
+      <c r="Y13" s="99"/>
       <c r="AA13"/>
       <c r="AB13"/>
     </row>
-    <row r="14" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="94" t="str">
+    <row r="14" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_SILLAMAE100</v>
       </c>
@@ -9617,18 +9649,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D14" s="94" t="str">
+      <c r="D14" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E14">
         <v>7.0999999999999995E-3</v>
       </c>
-      <c r="F14" s="106"/>
+      <c r="F14" s="104"/>
       <c r="G14">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H14" s="108">
+      <c r="H14" s="106">
         <v>0.95</v>
       </c>
       <c r="I14" s="7">
@@ -9643,18 +9675,18 @@
       <c r="L14">
         <v>72</v>
       </c>
-      <c r="M14" s="65">
+      <c r="M14" s="64">
         <v>8.76</v>
       </c>
-      <c r="N14" s="66">
+      <c r="N14" s="65">
         <v>1</v>
       </c>
       <c r="P14" s="29"/>
-      <c r="Q14" s="91" t="s">
+      <c r="Q14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R14" s="101"/>
-      <c r="S14" s="91" t="str">
+      <c r="R14" s="99"/>
+      <c r="S14" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_SILLAMAE100"</f>
         <v>ELCCEBIO_SILLAMAE100</v>
       </c>
@@ -9662,22 +9694,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S14,2)&amp;" Sillamae 1 CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Sillamae 1 CHP - Biomass</v>
       </c>
-      <c r="U14" s="101" t="s">
+      <c r="U14" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V14" s="101" t="s">
+      <c r="V14" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W14" t="s">
         <v>116</v>
       </c>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="101"/>
+      <c r="X14" s="99"/>
+      <c r="Y14" s="99"/>
       <c r="AA14"/>
       <c r="AB14"/>
     </row>
-    <row r="15" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="94" t="str">
+    <row r="15" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_SILLAMAE200</v>
       </c>
@@ -9685,18 +9717,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
         <v>ELCGAS</v>
       </c>
-      <c r="D15" s="94" t="str">
+      <c r="D15" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E15">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="F15" s="107"/>
+      <c r="F15" s="105"/>
       <c r="G15">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H15" s="108">
+      <c r="H15" s="106">
         <v>0.95</v>
       </c>
       <c r="I15" s="7">
@@ -9711,18 +9743,18 @@
       <c r="L15">
         <v>40</v>
       </c>
-      <c r="M15" s="65">
+      <c r="M15" s="64">
         <v>8.76</v>
       </c>
-      <c r="N15" s="66">
+      <c r="N15" s="65">
         <v>1</v>
       </c>
       <c r="P15" s="29"/>
-      <c r="Q15" s="91" t="s">
+      <c r="Q15" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R15" s="101"/>
-      <c r="S15" s="91" t="str">
+      <c r="R15" s="99"/>
+      <c r="S15" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_SILLAMAE200"</f>
         <v>ELCCEGAS_SILLAMAE200</v>
       </c>
@@ -9730,22 +9762,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S15,2)&amp;" Sillamae 2 CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Sillamae 2 CHP - Natural Gas</v>
       </c>
-      <c r="U15" s="101" t="s">
+      <c r="U15" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V15" s="101" t="s">
+      <c r="V15" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W15" t="s">
         <v>116</v>
       </c>
-      <c r="X15" s="101"/>
-      <c r="Y15" s="101"/>
+      <c r="X15" s="99"/>
+      <c r="Y15" s="99"/>
       <c r="AA15"/>
       <c r="AB15"/>
     </row>
-    <row r="16" spans="2:28" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="94" t="str">
+    <row r="16" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_HELME00</v>
       </c>
@@ -9753,18 +9785,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D16" s="94" t="str">
+      <c r="D16" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E16">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="105"/>
       <c r="G16">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H16" s="108">
+      <c r="H16" s="106">
         <v>0.95</v>
       </c>
       <c r="I16" s="7">
@@ -9779,18 +9811,18 @@
       <c r="L16">
         <v>40</v>
       </c>
-      <c r="M16" s="65">
+      <c r="M16" s="64">
         <v>8.76</v>
       </c>
-      <c r="N16" s="66">
+      <c r="N16" s="65">
         <v>1</v>
       </c>
       <c r="P16" s="29"/>
-      <c r="Q16" s="91" t="s">
+      <c r="Q16" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R16" s="101"/>
-      <c r="S16" s="91" t="str">
+      <c r="R16" s="99"/>
+      <c r="S16" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HELME00"</f>
         <v>ELCCEBIO_HELME00</v>
       </c>
@@ -9798,22 +9830,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S16,2)&amp;" Helme CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Helme CHP - Biomass</v>
       </c>
-      <c r="U16" s="101" t="s">
+      <c r="U16" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V16" s="101" t="s">
+      <c r="V16" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W16" t="s">
         <v>116</v>
       </c>
-      <c r="X16" s="101"/>
-      <c r="Y16" s="101"/>
+      <c r="X16" s="99"/>
+      <c r="Y16" s="99"/>
       <c r="AA16"/>
       <c r="AB16"/>
     </row>
-    <row r="17" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="94" t="str">
+    <row r="17" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_KURESSAARE00</v>
       </c>
@@ -9821,18 +9853,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D17" s="94" t="str">
+      <c r="D17" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E17">
         <v>1.8E-3</v>
       </c>
-      <c r="F17" s="107"/>
+      <c r="F17" s="105"/>
       <c r="G17">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H17" s="108">
+      <c r="H17" s="106">
         <v>0.95</v>
       </c>
       <c r="I17" s="7">
@@ -9847,18 +9879,18 @@
       <c r="L17">
         <v>40</v>
       </c>
-      <c r="M17" s="65">
+      <c r="M17" s="64">
         <v>8.76</v>
       </c>
-      <c r="N17" s="66">
+      <c r="N17" s="65">
         <v>1</v>
       </c>
       <c r="P17" s="29"/>
-      <c r="Q17" s="91" t="s">
+      <c r="Q17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R17" s="101"/>
-      <c r="S17" s="91" t="str">
+      <c r="R17" s="99"/>
+      <c r="S17" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_KURESSAARE00"</f>
         <v>ELCCEBIO_KURESSAARE00</v>
       </c>
@@ -9866,22 +9898,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S17,2)&amp;" Kuressaare CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Kuressaare CHP - Biomass</v>
       </c>
-      <c r="U17" s="101" t="s">
+      <c r="U17" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V17" s="101" t="s">
+      <c r="V17" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W17" t="s">
         <v>116</v>
       </c>
-      <c r="X17" s="101"/>
-      <c r="Y17" s="101"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
       <c r="AA17"/>
       <c r="AB17"/>
     </row>
-    <row r="18" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="94" t="str">
+    <row r="18" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_PAIDE00</v>
       </c>
@@ -9889,18 +9921,18 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D18" s="94" t="str">
+      <c r="D18" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
       <c r="E18">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="105"/>
       <c r="G18">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H18" s="108">
+      <c r="H18" s="106">
         <v>0.95</v>
       </c>
       <c r="I18" s="7">
@@ -9915,18 +9947,18 @@
       <c r="L18">
         <v>40</v>
       </c>
-      <c r="M18" s="65">
+      <c r="M18" s="64">
         <v>8.76</v>
       </c>
-      <c r="N18" s="66">
+      <c r="N18" s="65">
         <v>1</v>
       </c>
       <c r="P18" s="29"/>
-      <c r="Q18" s="91" t="s">
+      <c r="Q18" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R18" s="101"/>
-      <c r="S18" s="91" t="str">
+      <c r="R18" s="99"/>
+      <c r="S18" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PAIDE00"</f>
         <v>ELCCEBIO_PAIDE00</v>
       </c>
@@ -9934,22 +9966,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S18,2)&amp;" Paide CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Paide CHP - Biomass</v>
       </c>
-      <c r="U18" s="101" t="s">
+      <c r="U18" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V18" s="101" t="s">
+      <c r="V18" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W18" t="s">
         <v>116</v>
       </c>
-      <c r="X18" s="101"/>
-      <c r="Y18" s="101"/>
+      <c r="X18" s="99"/>
+      <c r="Y18" s="99"/>
       <c r="AA18"/>
       <c r="AB18"/>
     </row>
-    <row r="19" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="94" t="str">
+    <row r="19" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_JAMEJALA00</v>
       </c>
@@ -9957,7 +9989,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
         <v>ELCGAS</v>
       </c>
-      <c r="D19" s="94" t="str">
+      <c r="D19" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -9967,7 +9999,7 @@
       <c r="G19">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H19" s="108">
+      <c r="H19" s="106">
         <v>0.95</v>
       </c>
       <c r="I19" s="7">
@@ -9982,17 +10014,17 @@
       <c r="L19">
         <v>40</v>
       </c>
-      <c r="M19" s="65">
+      <c r="M19" s="64">
         <v>8.76</v>
       </c>
-      <c r="N19" s="66">
+      <c r="N19" s="65">
         <v>1</v>
       </c>
-      <c r="Q19" s="91" t="s">
+      <c r="Q19" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R19" s="101"/>
-      <c r="S19" s="91" t="str">
+      <c r="R19" s="99"/>
+      <c r="S19" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_JAMEJALA00"</f>
         <v>ELCCEGAS_JAMEJALA00</v>
       </c>
@@ -10000,22 +10032,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S19,2)&amp;" Jamejala CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Jamejala CHP - Natural Gas</v>
       </c>
-      <c r="U19" s="101" t="s">
+      <c r="U19" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V19" s="101" t="s">
+      <c r="V19" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W19" t="s">
         <v>116</v>
       </c>
-      <c r="X19" s="110"/>
-      <c r="Y19" s="110"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="108"/>
       <c r="AA19"/>
       <c r="AB19"/>
     </row>
-    <row r="20" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="94" t="str">
+    <row r="20" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_PUSSI00</v>
       </c>
@@ -10023,7 +10055,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)</f>
         <v>ELCGAS</v>
       </c>
-      <c r="D20" s="94" t="str">
+      <c r="D20" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -10033,7 +10065,7 @@
       <c r="G20">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H20" s="108">
+      <c r="H20" s="106">
         <v>0.95</v>
       </c>
       <c r="I20" s="7">
@@ -10048,17 +10080,17 @@
       <c r="L20">
         <v>40</v>
       </c>
-      <c r="M20" s="65">
+      <c r="M20" s="64">
         <v>8.76</v>
       </c>
-      <c r="N20" s="66">
+      <c r="N20" s="65">
         <v>1</v>
       </c>
-      <c r="Q20" s="91" t="s">
+      <c r="Q20" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R20" s="101"/>
-      <c r="S20" s="91" t="str">
+      <c r="R20" s="99"/>
+      <c r="S20" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_PUSSI00"</f>
         <v>ELCCEGAS_PUSSI00</v>
       </c>
@@ -10066,22 +10098,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S20,2)&amp;" Pussi CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Pussi CHP - Natural Gas</v>
       </c>
-      <c r="U20" s="101" t="s">
+      <c r="U20" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V20" s="101" t="s">
+      <c r="V20" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W20" t="s">
         <v>116</v>
       </c>
-      <c r="X20" s="110"/>
-      <c r="Y20" s="110"/>
+      <c r="X20" s="108"/>
+      <c r="Y20" s="108"/>
       <c r="AA20"/>
       <c r="AB20"/>
     </row>
-    <row r="21" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="94" t="str">
+    <row r="21" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_ILMATSALU00</v>
       </c>
@@ -10089,7 +10121,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D21" s="94" t="str">
+      <c r="D21" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -10099,7 +10131,7 @@
       <c r="G21">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H21" s="108">
+      <c r="H21" s="106">
         <v>0.95</v>
       </c>
       <c r="I21" s="7">
@@ -10114,17 +10146,17 @@
       <c r="L21">
         <v>40</v>
       </c>
-      <c r="M21" s="65">
+      <c r="M21" s="64">
         <v>8.76</v>
       </c>
-      <c r="N21" s="66">
+      <c r="N21" s="65">
         <v>1</v>
       </c>
-      <c r="Q21" s="91" t="s">
+      <c r="Q21" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R21" s="101"/>
-      <c r="S21" s="91" t="str">
+      <c r="R21" s="99"/>
+      <c r="S21" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_ILMATSALU00"</f>
         <v>ELCCEBIO_ILMATSALU00</v>
       </c>
@@ -10132,22 +10164,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S21,2)&amp;" Ilmatsalu CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Ilmatsalu CHP - Biomass</v>
       </c>
-      <c r="U21" s="101" t="s">
+      <c r="U21" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V21" s="101" t="s">
+      <c r="V21" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W21" t="s">
         <v>116</v>
       </c>
-      <c r="X21" s="110"/>
-      <c r="Y21" s="110"/>
+      <c r="X21" s="108"/>
+      <c r="Y21" s="108"/>
       <c r="AA21"/>
       <c r="AB21"/>
     </row>
-    <row r="22" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="94" t="str">
+    <row r="22" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_VINNI00</v>
       </c>
@@ -10155,7 +10187,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D22" s="94" t="str">
+      <c r="D22" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -10165,7 +10197,7 @@
       <c r="G22">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H22" s="108">
+      <c r="H22" s="106">
         <v>0.95</v>
       </c>
       <c r="I22" s="7">
@@ -10180,17 +10212,17 @@
       <c r="L22">
         <v>40</v>
       </c>
-      <c r="M22" s="65">
+      <c r="M22" s="64">
         <v>8.76</v>
       </c>
-      <c r="N22" s="66">
+      <c r="N22" s="65">
         <v>1</v>
       </c>
-      <c r="Q22" s="91" t="s">
+      <c r="Q22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R22" s="101"/>
-      <c r="S22" s="91" t="str">
+      <c r="R22" s="99"/>
+      <c r="S22" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_VINNI00"</f>
         <v>ELCCEBIO_VINNI00</v>
       </c>
@@ -10198,22 +10230,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S22,2)&amp;" Vinni CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Vinni CHP - Biomass</v>
       </c>
-      <c r="U22" s="101" t="s">
+      <c r="U22" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V22" s="101" t="s">
+      <c r="V22" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W22" t="s">
         <v>116</v>
       </c>
-      <c r="X22" s="110"/>
-      <c r="Y22" s="110"/>
+      <c r="X22" s="108"/>
+      <c r="Y22" s="108"/>
       <c r="AA22"/>
       <c r="AB22"/>
     </row>
-    <row r="23" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="94" t="str">
+    <row r="23" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="92" t="str">
         <f>S23</f>
         <v>ELCCEBIO_OISU00</v>
       </c>
@@ -10221,7 +10253,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D23" s="94" t="str">
+      <c r="D23" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -10231,7 +10263,7 @@
       <c r="G23">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H23" s="108">
+      <c r="H23" s="106">
         <v>0.95</v>
       </c>
       <c r="I23" s="7">
@@ -10246,17 +10278,17 @@
       <c r="L23">
         <v>40</v>
       </c>
-      <c r="M23" s="65">
+      <c r="M23" s="64">
         <v>8.76</v>
       </c>
-      <c r="N23" s="66">
+      <c r="N23" s="65">
         <v>1</v>
       </c>
-      <c r="Q23" s="91" t="s">
+      <c r="Q23" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R23" s="101"/>
-      <c r="S23" s="91" t="str">
+      <c r="R23" s="99"/>
+      <c r="S23" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OISU00"</f>
         <v>ELCCEBIO_OISU00</v>
       </c>
@@ -10264,22 +10296,22 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S23,2)&amp;" Oisu CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Oisu CHP - Biomass</v>
       </c>
-      <c r="U23" s="101" t="s">
+      <c r="U23" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V23" s="101" t="s">
+      <c r="V23" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W23" t="s">
         <v>116</v>
       </c>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="110"/>
+      <c r="X23" s="108"/>
+      <c r="Y23" s="108"/>
       <c r="AA23"/>
       <c r="AB23"/>
     </row>
-    <row r="24" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="94" t="str">
+    <row r="24" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_RAKVERE00</v>
       </c>
@@ -10287,7 +10319,7 @@
         <f>$B$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)</f>
         <v>ELCBIO</v>
       </c>
-      <c r="D24" s="94" t="str">
+      <c r="D24" s="92" t="str">
         <f>ELC!$V$5</f>
         <v>ELCC</v>
       </c>
@@ -10297,32 +10329,32 @@
       <c r="G24">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H24" s="108">
+      <c r="H24" s="106">
         <v>0.95</v>
       </c>
       <c r="I24" s="7">
         <v>4516.7133000000003</v>
       </c>
-      <c r="J24" s="85">
+      <c r="J24" s="83">
         <v>162.96753257730003</v>
       </c>
-      <c r="K24" s="85">
+      <c r="K24" s="83">
         <v>2.8138000000000001</v>
       </c>
       <c r="L24">
         <v>40</v>
       </c>
-      <c r="M24" s="65">
+      <c r="M24" s="64">
         <v>8.76</v>
       </c>
-      <c r="N24" s="66">
+      <c r="N24" s="65">
         <v>1</v>
       </c>
-      <c r="Q24" s="91" t="s">
+      <c r="Q24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R24" s="101"/>
-      <c r="S24" s="91" t="str">
+      <c r="R24" s="99"/>
+      <c r="S24" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_RAKVERE00"</f>
         <v>ELCCEBIO_RAKVERE00</v>
       </c>
@@ -10330,358 +10362,358 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S24,2)&amp;" Rakvere CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Rakvere CHP - Biomass</v>
       </c>
-      <c r="U24" s="101" t="s">
+      <c r="U24" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="V24" s="101" t="s">
+      <c r="V24" s="99" t="s">
         <v>101</v>
       </c>
       <c r="W24" t="s">
         <v>116</v>
       </c>
-      <c r="X24" s="110"/>
-      <c r="Y24" s="110"/>
+      <c r="X24" s="108"/>
+      <c r="Y24" s="108"/>
       <c r="AA24"/>
       <c r="AB24"/>
     </row>
-    <row r="25" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="110"/>
-      <c r="G25" s="108"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
-      <c r="N25" s="109"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="91"/>
+    <row r="25" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="108"/>
+      <c r="G25" s="106"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="N25" s="107"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="89"/>
       <c r="T25"/>
-      <c r="U25" s="101"/>
-      <c r="V25" s="101"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
       <c r="W25"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="110"/>
+      <c r="X25" s="108"/>
+      <c r="Y25" s="108"/>
       <c r="AA25"/>
       <c r="AB25"/>
     </row>
-    <row r="26" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E26" s="110"/>
-      <c r="G26" s="108"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="N26" s="109"/>
-      <c r="Q26" s="91"/>
-      <c r="R26" s="101"/>
-      <c r="S26" s="91"/>
+    <row r="26" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="108"/>
+      <c r="G26" s="106"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="105"/>
+      <c r="N26" s="107"/>
+      <c r="Q26" s="89"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="89"/>
       <c r="T26"/>
-      <c r="U26" s="101"/>
-      <c r="V26" s="101"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
       <c r="W26"/>
-      <c r="X26" s="110"/>
-      <c r="Y26" s="110"/>
+      <c r="X26" s="108"/>
+      <c r="Y26" s="108"/>
       <c r="AA26"/>
       <c r="AB26"/>
     </row>
-    <row r="27" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G27" s="110"/>
-      <c r="I27" s="108"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="107"/>
-      <c r="P27" s="109"/>
-      <c r="S27" s="101"/>
-      <c r="T27" s="110"/>
-      <c r="U27" s="101"/>
-      <c r="V27" s="101"/>
-      <c r="W27" s="110"/>
-      <c r="X27" s="110"/>
-      <c r="Y27" s="110"/>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="110"/>
+    <row r="27" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="108"/>
+      <c r="I27" s="106"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="105"/>
+      <c r="P27" s="107"/>
+      <c r="S27" s="99"/>
+      <c r="T27" s="108"/>
+      <c r="U27" s="99"/>
+      <c r="V27" s="99"/>
+      <c r="W27" s="108"/>
+      <c r="X27" s="108"/>
+      <c r="Y27" s="108"/>
+      <c r="Z27" s="108"/>
+      <c r="AA27" s="108"/>
       <c r="AC27"/>
       <c r="AD27"/>
     </row>
-    <row r="28" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G28" s="110"/>
-      <c r="I28" s="108"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="107"/>
-      <c r="P28" s="109"/>
-      <c r="S28" s="101"/>
-      <c r="T28" s="110"/>
-      <c r="U28" s="101"/>
-      <c r="V28" s="101"/>
-      <c r="W28" s="110"/>
-      <c r="X28" s="110"/>
-      <c r="Y28" s="110"/>
-      <c r="Z28" s="110"/>
-      <c r="AA28" s="110"/>
+    <row r="28" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="108"/>
+      <c r="I28" s="106"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="105"/>
+      <c r="P28" s="107"/>
+      <c r="S28" s="99"/>
+      <c r="T28" s="108"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="99"/>
+      <c r="W28" s="108"/>
+      <c r="X28" s="108"/>
+      <c r="Y28" s="108"/>
+      <c r="Z28" s="108"/>
+      <c r="AA28" s="108"/>
       <c r="AC28"/>
       <c r="AD28"/>
     </row>
-    <row r="29" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G29" s="110"/>
-      <c r="I29" s="108"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="107"/>
-      <c r="P29" s="109"/>
-      <c r="S29" s="101"/>
-      <c r="T29" s="110"/>
-      <c r="U29" s="101"/>
-      <c r="V29" s="101"/>
-      <c r="W29" s="110"/>
-      <c r="X29" s="110"/>
-      <c r="Y29" s="110"/>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="110"/>
-    </row>
-    <row r="30" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G30" s="110"/>
-      <c r="I30" s="108"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="107"/>
-      <c r="M30" s="107"/>
-      <c r="P30" s="109"/>
-      <c r="S30" s="101"/>
-      <c r="T30" s="110"/>
-      <c r="U30" s="101"/>
-      <c r="V30" s="101"/>
-      <c r="W30" s="110"/>
-      <c r="X30" s="110"/>
-      <c r="Y30" s="110"/>
-      <c r="Z30" s="110"/>
-      <c r="AA30" s="110"/>
-    </row>
-    <row r="31" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G31" s="110"/>
-      <c r="I31" s="108"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="107"/>
-      <c r="P31" s="109"/>
-      <c r="S31" s="101"/>
-      <c r="T31" s="110"/>
-      <c r="U31" s="101"/>
-      <c r="V31" s="101"/>
-      <c r="W31" s="110"/>
-      <c r="X31" s="110"/>
-      <c r="Y31" s="110"/>
-      <c r="Z31" s="110"/>
-      <c r="AA31" s="110"/>
-    </row>
-    <row r="32" spans="2:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G32" s="110"/>
-      <c r="I32" s="108"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="107"/>
-      <c r="P32" s="109"/>
-      <c r="S32" s="101"/>
-      <c r="T32" s="110"/>
-      <c r="U32" s="101"/>
-      <c r="V32" s="101"/>
-      <c r="W32" s="110"/>
-      <c r="X32" s="110"/>
-      <c r="Y32" s="110"/>
-      <c r="Z32" s="110"/>
-      <c r="AA32" s="110"/>
-    </row>
-    <row r="33" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G33" s="110"/>
-      <c r="I33" s="108"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="107"/>
-      <c r="M33" s="107"/>
-      <c r="P33" s="109"/>
-      <c r="S33" s="101"/>
-      <c r="T33" s="110"/>
-      <c r="U33" s="101"/>
-      <c r="V33" s="101"/>
-      <c r="W33" s="110"/>
-      <c r="X33" s="110"/>
-      <c r="Y33" s="110"/>
-      <c r="Z33" s="110"/>
-      <c r="AA33" s="110"/>
-    </row>
-    <row r="34" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G34" s="110"/>
-      <c r="I34" s="108"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="107"/>
-      <c r="M34" s="107"/>
-      <c r="N34" s="110"/>
-      <c r="P34" s="110"/>
-      <c r="S34" s="101"/>
-      <c r="T34" s="110"/>
-      <c r="U34" s="110"/>
-      <c r="V34" s="110"/>
-      <c r="W34" s="110"/>
-      <c r="X34" s="110"/>
-      <c r="Y34" s="110"/>
-      <c r="Z34" s="110"/>
-      <c r="AA34" s="110"/>
-    </row>
-    <row r="35" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G35" s="110"/>
-      <c r="I35" s="108"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="107"/>
-      <c r="N35" s="110"/>
-      <c r="P35" s="110"/>
-      <c r="S35" s="101"/>
-      <c r="T35" s="110"/>
-      <c r="U35" s="110"/>
-      <c r="V35" s="110"/>
-      <c r="W35" s="110"/>
-      <c r="X35" s="110"/>
-      <c r="Y35" s="110"/>
-      <c r="Z35" s="110"/>
-      <c r="AA35" s="110"/>
-    </row>
-    <row r="36" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G36" s="110"/>
-      <c r="I36" s="108"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="107"/>
-      <c r="N36" s="110"/>
-      <c r="P36" s="110"/>
-      <c r="S36" s="101"/>
-      <c r="T36" s="110"/>
-      <c r="U36" s="110"/>
-      <c r="V36" s="110"/>
-      <c r="W36" s="110"/>
-      <c r="X36" s="110"/>
-      <c r="Y36" s="110"/>
-      <c r="Z36" s="110"/>
-      <c r="AA36" s="110"/>
-    </row>
-    <row r="37" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G37" s="110"/>
-      <c r="I37" s="108"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="107"/>
-      <c r="N37" s="110"/>
-      <c r="P37" s="110"/>
-      <c r="S37" s="101"/>
-      <c r="T37" s="110"/>
-      <c r="U37" s="110"/>
-      <c r="V37" s="110"/>
-      <c r="W37" s="110"/>
-      <c r="X37" s="110"/>
-      <c r="Y37" s="110"/>
-      <c r="Z37" s="110"/>
-      <c r="AA37" s="110"/>
-    </row>
-    <row r="38" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G38" s="110"/>
-      <c r="I38" s="108"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="107"/>
-      <c r="M38" s="107"/>
-      <c r="N38" s="110"/>
-      <c r="P38" s="110"/>
-      <c r="S38" s="101"/>
-      <c r="T38" s="110"/>
-      <c r="U38" s="110"/>
-      <c r="V38" s="110"/>
-      <c r="W38" s="110"/>
-      <c r="X38" s="110"/>
-      <c r="Y38" s="110"/>
-      <c r="Z38" s="110"/>
-      <c r="AA38" s="110"/>
-    </row>
-    <row r="39" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G39" s="110"/>
-      <c r="I39" s="108"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="107"/>
-      <c r="M39" s="107"/>
-      <c r="N39" s="110"/>
-      <c r="P39" s="110"/>
-      <c r="S39" s="101"/>
-      <c r="T39" s="110"/>
-      <c r="U39" s="110"/>
-      <c r="V39" s="110"/>
-      <c r="W39" s="110"/>
-      <c r="X39" s="110"/>
-      <c r="Y39" s="110"/>
-      <c r="Z39" s="110"/>
-      <c r="AA39" s="110"/>
-    </row>
-    <row r="40" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G40" s="110"/>
-      <c r="I40" s="108"/>
-      <c r="K40" s="106"/>
-      <c r="L40" s="107"/>
-      <c r="M40" s="107"/>
-      <c r="N40" s="110"/>
-      <c r="P40" s="110"/>
-      <c r="S40" s="101"/>
-      <c r="T40" s="110"/>
-      <c r="U40" s="110"/>
-      <c r="V40" s="110"/>
-      <c r="W40" s="110"/>
-      <c r="X40" s="110"/>
-      <c r="Y40" s="110"/>
-      <c r="Z40" s="110"/>
-      <c r="AA40" s="110"/>
-    </row>
-    <row r="41" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G41" s="110"/>
-      <c r="I41" s="108"/>
-      <c r="K41" s="106"/>
-      <c r="L41" s="107"/>
-      <c r="M41" s="107"/>
-      <c r="N41" s="110"/>
-      <c r="P41" s="110"/>
-      <c r="S41" s="101"/>
-      <c r="T41" s="110"/>
-      <c r="U41" s="110"/>
-      <c r="V41" s="110"/>
-      <c r="W41" s="110"/>
-      <c r="X41" s="110"/>
-      <c r="Y41" s="110"/>
-      <c r="Z41" s="110"/>
-      <c r="AA41" s="110"/>
-    </row>
-    <row r="42" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G42" s="110"/>
-      <c r="I42" s="108"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="107"/>
-      <c r="N42" s="110"/>
-      <c r="P42" s="110"/>
-      <c r="S42" s="101"/>
-      <c r="T42" s="110"/>
-      <c r="U42" s="110"/>
-      <c r="V42" s="110"/>
-      <c r="W42" s="110"/>
-      <c r="X42" s="110"/>
-      <c r="Y42" s="110"/>
-      <c r="Z42" s="110"/>
-      <c r="AA42" s="110"/>
-    </row>
-    <row r="43" spans="7:30" s="102" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="K43" s="111"/>
-      <c r="L43" s="111"/>
-      <c r="M43" s="111"/>
-      <c r="N43" s="111"/>
-      <c r="P43" s="110"/>
-      <c r="S43" s="101"/>
-      <c r="T43" s="110"/>
-      <c r="U43" s="110"/>
-      <c r="V43" s="110"/>
-      <c r="W43" s="110"/>
-      <c r="X43" s="110"/>
-      <c r="Y43" s="110"/>
-      <c r="Z43" s="110"/>
-      <c r="AA43" s="110"/>
+    <row r="29" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="108"/>
+      <c r="I29" s="106"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="105"/>
+      <c r="P29" s="107"/>
+      <c r="S29" s="99"/>
+      <c r="T29" s="108"/>
+      <c r="U29" s="99"/>
+      <c r="V29" s="99"/>
+      <c r="W29" s="108"/>
+      <c r="X29" s="108"/>
+      <c r="Y29" s="108"/>
+      <c r="Z29" s="108"/>
+      <c r="AA29" s="108"/>
+    </row>
+    <row r="30" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="108"/>
+      <c r="I30" s="106"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="105"/>
+      <c r="P30" s="107"/>
+      <c r="S30" s="99"/>
+      <c r="T30" s="108"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="99"/>
+      <c r="W30" s="108"/>
+      <c r="X30" s="108"/>
+      <c r="Y30" s="108"/>
+      <c r="Z30" s="108"/>
+      <c r="AA30" s="108"/>
+    </row>
+    <row r="31" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="108"/>
+      <c r="I31" s="106"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="P31" s="107"/>
+      <c r="S31" s="99"/>
+      <c r="T31" s="108"/>
+      <c r="U31" s="99"/>
+      <c r="V31" s="99"/>
+      <c r="W31" s="108"/>
+      <c r="X31" s="108"/>
+      <c r="Y31" s="108"/>
+      <c r="Z31" s="108"/>
+      <c r="AA31" s="108"/>
+    </row>
+    <row r="32" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="108"/>
+      <c r="I32" s="106"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="P32" s="107"/>
+      <c r="S32" s="99"/>
+      <c r="T32" s="108"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="99"/>
+      <c r="W32" s="108"/>
+      <c r="X32" s="108"/>
+      <c r="Y32" s="108"/>
+      <c r="Z32" s="108"/>
+      <c r="AA32" s="108"/>
+    </row>
+    <row r="33" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="108"/>
+      <c r="I33" s="106"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="P33" s="107"/>
+      <c r="S33" s="99"/>
+      <c r="T33" s="108"/>
+      <c r="U33" s="99"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="108"/>
+      <c r="X33" s="108"/>
+      <c r="Y33" s="108"/>
+      <c r="Z33" s="108"/>
+      <c r="AA33" s="108"/>
+    </row>
+    <row r="34" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="108"/>
+      <c r="I34" s="106"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="S34" s="99"/>
+      <c r="T34" s="108"/>
+      <c r="U34" s="108"/>
+      <c r="V34" s="108"/>
+      <c r="W34" s="108"/>
+      <c r="X34" s="108"/>
+      <c r="Y34" s="108"/>
+      <c r="Z34" s="108"/>
+      <c r="AA34" s="108"/>
+    </row>
+    <row r="35" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="108"/>
+      <c r="I35" s="106"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="S35" s="99"/>
+      <c r="T35" s="108"/>
+      <c r="U35" s="108"/>
+      <c r="V35" s="108"/>
+      <c r="W35" s="108"/>
+      <c r="X35" s="108"/>
+      <c r="Y35" s="108"/>
+      <c r="Z35" s="108"/>
+      <c r="AA35" s="108"/>
+    </row>
+    <row r="36" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="108"/>
+      <c r="I36" s="106"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="105"/>
+      <c r="M36" s="105"/>
+      <c r="N36" s="108"/>
+      <c r="P36" s="108"/>
+      <c r="S36" s="99"/>
+      <c r="T36" s="108"/>
+      <c r="U36" s="108"/>
+      <c r="V36" s="108"/>
+      <c r="W36" s="108"/>
+      <c r="X36" s="108"/>
+      <c r="Y36" s="108"/>
+      <c r="Z36" s="108"/>
+      <c r="AA36" s="108"/>
+    </row>
+    <row r="37" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="108"/>
+      <c r="I37" s="106"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="105"/>
+      <c r="N37" s="108"/>
+      <c r="P37" s="108"/>
+      <c r="S37" s="99"/>
+      <c r="T37" s="108"/>
+      <c r="U37" s="108"/>
+      <c r="V37" s="108"/>
+      <c r="W37" s="108"/>
+      <c r="X37" s="108"/>
+      <c r="Y37" s="108"/>
+      <c r="Z37" s="108"/>
+      <c r="AA37" s="108"/>
+    </row>
+    <row r="38" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="108"/>
+      <c r="I38" s="106"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="105"/>
+      <c r="M38" s="105"/>
+      <c r="N38" s="108"/>
+      <c r="P38" s="108"/>
+      <c r="S38" s="99"/>
+      <c r="T38" s="108"/>
+      <c r="U38" s="108"/>
+      <c r="V38" s="108"/>
+      <c r="W38" s="108"/>
+      <c r="X38" s="108"/>
+      <c r="Y38" s="108"/>
+      <c r="Z38" s="108"/>
+      <c r="AA38" s="108"/>
+    </row>
+    <row r="39" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="108"/>
+      <c r="I39" s="106"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="105"/>
+      <c r="N39" s="108"/>
+      <c r="P39" s="108"/>
+      <c r="S39" s="99"/>
+      <c r="T39" s="108"/>
+      <c r="U39" s="108"/>
+      <c r="V39" s="108"/>
+      <c r="W39" s="108"/>
+      <c r="X39" s="108"/>
+      <c r="Y39" s="108"/>
+      <c r="Z39" s="108"/>
+      <c r="AA39" s="108"/>
+    </row>
+    <row r="40" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="108"/>
+      <c r="I40" s="106"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="105"/>
+      <c r="N40" s="108"/>
+      <c r="P40" s="108"/>
+      <c r="S40" s="99"/>
+      <c r="T40" s="108"/>
+      <c r="U40" s="108"/>
+      <c r="V40" s="108"/>
+      <c r="W40" s="108"/>
+      <c r="X40" s="108"/>
+      <c r="Y40" s="108"/>
+      <c r="Z40" s="108"/>
+      <c r="AA40" s="108"/>
+    </row>
+    <row r="41" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="108"/>
+      <c r="I41" s="106"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
+      <c r="N41" s="108"/>
+      <c r="P41" s="108"/>
+      <c r="S41" s="99"/>
+      <c r="T41" s="108"/>
+      <c r="U41" s="108"/>
+      <c r="V41" s="108"/>
+      <c r="W41" s="108"/>
+      <c r="X41" s="108"/>
+      <c r="Y41" s="108"/>
+      <c r="Z41" s="108"/>
+      <c r="AA41" s="108"/>
+    </row>
+    <row r="42" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="108"/>
+      <c r="I42" s="106"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="105"/>
+      <c r="N42" s="108"/>
+      <c r="P42" s="108"/>
+      <c r="S42" s="99"/>
+      <c r="T42" s="108"/>
+      <c r="U42" s="108"/>
+      <c r="V42" s="108"/>
+      <c r="W42" s="108"/>
+      <c r="X42" s="108"/>
+      <c r="Y42" s="108"/>
+      <c r="Z42" s="108"/>
+      <c r="AA42" s="108"/>
+    </row>
+    <row r="43" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K43" s="109"/>
+      <c r="L43" s="109"/>
+      <c r="M43" s="109"/>
+      <c r="N43" s="109"/>
+      <c r="P43" s="108"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="108"/>
+      <c r="U43" s="108"/>
+      <c r="V43" s="108"/>
+      <c r="W43" s="108"/>
+      <c r="X43" s="108"/>
+      <c r="Y43" s="108"/>
+      <c r="Z43" s="108"/>
+      <c r="AA43" s="108"/>
       <c r="AC43" s="21"/>
       <c r="AD43" s="21"/>
     </row>
@@ -10699,7 +10731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:J24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10734,23 +10766,29 @@
       <c r="C5" s="33"/>
     </row>
     <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="37" t="str">
+      <c r="C6" s="36" t="str">
         <f>Sector_Fuels_ELC!$L$5</f>
         <v>ELCCOA</v>
       </c>
-      <c r="D6" s="37" t="str">
+      <c r="D6" s="36" t="str">
         <f>Sector_Fuels_ELC!$L$6</f>
         <v>ELCGAS</v>
       </c>
-      <c r="E6" s="37" t="str">
+      <c r="E6" s="36" t="str">
         <f>Sector_Fuels_ELC!$L$7</f>
         <v>ELCOIL</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="F6" s="36" t="str">
+        <f>Sector_Fuels_ELC!$L$16</f>
+        <v>ELCSHL</v>
+      </c>
+      <c r="G6" s="36" t="str">
+        <f>Sector_Fuels_ELC!$L$15</f>
+        <v>ELCMSW</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -10766,8 +10804,12 @@
       <c r="E7" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
+      <c r="F7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>141</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -10775,27 +10817,31 @@
         <f>ELC!$V$6</f>
         <v>ELCCO2</v>
       </c>
-      <c r="C8" s="64">
+      <c r="C8" s="63">
         <v>95</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="63">
         <v>56.1</v>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="63">
         <v>76.400000000000006</v>
       </c>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
+      <c r="F8" s="63">
+        <v>100</v>
+      </c>
+      <c r="G8" s="63">
+        <v>41.4</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="44"/>
+      <c r="B23" s="43"/>
       <c r="C23" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="60"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="1" t="s">
         <v>143</v>
       </c>
@@ -10803,5 +10849,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03520AE-64B2-4014-B4AF-177EAA8A7857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E6EBA0-8112-4F88-87F6-AE9F44E93B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -6328,6 +6328,26 @@
         <v>30</v>
       </c>
     </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B36" s="21" t="str">
+        <f>Sector_Fuels_ELC!L33</f>
+        <v>FTE-ELCSHL</v>
+      </c>
+      <c r="C36" t="str">
+        <f>RIGHT(D36,3)</f>
+        <v>SHL</v>
+      </c>
+      <c r="D36" s="21" t="str">
+        <f>L16</f>
+        <v>ELCSHL</v>
+      </c>
+      <c r="G36" s="61">
+        <v>1</v>
+      </c>
+      <c r="H36" s="62">
+        <v>30</v>
+      </c>
+    </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="43"/>
       <c r="C40" s="1" t="s">

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E6EBA0-8112-4F88-87F6-AE9F44E93B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8ABFC7-940E-4F98-9961-D9F6D0E6B299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1967,7 +1967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="196">
   <si>
     <t>CommName</t>
   </si>
@@ -2456,9 +2456,6 @@
   </si>
   <si>
     <t>AFA</t>
-  </si>
-  <si>
-    <t>ELCC</t>
   </si>
   <si>
     <t>PARNU</t>
@@ -4521,7 +4518,7 @@
         <v>146</v>
       </c>
       <c r="AA2" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB2" s="10" t="s">
         <v>68</v>
@@ -4577,10 +4574,10 @@
         <v>149</v>
       </c>
       <c r="R3" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="S3" s="40" t="s">
         <v>190</v>
-      </c>
-      <c r="S3" s="40" t="s">
-        <v>191</v>
       </c>
       <c r="T3" s="40" t="s">
         <v>150</v>
@@ -5073,112 +5070,112 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5523,10 +5520,10 @@
       </c>
       <c r="K12" s="89"/>
       <c r="L12" s="89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M12" s="90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N12" s="89" t="s">
         <v>68</v>
@@ -5546,10 +5543,10 @@
       </c>
       <c r="K13" s="89"/>
       <c r="L13" s="89" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M13" s="90" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N13" s="89" t="s">
         <v>68</v>
@@ -5595,10 +5592,10 @@
       </c>
       <c r="K15" s="89"/>
       <c r="L15" s="89" t="s">
+        <v>191</v>
+      </c>
+      <c r="M15" s="90" t="s">
         <v>192</v>
-      </c>
-      <c r="M15" s="90" t="s">
-        <v>193</v>
       </c>
       <c r="N15" s="89" t="s">
         <v>68</v>
@@ -5618,10 +5615,10 @@
       </c>
       <c r="K16" s="89"/>
       <c r="L16" s="89" t="s">
+        <v>194</v>
+      </c>
+      <c r="M16" s="90" t="s">
         <v>195</v>
-      </c>
-      <c r="M16" s="90" t="s">
-        <v>196</v>
       </c>
       <c r="N16" s="89" t="s">
         <v>68</v>
@@ -6560,7 +6557,7 @@
       </c>
       <c r="U5" s="89"/>
       <c r="V5" s="85" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="W5" s="85" t="str">
         <f>'EB1'!$W$3</f>
@@ -6826,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P11" s="13"/>
       <c r="R11" s="81" t="s">
@@ -6856,7 +6853,7 @@
       </c>
       <c r="D12" s="21" t="str">
         <f t="shared" ref="D12:D48" si="0">$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
@@ -6898,7 +6895,7 @@
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
       <c r="X12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y12" s="89" t="str">
         <f t="shared" ref="Y12" si="1">$F$2</f>
@@ -6921,7 +6918,7 @@
       </c>
       <c r="D13" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G13">
         <v>0.24199999999999999</v>
@@ -6962,7 +6959,7 @@
         <v>Power Plants Existing00 in PARNU - Solar energy</v>
       </c>
       <c r="X13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y13" t="s">
         <v>101</v>
@@ -6982,7 +6979,7 @@
       </c>
       <c r="D14" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G14">
         <v>0.108</v>
@@ -7024,7 +7021,7 @@
         <v>Power Plants Existing00 in TARTU - Solar energy</v>
       </c>
       <c r="X14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s">
         <v>101</v>
@@ -7045,7 +7042,7 @@
       </c>
       <c r="D15" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G15">
         <v>0.13200000000000001</v>
@@ -7087,7 +7084,7 @@
         <v>Power Plants Existing00 in LVIRU - Solar energy</v>
       </c>
       <c r="X15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s">
         <v>101</v>
@@ -7108,7 +7105,7 @@
       </c>
       <c r="D16" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G16">
         <v>7.8E-2</v>
@@ -7150,7 +7147,7 @@
         <v>Power Plants Existing00 in IVIRU - Solar energy</v>
       </c>
       <c r="X16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s">
         <v>101</v>
@@ -7171,7 +7168,7 @@
       </c>
       <c r="D17" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G17">
         <v>7.4999999999999997E-2</v>
@@ -7213,7 +7210,7 @@
         <v>Power Plants Existing00 in JARVA - Solar energy</v>
       </c>
       <c r="X17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s">
         <v>101</v>
@@ -7234,7 +7231,7 @@
       </c>
       <c r="D18" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G18">
         <v>4.7E-2</v>
@@ -7276,7 +7273,7 @@
         <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
       </c>
       <c r="X18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y18" t="s">
         <v>101</v>
@@ -7296,7 +7293,7 @@
       </c>
       <c r="D19" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G19">
         <v>0.04</v>
@@ -7337,7 +7334,7 @@
         <v>Power Plants Existing00 in HARJU - Solar energy</v>
       </c>
       <c r="X19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y19" t="s">
         <v>101</v>
@@ -7357,7 +7354,7 @@
       </c>
       <c r="D20" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G20">
         <v>0.24199999999999999</v>
@@ -7398,7 +7395,7 @@
         <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
       <c r="X20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y20" t="s">
         <v>101</v>
@@ -7418,7 +7415,7 @@
       </c>
       <c r="D21" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G21">
         <v>4.2999999999999997E-2</v>
@@ -7459,7 +7456,7 @@
         <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
       <c r="X21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y21" t="s">
         <v>101</v>
@@ -7479,7 +7476,7 @@
       </c>
       <c r="D22" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G22">
         <v>0.08</v>
@@ -7520,7 +7517,7 @@
         <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
       <c r="X22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y22" t="s">
         <v>101</v>
@@ -7540,7 +7537,7 @@
       </c>
       <c r="D23" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G23">
         <v>3.5000000000000003E-2</v>
@@ -7581,7 +7578,7 @@
         <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
       <c r="X23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y23" t="s">
         <v>101</v>
@@ -7601,7 +7598,7 @@
       </c>
       <c r="D24" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G24">
         <v>3.1E-2</v>
@@ -7642,7 +7639,7 @@
         <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
       <c r="X24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y24" t="s">
         <v>101</v>
@@ -7662,7 +7659,7 @@
       </c>
       <c r="D25" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G25">
         <v>2.9000000000000001E-2</v>
@@ -7703,7 +7700,7 @@
         <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
       <c r="X25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y25" t="s">
         <v>101</v>
@@ -7723,7 +7720,7 @@
       </c>
       <c r="D26" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G26">
         <v>0.01</v>
@@ -7764,7 +7761,7 @@
         <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
       <c r="X26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y26" t="s">
         <v>101</v>
@@ -7784,7 +7781,7 @@
       </c>
       <c r="D27" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G27">
         <v>5.0000000000000001E-3</v>
@@ -7825,7 +7822,7 @@
         <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
       <c r="X27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y27" t="s">
         <v>101</v>
@@ -7845,7 +7842,7 @@
       </c>
       <c r="D28" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G28">
         <v>7.9699999999999993E-2</v>
@@ -7886,7 +7883,7 @@
         <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
       </c>
       <c r="X28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y28" t="s">
         <v>101</v>
@@ -7906,7 +7903,7 @@
       </c>
       <c r="D29" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G29">
         <v>0.17519999999999999</v>
@@ -7947,7 +7944,7 @@
         <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
       </c>
       <c r="X29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y29" t="s">
         <v>101</v>
@@ -7967,7 +7964,7 @@
       </c>
       <c r="D30" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G30">
         <v>8.130000000000015E-2</v>
@@ -8008,7 +8005,7 @@
         <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
       </c>
       <c r="X30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y30" t="s">
         <v>101</v>
@@ -8028,7 +8025,7 @@
       </c>
       <c r="D31" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G31">
         <v>1.6E-2</v>
@@ -8069,7 +8066,7 @@
         <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
       </c>
       <c r="X31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s">
         <v>101</v>
@@ -8089,7 +8086,7 @@
       </c>
       <c r="D32" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G32">
         <v>3.27E-2</v>
@@ -8130,7 +8127,7 @@
         <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
       </c>
       <c r="X32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y32" t="s">
         <v>101</v>
@@ -8150,7 +8147,7 @@
       </c>
       <c r="D33" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G33">
         <v>6.3399999999999998E-2</v>
@@ -8191,7 +8188,7 @@
         <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
       </c>
       <c r="X33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y33" t="s">
         <v>101</v>
@@ -8211,7 +8208,7 @@
       </c>
       <c r="D34" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G34">
         <v>0.06</v>
@@ -8252,7 +8249,7 @@
         <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
       </c>
       <c r="X34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y34" t="s">
         <v>101</v>
@@ -8272,7 +8269,7 @@
       </c>
       <c r="D35" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G35">
         <v>8.2000000000000003E-2</v>
@@ -8313,7 +8310,7 @@
         <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
       </c>
       <c r="X35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y35" t="s">
         <v>101</v>
@@ -8333,7 +8330,7 @@
       </c>
       <c r="D36" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G36">
         <v>0.1036</v>
@@ -8374,7 +8371,7 @@
         <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
       </c>
       <c r="X36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y36" t="s">
         <v>101</v>
@@ -8394,7 +8391,7 @@
       </c>
       <c r="D37" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G37" s="21">
         <v>1.7000000000000001E-2</v>
@@ -8435,7 +8432,7 @@
         <v>Power Plants Existing00 Iru Power plant - Municipal waste</v>
       </c>
       <c r="X37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s">
         <v>101</v>
@@ -8455,7 +8452,7 @@
       </c>
       <c r="D38" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G38" s="21">
         <v>0.77</v>
@@ -8497,7 +8494,7 @@
         <v>Power Plants Existing00 Eesti Power plant - Oil Shale</v>
       </c>
       <c r="X38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y38" t="s">
         <v>101</v>
@@ -8517,7 +8514,7 @@
       </c>
       <c r="D39" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G39" s="21">
         <v>0.26</v>
@@ -8559,7 +8556,7 @@
         <v>Power Plants Existing00 Auvere Power plant - Oil Shale</v>
       </c>
       <c r="X39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y39" t="s">
         <v>101</v>
@@ -8579,7 +8576,7 @@
       </c>
       <c r="D40" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G40" s="21">
         <v>0.01</v>
@@ -8621,7 +8618,7 @@
         <v>Power Plants Existing00 Eenefit Power plant - Oil Shale</v>
       </c>
       <c r="X40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y40" t="s">
         <v>101</v>
@@ -8641,7 +8638,7 @@
       </c>
       <c r="D41" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G41" s="21">
         <v>0.185</v>
@@ -8683,7 +8680,7 @@
         <v>Power Plants Existing00 Balti Power plant - Oil Shale</v>
       </c>
       <c r="X41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y41" t="s">
         <v>101</v>
@@ -8703,7 +8700,7 @@
       </c>
       <c r="D42" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G42" s="21">
         <v>0.01</v>
@@ -8744,7 +8741,7 @@
         <v>Power Plants Existing00 Sillamae Power plant - Oil Shale</v>
       </c>
       <c r="X42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y42" t="s">
         <v>101</v>
@@ -8764,7 +8761,7 @@
       </c>
       <c r="D43" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G43" s="21">
         <v>7.6999999999999999E-2</v>
@@ -8806,7 +8803,7 @@
         <v>Power Plants Existing00 Pohja Power plant - Natural Gas</v>
       </c>
       <c r="X43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y43" t="s">
         <v>101</v>
@@ -8826,7 +8823,7 @@
       </c>
       <c r="D44" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G44" s="21">
         <v>3.9E-2</v>
@@ -8867,7 +8864,7 @@
         <v>Power Plants Existing00 Tallinn Utilitas Power plant - Biomass</v>
       </c>
       <c r="X44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y44" t="s">
         <v>101</v>
@@ -8887,7 +8884,7 @@
       </c>
       <c r="D45" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G45" s="21">
         <v>2.2100000000000002E-2</v>
@@ -8928,7 +8925,7 @@
         <v>Power Plants Existing00 Tartu Power plant - Biomass</v>
       </c>
       <c r="X45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y45" t="s">
         <v>101</v>
@@ -8948,7 +8945,7 @@
       </c>
       <c r="D46" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G46" s="21">
         <v>2.0500000000000001E-2</v>
@@ -8989,7 +8986,7 @@
         <v>Power Plants Existing00 Parnu Power plant - Biomass</v>
       </c>
       <c r="X46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y46" t="s">
         <v>101</v>
@@ -9009,7 +9006,7 @@
       </c>
       <c r="D47" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G47" s="21">
         <v>1.3900000000000001E-2</v>
@@ -9050,7 +9047,7 @@
         <v>Power Plants Existing00 Horizon Power plant - Biomass</v>
       </c>
       <c r="X47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y47" t="s">
         <v>101</v>
@@ -9070,7 +9067,7 @@
       </c>
       <c r="D48" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="G48" s="21">
         <v>4.0999999999999995E-3</v>
@@ -9111,7 +9108,7 @@
         <v>Power Plants Existing00 GRUNE Power plant - Natural Gas</v>
       </c>
       <c r="X48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y48" t="s">
         <v>101</v>
@@ -9506,7 +9503,7 @@
         <v>77</v>
       </c>
       <c r="M11" s="101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N11" s="101"/>
       <c r="P11" s="28"/>
@@ -9535,7 +9532,7 @@
       </c>
       <c r="D12" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E12">
         <v>0.01</v>
@@ -9579,7 +9576,7 @@
         <v>Power Plants Existing00 Osula CHP - Biomass</v>
       </c>
       <c r="U12" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V12" s="99" t="s">
         <v>101</v>
@@ -9603,7 +9600,7 @@
       </c>
       <c r="D13" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E13">
         <v>9.300000000000001E-3</v>
@@ -9647,7 +9644,7 @@
         <v>Power Plants Existing00 Mustamae CHP - Biomass</v>
       </c>
       <c r="U13" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V13" s="99" t="s">
         <v>101</v>
@@ -9671,7 +9668,7 @@
       </c>
       <c r="D14" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E14">
         <v>7.0999999999999995E-3</v>
@@ -9715,7 +9712,7 @@
         <v>Power Plants Existing00 Sillamae 1 CHP - Biomass</v>
       </c>
       <c r="U14" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V14" s="99" t="s">
         <v>101</v>
@@ -9739,7 +9736,7 @@
       </c>
       <c r="D15" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E15">
         <v>5.7999999999999996E-3</v>
@@ -9783,7 +9780,7 @@
         <v>Power Plants Existing00 Sillamae 2 CHP - Natural Gas</v>
       </c>
       <c r="U15" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V15" s="99" t="s">
         <v>101</v>
@@ -9807,7 +9804,7 @@
       </c>
       <c r="D16" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E16">
         <v>6.4999999999999997E-3</v>
@@ -9851,7 +9848,7 @@
         <v>Power Plants Existing00 Helme CHP - Biomass</v>
       </c>
       <c r="U16" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V16" s="99" t="s">
         <v>101</v>
@@ -9875,7 +9872,7 @@
       </c>
       <c r="D17" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E17">
         <v>1.8E-3</v>
@@ -9919,7 +9916,7 @@
         <v>Power Plants Existing00 Kuressaare CHP - Biomass</v>
       </c>
       <c r="U17" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V17" s="99" t="s">
         <v>101</v>
@@ -9943,7 +9940,7 @@
       </c>
       <c r="D18" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E18">
         <v>1.6999999999999999E-3</v>
@@ -9987,7 +9984,7 @@
         <v>Power Plants Existing00 Paide CHP - Biomass</v>
       </c>
       <c r="U18" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V18" s="99" t="s">
         <v>101</v>
@@ -10011,7 +10008,7 @@
       </c>
       <c r="D19" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E19">
         <v>1.8E-3</v>
@@ -10053,7 +10050,7 @@
         <v>Power Plants Existing00 Jamejala CHP - Natural Gas</v>
       </c>
       <c r="U19" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V19" s="99" t="s">
         <v>101</v>
@@ -10077,7 +10074,7 @@
       </c>
       <c r="D20" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E20">
         <v>1.8E-3</v>
@@ -10119,7 +10116,7 @@
         <v>Power Plants Existing00 Pussi CHP - Natural Gas</v>
       </c>
       <c r="U20" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V20" s="99" t="s">
         <v>101</v>
@@ -10143,7 +10140,7 @@
       </c>
       <c r="D21" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E21">
         <v>1.5E-3</v>
@@ -10185,7 +10182,7 @@
         <v>Power Plants Existing00 Ilmatsalu CHP - Biomass</v>
       </c>
       <c r="U21" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V21" s="99" t="s">
         <v>101</v>
@@ -10209,7 +10206,7 @@
       </c>
       <c r="D22" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E22">
         <v>1.4E-3</v>
@@ -10251,7 +10248,7 @@
         <v>Power Plants Existing00 Vinni CHP - Biomass</v>
       </c>
       <c r="U22" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V22" s="99" t="s">
         <v>101</v>
@@ -10275,7 +10272,7 @@
       </c>
       <c r="D23" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E23">
         <v>1.1999999999999999E-3</v>
@@ -10317,7 +10314,7 @@
         <v>Power Plants Existing00 Oisu CHP - Biomass</v>
       </c>
       <c r="U23" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V23" s="99" t="s">
         <v>101</v>
@@ -10341,7 +10338,7 @@
       </c>
       <c r="D24" s="92" t="str">
         <f>ELC!$V$5</f>
-        <v>ELCC</v>
+        <v>ELC</v>
       </c>
       <c r="E24">
         <v>8.9999999999999998E-4</v>
@@ -10383,7 +10380,7 @@
         <v>Power Plants Existing00 Rakvere CHP - Biomass</v>
       </c>
       <c r="U24" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V24" s="99" t="s">
         <v>101</v>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8ABFC7-940E-4F98-9961-D9F6D0E6B299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D19DA-9F10-4BFF-839A-165D5F18F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -19,9 +19,11 @@
     <sheet name="ELC" sheetId="143" r:id="rId4"/>
     <sheet name="CHP" sheetId="151" r:id="rId5"/>
     <sheet name="Emi" sheetId="149" r:id="rId6"/>
+    <sheet name="TOTCO2" sheetId="152" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -1966,8 +1968,319 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gary Goldstein</author>
+    <author>Amit Kanudia</author>
+    <author>Maurizio Gargiulo</author>
+  </authors>
+  <commentList>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{B80C0A32-9BAB-467C-A52E-A3D5F8071DF6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
+Allowed Cset:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NRG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Energy)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ENV</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Emission)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DEM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>MAT</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Material)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIN</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Financial)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{1BF15F39-25A1-4915-939C-3CD63DDA4131}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+LO for PRODUCTION &gt;= CONSUMPTION (Default)
+FX for PRODUCTION = CONSUMPTION
+UP for PRODUCTION &lt;= CONSUMPTION</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="2" shapeId="0" xr:uid="{6AEF663A-72C5-451F-846F-204EA9232134}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed CTSLvl</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="2" shapeId="0" xr:uid="{C47A33E3-F10F-41FB-8D28-B632D3DFA5DE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed PeakTS</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ANNUAL </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for all the TimeSlices)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+User TS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for a single TS)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J10" authorId="2" shapeId="0" xr:uid="{821CB189-F643-4165-98CA-7DAA1583205B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed Ctype
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ELC</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Electricity)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="205">
   <si>
     <t>CommName</t>
   </si>
@@ -2555,6 +2868,33 @@
   </si>
   <si>
     <t>Electricity Plants Oil Shale</t>
+  </si>
+  <si>
+    <t>~COMAGG</t>
+  </si>
+  <si>
+    <t>AGRCO2</t>
+  </si>
+  <si>
+    <t>COMCO2</t>
+  </si>
+  <si>
+    <t>RSDCO2</t>
+  </si>
+  <si>
+    <t>ELCCO2</t>
+  </si>
+  <si>
+    <t>TRACO2</t>
+  </si>
+  <si>
+    <t>INDCO2</t>
+  </si>
+  <si>
+    <t>TOTCO2</t>
+  </si>
+  <si>
+    <t>Total CO2</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2909,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2745,14 +3085,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2841,6 +3175,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3079,7 +3419,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="30">
+  <cellStyleXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3110,8 +3450,9 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3305,18 +3646,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3326,14 +3662,17 @@
     <xf numFmtId="168" fontId="20" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="30">
+  <cellStyles count="31">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
     <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
     <cellStyle name="Accent2" xfId="3" builtinId="33"/>
@@ -3341,6 +3680,7 @@
     <cellStyle name="Comma 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Good" xfId="6" builtinId="26"/>
     <cellStyle name="Input" xfId="7" builtinId="20"/>
+    <cellStyle name="Migliaia_tab emissioni" xfId="30" xr:uid="{68D37FEC-E0B2-4C94-81BB-226DC57F7266}"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
@@ -3921,6 +4261,150 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>14653</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>153866</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA02594B-3B5C-4362-9FC5-B674C592FA9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2552700"/>
+          <a:ext cx="5062903" cy="639641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>~COMAGG </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>is used to define an aggregated commodity, TOTCO2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>in this example, multiplying the sectoral</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> emissions by a coefficient 1 (cells C1:H1). It is possible to add more aggregated commodities and change multipliers.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -4051,6 +4535,49 @@
       <sheetData sheetId="56"/>
       <sheetData sheetId="57"/>
       <sheetData sheetId="58"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EB1"/>
+      <sheetName val="RES_PRI"/>
+      <sheetName val="Pri_COA"/>
+      <sheetName val="Pri_GAS"/>
+      <sheetName val="Pri_OIL"/>
+      <sheetName val="Pri_NUC"/>
+      <sheetName val="Pri_RNW"/>
+      <sheetName val="Pri_PP"/>
+      <sheetName val="Pri_ELC"/>
+      <sheetName val="Con_REF"/>
+      <sheetName val="TOTCO2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="AA2" t="str">
+            <v>kt</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5803,19 +6330,19 @@
       </c>
       <c r="K22" s="92"/>
       <c r="L22" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <f t="shared" ref="L22:L33" si="1">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-ELCCOA</v>
       </c>
       <c r="M22" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <f t="shared" ref="M22:M33" si="2">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
       <c r="N22" s="89" t="str">
-        <f t="shared" ref="N22:N33" si="1">$E$2</f>
+        <f t="shared" ref="N22:N33" si="3">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O22" s="89" t="str">
-        <f t="shared" ref="O22:O33" si="2">$E$2&amp;"a"</f>
+        <f t="shared" ref="O22:O33" si="4">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P22" s="89"/>
@@ -5848,19 +6375,19 @@
       </c>
       <c r="K23" s="92"/>
       <c r="L23" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCGAS</v>
       </c>
       <c r="M23" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
       </c>
       <c r="N23" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O23" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P23" s="89"/>
@@ -5896,19 +6423,19 @@
       </c>
       <c r="K24" s="92"/>
       <c r="L24" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCOIL</v>
       </c>
       <c r="M24" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants oil</v>
       </c>
       <c r="N24" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O24" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P24" s="89"/>
@@ -5934,19 +6461,19 @@
       </c>
       <c r="K25" s="89"/>
       <c r="L25" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCNUC</v>
       </c>
       <c r="M25" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
       </c>
       <c r="N25" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O25" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P25" s="89"/>
@@ -5972,19 +6499,19 @@
       </c>
       <c r="K26" s="89"/>
       <c r="L26" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCBIO</v>
       </c>
       <c r="M26" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
       </c>
       <c r="N26" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O26" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P26" s="89"/>
@@ -6010,19 +6537,19 @@
       </c>
       <c r="K27" s="89"/>
       <c r="L27" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCHYD</v>
       </c>
       <c r="M27" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
       </c>
       <c r="N27" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O27" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P27" s="89"/>
@@ -6039,7 +6566,7 @@
         <v>NUC</v>
       </c>
       <c r="D28" s="21" t="str">
-        <f>L8</f>
+        <f t="shared" ref="D28:D36" si="5">L8</f>
         <v>ELCNUC</v>
       </c>
       <c r="E28" s="12"/>
@@ -6055,26 +6582,26 @@
       </c>
       <c r="K28" s="89"/>
       <c r="L28" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCWIN</v>
       </c>
       <c r="M28" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
       </c>
       <c r="N28" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O28" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P28" s="89"/>
       <c r="Q28" s="89"/>
       <c r="R28" s="89"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
         <f>Sector_Fuels_ELC!L26</f>
         <v>FTE-ELCBIO</v>
@@ -6084,7 +6611,7 @@
         <v>BIO</v>
       </c>
       <c r="D29" s="21" t="str">
-        <f>L9</f>
+        <f t="shared" si="5"/>
         <v>ELCBIO</v>
       </c>
       <c r="E29" s="12"/>
@@ -6100,26 +6627,26 @@
       </c>
       <c r="K29" s="89"/>
       <c r="L29" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCWON</v>
       </c>
       <c r="M29" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Wind Onshore energy</v>
       </c>
       <c r="N29" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O29" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
       <c r="P29" s="89"/>
       <c r="Q29" s="89"/>
       <c r="R29" s="89"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
         <f>Sector_Fuels_ELC!L27</f>
         <v>FTE-ELCHYD</v>
@@ -6129,7 +6656,7 @@
         <v>HYD</v>
       </c>
       <c r="D30" s="21" t="str">
-        <f>L10</f>
+        <f t="shared" si="5"/>
         <v>ELCHYD</v>
       </c>
       <c r="E30" s="12"/>
@@ -6145,19 +6672,19 @@
       </c>
       <c r="K30" s="89"/>
       <c r="L30" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L13</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCWOF</v>
       </c>
       <c r="M30" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M13</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Wind Offshore energy</v>
       </c>
       <c r="N30" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O30" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
     </row>
@@ -6171,7 +6698,7 @@
         <v>WIN</v>
       </c>
       <c r="D31" s="21" t="str">
-        <f>L11</f>
+        <f t="shared" si="5"/>
         <v>ELCWIN</v>
       </c>
       <c r="E31" s="12"/>
@@ -6187,19 +6714,19 @@
       </c>
       <c r="K31" s="89"/>
       <c r="L31" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L14</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCSOL</v>
       </c>
       <c r="M31" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M14</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
       </c>
       <c r="N31" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O31" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
     </row>
@@ -6212,7 +6739,7 @@
         <v>152</v>
       </c>
       <c r="D32" s="21" t="str">
-        <f>L12</f>
+        <f t="shared" si="5"/>
         <v>ELCWON</v>
       </c>
       <c r="E32" s="12"/>
@@ -6227,19 +6754,19 @@
         <v>95</v>
       </c>
       <c r="L32" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L15</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCMSW</v>
       </c>
       <c r="M32" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M15</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Municipal Waste</v>
       </c>
       <c r="N32" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O32" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
     </row>
@@ -6252,7 +6779,7 @@
         <v>152</v>
       </c>
       <c r="D33" s="21" t="str">
-        <f>L13</f>
+        <f t="shared" si="5"/>
         <v>ELCWOF</v>
       </c>
       <c r="E33" s="12"/>
@@ -6267,19 +6794,19 @@
         <v>95</v>
       </c>
       <c r="L33" s="89" t="str">
-        <f>"FT"&amp;$G$2&amp;"-"&amp;L16</f>
+        <f t="shared" si="1"/>
         <v>FTE-ELCSHL</v>
       </c>
       <c r="M33" s="90" t="str">
-        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M16</f>
+        <f t="shared" si="2"/>
         <v>Sector Fuel Technology Existing Electricity Plants Oil Shale</v>
       </c>
       <c r="N33" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="O33" s="89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PJa</v>
       </c>
     </row>
@@ -6293,7 +6820,7 @@
         <v>SOL</v>
       </c>
       <c r="D34" s="21" t="str">
-        <f>L14</f>
+        <f t="shared" si="5"/>
         <v>ELCSOL</v>
       </c>
       <c r="E34" s="12"/>
@@ -6315,7 +6842,7 @@
         <v>MSW</v>
       </c>
       <c r="D35" s="21" t="str">
-        <f>L15</f>
+        <f t="shared" si="5"/>
         <v>ELCMSW</v>
       </c>
       <c r="G35" s="61">
@@ -6335,7 +6862,7 @@
         <v>SHL</v>
       </c>
       <c r="D36" s="21" t="str">
-        <f>L16</f>
+        <f t="shared" si="5"/>
         <v>ELCSHL</v>
       </c>
       <c r="G36" s="61">
@@ -6367,7 +6894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AB65529"/>
+  <dimension ref="B1:AB65529"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -6398,7 +6925,7 @@
     <col min="29" max="16384" width="8.85546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>65</v>
       </c>
@@ -6421,7 +6948,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -6459,7 +6986,7 @@
       <c r="AA2" s="85"/>
       <c r="AB2" s="85"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T3" s="86" t="s">
         <v>7</v>
       </c>
@@ -6488,7 +7015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:28" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>107</v>
       </c>
@@ -6534,7 +7061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
@@ -6576,7 +7103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T6" s="89" t="s">
         <v>88</v>
       </c>
@@ -6598,11 +7125,11 @@
       <c r="AA6" s="89"/>
       <c r="AB6" s="89"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -6626,7 +7153,7 @@
       <c r="AA8" s="85"/>
       <c r="AB8" s="85"/>
     </row>
-    <row r="9" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -6705,7 +7232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -6783,7 +7310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -6842,7 +7369,7 @@
       <c r="AA11" s="88"/>
       <c r="AB11" s="88"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B12" s="21" t="str">
         <f>V12</f>
         <v>ELCREHYD00</v>
@@ -6907,7 +7434,7 @@
       <c r="AA12" s="89"/>
       <c r="AB12" s="89"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
         <f>V13</f>
         <v>ELCRESOL_PARNU00</v>
@@ -6923,7 +7450,7 @@
       <c r="G13">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I13" s="94">
+      <c r="I13" s="93">
         <v>1</v>
       </c>
       <c r="J13" s="63">
@@ -6968,7 +7495,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B14" s="21" t="str">
         <f t="shared" ref="B14:B37" si="2">V14</f>
         <v>ELCRESOL_TARTU00</v>
@@ -6984,7 +7511,7 @@
       <c r="G14">
         <v>0.108</v>
       </c>
-      <c r="I14" s="94">
+      <c r="I14" s="93">
         <v>1</v>
       </c>
       <c r="J14" s="63">
@@ -7030,8 +7557,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="93"/>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B15" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_LVIRU00</v>
@@ -7047,7 +7573,7 @@
       <c r="G15">
         <v>0.13200000000000001</v>
       </c>
-      <c r="I15" s="94">
+      <c r="I15" s="93">
         <v>1</v>
       </c>
       <c r="J15" s="63">
@@ -7093,8 +7619,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="93"/>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B16" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_IVIRU00</v>
@@ -7110,7 +7635,7 @@
       <c r="G16">
         <v>7.8E-2</v>
       </c>
-      <c r="I16" s="94">
+      <c r="I16" s="93">
         <v>1</v>
       </c>
       <c r="J16" s="63">
@@ -7156,8 +7681,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="93"/>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B17" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JARVA00</v>
@@ -7173,7 +7697,7 @@
       <c r="G17">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I17" s="94">
+      <c r="I17" s="93">
         <v>1</v>
       </c>
       <c r="J17" s="63">
@@ -7219,8 +7743,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="93"/>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JOGEVA00</v>
@@ -7236,7 +7759,7 @@
       <c r="G18">
         <v>4.7E-2</v>
       </c>
-      <c r="I18" s="94">
+      <c r="I18" s="93">
         <v>1</v>
       </c>
       <c r="J18" s="63">
@@ -7282,7 +7805,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_HARJU00</v>
@@ -7298,7 +7821,7 @@
       <c r="G19">
         <v>0.04</v>
       </c>
-      <c r="I19" s="94">
+      <c r="I19" s="93">
         <v>1</v>
       </c>
       <c r="J19" s="63">
@@ -7343,7 +7866,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_POLVA00</v>
@@ -7359,7 +7882,7 @@
       <c r="G20">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I20" s="94">
+      <c r="I20" s="93">
         <v>1</v>
       </c>
       <c r="J20" s="63">
@@ -7404,7 +7927,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B21" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VALGA00</v>
@@ -7420,7 +7943,7 @@
       <c r="G21">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I21" s="94">
+      <c r="I21" s="93">
         <v>1</v>
       </c>
       <c r="J21" s="63">
@@ -7465,7 +7988,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VILJANDI00</v>
@@ -7481,7 +8004,7 @@
       <c r="G22">
         <v>0.08</v>
       </c>
-      <c r="I22" s="94">
+      <c r="I22" s="93">
         <v>1</v>
       </c>
       <c r="J22" s="63">
@@ -7526,7 +8049,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VORU00</v>
@@ -7542,7 +8065,7 @@
       <c r="G23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I23" s="94">
+      <c r="I23" s="93">
         <v>1</v>
       </c>
       <c r="J23" s="63">
@@ -7587,7 +8110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_SAARE00</v>
@@ -7603,7 +8126,7 @@
       <c r="G24">
         <v>3.1E-2</v>
       </c>
-      <c r="I24" s="94">
+      <c r="I24" s="93">
         <v>1</v>
       </c>
       <c r="J24" s="63">
@@ -7648,7 +8171,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B25" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_RAPLA00</v>
@@ -7664,7 +8187,7 @@
       <c r="G25">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I25" s="94">
+      <c r="I25" s="93">
         <v>1</v>
       </c>
       <c r="J25" s="63">
@@ -7709,7 +8232,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_LAANE00</v>
@@ -7725,7 +8248,7 @@
       <c r="G26">
         <v>0.01</v>
       </c>
-      <c r="I26" s="94">
+      <c r="I26" s="93">
         <v>1</v>
       </c>
       <c r="J26" s="63">
@@ -7770,7 +8293,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_HIIU00</v>
@@ -7786,7 +8309,7 @@
       <c r="G27">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="94">
+      <c r="I27" s="93">
         <v>1</v>
       </c>
       <c r="J27" s="63">
@@ -7831,7 +8354,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SOPITOOTSI00</v>
@@ -7847,7 +8370,7 @@
       <c r="G28">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="I28" s="94">
+      <c r="I28" s="93">
         <v>1</v>
       </c>
       <c r="J28" s="63">
@@ -7892,7 +8415,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SOPIPURTSE00</v>
@@ -7908,7 +8431,7 @@
       <c r="G29">
         <v>0.17519999999999999</v>
       </c>
-      <c r="I29" s="94">
+      <c r="I29" s="93">
         <v>1</v>
       </c>
       <c r="J29" s="63">
@@ -7953,7 +8476,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_OTHER00</v>
@@ -7969,7 +8492,7 @@
       <c r="G30">
         <v>8.130000000000015E-2</v>
       </c>
-      <c r="I30" s="94">
+      <c r="I30" s="93">
         <v>1</v>
       </c>
       <c r="J30" s="63">
@@ -8014,7 +8537,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SAARE00</v>
@@ -8030,7 +8553,7 @@
       <c r="G31">
         <v>1.6E-2</v>
       </c>
-      <c r="I31" s="94">
+      <c r="I31" s="93">
         <v>1</v>
       </c>
       <c r="J31" s="63">
@@ -8075,7 +8598,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_LVIRU00</v>
@@ -8091,7 +8614,7 @@
       <c r="G32">
         <v>3.27E-2</v>
       </c>
-      <c r="I32" s="94">
+      <c r="I32" s="93">
         <v>1</v>
       </c>
       <c r="J32" s="63">
@@ -8152,7 +8675,7 @@
       <c r="G33">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="I33" s="94">
+      <c r="I33" s="93">
         <v>1</v>
       </c>
       <c r="J33" s="63">
@@ -8213,7 +8736,7 @@
       <c r="G34">
         <v>0.06</v>
       </c>
-      <c r="I34" s="94">
+      <c r="I34" s="93">
         <v>1</v>
       </c>
       <c r="J34" s="63">
@@ -8274,7 +8797,7 @@
       <c r="G35">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="I35" s="94">
+      <c r="I35" s="93">
         <v>1</v>
       </c>
       <c r="J35" s="63">
@@ -8335,7 +8858,7 @@
       <c r="G36">
         <v>0.1036</v>
       </c>
-      <c r="I36" s="94">
+      <c r="I36" s="93">
         <v>1</v>
       </c>
       <c r="J36" s="63">
@@ -9212,26 +9735,26 @@
       <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="96"/>
-      <c r="W2" s="96"/>
-      <c r="X2" s="96"/>
-      <c r="Y2" s="96"/>
-      <c r="Z2" s="96"/>
-      <c r="AA2" s="96"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="97"/>
-      <c r="Y3" s="97"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="94"/>
+      <c r="V3" s="94"/>
+      <c r="W3" s="94"/>
+      <c r="X3" s="94"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="4" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
@@ -9251,15 +9774,15 @@
       </c>
       <c r="H4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="95"/>
+      <c r="U4" s="95"/>
+      <c r="V4" s="95"/>
+      <c r="W4" s="95"/>
+      <c r="X4" s="95"/>
+      <c r="Y4" s="95"/>
+      <c r="Z4" s="95"/>
+      <c r="AA4" s="95"/>
     </row>
     <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
@@ -9279,26 +9802,26 @@
       </c>
       <c r="H5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="S6" s="99"/>
-      <c r="T6" s="99"/>
-      <c r="U6" s="99"/>
-      <c r="V6" s="99"/>
-      <c r="W6" s="99"/>
-      <c r="X6" s="99"/>
-      <c r="Y6" s="99"/>
-      <c r="Z6" s="99"/>
-      <c r="AA6" s="99"/>
+      <c r="S6" s="89"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="89"/>
+      <c r="W6" s="89"/>
+      <c r="X6" s="89"/>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.2">
       <c r="S7" s="2"/>
@@ -9477,51 +10000,51 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="101" t="str">
+      <c r="E11" s="96" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="F11" s="102" t="str">
+      <c r="F11" s="97" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="G11" s="101"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="101" t="str">
+      <c r="G11" s="96"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="96" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
-      <c r="J11" s="101" t="str">
+      <c r="J11" s="96" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
-      <c r="K11" s="101" t="str">
+      <c r="K11" s="96" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2025/PJ</v>
       </c>
-      <c r="L11" s="101" t="s">
+      <c r="L11" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="101" t="s">
+      <c r="M11" s="96" t="s">
         <v>193</v>
       </c>
-      <c r="N11" s="101"/>
+      <c r="N11" s="96"/>
       <c r="P11" s="28"/>
-      <c r="Q11" s="103" t="s">
+      <c r="Q11" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="R11" s="103"/>
-      <c r="S11" s="103"/>
-      <c r="T11" s="103"/>
-      <c r="U11" s="103"/>
-      <c r="V11" s="103"/>
-      <c r="W11" s="103"/>
-      <c r="X11" s="103"/>
-      <c r="Y11" s="103"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
       <c r="Z11" s="21"/>
       <c r="AA11" s="21"/>
     </row>
-    <row r="12" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B12" s="92" t="str">
         <f>S12</f>
         <v>ELCCEBIO_OSULA00</v>
@@ -9537,11 +10060,11 @@
       <c r="E12">
         <v>0.01</v>
       </c>
-      <c r="F12" s="105"/>
+      <c r="F12" s="83"/>
       <c r="G12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H12" s="106">
+      <c r="H12" s="93">
         <v>0.95</v>
       </c>
       <c r="I12" s="7">
@@ -9566,7 +10089,7 @@
       <c r="Q12" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R12" s="99"/>
+      <c r="R12" s="89"/>
       <c r="S12" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OSULA00"</f>
         <v>ELCCEBIO_OSULA00</v>
@@ -9575,21 +10098,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S12,2)&amp;" Osula CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Osula CHP - Biomass</v>
       </c>
-      <c r="U12" s="99" t="s">
+      <c r="U12" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V12" s="99" t="s">
+      <c r="V12" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W12" t="s">
         <v>116</v>
       </c>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="99"/>
-      <c r="AA12"/>
+      <c r="X12" s="89"/>
+      <c r="Y12" s="89"/>
+      <c r="Z12" s="21"/>
       <c r="AB12"/>
     </row>
-    <row r="13" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B13" s="92" t="str">
         <f t="shared" ref="B13:B24" si="0">S13</f>
         <v>ELCCEBIO_MUSTAMAE00</v>
@@ -9605,11 +10128,11 @@
       <c r="E13">
         <v>9.300000000000001E-3</v>
       </c>
-      <c r="F13" s="105"/>
+      <c r="F13" s="83"/>
       <c r="G13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H13" s="106">
+      <c r="H13" s="93">
         <v>0.95</v>
       </c>
       <c r="I13" s="7">
@@ -9634,7 +10157,7 @@
       <c r="Q13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R13" s="99"/>
+      <c r="R13" s="89"/>
       <c r="S13" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_MUSTAMAE00"</f>
         <v>ELCCEBIO_MUSTAMAE00</v>
@@ -9643,21 +10166,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S13,2)&amp;" Mustamae CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Mustamae CHP - Biomass</v>
       </c>
-      <c r="U13" s="99" t="s">
+      <c r="U13" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V13" s="99" t="s">
+      <c r="V13" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W13" t="s">
         <v>116</v>
       </c>
-      <c r="X13" s="99"/>
-      <c r="Y13" s="99"/>
-      <c r="AA13"/>
+      <c r="X13" s="89"/>
+      <c r="Y13" s="89"/>
+      <c r="Z13" s="21"/>
       <c r="AB13"/>
     </row>
-    <row r="14" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B14" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_SILLAMAE100</v>
@@ -9673,11 +10196,11 @@
       <c r="E14">
         <v>7.0999999999999995E-3</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="7"/>
       <c r="G14">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H14" s="106">
+      <c r="H14" s="93">
         <v>0.95</v>
       </c>
       <c r="I14" s="7">
@@ -9702,7 +10225,7 @@
       <c r="Q14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R14" s="99"/>
+      <c r="R14" s="89"/>
       <c r="S14" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_SILLAMAE100"</f>
         <v>ELCCEBIO_SILLAMAE100</v>
@@ -9711,21 +10234,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S14,2)&amp;" Sillamae 1 CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Sillamae 1 CHP - Biomass</v>
       </c>
-      <c r="U14" s="99" t="s">
+      <c r="U14" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V14" s="99" t="s">
+      <c r="V14" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W14" t="s">
         <v>116</v>
       </c>
-      <c r="X14" s="99"/>
-      <c r="Y14" s="99"/>
-      <c r="AA14"/>
+      <c r="X14" s="89"/>
+      <c r="Y14" s="89"/>
+      <c r="Z14" s="21"/>
       <c r="AB14"/>
     </row>
-    <row r="15" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B15" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_SILLAMAE200</v>
@@ -9741,11 +10264,11 @@
       <c r="E15">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="F15" s="105"/>
+      <c r="F15" s="83"/>
       <c r="G15">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H15" s="106">
+      <c r="H15" s="93">
         <v>0.95</v>
       </c>
       <c r="I15" s="7">
@@ -9770,7 +10293,7 @@
       <c r="Q15" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R15" s="99"/>
+      <c r="R15" s="89"/>
       <c r="S15" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_SILLAMAE200"</f>
         <v>ELCCEGAS_SILLAMAE200</v>
@@ -9779,21 +10302,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S15,2)&amp;" Sillamae 2 CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Sillamae 2 CHP - Natural Gas</v>
       </c>
-      <c r="U15" s="99" t="s">
+      <c r="U15" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V15" s="99" t="s">
+      <c r="V15" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W15" t="s">
         <v>116</v>
       </c>
-      <c r="X15" s="99"/>
-      <c r="Y15" s="99"/>
-      <c r="AA15"/>
+      <c r="X15" s="89"/>
+      <c r="Y15" s="89"/>
+      <c r="Z15" s="21"/>
       <c r="AB15"/>
     </row>
-    <row r="16" spans="2:28" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B16" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_HELME00</v>
@@ -9809,11 +10332,11 @@
       <c r="E16">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="F16" s="105"/>
+      <c r="F16" s="83"/>
       <c r="G16">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H16" s="106">
+      <c r="H16" s="93">
         <v>0.95</v>
       </c>
       <c r="I16" s="7">
@@ -9838,7 +10361,7 @@
       <c r="Q16" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R16" s="99"/>
+      <c r="R16" s="89"/>
       <c r="S16" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HELME00"</f>
         <v>ELCCEBIO_HELME00</v>
@@ -9847,21 +10370,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S16,2)&amp;" Helme CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Helme CHP - Biomass</v>
       </c>
-      <c r="U16" s="99" t="s">
+      <c r="U16" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V16" s="99" t="s">
+      <c r="V16" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W16" t="s">
         <v>116</v>
       </c>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="99"/>
-      <c r="AA16"/>
+      <c r="X16" s="89"/>
+      <c r="Y16" s="89"/>
+      <c r="Z16" s="21"/>
       <c r="AB16"/>
     </row>
-    <row r="17" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B17" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_KURESSAARE00</v>
@@ -9877,11 +10400,11 @@
       <c r="E17">
         <v>1.8E-3</v>
       </c>
-      <c r="F17" s="105"/>
+      <c r="F17" s="83"/>
       <c r="G17">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H17" s="106">
+      <c r="H17" s="93">
         <v>0.95</v>
       </c>
       <c r="I17" s="7">
@@ -9906,7 +10429,7 @@
       <c r="Q17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R17" s="99"/>
+      <c r="R17" s="89"/>
       <c r="S17" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_KURESSAARE00"</f>
         <v>ELCCEBIO_KURESSAARE00</v>
@@ -9915,21 +10438,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S17,2)&amp;" Kuressaare CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Kuressaare CHP - Biomass</v>
       </c>
-      <c r="U17" s="99" t="s">
+      <c r="U17" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V17" s="99" t="s">
+      <c r="V17" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W17" t="s">
         <v>116</v>
       </c>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="AA17"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="21"/>
       <c r="AB17"/>
     </row>
-    <row r="18" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B18" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_PAIDE00</v>
@@ -9945,11 +10468,11 @@
       <c r="E18">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F18" s="105"/>
+      <c r="F18" s="83"/>
       <c r="G18">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H18" s="106">
+      <c r="H18" s="93">
         <v>0.95</v>
       </c>
       <c r="I18" s="7">
@@ -9974,7 +10497,7 @@
       <c r="Q18" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R18" s="99"/>
+      <c r="R18" s="89"/>
       <c r="S18" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PAIDE00"</f>
         <v>ELCCEBIO_PAIDE00</v>
@@ -9983,21 +10506,21 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S18,2)&amp;" Paide CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Paide CHP - Biomass</v>
       </c>
-      <c r="U18" s="99" t="s">
+      <c r="U18" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V18" s="99" t="s">
+      <c r="V18" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W18" t="s">
         <v>116</v>
       </c>
-      <c r="X18" s="99"/>
-      <c r="Y18" s="99"/>
-      <c r="AA18"/>
+      <c r="X18" s="89"/>
+      <c r="Y18" s="89"/>
+      <c r="Z18" s="21"/>
       <c r="AB18"/>
     </row>
-    <row r="19" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B19" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_JAMEJALA00</v>
@@ -10016,7 +10539,7 @@
       <c r="G19">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H19" s="106">
+      <c r="H19" s="93">
         <v>0.95</v>
       </c>
       <c r="I19" s="7">
@@ -10040,7 +10563,7 @@
       <c r="Q19" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R19" s="99"/>
+      <c r="R19" s="89"/>
       <c r="S19" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_JAMEJALA00"</f>
         <v>ELCCEGAS_JAMEJALA00</v>
@@ -10049,21 +10572,19 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S19,2)&amp;" Jamejala CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Jamejala CHP - Natural Gas</v>
       </c>
-      <c r="U19" s="99" t="s">
+      <c r="U19" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V19" s="99" t="s">
+      <c r="V19" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W19" t="s">
         <v>116</v>
       </c>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="108"/>
-      <c r="AA19"/>
+      <c r="Z19" s="21"/>
       <c r="AB19"/>
     </row>
-    <row r="20" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B20" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEGAS_PUSSI00</v>
@@ -10082,7 +10603,7 @@
       <c r="G20">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H20" s="106">
+      <c r="H20" s="93">
         <v>0.95</v>
       </c>
       <c r="I20" s="7">
@@ -10106,7 +10627,7 @@
       <c r="Q20" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R20" s="99"/>
+      <c r="R20" s="89"/>
       <c r="S20" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_PUSSI00"</f>
         <v>ELCCEGAS_PUSSI00</v>
@@ -10115,21 +10636,19 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S20,2)&amp;" Pussi CHP - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 Pussi CHP - Natural Gas</v>
       </c>
-      <c r="U20" s="99" t="s">
+      <c r="U20" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V20" s="99" t="s">
+      <c r="V20" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W20" t="s">
         <v>116</v>
       </c>
-      <c r="X20" s="108"/>
-      <c r="Y20" s="108"/>
-      <c r="AA20"/>
+      <c r="Z20" s="21"/>
       <c r="AB20"/>
     </row>
-    <row r="21" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B21" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_ILMATSALU00</v>
@@ -10148,7 +10667,7 @@
       <c r="G21">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H21" s="106">
+      <c r="H21" s="93">
         <v>0.95</v>
       </c>
       <c r="I21" s="7">
@@ -10172,7 +10691,7 @@
       <c r="Q21" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R21" s="99"/>
+      <c r="R21" s="89"/>
       <c r="S21" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_ILMATSALU00"</f>
         <v>ELCCEBIO_ILMATSALU00</v>
@@ -10181,21 +10700,19 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S21,2)&amp;" Ilmatsalu CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Ilmatsalu CHP - Biomass</v>
       </c>
-      <c r="U21" s="99" t="s">
+      <c r="U21" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V21" s="99" t="s">
+      <c r="V21" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W21" t="s">
         <v>116</v>
       </c>
-      <c r="X21" s="108"/>
-      <c r="Y21" s="108"/>
-      <c r="AA21"/>
+      <c r="Z21" s="21"/>
       <c r="AB21"/>
     </row>
-    <row r="22" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B22" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_VINNI00</v>
@@ -10214,7 +10731,7 @@
       <c r="G22">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H22" s="106">
+      <c r="H22" s="93">
         <v>0.95</v>
       </c>
       <c r="I22" s="7">
@@ -10238,7 +10755,7 @@
       <c r="Q22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R22" s="99"/>
+      <c r="R22" s="89"/>
       <c r="S22" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_VINNI00"</f>
         <v>ELCCEBIO_VINNI00</v>
@@ -10247,21 +10764,19 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S22,2)&amp;" Vinni CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Vinni CHP - Biomass</v>
       </c>
-      <c r="U22" s="99" t="s">
+      <c r="U22" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V22" s="99" t="s">
+      <c r="V22" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W22" t="s">
         <v>116</v>
       </c>
-      <c r="X22" s="108"/>
-      <c r="Y22" s="108"/>
-      <c r="AA22"/>
+      <c r="Z22" s="21"/>
       <c r="AB22"/>
     </row>
-    <row r="23" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B23" s="92" t="str">
         <f>S23</f>
         <v>ELCCEBIO_OISU00</v>
@@ -10280,7 +10795,7 @@
       <c r="G23">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H23" s="106">
+      <c r="H23" s="93">
         <v>0.95</v>
       </c>
       <c r="I23" s="7">
@@ -10304,7 +10819,7 @@
       <c r="Q23" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R23" s="99"/>
+      <c r="R23" s="89"/>
       <c r="S23" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_OISU00"</f>
         <v>ELCCEBIO_OISU00</v>
@@ -10313,21 +10828,19 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S23,2)&amp;" Oisu CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Oisu CHP - Biomass</v>
       </c>
-      <c r="U23" s="99" t="s">
+      <c r="U23" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V23" s="99" t="s">
+      <c r="V23" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W23" t="s">
         <v>116</v>
       </c>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="108"/>
-      <c r="AA23"/>
+      <c r="Z23" s="21"/>
       <c r="AB23"/>
     </row>
-    <row r="24" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B24" s="92" t="str">
         <f t="shared" si="0"/>
         <v>ELCCEBIO_RAKVERE00</v>
@@ -10346,7 +10859,7 @@
       <c r="G24">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H24" s="106">
+      <c r="H24" s="93">
         <v>0.95</v>
       </c>
       <c r="I24" s="7">
@@ -10370,7 +10883,7 @@
       <c r="Q24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="R24" s="99"/>
+      <c r="R24" s="89"/>
       <c r="S24" s="89" t="str">
         <f>$B$2&amp;$D$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_RAKVERE00"</f>
         <v>ELCCEBIO_RAKVERE00</v>
@@ -10379,360 +10892,226 @@
         <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(S24,2)&amp;" Rakvere CHP - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Rakvere CHP - Biomass</v>
       </c>
-      <c r="U24" s="99" t="s">
+      <c r="U24" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="V24" s="99" t="s">
+      <c r="V24" s="89" t="s">
         <v>101</v>
       </c>
       <c r="W24" t="s">
         <v>116</v>
       </c>
-      <c r="X24" s="108"/>
-      <c r="Y24" s="108"/>
-      <c r="AA24"/>
+      <c r="Z24" s="21"/>
       <c r="AB24"/>
     </row>
-    <row r="25" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="108"/>
-      <c r="G25" s="106"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="N25" s="107"/>
+    <row r="25" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="E25"/>
+      <c r="G25" s="93"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="83"/>
+      <c r="N25" s="74"/>
       <c r="Q25" s="89"/>
-      <c r="R25" s="99"/>
+      <c r="R25" s="89"/>
       <c r="S25" s="89"/>
-      <c r="T25"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25"/>
-      <c r="X25" s="108"/>
-      <c r="Y25" s="108"/>
-      <c r="AA25"/>
+      <c r="U25" s="89"/>
+      <c r="V25" s="89"/>
+      <c r="Z25" s="21"/>
       <c r="AB25"/>
     </row>
-    <row r="26" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E26" s="108"/>
-      <c r="G26" s="106"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="N26" s="107"/>
+    <row r="26" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="E26"/>
+      <c r="G26" s="93"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="N26" s="74"/>
       <c r="Q26" s="89"/>
-      <c r="R26" s="99"/>
+      <c r="R26" s="89"/>
       <c r="S26" s="89"/>
-      <c r="T26"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26"/>
-      <c r="X26" s="108"/>
-      <c r="Y26" s="108"/>
-      <c r="AA26"/>
+      <c r="U26" s="89"/>
+      <c r="V26" s="89"/>
+      <c r="Z26" s="21"/>
       <c r="AB26"/>
     </row>
-    <row r="27" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G27" s="108"/>
-      <c r="I27" s="106"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="105"/>
-      <c r="P27" s="107"/>
-      <c r="S27" s="99"/>
-      <c r="T27" s="108"/>
-      <c r="U27" s="99"/>
-      <c r="V27" s="99"/>
-      <c r="W27" s="108"/>
-      <c r="X27" s="108"/>
-      <c r="Y27" s="108"/>
-      <c r="Z27" s="108"/>
-      <c r="AA27" s="108"/>
+    <row r="27" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G27"/>
+      <c r="I27" s="93"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="83"/>
+      <c r="M27" s="83"/>
+      <c r="P27" s="74"/>
+      <c r="S27" s="89"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="89"/>
       <c r="AC27"/>
       <c r="AD27"/>
     </row>
-    <row r="28" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G28" s="108"/>
-      <c r="I28" s="106"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="105"/>
-      <c r="M28" s="105"/>
-      <c r="P28" s="107"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="108"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="108"/>
-      <c r="X28" s="108"/>
-      <c r="Y28" s="108"/>
-      <c r="Z28" s="108"/>
-      <c r="AA28" s="108"/>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G28"/>
+      <c r="I28" s="93"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="P28" s="74"/>
+      <c r="S28" s="89"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="89"/>
       <c r="AC28"/>
       <c r="AD28"/>
     </row>
-    <row r="29" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G29" s="108"/>
-      <c r="I29" s="106"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="105"/>
-      <c r="M29" s="105"/>
-      <c r="P29" s="107"/>
-      <c r="S29" s="99"/>
-      <c r="T29" s="108"/>
-      <c r="U29" s="99"/>
-      <c r="V29" s="99"/>
-      <c r="W29" s="108"/>
-      <c r="X29" s="108"/>
-      <c r="Y29" s="108"/>
-      <c r="Z29" s="108"/>
-      <c r="AA29" s="108"/>
-    </row>
-    <row r="30" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G30" s="108"/>
-      <c r="I30" s="106"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="105"/>
-      <c r="P30" s="107"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="108"/>
-      <c r="U30" s="99"/>
-      <c r="V30" s="99"/>
-      <c r="W30" s="108"/>
-      <c r="X30" s="108"/>
-      <c r="Y30" s="108"/>
-      <c r="Z30" s="108"/>
-      <c r="AA30" s="108"/>
-    </row>
-    <row r="31" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G31" s="108"/>
-      <c r="I31" s="106"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="105"/>
-      <c r="P31" s="107"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="108"/>
-      <c r="U31" s="99"/>
-      <c r="V31" s="99"/>
-      <c r="W31" s="108"/>
-      <c r="X31" s="108"/>
-      <c r="Y31" s="108"/>
-      <c r="Z31" s="108"/>
-      <c r="AA31" s="108"/>
-    </row>
-    <row r="32" spans="2:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G32" s="108"/>
-      <c r="I32" s="106"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="P32" s="107"/>
-      <c r="S32" s="99"/>
-      <c r="T32" s="108"/>
-      <c r="U32" s="99"/>
-      <c r="V32" s="99"/>
-      <c r="W32" s="108"/>
-      <c r="X32" s="108"/>
-      <c r="Y32" s="108"/>
-      <c r="Z32" s="108"/>
-      <c r="AA32" s="108"/>
-    </row>
-    <row r="33" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G33" s="108"/>
-      <c r="I33" s="106"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="105"/>
-      <c r="M33" s="105"/>
-      <c r="P33" s="107"/>
-      <c r="S33" s="99"/>
-      <c r="T33" s="108"/>
-      <c r="U33" s="99"/>
-      <c r="V33" s="99"/>
-      <c r="W33" s="108"/>
-      <c r="X33" s="108"/>
-      <c r="Y33" s="108"/>
-      <c r="Z33" s="108"/>
-      <c r="AA33" s="108"/>
-    </row>
-    <row r="34" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G34" s="108"/>
-      <c r="I34" s="106"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="105"/>
-      <c r="M34" s="105"/>
-      <c r="N34" s="108"/>
-      <c r="P34" s="108"/>
-      <c r="S34" s="99"/>
-      <c r="T34" s="108"/>
-      <c r="U34" s="108"/>
-      <c r="V34" s="108"/>
-      <c r="W34" s="108"/>
-      <c r="X34" s="108"/>
-      <c r="Y34" s="108"/>
-      <c r="Z34" s="108"/>
-      <c r="AA34" s="108"/>
-    </row>
-    <row r="35" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G35" s="108"/>
-      <c r="I35" s="106"/>
-      <c r="K35" s="104"/>
-      <c r="L35" s="105"/>
-      <c r="M35" s="105"/>
-      <c r="N35" s="108"/>
-      <c r="P35" s="108"/>
-      <c r="S35" s="99"/>
-      <c r="T35" s="108"/>
-      <c r="U35" s="108"/>
-      <c r="V35" s="108"/>
-      <c r="W35" s="108"/>
-      <c r="X35" s="108"/>
-      <c r="Y35" s="108"/>
-      <c r="Z35" s="108"/>
-      <c r="AA35" s="108"/>
-    </row>
-    <row r="36" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G36" s="108"/>
-      <c r="I36" s="106"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="105"/>
-      <c r="M36" s="105"/>
-      <c r="N36" s="108"/>
-      <c r="P36" s="108"/>
-      <c r="S36" s="99"/>
-      <c r="T36" s="108"/>
-      <c r="U36" s="108"/>
-      <c r="V36" s="108"/>
-      <c r="W36" s="108"/>
-      <c r="X36" s="108"/>
-      <c r="Y36" s="108"/>
-      <c r="Z36" s="108"/>
-      <c r="AA36" s="108"/>
-    </row>
-    <row r="37" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G37" s="108"/>
-      <c r="I37" s="106"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="108"/>
-      <c r="P37" s="108"/>
-      <c r="S37" s="99"/>
-      <c r="T37" s="108"/>
-      <c r="U37" s="108"/>
-      <c r="V37" s="108"/>
-      <c r="W37" s="108"/>
-      <c r="X37" s="108"/>
-      <c r="Y37" s="108"/>
-      <c r="Z37" s="108"/>
-      <c r="AA37" s="108"/>
-    </row>
-    <row r="38" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G38" s="108"/>
-      <c r="I38" s="106"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="105"/>
-      <c r="M38" s="105"/>
-      <c r="N38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="S38" s="99"/>
-      <c r="T38" s="108"/>
-      <c r="U38" s="108"/>
-      <c r="V38" s="108"/>
-      <c r="W38" s="108"/>
-      <c r="X38" s="108"/>
-      <c r="Y38" s="108"/>
-      <c r="Z38" s="108"/>
-      <c r="AA38" s="108"/>
-    </row>
-    <row r="39" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G39" s="108"/>
-      <c r="I39" s="106"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="105"/>
-      <c r="M39" s="105"/>
-      <c r="N39" s="108"/>
-      <c r="P39" s="108"/>
-      <c r="S39" s="99"/>
-      <c r="T39" s="108"/>
-      <c r="U39" s="108"/>
-      <c r="V39" s="108"/>
-      <c r="W39" s="108"/>
-      <c r="X39" s="108"/>
-      <c r="Y39" s="108"/>
-      <c r="Z39" s="108"/>
-      <c r="AA39" s="108"/>
-    </row>
-    <row r="40" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G40" s="108"/>
-      <c r="I40" s="106"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="105"/>
-      <c r="M40" s="105"/>
-      <c r="N40" s="108"/>
-      <c r="P40" s="108"/>
-      <c r="S40" s="99"/>
-      <c r="T40" s="108"/>
-      <c r="U40" s="108"/>
-      <c r="V40" s="108"/>
-      <c r="W40" s="108"/>
-      <c r="X40" s="108"/>
-      <c r="Y40" s="108"/>
-      <c r="Z40" s="108"/>
-      <c r="AA40" s="108"/>
-    </row>
-    <row r="41" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G41" s="108"/>
-      <c r="I41" s="106"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="105"/>
-      <c r="M41" s="105"/>
-      <c r="N41" s="108"/>
-      <c r="P41" s="108"/>
-      <c r="S41" s="99"/>
-      <c r="T41" s="108"/>
-      <c r="U41" s="108"/>
-      <c r="V41" s="108"/>
-      <c r="W41" s="108"/>
-      <c r="X41" s="108"/>
-      <c r="Y41" s="108"/>
-      <c r="Z41" s="108"/>
-      <c r="AA41" s="108"/>
-    </row>
-    <row r="42" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G42" s="108"/>
-      <c r="I42" s="106"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="105"/>
-      <c r="M42" s="105"/>
-      <c r="N42" s="108"/>
-      <c r="P42" s="108"/>
-      <c r="S42" s="99"/>
-      <c r="T42" s="108"/>
-      <c r="U42" s="108"/>
-      <c r="V42" s="108"/>
-      <c r="W42" s="108"/>
-      <c r="X42" s="108"/>
-      <c r="Y42" s="108"/>
-      <c r="Z42" s="108"/>
-      <c r="AA42" s="108"/>
-    </row>
-    <row r="43" spans="7:30" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="K43" s="109"/>
-      <c r="L43" s="109"/>
-      <c r="M43" s="109"/>
-      <c r="N43" s="109"/>
-      <c r="P43" s="108"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="108"/>
-      <c r="U43" s="108"/>
-      <c r="V43" s="108"/>
-      <c r="W43" s="108"/>
-      <c r="X43" s="108"/>
-      <c r="Y43" s="108"/>
-      <c r="Z43" s="108"/>
-      <c r="AA43" s="108"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
+    <row r="29" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G29"/>
+      <c r="I29" s="93"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="P29" s="74"/>
+      <c r="S29" s="89"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="89"/>
+    </row>
+    <row r="30" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G30"/>
+      <c r="I30" s="93"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
+      <c r="P30" s="74"/>
+      <c r="S30" s="89"/>
+      <c r="U30" s="89"/>
+      <c r="V30" s="89"/>
+    </row>
+    <row r="31" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G31"/>
+      <c r="I31" s="93"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83"/>
+      <c r="P31" s="74"/>
+      <c r="S31" s="89"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="89"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="G32"/>
+      <c r="I32" s="93"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="83"/>
+      <c r="M32" s="83"/>
+      <c r="P32" s="74"/>
+      <c r="S32" s="89"/>
+      <c r="U32" s="89"/>
+      <c r="V32" s="89"/>
+    </row>
+    <row r="33" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G33"/>
+      <c r="I33" s="93"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="83"/>
+      <c r="M33" s="83"/>
+      <c r="P33" s="74"/>
+      <c r="S33" s="89"/>
+      <c r="U33" s="89"/>
+      <c r="V33" s="89"/>
+    </row>
+    <row r="34" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G34"/>
+      <c r="I34" s="93"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="83"/>
+      <c r="M34" s="83"/>
+      <c r="N34"/>
+      <c r="P34"/>
+      <c r="S34" s="89"/>
+    </row>
+    <row r="35" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G35"/>
+      <c r="I35" s="93"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="83"/>
+      <c r="N35"/>
+      <c r="P35"/>
+      <c r="S35" s="89"/>
+    </row>
+    <row r="36" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G36"/>
+      <c r="I36" s="93"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="83"/>
+      <c r="N36"/>
+      <c r="P36"/>
+      <c r="S36" s="89"/>
+    </row>
+    <row r="37" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G37"/>
+      <c r="I37" s="93"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="83"/>
+      <c r="N37"/>
+      <c r="P37"/>
+      <c r="S37" s="89"/>
+    </row>
+    <row r="38" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G38"/>
+      <c r="I38" s="93"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="83"/>
+      <c r="M38" s="83"/>
+      <c r="N38"/>
+      <c r="P38"/>
+      <c r="S38" s="89"/>
+    </row>
+    <row r="39" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G39"/>
+      <c r="I39" s="93"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="83"/>
+      <c r="M39" s="83"/>
+      <c r="N39"/>
+      <c r="P39"/>
+      <c r="S39" s="89"/>
+    </row>
+    <row r="40" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G40"/>
+      <c r="I40" s="93"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="83"/>
+      <c r="M40" s="83"/>
+      <c r="N40"/>
+      <c r="P40"/>
+      <c r="S40" s="89"/>
+    </row>
+    <row r="41" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G41"/>
+      <c r="I41" s="93"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83"/>
+      <c r="N41"/>
+      <c r="P41"/>
+      <c r="S41" s="89"/>
+    </row>
+    <row r="42" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="G42"/>
+      <c r="I42" s="93"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="83"/>
+      <c r="M42" s="83"/>
+      <c r="N42"/>
+      <c r="P42"/>
+      <c r="S42" s="89"/>
+    </row>
+    <row r="43" spans="7:22" x14ac:dyDescent="0.2">
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="P43"/>
+      <c r="S43" s="89"/>
     </row>
     <row r="65535" spans="18:18" x14ac:dyDescent="0.2">
       <c r="R65535" s="29"/>
@@ -10868,4 +11247,168 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002CFCD1-25AD-42A5-9F77-F4D75C1B60FE}">
+  <dimension ref="B4:K12"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="99" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+    </row>
+    <row r="5" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="101" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="101" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="101" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="101" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" s="101" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="102" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="103">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="84"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="88" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="88" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B12" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="89"/>
+      <c r="D12" s="85" t="str">
+        <f>B6</f>
+        <v>TOTCO2</v>
+      </c>
+      <c r="E12" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="85" t="str">
+        <f>[2]EB1!AA2</f>
+        <v>kt</v>
+      </c>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D19DA-9F10-4BFF-839A-165D5F18F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82AF2F4-6681-4C4E-B585-55D05881DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -786,9 +786,10 @@
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
+    <author>Kristopher Raik</author>
   </authors>
   <commentList>
-    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -902,7 +903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="Z3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -928,7 +929,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="AA3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1001,7 +1002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="AB3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1054,7 +1055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="AC3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1087,7 +1088,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="G9" authorId="3" shapeId="0" xr:uid="{4CC104A8-D70F-4C07-9649-7404261279B2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="186"/>
+          </rPr>
+          <t>Kristopher Raik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="186"/>
+          </rPr>
+          <t xml:space="preserve">
+use PASTI (2024) is constant over technical life</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1180,7 +1207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="AB9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1205,7 +1232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="AC9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1268,7 +1295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="U10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1508,6 +1535,32 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> (Heating Plant)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="3" shapeId="0" xr:uid="{49F8970F-654D-4377-A47F-D4881BFD24ED}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="186"/>
+          </rPr>
+          <t>Kristopher Raik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="186"/>
+          </rPr>
+          <t xml:space="preserve">
+Variable == 2 means that. So new capacity = 0</t>
         </r>
       </text>
     </comment>
@@ -2280,7 +2333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="207">
   <si>
     <t>CommName</t>
   </si>
@@ -2895,6 +2948,12 @@
   </si>
   <si>
     <t>Total CO2</t>
+  </si>
+  <si>
+    <t>NCAP_BND~0</t>
+  </si>
+  <si>
+    <t>PASTI~2025</t>
   </si>
 </sst>
 </file>
@@ -2909,7 +2968,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2917,6 +2976,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2979,6 +3040,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3084,6 +3147,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="186"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="18">
@@ -3881,13 +3959,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>871640</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>120128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>692699</xdr:colOff>
       <xdr:row>71</xdr:row>
       <xdr:rowOff>115715</xdr:rowOff>
@@ -6894,7 +6972,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:AB65529"/>
+  <dimension ref="B1:AC65529"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -6903,29 +6981,30 @@
     <col min="4" max="4" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="21" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2" style="21" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.85546875" style="21"/>
+    <col min="9" max="9" width="13" style="21" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.85546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:29" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>65</v>
       </c>
@@ -6947,8 +7026,9 @@
       <c r="H1" s="20" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -6974,48 +7054,49 @@
       <c r="H2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="84" t="s">
+      <c r="I2" s="10"/>
+      <c r="U2" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="84"/>
-      <c r="V2" s="85"/>
+      <c r="V2" s="84"/>
       <c r="W2" s="85"/>
       <c r="X2" s="85"/>
       <c r="Y2" s="85"/>
       <c r="Z2" s="85"/>
       <c r="AA2" s="85"/>
       <c r="AB2" s="85"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="T3" s="86" t="s">
+      <c r="AC2" s="85"/>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="U3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="87" t="s">
+      <c r="V3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="86" t="s">
+      <c r="W3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="W3" s="86" t="s">
+      <c r="X3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="X3" s="86" t="s">
+      <c r="Y3" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="86" t="s">
+      <c r="Z3" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="86" t="s">
+      <c r="AA3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="86" t="s">
+      <c r="AB3" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="86" t="s">
+      <c r="AC3" s="86" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:29" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>107</v>
       </c>
@@ -7032,36 +7113,37 @@
         <v>121</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="T4" s="88" t="s">
+      <c r="I4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="U4" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="88" t="s">
+      <c r="V4" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="88" t="s">
+      <c r="W4" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="88" t="s">
+      <c r="X4" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="88" t="s">
+      <c r="Y4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="Y4" s="88" t="s">
+      <c r="Z4" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" s="88" t="s">
+      <c r="AA4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="AA4" s="88" t="s">
+      <c r="AB4" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="88" t="s">
+      <c r="AC4" s="88" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
@@ -7078,58 +7160,59 @@
         <v>85</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="T5" s="85" t="s">
+      <c r="I5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="U5" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="89"/>
-      <c r="V5" s="85" t="s">
+      <c r="V5" s="89"/>
+      <c r="W5" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="W5" s="85" t="str">
+      <c r="X5" s="85" t="str">
         <f>'EB1'!$W$3</f>
         <v>Electricity</v>
       </c>
-      <c r="X5" s="85" t="str">
+      <c r="Y5" s="85" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Y5" s="85"/>
-      <c r="Z5" s="85" t="s">
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85" t="s">
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="T6" s="89" t="s">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="U6" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="U6" s="89"/>
-      <c r="V6" s="89" t="str">
+      <c r="V6" s="89"/>
+      <c r="W6" s="89" t="str">
         <f>$B$2&amp;'EB1'!$C$15</f>
         <v>ELCCO2</v>
       </c>
-      <c r="W6" s="89" t="str">
+      <c r="X6" s="89" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$16</f>
         <v>Electricity Plants Carbon dioxide</v>
       </c>
-      <c r="X6" s="89" t="str">
+      <c r="Y6" s="89" t="str">
         <f>'EB1'!$AC$2</f>
         <v>kt</v>
       </c>
-      <c r="Y6" s="89"/>
       <c r="Z6" s="89"/>
       <c r="AA6" s="89"/>
       <c r="AB6" s="89"/>
-    </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="T7" s="2"/>
+      <c r="AC6" s="89"/>
+    </row>
+    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
       <c r="U7" s="2"/>
-    </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -7138,22 +7221,23 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="L8" s="5"/>
+      <c r="J8" s="4"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="3"/>
-      <c r="T8" s="84" t="s">
+      <c r="N8" s="5"/>
+      <c r="O8" s="3"/>
+      <c r="U8" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="U8" s="84"/>
-      <c r="V8" s="85"/>
+      <c r="V8" s="84"/>
       <c r="W8" s="85"/>
       <c r="X8" s="85"/>
       <c r="Y8" s="85"/>
       <c r="Z8" s="85"/>
       <c r="AA8" s="85"/>
       <c r="AB8" s="85"/>
-    </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC8" s="85"/>
+    </row>
+    <row r="9" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -7170,69 +7254,72 @@
         <v>160</v>
       </c>
       <c r="G9" s="67" t="s">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="H9" s="67" t="s">
         <v>144</v>
       </c>
       <c r="I9" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="J9" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="67" t="s">
+      <c r="K9" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="K9" s="67" t="s">
+      <c r="L9" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="67" t="s">
+      <c r="M9" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="67" t="s">
+      <c r="N9" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="67" t="s">
+      <c r="O9" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="67" t="s">
+      <c r="P9" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="P9" s="67" t="s">
+      <c r="Q9" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="80" t="s">
+      <c r="R9" s="23"/>
+      <c r="S9" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="S9" s="27"/>
-      <c r="T9" s="86" t="s">
+      <c r="T9" s="27"/>
+      <c r="U9" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="87" t="s">
+      <c r="V9" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="86" t="s">
+      <c r="W9" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="W9" s="86" t="s">
+      <c r="X9" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="X9" s="86" t="s">
+      <c r="Y9" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="Y9" s="86" t="s">
+      <c r="Z9" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="86" t="s">
+      <c r="AA9" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="AA9" s="86" t="s">
+      <c r="AB9" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" s="86" t="s">
+      <c r="AC9" s="86" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:29" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -7254,63 +7341,64 @@
       <c r="H10" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="73" t="s">
+      <c r="K10" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="Q10" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="S10" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="S10" s="28"/>
-      <c r="T10" s="88" t="s">
+      <c r="T10" s="28"/>
+      <c r="U10" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="88" t="s">
+      <c r="V10" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="V10" s="88" t="s">
+      <c r="W10" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="W10" s="88" t="s">
+      <c r="X10" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="X10" s="88" t="s">
+      <c r="Y10" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="Y10" s="88" t="s">
+      <c r="Z10" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="88" t="s">
+      <c r="AA10" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="AA10" s="88" t="s">
+      <c r="AB10" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="AB10" s="88" t="s">
+      <c r="AC10" s="88" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -7332,35 +7420,35 @@
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="13" t="str">
-        <f>$G$2&amp;"/"&amp;$F$2</f>
-        <v>M€2025/GW</v>
-      </c>
+      <c r="I11" s="68"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="68"/>
       <c r="L11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
       <c r="M11" s="13" t="str">
+        <f>$G$2&amp;"/"&amp;$F$2</f>
+        <v>M€2025/GW</v>
+      </c>
+      <c r="N11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2025/PJ</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="O11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="P11" s="13"/>
-      <c r="R11" s="81" t="s">
+      <c r="Q11" s="13"/>
+      <c r="S11" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="S11" s="28"/>
-      <c r="T11" s="88" t="s">
+      <c r="T11" s="28"/>
+      <c r="U11" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="88"/>
       <c r="V11" s="88"/>
       <c r="W11" s="88"/>
       <c r="X11" s="88"/>
@@ -7368,10 +7456,11 @@
       <c r="Z11" s="88"/>
       <c r="AA11" s="88"/>
       <c r="AB11" s="88"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="88"/>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B12" s="21" t="str">
-        <f>V12</f>
+        <f>W12</f>
         <v>ELCREHYD00</v>
       </c>
       <c r="C12" s="21" t="str">
@@ -7379,7 +7468,7 @@
         <v>ELCHYD</v>
       </c>
       <c r="D12" s="21" t="str">
-        <f t="shared" ref="D12:D48" si="0">$V$5</f>
+        <f t="shared" ref="D12:D48" si="0">$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E12" s="42"/>
@@ -7388,55 +7477,58 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="H12" s="83"/>
-      <c r="I12" s="63">
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+      <c r="J12" s="63">
         <v>1</v>
       </c>
-      <c r="J12" s="63">
+      <c r="K12" s="63">
         <v>0.5</v>
       </c>
-      <c r="K12" s="63"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="64">
+      <c r="L12" s="63"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="64">
         <v>8.76</v>
       </c>
-      <c r="P12" s="65">
+      <c r="Q12" s="65">
         <v>0.5</v>
       </c>
-      <c r="R12" s="26">
-        <f>(E12+F12)*$J12*$O12</f>
+      <c r="S12" s="26">
+        <f>(E12+F12)*$K12*$P12</f>
         <v>0</v>
       </c>
-      <c r="S12" s="29"/>
-      <c r="T12" s="89" t="s">
+      <c r="T12" s="29"/>
+      <c r="U12" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U12" s="89"/>
-      <c r="V12" s="89" t="str">
+      <c r="V12" s="89"/>
+      <c r="W12" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
         <v>ELCREHYD00</v>
       </c>
-      <c r="W12" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V12,2)&amp;" - "&amp;'EB1'!P3</f>
+      <c r="X12" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W12,2)&amp;" - "&amp;'EB1'!P3</f>
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>180</v>
       </c>
-      <c r="Y12" s="89" t="str">
-        <f t="shared" ref="Y12" si="1">$F$2</f>
+      <c r="Z12" s="89" t="str">
+        <f t="shared" ref="Z12" si="1">$F$2</f>
         <v>GW</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>116</v>
       </c>
-      <c r="AA12" s="89"/>
       <c r="AB12" s="89"/>
-    </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="89"/>
+    </row>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
-        <f>V13</f>
+        <f>W13</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="C13" s="21" t="str">
@@ -7450,54 +7542,57 @@
       <c r="G13">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I13" s="93">
+      <c r="I13" s="7">
+        <v>2</v>
+      </c>
+      <c r="J13" s="93">
         <v>1</v>
       </c>
-      <c r="J13" s="63">
+      <c r="K13" s="63">
         <v>0.3</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>1018</v>
       </c>
-      <c r="L13" s="83">
+      <c r="M13" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M13" s="83">
+      <c r="N13" s="83">
         <v>0</v>
       </c>
-      <c r="N13" s="21">
+      <c r="O13" s="21">
         <v>35</v>
       </c>
-      <c r="O13" s="64">
+      <c r="P13" s="64">
         <v>8.76</v>
       </c>
-      <c r="P13" s="74">
+      <c r="Q13" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T13" s="89" t="s">
+      <c r="U13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V13" s="89" t="str">
+      <c r="W13" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
-      <c r="W13" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X13" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in PARNU - Solar energy</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>180</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
         <v>101</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AA13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B14" s="21" t="str">
-        <f t="shared" ref="B14:B37" si="2">V14</f>
+        <f t="shared" ref="B14:B37" si="2">W14</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
       <c r="C14" s="21" t="str">
@@ -7511,53 +7606,56 @@
       <c r="G14">
         <v>0.108</v>
       </c>
-      <c r="I14" s="93">
+      <c r="I14" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" s="93">
         <v>1</v>
       </c>
-      <c r="J14" s="63">
+      <c r="K14" s="63">
         <v>0.3</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>1018</v>
       </c>
-      <c r="L14" s="83">
+      <c r="M14" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M14" s="83">
+      <c r="N14" s="83">
         <v>0</v>
       </c>
-      <c r="N14" s="21">
+      <c r="O14" s="21">
         <v>35</v>
       </c>
-      <c r="O14" s="64">
+      <c r="P14" s="64">
         <v>8.76</v>
       </c>
-      <c r="P14" s="74">
+      <c r="Q14" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="R14" s="79"/>
-      <c r="T14" s="89" t="s">
+      <c r="S14" s="79"/>
+      <c r="U14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V14" s="89" t="str">
+      <c r="W14" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
-      <c r="W14" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X14" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in TARTU - Solar energy</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>180</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
         <v>101</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AA14" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B15" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_LVIRU00</v>
@@ -7573,53 +7671,56 @@
       <c r="G15">
         <v>0.13200000000000001</v>
       </c>
-      <c r="I15" s="93">
+      <c r="I15" s="7">
+        <v>2</v>
+      </c>
+      <c r="J15" s="93">
         <v>1</v>
       </c>
-      <c r="J15" s="63">
+      <c r="K15" s="63">
         <v>0.3</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>1018</v>
       </c>
-      <c r="L15" s="83">
+      <c r="M15" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M15" s="83">
+      <c r="N15" s="83">
         <v>0</v>
       </c>
-      <c r="N15" s="21">
+      <c r="O15" s="21">
         <v>35</v>
       </c>
-      <c r="O15" s="64">
+      <c r="P15" s="64">
         <v>8.76</v>
       </c>
-      <c r="P15" s="74">
+      <c r="Q15" s="74">
         <v>0.14867925344692126</v>
       </c>
-      <c r="R15" s="79"/>
-      <c r="T15" s="89" t="s">
+      <c r="S15" s="79"/>
+      <c r="U15" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V15" s="89" t="str">
+      <c r="W15" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
         <v>ELCRESOL_LVIRU00</v>
       </c>
-      <c r="W15" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X15" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LVIRU - Solar energy</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>180</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Z15" t="s">
         <v>101</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B16" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_IVIRU00</v>
@@ -7635,53 +7736,56 @@
       <c r="G16">
         <v>7.8E-2</v>
       </c>
-      <c r="I16" s="93">
+      <c r="I16" s="7">
+        <v>2</v>
+      </c>
+      <c r="J16" s="93">
         <v>1</v>
       </c>
-      <c r="J16" s="63">
+      <c r="K16" s="63">
         <v>0.3</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="7">
         <v>1018</v>
       </c>
-      <c r="L16" s="83">
+      <c r="M16" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M16" s="83">
+      <c r="N16" s="83">
         <v>0</v>
       </c>
-      <c r="N16" s="21">
+      <c r="O16" s="21">
         <v>35</v>
       </c>
-      <c r="O16" s="64">
+      <c r="P16" s="64">
         <v>8.76</v>
       </c>
-      <c r="P16" s="74">
+      <c r="Q16" s="74">
         <v>0.14701259708091721</v>
       </c>
-      <c r="R16" s="79"/>
-      <c r="T16" s="89" t="s">
+      <c r="S16" s="79"/>
+      <c r="U16" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V16" s="89" t="str">
+      <c r="W16" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
         <v>ELCRESOL_IVIRU00</v>
       </c>
-      <c r="W16" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X16" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in IVIRU - Solar energy</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>180</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Z16" t="s">
         <v>101</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B17" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JARVA00</v>
@@ -7697,53 +7801,56 @@
       <c r="G17">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I17" s="93">
+      <c r="I17" s="7">
+        <v>2</v>
+      </c>
+      <c r="J17" s="93">
         <v>1</v>
       </c>
-      <c r="J17" s="63">
+      <c r="K17" s="63">
         <v>0.3</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>1018</v>
       </c>
-      <c r="L17" s="83">
+      <c r="M17" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M17" s="83">
+      <c r="N17" s="83">
         <v>0</v>
       </c>
-      <c r="N17" s="21">
+      <c r="O17" s="21">
         <v>35</v>
       </c>
-      <c r="O17" s="64">
+      <c r="P17" s="64">
         <v>8.76</v>
       </c>
-      <c r="P17" s="74">
+      <c r="Q17" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="R17" s="79"/>
-      <c r="T17" s="89" t="s">
+      <c r="S17" s="79"/>
+      <c r="U17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V17" s="89" t="str">
+      <c r="W17" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
         <v>ELCRESOL_JARVA00</v>
       </c>
-      <c r="W17" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X17" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JARVA - Solar energy</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
         <v>180</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Z17" t="s">
         <v>101</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B18" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_JOGEVA00</v>
@@ -7759,53 +7866,56 @@
       <c r="G18">
         <v>4.7E-2</v>
       </c>
-      <c r="I18" s="93">
+      <c r="I18" s="7">
+        <v>2</v>
+      </c>
+      <c r="J18" s="93">
         <v>1</v>
       </c>
-      <c r="J18" s="63">
+      <c r="K18" s="63">
         <v>0.3</v>
       </c>
-      <c r="K18" s="7">
+      <c r="L18" s="7">
         <v>1018</v>
       </c>
-      <c r="L18" s="83">
+      <c r="M18" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M18" s="83">
+      <c r="N18" s="83">
         <v>0</v>
       </c>
-      <c r="N18" s="21">
+      <c r="O18" s="21">
         <v>35</v>
       </c>
-      <c r="O18" s="64">
+      <c r="P18" s="64">
         <v>8.76</v>
       </c>
-      <c r="P18" s="74">
+      <c r="Q18" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="R18" s="79"/>
-      <c r="T18" s="89" t="s">
+      <c r="S18" s="79"/>
+      <c r="U18" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V18" s="89" t="str">
+      <c r="W18" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
         <v>ELCRESOL_JOGEVA00</v>
       </c>
-      <c r="W18" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X18" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>180</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="Z18" t="s">
         <v>101</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B19" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_HARJU00</v>
@@ -7821,52 +7931,55 @@
       <c r="G19">
         <v>0.04</v>
       </c>
-      <c r="I19" s="93">
+      <c r="I19" s="7">
+        <v>2</v>
+      </c>
+      <c r="J19" s="93">
         <v>1</v>
       </c>
-      <c r="J19" s="63">
+      <c r="K19" s="63">
         <v>0.3</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>1018</v>
       </c>
-      <c r="L19" s="83">
+      <c r="M19" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M19" s="83">
+      <c r="N19" s="83">
         <v>0</v>
       </c>
-      <c r="N19" s="21">
+      <c r="O19" s="21">
         <v>35</v>
       </c>
-      <c r="O19" s="64">
+      <c r="P19" s="64">
         <v>8.76</v>
       </c>
-      <c r="P19" s="74">
+      <c r="Q19" s="74">
         <v>0.15619560585976827</v>
       </c>
-      <c r="T19" s="89" t="s">
+      <c r="U19" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V19" s="89" t="str">
+      <c r="W19" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
         <v>ELCRESOL_HARJU00</v>
       </c>
-      <c r="W19" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X19" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HARJU - Solar energy</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
         <v>180</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
         <v>101</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B20" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_POLVA00</v>
@@ -7882,52 +7995,55 @@
       <c r="G20">
         <v>0.24199999999999999</v>
       </c>
-      <c r="I20" s="93">
+      <c r="I20" s="7">
+        <v>2</v>
+      </c>
+      <c r="J20" s="93">
         <v>1</v>
       </c>
-      <c r="J20" s="63">
+      <c r="K20" s="63">
         <v>0.3</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="7">
         <v>1018</v>
       </c>
-      <c r="L20" s="83">
+      <c r="M20" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M20" s="83">
+      <c r="N20" s="83">
         <v>0</v>
       </c>
-      <c r="N20" s="21">
+      <c r="O20" s="21">
         <v>35</v>
       </c>
-      <c r="O20" s="64">
+      <c r="P20" s="64">
         <v>8.76</v>
       </c>
-      <c r="P20" s="74">
+      <c r="Q20" s="74">
         <v>0.14537310453496291</v>
       </c>
-      <c r="T20" s="89" t="s">
+      <c r="U20" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V20" s="89" t="str">
+      <c r="W20" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
         <v>ELCRESOL_POLVA00</v>
       </c>
-      <c r="W20" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X20" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
         <v>180</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Z20" t="s">
         <v>101</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B21" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VALGA00</v>
@@ -7943,52 +8059,55 @@
       <c r="G21">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I21" s="93">
+      <c r="I21" s="7">
+        <v>2</v>
+      </c>
+      <c r="J21" s="93">
         <v>1</v>
       </c>
-      <c r="J21" s="63">
+      <c r="K21" s="63">
         <v>0.3</v>
       </c>
-      <c r="K21" s="7">
+      <c r="L21" s="7">
         <v>1018</v>
       </c>
-      <c r="L21" s="83">
+      <c r="M21" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M21" s="83">
+      <c r="N21" s="83">
         <v>0</v>
       </c>
-      <c r="N21" s="21">
+      <c r="O21" s="21">
         <v>35</v>
       </c>
-      <c r="O21" s="64">
+      <c r="P21" s="64">
         <v>8.76</v>
       </c>
-      <c r="P21" s="74">
+      <c r="Q21" s="74">
         <v>0.14763873655681015</v>
       </c>
-      <c r="T21" s="89" t="s">
+      <c r="U21" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V21" s="89" t="str">
+      <c r="W21" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
         <v>ELCRESOL_VALGA00</v>
       </c>
-      <c r="W21" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X21" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
         <v>180</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Z21" t="s">
         <v>101</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VILJANDI00</v>
@@ -8004,52 +8123,55 @@
       <c r="G22">
         <v>0.08</v>
       </c>
-      <c r="I22" s="93">
+      <c r="I22" s="7">
+        <v>2</v>
+      </c>
+      <c r="J22" s="93">
         <v>1</v>
       </c>
-      <c r="J22" s="63">
+      <c r="K22" s="63">
         <v>0.3</v>
       </c>
-      <c r="K22" s="7">
+      <c r="L22" s="7">
         <v>1018</v>
       </c>
-      <c r="L22" s="83">
+      <c r="M22" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="M22" s="83">
+      <c r="N22" s="83">
         <v>0</v>
       </c>
-      <c r="N22" s="21">
+      <c r="O22" s="21">
         <v>35</v>
       </c>
-      <c r="O22" s="64">
+      <c r="P22" s="64">
         <v>8.76</v>
       </c>
-      <c r="P22" s="74">
+      <c r="Q22" s="74">
         <v>0.1532628310027955</v>
       </c>
-      <c r="T22" s="89" t="s">
+      <c r="U22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V22" s="89" t="str">
+      <c r="W22" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
         <v>ELCRESOL_VILJANDI00</v>
       </c>
-      <c r="W22" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X22" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>180</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Z22" t="s">
         <v>101</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AA22" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_VORU00</v>
@@ -8065,52 +8187,55 @@
       <c r="G23">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I23" s="93">
+      <c r="I23" s="7">
+        <v>2</v>
+      </c>
+      <c r="J23" s="93">
         <v>1</v>
       </c>
-      <c r="J23" s="63">
+      <c r="K23" s="63">
         <v>0.3</v>
       </c>
-      <c r="K23" s="7">
+      <c r="L23" s="7">
         <v>1019</v>
       </c>
-      <c r="L23" s="83">
+      <c r="M23" s="83">
         <v>16.079820000000002</v>
       </c>
-      <c r="M23" s="83">
+      <c r="N23" s="83">
         <v>0</v>
       </c>
-      <c r="N23" s="21">
+      <c r="O23" s="21">
         <v>35</v>
       </c>
-      <c r="O23" s="64">
+      <c r="P23" s="64">
         <v>8.76</v>
       </c>
-      <c r="P23" s="74">
+      <c r="Q23" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T23" s="89" t="s">
+      <c r="U23" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V23" s="89" t="str">
+      <c r="W23" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
         <v>ELCRESOL_VORU00</v>
       </c>
-      <c r="W23" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X23" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>180</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Z23" t="s">
         <v>101</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_SAARE00</v>
@@ -8126,52 +8251,55 @@
       <c r="G24">
         <v>3.1E-2</v>
       </c>
-      <c r="I24" s="93">
+      <c r="I24" s="7">
+        <v>2</v>
+      </c>
+      <c r="J24" s="93">
         <v>1</v>
       </c>
-      <c r="J24" s="63">
+      <c r="K24" s="63">
         <v>0.3</v>
       </c>
-      <c r="K24" s="7">
+      <c r="L24" s="7">
         <v>1020</v>
       </c>
-      <c r="L24" s="83">
+      <c r="M24" s="83">
         <v>16.095600000000001</v>
       </c>
-      <c r="M24" s="83">
+      <c r="N24" s="83">
         <v>0</v>
       </c>
-      <c r="N24" s="21">
+      <c r="O24" s="21">
         <v>35</v>
       </c>
-      <c r="O24" s="64">
+      <c r="P24" s="64">
         <v>8.76</v>
       </c>
-      <c r="P24" s="74">
+      <c r="Q24" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T24" s="89" t="s">
+      <c r="U24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V24" s="89" t="str">
+      <c r="W24" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
         <v>ELCRESOL_SAARE00</v>
       </c>
-      <c r="W24" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X24" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>180</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Z24" t="s">
         <v>101</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B25" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_RAPLA00</v>
@@ -8187,52 +8315,55 @@
       <c r="G25">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I25" s="93">
+      <c r="I25" s="7">
+        <v>2</v>
+      </c>
+      <c r="J25" s="93">
         <v>1</v>
       </c>
-      <c r="J25" s="63">
+      <c r="K25" s="63">
         <v>0.3</v>
       </c>
-      <c r="K25" s="7">
+      <c r="L25" s="7">
         <v>1021</v>
       </c>
-      <c r="L25" s="83">
+      <c r="M25" s="83">
         <v>16.111380000000004</v>
       </c>
-      <c r="M25" s="83">
+      <c r="N25" s="83">
         <v>0</v>
       </c>
-      <c r="N25" s="21">
+      <c r="O25" s="21">
         <v>35</v>
       </c>
-      <c r="O25" s="64">
+      <c r="P25" s="64">
         <v>8.76</v>
       </c>
-      <c r="P25" s="74">
+      <c r="Q25" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T25" s="89" t="s">
+      <c r="U25" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V25" s="89" t="str">
+      <c r="W25" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
         <v>ELCRESOL_RAPLA00</v>
       </c>
-      <c r="W25" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X25" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>180</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Z25" t="s">
         <v>101</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_LAANE00</v>
@@ -8248,52 +8379,55 @@
       <c r="G26">
         <v>0.01</v>
       </c>
-      <c r="I26" s="93">
+      <c r="I26" s="7">
+        <v>2</v>
+      </c>
+      <c r="J26" s="93">
         <v>1</v>
       </c>
-      <c r="J26" s="63">
+      <c r="K26" s="63">
         <v>0.3</v>
       </c>
-      <c r="K26" s="7">
+      <c r="L26" s="7">
         <v>1022</v>
       </c>
-      <c r="L26" s="83">
+      <c r="M26" s="83">
         <v>16.127160000000003</v>
       </c>
-      <c r="M26" s="83">
+      <c r="N26" s="83">
         <v>0</v>
       </c>
-      <c r="N26" s="21">
+      <c r="O26" s="21">
         <v>35</v>
       </c>
-      <c r="O26" s="64">
+      <c r="P26" s="64">
         <v>8.76</v>
       </c>
-      <c r="P26" s="74">
+      <c r="Q26" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T26" s="89" t="s">
+      <c r="U26" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V26" s="89" t="str">
+      <c r="W26" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
         <v>ELCRESOL_LAANE00</v>
       </c>
-      <c r="W26" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X26" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>180</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>101</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCRESOL_HIIU00</v>
@@ -8309,52 +8443,55 @@
       <c r="G27">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="93">
+      <c r="I27" s="7">
+        <v>2</v>
+      </c>
+      <c r="J27" s="93">
         <v>1</v>
       </c>
-      <c r="J27" s="63">
+      <c r="K27" s="63">
         <v>0.3</v>
       </c>
-      <c r="K27" s="7">
+      <c r="L27" s="7">
         <v>1023</v>
       </c>
-      <c r="L27" s="83">
+      <c r="M27" s="83">
         <v>16.142940000000003</v>
       </c>
-      <c r="M27" s="83">
+      <c r="N27" s="83">
         <v>0</v>
       </c>
-      <c r="N27" s="21">
+      <c r="O27" s="21">
         <v>35</v>
       </c>
-      <c r="O27" s="21">
+      <c r="P27" s="21">
         <v>8.76</v>
       </c>
-      <c r="P27" s="74">
+      <c r="Q27" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T27" s="89" t="s">
+      <c r="U27" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V27" s="89" t="str">
+      <c r="W27" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
         <v>ELCRESOL_HIIU00</v>
       </c>
-      <c r="W27" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="X27" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>180</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>101</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SOPITOOTSI00</v>
@@ -8370,52 +8507,55 @@
       <c r="G28">
         <v>7.9699999999999993E-2</v>
       </c>
-      <c r="I28" s="93">
+      <c r="I28" s="7">
+        <v>2</v>
+      </c>
+      <c r="J28" s="93">
         <v>1</v>
       </c>
-      <c r="J28" s="63">
+      <c r="K28" s="63">
         <v>0.3</v>
       </c>
-      <c r="K28" s="7">
+      <c r="L28" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L28" s="83">
+      <c r="M28" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M28" s="83">
+      <c r="N28" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>27</v>
       </c>
-      <c r="O28" s="21">
+      <c r="P28" s="21">
         <v>8.76</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>0.4</v>
       </c>
-      <c r="T28" s="89" t="s">
+      <c r="U28" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V28" t="str">
+      <c r="W28" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
         <v>ELCREWON_SOPITOOTSI00</v>
       </c>
-      <c r="W28" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X28" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
         <v>180</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>101</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SOPIPURTSE00</v>
@@ -8431,52 +8571,55 @@
       <c r="G29">
         <v>0.17519999999999999</v>
       </c>
-      <c r="I29" s="93">
+      <c r="I29" s="7">
+        <v>2</v>
+      </c>
+      <c r="J29" s="93">
         <v>1</v>
       </c>
-      <c r="J29" s="63">
+      <c r="K29" s="63">
         <v>0.3</v>
       </c>
-      <c r="K29" s="7">
+      <c r="L29" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L29" s="83">
+      <c r="M29" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M29" s="83">
+      <c r="N29" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>27</v>
       </c>
-      <c r="O29" s="21">
+      <c r="P29" s="21">
         <v>8.76</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>0.4</v>
       </c>
-      <c r="T29" s="89" t="s">
+      <c r="U29" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V29" t="str">
+      <c r="W29" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
         <v>ELCREWON_SOPIPURTSE00</v>
       </c>
-      <c r="W29" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X29" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
         <v>180</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" t="s">
         <v>101</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_OTHER00</v>
@@ -8492,52 +8635,55 @@
       <c r="G30">
         <v>8.130000000000015E-2</v>
       </c>
-      <c r="I30" s="93">
+      <c r="I30" s="7">
+        <v>2</v>
+      </c>
+      <c r="J30" s="93">
         <v>1</v>
       </c>
-      <c r="J30" s="63">
+      <c r="K30" s="63">
         <v>0.3</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L30" s="83">
+      <c r="M30" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M30" s="83">
+      <c r="N30" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>27</v>
       </c>
-      <c r="O30" s="21">
+      <c r="P30" s="21">
         <v>8.76</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>0.4</v>
       </c>
-      <c r="T30" s="89" t="s">
+      <c r="U30" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V30" t="str">
+      <c r="W30" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
         <v>ELCREWON_OTHER00</v>
       </c>
-      <c r="W30" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X30" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>180</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>101</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_SAARE00</v>
@@ -8553,52 +8699,55 @@
       <c r="G31">
         <v>1.6E-2</v>
       </c>
-      <c r="I31" s="93">
+      <c r="I31" s="7">
+        <v>2</v>
+      </c>
+      <c r="J31" s="93">
         <v>1</v>
       </c>
-      <c r="J31" s="63">
+      <c r="K31" s="63">
         <v>0.3</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L31" s="83">
+      <c r="M31" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M31" s="83">
+      <c r="N31" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>27</v>
       </c>
-      <c r="O31" s="21">
+      <c r="P31" s="21">
         <v>8.76</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>0.4</v>
       </c>
-      <c r="T31" s="89" t="s">
+      <c r="U31" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V31" t="str">
+      <c r="W31" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
         <v>ELCREWON_SAARE00</v>
       </c>
-      <c r="W31" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X31" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>180</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>101</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_LVIRU00</v>
@@ -8614,52 +8763,55 @@
       <c r="G32">
         <v>3.27E-2</v>
       </c>
-      <c r="I32" s="93">
+      <c r="I32" s="7">
+        <v>2</v>
+      </c>
+      <c r="J32" s="93">
         <v>1</v>
       </c>
-      <c r="J32" s="63">
+      <c r="K32" s="63">
         <v>0.3</v>
       </c>
-      <c r="K32" s="7">
+      <c r="L32" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L32" s="83">
+      <c r="M32" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M32" s="83">
+      <c r="N32" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>27</v>
       </c>
-      <c r="O32" s="21">
+      <c r="P32" s="21">
         <v>8.76</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>0.4</v>
       </c>
-      <c r="T32" s="89" t="s">
+      <c r="U32" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V32" t="str">
+      <c r="W32" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
         <v>ELCREWON_LVIRU00</v>
       </c>
-      <c r="W32" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X32" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Y32" t="s">
         <v>180</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Z32" t="s">
         <v>101</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B33" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_HARJU00</v>
@@ -8675,52 +8827,55 @@
       <c r="G33">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="I33" s="93">
+      <c r="I33" s="7">
+        <v>2</v>
+      </c>
+      <c r="J33" s="93">
         <v>1</v>
       </c>
-      <c r="J33" s="63">
+      <c r="K33" s="63">
         <v>0.3</v>
       </c>
-      <c r="K33" s="7">
+      <c r="L33" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L33" s="83">
+      <c r="M33" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M33" s="83">
+      <c r="N33" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>27</v>
       </c>
-      <c r="O33" s="21">
+      <c r="P33" s="21">
         <v>8.76</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>0.4</v>
       </c>
-      <c r="T33" s="89" t="s">
+      <c r="U33" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V33" t="str">
+      <c r="W33" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
         <v>ELCREWON_HARJU00</v>
       </c>
-      <c r="W33" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X33" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Y33" t="s">
         <v>180</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Z33" t="s">
         <v>101</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B34" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_LAANE00</v>
@@ -8736,52 +8891,55 @@
       <c r="G34">
         <v>0.06</v>
       </c>
-      <c r="I34" s="93">
+      <c r="I34" s="7">
+        <v>2</v>
+      </c>
+      <c r="J34" s="93">
         <v>1</v>
       </c>
-      <c r="J34" s="63">
+      <c r="K34" s="63">
         <v>0.3</v>
       </c>
-      <c r="K34" s="7">
+      <c r="L34" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L34" s="83">
+      <c r="M34" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M34" s="83">
+      <c r="N34" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>27</v>
       </c>
-      <c r="O34" s="21">
+      <c r="P34" s="21">
         <v>8.76</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>0.4</v>
       </c>
-      <c r="T34" s="89" t="s">
+      <c r="U34" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V34" t="str">
+      <c r="W34" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
         <v>ELCREWON_LAANE00</v>
       </c>
-      <c r="W34" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X34" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
       </c>
-      <c r="X34" t="s">
+      <c r="Y34" t="s">
         <v>180</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>101</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AA34" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B35" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_IVIRU00</v>
@@ -8797,52 +8955,55 @@
       <c r="G35">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="I35" s="93">
+      <c r="I35" s="7">
+        <v>2</v>
+      </c>
+      <c r="J35" s="93">
         <v>1</v>
       </c>
-      <c r="J35" s="63">
+      <c r="K35" s="63">
         <v>0.3</v>
       </c>
-      <c r="K35" s="7">
+      <c r="L35" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L35" s="83">
+      <c r="M35" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M35" s="83">
+      <c r="N35" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>27</v>
       </c>
-      <c r="O35" s="21">
+      <c r="P35" s="21">
         <v>8.76</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>0.4</v>
       </c>
-      <c r="T35" s="89" t="s">
+      <c r="U35" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V35" t="str">
+      <c r="W35" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
         <v>ELCREWON_IVIRU00</v>
       </c>
-      <c r="W35" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X35" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
         <v>180</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="Z35" t="s">
         <v>101</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AA35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B36" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREWON_PARNU00</v>
@@ -8858,52 +9019,55 @@
       <c r="G36">
         <v>0.1036</v>
       </c>
-      <c r="I36" s="93">
+      <c r="I36" s="7">
+        <v>2</v>
+      </c>
+      <c r="J36" s="93">
         <v>1</v>
       </c>
-      <c r="J36" s="63">
+      <c r="K36" s="63">
         <v>0.3</v>
       </c>
-      <c r="K36" s="7">
+      <c r="L36" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="L36" s="83">
+      <c r="M36" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="M36" s="83">
+      <c r="N36" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>27</v>
       </c>
-      <c r="O36" s="21">
+      <c r="P36" s="21">
         <v>8.76</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>0.4</v>
       </c>
-      <c r="T36" s="89" t="s">
+      <c r="U36" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V36" t="str">
+      <c r="W36" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
         <v>ELCREWON_PARNU00</v>
       </c>
-      <c r="W36" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="X36" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
       </c>
-      <c r="X36" t="s">
+      <c r="Y36" t="s">
         <v>180</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="Z36" t="s">
         <v>101</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AA36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ELCREMSW_IRU00</v>
@@ -8919,54 +9083,57 @@
       <c r="G37" s="21">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="7">
+        <v>2</v>
+      </c>
+      <c r="J37" s="21">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J37" s="21">
+      <c r="K37" s="21">
         <v>0.9</v>
       </c>
-      <c r="K37" s="79">
+      <c r="L37" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L37" s="79">
+      <c r="M37" s="79">
         <v>160.216352398</v>
       </c>
-      <c r="M37" s="79">
+      <c r="N37" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="N37" s="79">
+      <c r="O37" s="79">
         <v>53</v>
       </c>
-      <c r="O37" s="21">
+      <c r="P37" s="21">
         <v>8.76</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>1</v>
       </c>
-      <c r="T37" s="89" t="s">
+      <c r="U37" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V37" t="str">
+      <c r="W37" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)&amp;"_IRU"&amp;"00"</f>
         <v>ELCREMSW_IRU00</v>
       </c>
-      <c r="W37" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V37,2)&amp;" Iru Power plant - Municipal waste"</f>
+      <c r="X37" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W37,2)&amp;" Iru Power plant - Municipal waste"</f>
         <v>Power Plants Existing00 Iru Power plant - Municipal waste</v>
       </c>
-      <c r="X37" t="s">
+      <c r="Y37" t="s">
         <v>180</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Z37" t="s">
         <v>101</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AA37" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B38" s="21" t="str">
-        <f>V38</f>
+        <f>W38</f>
         <v>ELCTESHL_EESTI00</v>
       </c>
       <c r="C38" s="21" t="str">
@@ -8980,55 +9147,58 @@
       <c r="G38" s="21">
         <v>0.77</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="7">
+        <v>2</v>
+      </c>
+      <c r="J38" s="21">
         <v>0.33</v>
       </c>
-      <c r="J38" s="21">
+      <c r="K38" s="21">
         <v>0.95</v>
       </c>
-      <c r="K38" s="79">
+      <c r="L38" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L38" s="79">
+      <c r="M38" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M38" s="79">
+      <c r="N38" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N38" s="79">
+      <c r="O38" s="79">
         <v>40</v>
       </c>
-      <c r="O38" s="21">
+      <c r="P38" s="21">
         <v>8.76</v>
       </c>
-      <c r="P38" s="21">
+      <c r="Q38" s="21">
         <v>1</v>
       </c>
-      <c r="T38" s="89" t="s">
+      <c r="U38" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U38" s="89"/>
-      <c r="V38" s="89" t="str">
+      <c r="V38" s="89"/>
+      <c r="W38" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_EESTI00"</f>
         <v>ELCTESHL_EESTI00</v>
       </c>
-      <c r="W38" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V38,2)&amp;" Eesti Power plant - Oil Shale"</f>
+      <c r="X38" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W38,2)&amp;" Eesti Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Eesti Power plant - Oil Shale</v>
       </c>
-      <c r="X38" t="s">
+      <c r="Y38" t="s">
         <v>180</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="Z38" t="s">
         <v>101</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B39" s="21" t="str">
-        <f>V39</f>
+        <f>W39</f>
         <v>ELCTESHL_AUVERE00</v>
       </c>
       <c r="C39" s="21" t="str">
@@ -9042,55 +9212,58 @@
       <c r="G39" s="21">
         <v>0.26</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="7">
+        <v>2</v>
+      </c>
+      <c r="J39" s="21">
         <v>0.33</v>
       </c>
-      <c r="J39" s="21">
+      <c r="K39" s="21">
         <v>0.95</v>
       </c>
-      <c r="K39" s="79">
+      <c r="L39" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L39" s="79">
+      <c r="M39" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M39" s="79">
+      <c r="N39" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N39" s="21">
+      <c r="O39" s="21">
         <v>40</v>
       </c>
-      <c r="O39" s="21">
+      <c r="P39" s="21">
         <v>8.76</v>
       </c>
-      <c r="P39" s="21">
+      <c r="Q39" s="21">
         <v>1</v>
       </c>
-      <c r="T39" s="89" t="s">
+      <c r="U39" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U39" s="89"/>
-      <c r="V39" s="89" t="str">
+      <c r="V39" s="89"/>
+      <c r="W39" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_AUVERE00"</f>
         <v>ELCTESHL_AUVERE00</v>
       </c>
-      <c r="W39" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V39,2)&amp;" Auvere Power plant - Oil Shale"</f>
+      <c r="X39" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W39,2)&amp;" Auvere Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Auvere Power plant - Oil Shale</v>
       </c>
-      <c r="X39" t="s">
+      <c r="Y39" t="s">
         <v>180</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Z39" t="s">
         <v>101</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B40" s="21" t="str">
-        <f>V40</f>
+        <f>W40</f>
         <v>ELCTESHL_ENEFIT00</v>
       </c>
       <c r="C40" s="21" t="str">
@@ -9104,55 +9277,58 @@
       <c r="G40" s="21">
         <v>0.01</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="7">
+        <v>2</v>
+      </c>
+      <c r="J40" s="21">
         <v>0.33</v>
       </c>
-      <c r="J40" s="21">
+      <c r="K40" s="21">
         <v>0.95</v>
       </c>
-      <c r="K40" s="79">
+      <c r="L40" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L40" s="79">
+      <c r="M40" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M40" s="79">
+      <c r="N40" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N40" s="21">
+      <c r="O40" s="21">
         <v>40</v>
       </c>
-      <c r="O40" s="21">
+      <c r="P40" s="21">
         <v>8.76</v>
       </c>
-      <c r="P40" s="21">
+      <c r="Q40" s="21">
         <v>1</v>
       </c>
-      <c r="T40" s="89" t="s">
+      <c r="U40" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U40" s="89"/>
-      <c r="V40" s="89" t="str">
+      <c r="V40" s="89"/>
+      <c r="W40" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_ENEFIT00"</f>
         <v>ELCTESHL_ENEFIT00</v>
       </c>
-      <c r="W40" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V40,2)&amp;" Eenefit Power plant - Oil Shale"</f>
+      <c r="X40" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W40,2)&amp;" Eenefit Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Eenefit Power plant - Oil Shale</v>
       </c>
-      <c r="X40" t="s">
+      <c r="Y40" t="s">
         <v>180</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Z40" t="s">
         <v>101</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AA40" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B41" s="21" t="str">
-        <f>V41</f>
+        <f>W41</f>
         <v>ELCTESHL_BALTI00</v>
       </c>
       <c r="C41" s="21" t="str">
@@ -9166,55 +9342,58 @@
       <c r="G41" s="21">
         <v>0.185</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="7">
+        <v>2</v>
+      </c>
+      <c r="J41" s="21">
         <v>0.33</v>
       </c>
-      <c r="J41" s="21">
+      <c r="K41" s="21">
         <v>0.95</v>
       </c>
-      <c r="K41" s="79">
+      <c r="L41" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L41" s="79">
+      <c r="M41" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M41" s="79">
+      <c r="N41" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N41" s="21">
+      <c r="O41" s="21">
         <v>40</v>
       </c>
-      <c r="O41" s="21">
+      <c r="P41" s="21">
         <v>8.76</v>
       </c>
-      <c r="P41" s="21">
+      <c r="Q41" s="21">
         <v>1</v>
       </c>
-      <c r="T41" s="89" t="s">
+      <c r="U41" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U41" s="89"/>
-      <c r="V41" s="89" t="str">
+      <c r="V41" s="89"/>
+      <c r="W41" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_BALTI00"</f>
         <v>ELCTESHL_BALTI00</v>
       </c>
-      <c r="W41" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V41,2)&amp;" Balti Power plant - Oil Shale"</f>
+      <c r="X41" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W41,2)&amp;" Balti Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Balti Power plant - Oil Shale</v>
       </c>
-      <c r="X41" t="s">
+      <c r="Y41" t="s">
         <v>180</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="Z41" t="s">
         <v>101</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AA41" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B42" s="21" t="str">
-        <f>V42</f>
+        <f>W42</f>
         <v>ELCTESHL_SILLAMAE00</v>
       </c>
       <c r="C42" s="21" t="str">
@@ -9228,54 +9407,57 @@
       <c r="G42" s="21">
         <v>0.01</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="7">
+        <v>2</v>
+      </c>
+      <c r="J42" s="21">
         <v>0.33</v>
       </c>
-      <c r="J42" s="21">
+      <c r="K42" s="21">
         <v>0.95</v>
       </c>
-      <c r="K42" s="79">
+      <c r="L42" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="L42" s="79">
+      <c r="M42" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="M42" s="79">
+      <c r="N42" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="N42" s="21">
+      <c r="O42" s="21">
         <v>40</v>
       </c>
-      <c r="O42" s="21">
+      <c r="P42" s="21">
         <v>8.76</v>
       </c>
-      <c r="P42" s="21">
+      <c r="Q42" s="21">
         <v>1</v>
       </c>
-      <c r="T42" s="89" t="s">
+      <c r="U42" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V42" s="89" t="str">
+      <c r="W42" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_SILLAMAE00"</f>
         <v>ELCTESHL_SILLAMAE00</v>
       </c>
-      <c r="W42" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V42,2)&amp;" Sillamae Power plant - Oil Shale"</f>
+      <c r="X42" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W42,2)&amp;" Sillamae Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Sillamae Power plant - Oil Shale</v>
       </c>
-      <c r="X42" t="s">
+      <c r="Y42" t="s">
         <v>180</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Z42" t="s">
         <v>101</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="AA42" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B43" s="21" t="str">
-        <f t="shared" ref="B43:B45" si="3">V43</f>
+        <f t="shared" ref="B43:B45" si="3">W43</f>
         <v>ELCTEGAS_POHJA00</v>
       </c>
       <c r="C43" s="21" t="str">
@@ -9289,53 +9471,56 @@
       <c r="G43" s="21">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I43" s="74">
+      <c r="I43" s="7">
+        <v>2</v>
+      </c>
+      <c r="J43" s="74">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J43" s="21">
+      <c r="K43" s="21">
         <v>0.95</v>
       </c>
-      <c r="K43" s="79">
+      <c r="L43" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L43" s="79">
+      <c r="M43" s="79">
         <v>39.138495576499992</v>
       </c>
-      <c r="M43" s="79">
+      <c r="N43" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="N43" s="79">
+      <c r="O43" s="79">
         <v>40</v>
       </c>
-      <c r="O43" s="21">
+      <c r="P43" s="21">
         <v>8.76</v>
       </c>
-      <c r="P43" s="21">
+      <c r="Q43" s="21">
         <v>1</v>
       </c>
-      <c r="T43" s="89" t="s">
+      <c r="U43" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="U43" s="89"/>
-      <c r="V43" s="89" t="str">
+      <c r="V43" s="89"/>
+      <c r="W43" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_POHJA00"</f>
         <v>ELCTEGAS_POHJA00</v>
       </c>
-      <c r="W43" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V43,2)&amp;" Pohja Power plant - "&amp;'EB1'!E3</f>
+      <c r="X43" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W43,2)&amp;" Pohja Power plant - "&amp;'EB1'!E3</f>
         <v>Power Plants Existing00 Pohja Power plant - Natural Gas</v>
       </c>
-      <c r="X43" t="s">
+      <c r="Y43" t="s">
         <v>180</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="Z43" t="s">
         <v>101</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AA43" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B44" s="21" t="str">
         <f t="shared" si="3"/>
         <v>ELCTEBIO_TLNUTILITAS00</v>
@@ -9351,52 +9536,55 @@
       <c r="G44" s="21">
         <v>3.9E-2</v>
       </c>
-      <c r="I44" s="74">
+      <c r="I44" s="7">
+        <v>2</v>
+      </c>
+      <c r="J44" s="74">
         <v>0.46800000000000003</v>
       </c>
-      <c r="J44" s="21">
+      <c r="K44" s="21">
         <v>0.95</v>
       </c>
-      <c r="K44" s="79">
+      <c r="L44" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L44" s="79">
+      <c r="M44" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M44" s="79">
+      <c r="N44" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N44" s="79">
+      <c r="O44" s="79">
         <v>40</v>
       </c>
-      <c r="O44" s="21">
+      <c r="P44" s="21">
         <v>8.76</v>
       </c>
-      <c r="P44" s="21">
+      <c r="Q44" s="21">
         <v>1</v>
       </c>
-      <c r="T44" s="89" t="s">
+      <c r="U44" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V44" s="89" t="str">
+      <c r="W44" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TLNUTILITAS00"</f>
         <v>ELCTEBIO_TLNUTILITAS00</v>
       </c>
-      <c r="W44" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V44,2)&amp;" Tallinn Utilitas Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="X44" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W44,2)&amp;" Tallinn Utilitas Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Tallinn Utilitas Power plant - Biomass</v>
       </c>
-      <c r="X44" t="s">
+      <c r="Y44" t="s">
         <v>180</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="Z44" t="s">
         <v>101</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AA44" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B45" s="21" t="str">
         <f t="shared" si="3"/>
         <v>ELCTEBIO_TARTU00</v>
@@ -9412,54 +9600,57 @@
       <c r="G45" s="21">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="I45" s="74">
+      <c r="I45" s="7">
+        <v>2</v>
+      </c>
+      <c r="J45" s="74">
         <v>0.46800000000000003</v>
       </c>
-      <c r="J45" s="21">
+      <c r="K45" s="21">
         <v>0.95</v>
       </c>
-      <c r="K45" s="79">
+      <c r="L45" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L45" s="79">
+      <c r="M45" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M45" s="79">
+      <c r="N45" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N45" s="79">
+      <c r="O45" s="79">
         <v>40</v>
       </c>
-      <c r="O45" s="21">
+      <c r="P45" s="21">
         <v>8.76</v>
       </c>
-      <c r="P45" s="21">
+      <c r="Q45" s="21">
         <v>1</v>
       </c>
-      <c r="T45" s="89" t="s">
+      <c r="U45" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V45" s="89" t="str">
+      <c r="W45" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TARTU00"</f>
         <v>ELCTEBIO_TARTU00</v>
       </c>
-      <c r="W45" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V45,2)&amp;" Tartu Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="X45" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W45,2)&amp;" Tartu Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Tartu Power plant - Biomass</v>
       </c>
-      <c r="X45" t="s">
+      <c r="Y45" t="s">
         <v>180</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="Z45" t="s">
         <v>101</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AA45" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B46" s="21" t="str">
-        <f>V46</f>
+        <f>W46</f>
         <v>ELCTEBIO_PARNU00</v>
       </c>
       <c r="C46" s="21" t="str">
@@ -9473,54 +9664,57 @@
       <c r="G46" s="21">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="I46" s="74">
+      <c r="I46" s="7">
+        <v>2</v>
+      </c>
+      <c r="J46" s="74">
         <v>0.46800000000000003</v>
       </c>
-      <c r="J46" s="21">
+      <c r="K46" s="21">
         <v>0.95</v>
       </c>
-      <c r="K46" s="79">
+      <c r="L46" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L46" s="79">
+      <c r="M46" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M46" s="79">
+      <c r="N46" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N46" s="79">
+      <c r="O46" s="79">
         <v>40</v>
       </c>
-      <c r="O46" s="21">
+      <c r="P46" s="21">
         <v>8.76</v>
       </c>
-      <c r="P46" s="21">
+      <c r="Q46" s="21">
         <v>1</v>
       </c>
-      <c r="T46" s="89" t="s">
+      <c r="U46" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V46" s="89" t="str">
+      <c r="W46" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PARNU00"</f>
         <v>ELCTEBIO_PARNU00</v>
       </c>
-      <c r="W46" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V46,2)&amp;" Parnu Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="X46" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W46,2)&amp;" Parnu Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Parnu Power plant - Biomass</v>
       </c>
-      <c r="X46" t="s">
+      <c r="Y46" t="s">
         <v>180</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="Z46" t="s">
         <v>101</v>
       </c>
-      <c r="Z46" t="s">
+      <c r="AA46" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B47" s="21" t="str">
-        <f>V47</f>
+        <f>W47</f>
         <v>ELCTEBIO_HORIZON00</v>
       </c>
       <c r="C47" s="21" t="str">
@@ -9534,54 +9728,57 @@
       <c r="G47" s="21">
         <v>1.3900000000000001E-2</v>
       </c>
-      <c r="I47" s="74">
+      <c r="I47" s="7">
+        <v>2</v>
+      </c>
+      <c r="J47" s="74">
         <v>0.46800000000000003</v>
       </c>
-      <c r="J47" s="21">
+      <c r="K47" s="21">
         <v>0.95</v>
       </c>
-      <c r="K47" s="79">
+      <c r="L47" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="L47" s="79">
+      <c r="M47" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="M47" s="79">
+      <c r="N47" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="N47" s="79">
+      <c r="O47" s="79">
         <v>40</v>
       </c>
-      <c r="O47" s="21">
+      <c r="P47" s="21">
         <v>8.76</v>
       </c>
-      <c r="P47" s="21">
+      <c r="Q47" s="21">
         <v>1</v>
       </c>
-      <c r="T47" s="89" t="s">
+      <c r="U47" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V47" s="89" t="str">
+      <c r="W47" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HORIZON00"</f>
         <v>ELCTEBIO_HORIZON00</v>
       </c>
-      <c r="W47" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V47,2)&amp;" Horizon Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="X47" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W47,2)&amp;" Horizon Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Horizon Power plant - Biomass</v>
       </c>
-      <c r="X47" t="s">
+      <c r="Y47" t="s">
         <v>180</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="Z47" t="s">
         <v>101</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="AA47" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B48" s="21" t="str">
-        <f>V48</f>
+        <f>W48</f>
         <v>ELCTEGAS_GRUNE00</v>
       </c>
       <c r="C48" s="21" t="str">
@@ -9595,53 +9792,56 @@
       <c r="G48" s="21">
         <v>4.0999999999999995E-3</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="7">
+        <v>2</v>
+      </c>
+      <c r="J48">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J48" s="21">
+      <c r="K48" s="21">
         <v>0.95</v>
       </c>
-      <c r="K48" s="7">
+      <c r="L48" s="7">
         <v>1175.5066999999999</v>
       </c>
-      <c r="L48" s="83">
+      <c r="M48" s="83">
         <v>39.138495576499992</v>
       </c>
-      <c r="M48" s="83">
+      <c r="N48" s="83">
         <v>5.8775000000000004</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>40</v>
       </c>
-      <c r="O48" s="21">
+      <c r="P48" s="21">
         <v>8.76</v>
       </c>
-      <c r="P48" s="21">
+      <c r="Q48" s="21">
         <v>1</v>
       </c>
-      <c r="T48" s="89" t="s">
+      <c r="U48" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V48" s="89" t="str">
+      <c r="W48" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_GRUNE00"</f>
         <v>ELCTEGAS_GRUNE00</v>
       </c>
-      <c r="W48" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(V48,2)&amp;" GRUNE Power plant - "&amp;'EB1'!$E$3</f>
+      <c r="X48" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W48,2)&amp;" GRUNE Power plant - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 GRUNE Power plant - Natural Gas</v>
       </c>
-      <c r="X48" t="s">
+      <c r="Y48" t="s">
         <v>180</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="Z48" t="s">
         <v>101</v>
       </c>
-      <c r="Z48" t="s">
+      <c r="AA48" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="65529" spans="19:19" x14ac:dyDescent="0.2">
-      <c r="S65529" s="29"/>
+    <row r="65529" spans="20:20" x14ac:dyDescent="0.2">
+      <c r="T65529" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10054,7 +10254,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D12" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E12">
@@ -10122,7 +10322,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D13" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E13">
@@ -10190,7 +10390,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D14" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E14">
@@ -10258,7 +10458,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D15" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E15">
@@ -10326,7 +10526,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D16" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E16">
@@ -10394,7 +10594,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D17" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E17">
@@ -10462,7 +10662,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D18" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E18">
@@ -10530,7 +10730,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D19" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E19">
@@ -10594,7 +10794,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D20" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E20">
@@ -10658,7 +10858,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D21" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E21">
@@ -10722,7 +10922,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D22" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E22">
@@ -10786,7 +10986,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D23" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E23">
@@ -10850,7 +11050,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D24" s="92" t="str">
-        <f>ELC!$V$5</f>
+        <f>ELC!$W$5</f>
         <v>ELC</v>
       </c>
       <c r="E24">
@@ -11210,7 +11410,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="21" t="str">
-        <f>ELC!$V$6</f>
+        <f>ELC!$W$6</f>
         <v>ELCCO2</v>
       </c>
       <c r="C8" s="63">

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82AF2F4-6681-4C4E-B585-55D05881DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792619DC-794A-4EFD-87FE-9336FA30E4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -789,7 +789,7 @@
     <author>Kristopher Raik</author>
   </authors>
   <commentList>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -903,7 +903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="AA3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -929,7 +929,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="AB3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1002,7 +1002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="AC3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1055,7 +1055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="AD3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1114,7 +1114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="AB9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1207,7 +1207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="AC9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1232,7 +1232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="AD9" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1295,7 +1295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="V10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -2333,7 +2333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="210">
   <si>
     <t>CommName</t>
   </si>
@@ -2954,6 +2954,15 @@
   </si>
   <si>
     <t>PASTI~2025</t>
+  </si>
+  <si>
+    <t>TWh2PJ</t>
+  </si>
+  <si>
+    <t>Efficiency TWh -&gt; PJ</t>
+  </si>
+  <si>
+    <t>EFF TWh</t>
   </si>
 </sst>
 </file>
@@ -3530,7 +3539,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3749,6 +3758,7 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="31">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3959,13 +3969,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>871640</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>120128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>692699</xdr:colOff>
       <xdr:row>71</xdr:row>
       <xdr:rowOff>115715</xdr:rowOff>
@@ -6972,7 +6982,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:AC65529"/>
+  <dimension ref="B1:AD65529"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -6981,30 +6991,30 @@
     <col min="4" max="4" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="21" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="21" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2" style="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.28515625" customWidth="1"/>
-    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.85546875" style="21"/>
+    <col min="9" max="10" width="13" style="21" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15" style="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.85546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:30" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="20" t="s">
         <v>65</v>
       </c>
@@ -7027,8 +7037,9 @@
         <v>83</v>
       </c>
       <c r="I1" s="20"/>
-    </row>
-    <row r="2" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="2:30" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -7055,48 +7066,49 @@
         <v>84</v>
       </c>
       <c r="I2" s="10"/>
-      <c r="U2" s="84" t="s">
+      <c r="J2" s="10"/>
+      <c r="V2" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="84"/>
-      <c r="W2" s="85"/>
+      <c r="W2" s="84"/>
       <c r="X2" s="85"/>
       <c r="Y2" s="85"/>
       <c r="Z2" s="85"/>
       <c r="AA2" s="85"/>
       <c r="AB2" s="85"/>
       <c r="AC2" s="85"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="U3" s="86" t="s">
+      <c r="AD2" s="85"/>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="V3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="V3" s="87" t="s">
+      <c r="W3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="86" t="s">
+      <c r="X3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="X3" s="86" t="s">
+      <c r="Y3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="86" t="s">
+      <c r="Z3" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="86" t="s">
+      <c r="AA3" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="AA3" s="86" t="s">
+      <c r="AB3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="86" t="s">
+      <c r="AC3" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="AC3" s="86" t="s">
+      <c r="AD3" s="86" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:29" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:30" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>107</v>
       </c>
@@ -7114,36 +7126,37 @@
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="U4" s="88" t="s">
+      <c r="J4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="V4" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="V4" s="88" t="s">
+      <c r="W4" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="W4" s="88" t="s">
+      <c r="X4" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="88" t="s">
+      <c r="Y4" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="88" t="s">
+      <c r="Z4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="Z4" s="88" t="s">
+      <c r="AA4" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="AA4" s="88" t="s">
+      <c r="AB4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="88" t="s">
+      <c r="AC4" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="AC4" s="88" t="s">
+      <c r="AD4" s="88" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
@@ -7161,58 +7174,64 @@
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="U5" s="85" t="s">
+      <c r="J5" s="9"/>
+      <c r="L5" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="V5" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="V5" s="89"/>
-      <c r="W5" s="85" t="s">
+      <c r="W5" s="89"/>
+      <c r="X5" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="X5" s="85" t="str">
+      <c r="Y5" s="85" t="str">
         <f>'EB1'!$W$3</f>
         <v>Electricity</v>
       </c>
-      <c r="Y5" s="85" t="str">
-        <f>$E$2</f>
-        <v>PJ</v>
-      </c>
-      <c r="Z5" s="85"/>
-      <c r="AA5" s="85" t="s">
+      <c r="Z5" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="85" t="s">
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="U6" s="89" t="s">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="L6" s="21">
+        <v>3.6</v>
+      </c>
+      <c r="V6" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="V6" s="89"/>
-      <c r="W6" s="89" t="str">
+      <c r="W6" s="89"/>
+      <c r="X6" s="89" t="str">
         <f>$B$2&amp;'EB1'!$C$15</f>
         <v>ELCCO2</v>
       </c>
-      <c r="X6" s="89" t="str">
+      <c r="Y6" s="89" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$16</f>
         <v>Electricity Plants Carbon dioxide</v>
       </c>
-      <c r="Y6" s="89" t="str">
+      <c r="Z6" s="89" t="str">
         <f>'EB1'!$AC$2</f>
         <v>kt</v>
       </c>
-      <c r="Z6" s="89"/>
       <c r="AA6" s="89"/>
       <c r="AB6" s="89"/>
       <c r="AC6" s="89"/>
-    </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="U7" s="2"/>
+      <c r="AD6" s="89"/>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.2">
       <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -7222,22 +7241,23 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="M8" s="5"/>
+      <c r="K8" s="4"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="3"/>
-      <c r="U8" s="84" t="s">
+      <c r="O8" s="5"/>
+      <c r="P8" s="3"/>
+      <c r="V8" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="84"/>
-      <c r="W8" s="85"/>
+      <c r="W8" s="84"/>
       <c r="X8" s="85"/>
       <c r="Y8" s="85"/>
       <c r="Z8" s="85"/>
       <c r="AA8" s="85"/>
       <c r="AB8" s="85"/>
       <c r="AC8" s="85"/>
-    </row>
-    <row r="9" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD8" s="85"/>
+    </row>
+    <row r="9" spans="2:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -7263,63 +7283,66 @@
         <v>205</v>
       </c>
       <c r="J9" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="67" t="s">
+      <c r="L9" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="L9" s="67" t="s">
+      <c r="M9" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="M9" s="67" t="s">
+      <c r="N9" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="67" t="s">
+      <c r="O9" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="O9" s="67" t="s">
+      <c r="P9" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="P9" s="67" t="s">
+      <c r="Q9" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="Q9" s="67" t="s">
+      <c r="R9" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="R9" s="23"/>
-      <c r="S9" s="80" t="s">
+      <c r="S9" s="23"/>
+      <c r="T9" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="T9" s="27"/>
-      <c r="U9" s="86" t="s">
+      <c r="U9" s="27"/>
+      <c r="V9" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="V9" s="87" t="s">
+      <c r="W9" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="W9" s="86" t="s">
+      <c r="X9" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="X9" s="86" t="s">
+      <c r="Y9" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="Y9" s="86" t="s">
+      <c r="Z9" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="Z9" s="86" t="s">
+      <c r="AA9" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="AA9" s="86" t="s">
+      <c r="AB9" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="AB9" s="86" t="s">
+      <c r="AC9" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="AC9" s="86" t="s">
+      <c r="AD9" s="86" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:29" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:30" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -7343,62 +7366,65 @@
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="L10" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="Q10" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="R10" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="S10" s="30" t="s">
+      <c r="T10" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="T10" s="28"/>
-      <c r="U10" s="88" t="s">
+      <c r="U10" s="28"/>
+      <c r="V10" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="V10" s="88" t="s">
+      <c r="W10" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="W10" s="88" t="s">
+      <c r="X10" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="X10" s="88" t="s">
+      <c r="Y10" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="Y10" s="88" t="s">
+      <c r="Z10" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="Z10" s="88" t="s">
+      <c r="AA10" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="AA10" s="88" t="s">
+      <c r="AB10" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="AB10" s="88" t="s">
+      <c r="AC10" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="AC10" s="88" t="s">
+      <c r="AD10" s="88" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -7421,35 +7447,35 @@
         <v>GW</v>
       </c>
       <c r="I11" s="68"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="13" t="str">
-        <f>$G$2&amp;"/"&amp;$F$2</f>
-        <v>M€2025/GW</v>
-      </c>
+      <c r="J11" s="68"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="68"/>
       <c r="M11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
       <c r="N11" s="13" t="str">
+        <f>$G$2&amp;"/"&amp;$F$2</f>
+        <v>M€2025/GW</v>
+      </c>
+      <c r="O11" s="13" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2025/PJ</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="Q11" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="Q11" s="13"/>
-      <c r="S11" s="81" t="s">
+      <c r="R11" s="13"/>
+      <c r="T11" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="88" t="s">
+      <c r="U11" s="28"/>
+      <c r="V11" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="V11" s="88"/>
       <c r="W11" s="88"/>
       <c r="X11" s="88"/>
       <c r="Y11" s="88"/>
@@ -7457,10 +7483,11 @@
       <c r="AA11" s="88"/>
       <c r="AB11" s="88"/>
       <c r="AC11" s="88"/>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="88"/>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B12" s="21" t="str">
-        <f>W12</f>
+        <f>X12</f>
         <v>ELCREHYD00</v>
       </c>
       <c r="C12" s="21" t="str">
@@ -7468,7 +7495,7 @@
         <v>ELCHYD</v>
       </c>
       <c r="D12" s="21" t="str">
-        <f t="shared" ref="D12:D48" si="0">$W$5</f>
+        <f t="shared" ref="D12:D48" si="0">$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E12" s="42"/>
@@ -7483,52 +7510,56 @@
       <c r="J12" s="63">
         <v>1</v>
       </c>
-      <c r="K12" s="63">
+      <c r="K12" s="21">
+        <f>J12*$L$6</f>
+        <v>3.6</v>
+      </c>
+      <c r="L12" s="63">
         <v>0.5</v>
       </c>
-      <c r="L12" s="63"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="64">
+      <c r="M12" s="63"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q12" s="65">
+      <c r="R12" s="65">
         <v>0.5</v>
       </c>
-      <c r="S12" s="26">
-        <f>(E12+F12)*$K12*$P12</f>
+      <c r="T12" s="26">
+        <f>(E12+F12)*$L12*$Q12</f>
         <v>0</v>
       </c>
-      <c r="T12" s="29"/>
-      <c r="U12" s="89" t="s">
+      <c r="U12" s="29"/>
+      <c r="V12" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V12" s="89"/>
-      <c r="W12" s="89" t="str">
+      <c r="W12" s="89"/>
+      <c r="X12" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$10,3)&amp;"00"</f>
         <v>ELCREHYD00</v>
       </c>
-      <c r="X12" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W12,2)&amp;" - "&amp;'EB1'!P3</f>
+      <c r="Y12" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X12,2)&amp;" - "&amp;'EB1'!P3</f>
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Z12" t="s">
         <v>180</v>
       </c>
-      <c r="Z12" s="89" t="str">
-        <f t="shared" ref="Z12" si="1">$F$2</f>
+      <c r="AA12" s="89" t="str">
+        <f t="shared" ref="AA12" si="1">$F$2</f>
         <v>GW</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>116</v>
       </c>
-      <c r="AB12" s="89"/>
       <c r="AC12" s="89"/>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="89"/>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B13" s="21" t="str">
-        <f>W13</f>
+        <f>X13</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
       <c r="C13" s="21" t="str">
@@ -7548,51 +7579,55 @@
       <c r="J13" s="93">
         <v>1</v>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="21">
+        <f t="shared" ref="K13:K48" si="2">J13*$L$6</f>
+        <v>3.6</v>
+      </c>
+      <c r="L13" s="63">
         <v>0.3</v>
       </c>
-      <c r="L13" s="7">
+      <c r="M13" s="7">
         <v>1018</v>
       </c>
-      <c r="M13" s="83">
+      <c r="N13" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N13" s="83">
+      <c r="O13" s="83">
         <v>0</v>
       </c>
-      <c r="O13" s="21">
+      <c r="P13" s="21">
         <v>35</v>
       </c>
-      <c r="P13" s="64">
+      <c r="Q13" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q13" s="74">
+      <c r="R13" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U13" s="89" t="s">
+      <c r="V13" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W13" s="89" t="str">
+      <c r="X13" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B3&amp;"00"</f>
         <v>ELCRESOL_PARNU00</v>
       </c>
-      <c r="X13" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y13" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X13,2)&amp;" in "&amp;Intra_areas!B3&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in PARNU - Solar energy</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
         <v>180</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AA13" t="s">
         <v>101</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B14" s="21" t="str">
-        <f t="shared" ref="B14:B37" si="2">W14</f>
+        <f t="shared" ref="B14:B37" si="3">X14</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
       <c r="C14" s="21" t="str">
@@ -7612,52 +7647,56 @@
       <c r="J14" s="93">
         <v>1</v>
       </c>
-      <c r="K14" s="63">
+      <c r="K14" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L14" s="63">
         <v>0.3</v>
       </c>
-      <c r="L14" s="7">
+      <c r="M14" s="7">
         <v>1018</v>
       </c>
-      <c r="M14" s="83">
+      <c r="N14" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N14" s="83">
+      <c r="O14" s="83">
         <v>0</v>
       </c>
-      <c r="O14" s="21">
+      <c r="P14" s="21">
         <v>35</v>
       </c>
-      <c r="P14" s="64">
+      <c r="Q14" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q14" s="74">
+      <c r="R14" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="S14" s="79"/>
-      <c r="U14" s="89" t="s">
+      <c r="T14" s="79"/>
+      <c r="V14" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W14" s="89" t="str">
+      <c r="X14" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B4&amp;"00"</f>
         <v>ELCRESOL_TARTU00</v>
       </c>
-      <c r="X14" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y14" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X14,2)&amp;" in "&amp;Intra_areas!B4&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in TARTU - Solar energy</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
         <v>180</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AA14" t="s">
         <v>101</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B15" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_LVIRU00</v>
       </c>
       <c r="C15" s="21" t="str">
@@ -7677,52 +7716,56 @@
       <c r="J15" s="93">
         <v>1</v>
       </c>
-      <c r="K15" s="63">
+      <c r="K15" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L15" s="63">
         <v>0.3</v>
       </c>
-      <c r="L15" s="7">
+      <c r="M15" s="7">
         <v>1018</v>
       </c>
-      <c r="M15" s="83">
+      <c r="N15" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N15" s="83">
+      <c r="O15" s="83">
         <v>0</v>
       </c>
-      <c r="O15" s="21">
+      <c r="P15" s="21">
         <v>35</v>
       </c>
-      <c r="P15" s="64">
+      <c r="Q15" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q15" s="74">
+      <c r="R15" s="74">
         <v>0.14867925344692126</v>
       </c>
-      <c r="S15" s="79"/>
-      <c r="U15" s="89" t="s">
+      <c r="T15" s="79"/>
+      <c r="V15" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W15" s="89" t="str">
+      <c r="X15" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B5&amp;"00"</f>
         <v>ELCRESOL_LVIRU00</v>
       </c>
-      <c r="X15" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y15" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X15,2)&amp;" in "&amp;Intra_areas!B5&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LVIRU - Solar energy</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Z15" t="s">
         <v>180</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>101</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B16" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_IVIRU00</v>
       </c>
       <c r="C16" s="21" t="str">
@@ -7742,52 +7785,56 @@
       <c r="J16" s="93">
         <v>1</v>
       </c>
-      <c r="K16" s="63">
+      <c r="K16" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L16" s="63">
         <v>0.3</v>
       </c>
-      <c r="L16" s="7">
+      <c r="M16" s="7">
         <v>1018</v>
       </c>
-      <c r="M16" s="83">
+      <c r="N16" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N16" s="83">
+      <c r="O16" s="83">
         <v>0</v>
       </c>
-      <c r="O16" s="21">
+      <c r="P16" s="21">
         <v>35</v>
       </c>
-      <c r="P16" s="64">
+      <c r="Q16" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q16" s="74">
+      <c r="R16" s="74">
         <v>0.14701259708091721</v>
       </c>
-      <c r="S16" s="79"/>
-      <c r="U16" s="89" t="s">
+      <c r="T16" s="79"/>
+      <c r="V16" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W16" s="89" t="str">
+      <c r="X16" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B6&amp;"00"</f>
         <v>ELCRESOL_IVIRU00</v>
       </c>
-      <c r="X16" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y16" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X16,2)&amp;" in "&amp;Intra_areas!B6&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in IVIRU - Solar energy</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Z16" t="s">
         <v>180</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>101</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B17" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_JARVA00</v>
       </c>
       <c r="C17" s="21" t="str">
@@ -7807,52 +7854,56 @@
       <c r="J17" s="93">
         <v>1</v>
       </c>
-      <c r="K17" s="63">
+      <c r="K17" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L17" s="63">
         <v>0.3</v>
       </c>
-      <c r="L17" s="7">
+      <c r="M17" s="7">
         <v>1018</v>
       </c>
-      <c r="M17" s="83">
+      <c r="N17" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N17" s="83">
+      <c r="O17" s="83">
         <v>0</v>
       </c>
-      <c r="O17" s="21">
+      <c r="P17" s="21">
         <v>35</v>
       </c>
-      <c r="P17" s="64">
+      <c r="Q17" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q17" s="74">
+      <c r="R17" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="S17" s="79"/>
-      <c r="U17" s="89" t="s">
+      <c r="T17" s="79"/>
+      <c r="V17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W17" s="89" t="str">
+      <c r="X17" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B7&amp;"00"</f>
         <v>ELCRESOL_JARVA00</v>
       </c>
-      <c r="X17" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y17" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X17,2)&amp;" in "&amp;Intra_areas!B7&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JARVA - Solar energy</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Z17" t="s">
         <v>180</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>101</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B18" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_JOGEVA00</v>
       </c>
       <c r="C18" s="21" t="str">
@@ -7872,52 +7923,56 @@
       <c r="J18" s="93">
         <v>1</v>
       </c>
-      <c r="K18" s="63">
+      <c r="K18" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L18" s="63">
         <v>0.3</v>
       </c>
-      <c r="L18" s="7">
+      <c r="M18" s="7">
         <v>1018</v>
       </c>
-      <c r="M18" s="83">
+      <c r="N18" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N18" s="83">
+      <c r="O18" s="83">
         <v>0</v>
       </c>
-      <c r="O18" s="21">
+      <c r="P18" s="21">
         <v>35</v>
       </c>
-      <c r="P18" s="64">
+      <c r="Q18" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q18" s="74">
+      <c r="R18" s="74">
         <v>0.15309859852159369</v>
       </c>
-      <c r="S18" s="79"/>
-      <c r="U18" s="89" t="s">
+      <c r="T18" s="79"/>
+      <c r="V18" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W18" s="89" t="str">
+      <c r="X18" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B8&amp;"00"</f>
         <v>ELCRESOL_JOGEVA00</v>
       </c>
-      <c r="X18" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y18" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X18,2)&amp;" in "&amp;Intra_areas!B8&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in JOGEVA - Solar energy</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="Z18" s="104" t="s">
         <v>180</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>101</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B19" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_HARJU00</v>
       </c>
       <c r="C19" s="21" t="str">
@@ -7937,51 +7992,55 @@
       <c r="J19" s="93">
         <v>1</v>
       </c>
-      <c r="K19" s="63">
+      <c r="K19" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L19" s="63">
         <v>0.3</v>
       </c>
-      <c r="L19" s="7">
+      <c r="M19" s="7">
         <v>1018</v>
       </c>
-      <c r="M19" s="83">
+      <c r="N19" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N19" s="83">
+      <c r="O19" s="83">
         <v>0</v>
       </c>
-      <c r="O19" s="21">
+      <c r="P19" s="21">
         <v>35</v>
       </c>
-      <c r="P19" s="64">
+      <c r="Q19" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q19" s="74">
+      <c r="R19" s="74">
         <v>0.15619560585976827</v>
       </c>
-      <c r="U19" s="89" t="s">
+      <c r="V19" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W19" s="89" t="str">
+      <c r="X19" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B9&amp;"00"</f>
         <v>ELCRESOL_HARJU00</v>
       </c>
-      <c r="X19" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y19" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X19,2)&amp;" in "&amp;Intra_areas!B9&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HARJU - Solar energy</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
         <v>180</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
         <v>101</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B20" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_POLVA00</v>
       </c>
       <c r="C20" s="21" t="str">
@@ -8001,51 +8060,55 @@
       <c r="J20" s="93">
         <v>1</v>
       </c>
-      <c r="K20" s="63">
+      <c r="K20" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L20" s="63">
         <v>0.3</v>
       </c>
-      <c r="L20" s="7">
+      <c r="M20" s="7">
         <v>1018</v>
       </c>
-      <c r="M20" s="83">
+      <c r="N20" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N20" s="83">
+      <c r="O20" s="83">
         <v>0</v>
       </c>
-      <c r="O20" s="21">
+      <c r="P20" s="21">
         <v>35</v>
       </c>
-      <c r="P20" s="64">
+      <c r="Q20" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q20" s="74">
+      <c r="R20" s="74">
         <v>0.14537310453496291</v>
       </c>
-      <c r="U20" s="89" t="s">
+      <c r="V20" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W20" s="89" t="str">
+      <c r="X20" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B10&amp;"00"</f>
         <v>ELCRESOL_POLVA00</v>
       </c>
-      <c r="X20" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y20" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X20,2)&amp;" in "&amp;Intra_areas!B10&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in POLVA - Solar energy</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Z20" t="s">
         <v>180</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>101</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_VALGA00</v>
       </c>
       <c r="C21" s="21" t="str">
@@ -8065,51 +8128,55 @@
       <c r="J21" s="93">
         <v>1</v>
       </c>
-      <c r="K21" s="63">
+      <c r="K21" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L21" s="63">
         <v>0.3</v>
       </c>
-      <c r="L21" s="7">
+      <c r="M21" s="7">
         <v>1018</v>
       </c>
-      <c r="M21" s="83">
+      <c r="N21" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N21" s="83">
+      <c r="O21" s="83">
         <v>0</v>
       </c>
-      <c r="O21" s="21">
+      <c r="P21" s="21">
         <v>35</v>
       </c>
-      <c r="P21" s="64">
+      <c r="Q21" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q21" s="74">
+      <c r="R21" s="74">
         <v>0.14763873655681015</v>
       </c>
-      <c r="U21" s="89" t="s">
+      <c r="V21" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W21" s="89" t="str">
+      <c r="X21" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B11&amp;"00"</f>
         <v>ELCRESOL_VALGA00</v>
       </c>
-      <c r="X21" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y21" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X21,2)&amp;" in "&amp;Intra_areas!B11&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VALGA - Solar energy</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Z21" t="s">
         <v>180</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>101</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_VILJANDI00</v>
       </c>
       <c r="C22" s="21" t="str">
@@ -8129,51 +8196,55 @@
       <c r="J22" s="93">
         <v>1</v>
       </c>
-      <c r="K22" s="63">
+      <c r="K22" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L22" s="63">
         <v>0.3</v>
       </c>
-      <c r="L22" s="7">
+      <c r="M22" s="7">
         <v>1018</v>
       </c>
-      <c r="M22" s="83">
+      <c r="N22" s="83">
         <v>16.064040000000002</v>
       </c>
-      <c r="N22" s="83">
+      <c r="O22" s="83">
         <v>0</v>
       </c>
-      <c r="O22" s="21">
+      <c r="P22" s="21">
         <v>35</v>
       </c>
-      <c r="P22" s="64">
+      <c r="Q22" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q22" s="74">
+      <c r="R22" s="74">
         <v>0.1532628310027955</v>
       </c>
-      <c r="U22" s="89" t="s">
+      <c r="V22" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W22" s="89" t="str">
+      <c r="X22" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B12&amp;"00"</f>
         <v>ELCRESOL_VILJANDI00</v>
       </c>
-      <c r="X22" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y22" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X22,2)&amp;" in "&amp;Intra_areas!B12&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VILJANDI - Solar energy</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Z22" t="s">
         <v>180</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AA22" t="s">
         <v>101</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_VORU00</v>
       </c>
       <c r="C23" s="21" t="str">
@@ -8193,51 +8264,55 @@
       <c r="J23" s="93">
         <v>1</v>
       </c>
-      <c r="K23" s="63">
+      <c r="K23" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L23" s="63">
         <v>0.3</v>
       </c>
-      <c r="L23" s="7">
+      <c r="M23" s="7">
         <v>1019</v>
       </c>
-      <c r="M23" s="83">
+      <c r="N23" s="83">
         <v>16.079820000000002</v>
       </c>
-      <c r="N23" s="83">
+      <c r="O23" s="83">
         <v>0</v>
       </c>
-      <c r="O23" s="21">
+      <c r="P23" s="21">
         <v>35</v>
       </c>
-      <c r="P23" s="64">
+      <c r="Q23" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q23" s="74">
+      <c r="R23" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U23" s="89" t="s">
+      <c r="V23" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W23" s="89" t="str">
+      <c r="X23" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B13&amp;"00"</f>
         <v>ELCRESOL_VORU00</v>
       </c>
-      <c r="X23" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y23" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X23,2)&amp;" in "&amp;Intra_areas!B13&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in VORU - Solar energy</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Z23" t="s">
         <v>180</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>101</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B24" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_SAARE00</v>
       </c>
       <c r="C24" s="21" t="str">
@@ -8257,51 +8332,55 @@
       <c r="J24" s="93">
         <v>1</v>
       </c>
-      <c r="K24" s="63">
+      <c r="K24" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L24" s="63">
         <v>0.3</v>
       </c>
-      <c r="L24" s="7">
+      <c r="M24" s="7">
         <v>1020</v>
       </c>
-      <c r="M24" s="83">
+      <c r="N24" s="83">
         <v>16.095600000000001</v>
       </c>
-      <c r="N24" s="83">
+      <c r="O24" s="83">
         <v>0</v>
       </c>
-      <c r="O24" s="21">
+      <c r="P24" s="21">
         <v>35</v>
       </c>
-      <c r="P24" s="64">
+      <c r="Q24" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q24" s="74">
+      <c r="R24" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U24" s="89" t="s">
+      <c r="V24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W24" s="89" t="str">
+      <c r="X24" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B14&amp;"00"</f>
         <v>ELCRESOL_SAARE00</v>
       </c>
-      <c r="X24" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y24" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X24,2)&amp;" in "&amp;Intra_areas!B14&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in SAARE - Solar energy</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Z24" t="s">
         <v>180</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>101</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B25" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_RAPLA00</v>
       </c>
       <c r="C25" s="21" t="str">
@@ -8321,51 +8400,55 @@
       <c r="J25" s="93">
         <v>1</v>
       </c>
-      <c r="K25" s="63">
+      <c r="K25" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L25" s="63">
         <v>0.3</v>
       </c>
-      <c r="L25" s="7">
+      <c r="M25" s="7">
         <v>1021</v>
       </c>
-      <c r="M25" s="83">
+      <c r="N25" s="83">
         <v>16.111380000000004</v>
       </c>
-      <c r="N25" s="83">
+      <c r="O25" s="83">
         <v>0</v>
       </c>
-      <c r="O25" s="21">
+      <c r="P25" s="21">
         <v>35</v>
       </c>
-      <c r="P25" s="64">
+      <c r="Q25" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q25" s="74">
+      <c r="R25" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U25" s="89" t="s">
+      <c r="V25" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W25" s="89" t="str">
+      <c r="X25" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B15&amp;"00"</f>
         <v>ELCRESOL_RAPLA00</v>
       </c>
-      <c r="X25" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y25" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X25,2)&amp;" in "&amp;Intra_areas!B15&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in RAPLA - Solar energy</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Z25" t="s">
         <v>180</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>101</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B26" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_LAANE00</v>
       </c>
       <c r="C26" s="21" t="str">
@@ -8385,51 +8468,55 @@
       <c r="J26" s="93">
         <v>1</v>
       </c>
-      <c r="K26" s="63">
+      <c r="K26" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L26" s="63">
         <v>0.3</v>
       </c>
-      <c r="L26" s="7">
+      <c r="M26" s="7">
         <v>1022</v>
       </c>
-      <c r="M26" s="83">
+      <c r="N26" s="83">
         <v>16.127160000000003</v>
       </c>
-      <c r="N26" s="83">
+      <c r="O26" s="83">
         <v>0</v>
       </c>
-      <c r="O26" s="21">
+      <c r="P26" s="21">
         <v>35</v>
       </c>
-      <c r="P26" s="64">
+      <c r="Q26" s="64">
         <v>8.76</v>
       </c>
-      <c r="Q26" s="74">
+      <c r="R26" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U26" s="89" t="s">
+      <c r="V26" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W26" s="89" t="str">
+      <c r="X26" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B16&amp;"00"</f>
         <v>ELCRESOL_LAANE00</v>
       </c>
-      <c r="X26" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y26" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X26,2)&amp;" in "&amp;Intra_areas!B16&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in LAANE - Solar energy</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>180</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>101</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCRESOL_HIIU00</v>
       </c>
       <c r="C27" s="21" t="str">
@@ -8449,51 +8536,55 @@
       <c r="J27" s="93">
         <v>1</v>
       </c>
-      <c r="K27" s="63">
+      <c r="K27" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L27" s="63">
         <v>0.3</v>
       </c>
-      <c r="L27" s="7">
+      <c r="M27" s="7">
         <v>1023</v>
       </c>
-      <c r="M27" s="83">
+      <c r="N27" s="83">
         <v>16.142940000000003</v>
       </c>
-      <c r="N27" s="83">
+      <c r="O27" s="83">
         <v>0</v>
       </c>
-      <c r="O27" s="21">
+      <c r="P27" s="21">
         <v>35</v>
       </c>
-      <c r="P27" s="21">
+      <c r="Q27" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q27" s="74">
+      <c r="R27" s="74">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U27" s="89" t="s">
+      <c r="V27" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W27" s="89" t="str">
+      <c r="X27" s="89" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$14,3)&amp;"_"&amp;Intra_areas!B17&amp;"00"</f>
         <v>ELCRESOL_HIIU00</v>
       </c>
-      <c r="X27" s="89" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
+      <c r="Y27" s="89" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X27,2)&amp;" in "&amp;Intra_areas!B17&amp;" - "&amp;'EB1'!$T$3</f>
         <v>Power Plants Existing00 in HIIU - Solar energy</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>180</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>101</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B28" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_SOPITOOTSI00</v>
       </c>
       <c r="C28" s="21" t="str">
@@ -8513,51 +8604,55 @@
       <c r="J28" s="93">
         <v>1</v>
       </c>
-      <c r="K28" s="63">
+      <c r="K28" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L28" s="63">
         <v>0.3</v>
       </c>
-      <c r="L28" s="7">
+      <c r="M28" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M28" s="83">
+      <c r="N28" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N28" s="83">
+      <c r="O28" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>27</v>
       </c>
-      <c r="P28" s="21">
+      <c r="Q28" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>0.4</v>
       </c>
-      <c r="U28" s="89" t="s">
+      <c r="V28" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W28" t="str">
+      <c r="X28" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C3&amp;"00"</f>
         <v>ELCREWON_SOPITOOTSI00</v>
       </c>
-      <c r="X28" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y28" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X28,2)&amp;" in "&amp;Intra_areas!C3&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SOPITOOTSI - Wind onshore energy</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>180</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>101</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B29" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_SOPIPURTSE00</v>
       </c>
       <c r="C29" s="21" t="str">
@@ -8577,51 +8672,55 @@
       <c r="J29" s="93">
         <v>1</v>
       </c>
-      <c r="K29" s="63">
+      <c r="K29" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L29" s="63">
         <v>0.3</v>
       </c>
-      <c r="L29" s="7">
+      <c r="M29" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M29" s="83">
+      <c r="N29" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N29" s="83">
+      <c r="O29" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>27</v>
       </c>
-      <c r="P29" s="21">
+      <c r="Q29" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>0.4</v>
       </c>
-      <c r="U29" s="89" t="s">
+      <c r="V29" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W29" t="str">
+      <c r="X29" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C4&amp;"00"</f>
         <v>ELCREWON_SOPIPURTSE00</v>
       </c>
-      <c r="X29" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y29" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X29,2)&amp;" in "&amp;Intra_areas!C4&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SOPIPURTSE - Wind onshore energy</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" t="s">
         <v>180</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>101</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B30" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_OTHER00</v>
       </c>
       <c r="C30" s="21" t="str">
@@ -8641,51 +8740,55 @@
       <c r="J30" s="93">
         <v>1</v>
       </c>
-      <c r="K30" s="63">
+      <c r="K30" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L30" s="63">
         <v>0.3</v>
       </c>
-      <c r="L30" s="7">
+      <c r="M30" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M30" s="83">
+      <c r="N30" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N30" s="83">
+      <c r="O30" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>27</v>
       </c>
-      <c r="P30" s="21">
+      <c r="Q30" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0.4</v>
       </c>
-      <c r="U30" s="89" t="s">
+      <c r="V30" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W30" t="str">
+      <c r="X30" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C5&amp;"00"</f>
         <v>ELCREWON_OTHER00</v>
       </c>
-      <c r="X30" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y30" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X30,2)&amp;" in "&amp;Intra_areas!C5&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in OTHER - Wind onshore energy</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>180</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>101</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B31" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_SAARE00</v>
       </c>
       <c r="C31" s="21" t="str">
@@ -8705,51 +8808,55 @@
       <c r="J31" s="93">
         <v>1</v>
       </c>
-      <c r="K31" s="63">
+      <c r="K31" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L31" s="63">
         <v>0.3</v>
       </c>
-      <c r="L31" s="7">
+      <c r="M31" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M31" s="83">
+      <c r="N31" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N31" s="83">
+      <c r="O31" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>27</v>
       </c>
-      <c r="P31" s="21">
+      <c r="Q31" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.4</v>
       </c>
-      <c r="U31" s="89" t="s">
+      <c r="V31" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W31" t="str">
+      <c r="X31" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C6&amp;"00"</f>
         <v>ELCREWON_SAARE00</v>
       </c>
-      <c r="X31" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y31" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X31,2)&amp;" in "&amp;Intra_areas!C6&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in SAARE - Wind onshore energy</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>180</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>101</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_LVIRU00</v>
       </c>
       <c r="C32" s="21" t="str">
@@ -8769,51 +8876,55 @@
       <c r="J32" s="93">
         <v>1</v>
       </c>
-      <c r="K32" s="63">
+      <c r="K32" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L32" s="63">
         <v>0.3</v>
       </c>
-      <c r="L32" s="7">
+      <c r="M32" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M32" s="83">
+      <c r="N32" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N32" s="83">
+      <c r="O32" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>27</v>
       </c>
-      <c r="P32" s="21">
+      <c r="Q32" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.4</v>
       </c>
-      <c r="U32" s="89" t="s">
+      <c r="V32" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W32" t="str">
+      <c r="X32" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C7&amp;"00"</f>
         <v>ELCREWON_LVIRU00</v>
       </c>
-      <c r="X32" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y32" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X32,2)&amp;" in "&amp;Intra_areas!C7&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in LVIRU - Wind onshore energy</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Z32" t="s">
         <v>180</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>101</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B33" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_HARJU00</v>
       </c>
       <c r="C33" s="21" t="str">
@@ -8833,51 +8944,55 @@
       <c r="J33" s="93">
         <v>1</v>
       </c>
-      <c r="K33" s="63">
+      <c r="K33" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L33" s="63">
         <v>0.3</v>
       </c>
-      <c r="L33" s="7">
+      <c r="M33" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M33" s="83">
+      <c r="N33" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N33" s="83">
+      <c r="O33" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>27</v>
       </c>
-      <c r="P33" s="21">
+      <c r="Q33" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>0.4</v>
       </c>
-      <c r="U33" s="89" t="s">
+      <c r="V33" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W33" t="str">
+      <c r="X33" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C8&amp;"00"</f>
         <v>ELCREWON_HARJU00</v>
       </c>
-      <c r="X33" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y33" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X33,2)&amp;" in "&amp;Intra_areas!C8&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in HARJU - Wind onshore energy</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Z33" t="s">
         <v>180</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>101</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B34" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_LAANE00</v>
       </c>
       <c r="C34" s="21" t="str">
@@ -8897,51 +9012,55 @@
       <c r="J34" s="93">
         <v>1</v>
       </c>
-      <c r="K34" s="63">
+      <c r="K34" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L34" s="63">
         <v>0.3</v>
       </c>
-      <c r="L34" s="7">
+      <c r="M34" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M34" s="83">
+      <c r="N34" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N34" s="83">
+      <c r="O34" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>27</v>
       </c>
-      <c r="P34" s="21">
+      <c r="Q34" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>0.4</v>
       </c>
-      <c r="U34" s="89" t="s">
+      <c r="V34" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W34" t="str">
+      <c r="X34" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C9&amp;"00"</f>
         <v>ELCREWON_LAANE00</v>
       </c>
-      <c r="X34" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y34" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X34,2)&amp;" in "&amp;Intra_areas!C9&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in LAANE - Wind onshore energy</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>180</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AA34" t="s">
         <v>101</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B35" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_IVIRU00</v>
       </c>
       <c r="C35" s="21" t="str">
@@ -8961,51 +9080,55 @@
       <c r="J35" s="93">
         <v>1</v>
       </c>
-      <c r="K35" s="63">
+      <c r="K35" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L35" s="63">
         <v>0.3</v>
       </c>
-      <c r="L35" s="7">
+      <c r="M35" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M35" s="83">
+      <c r="N35" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N35" s="83">
+      <c r="O35" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>27</v>
       </c>
-      <c r="P35" s="21">
+      <c r="Q35" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.4</v>
       </c>
-      <c r="U35" s="89" t="s">
+      <c r="V35" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W35" t="str">
+      <c r="X35" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C10&amp;"00"</f>
         <v>ELCREWON_IVIRU00</v>
       </c>
-      <c r="X35" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y35" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X35,2)&amp;" in "&amp;Intra_areas!C10&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in IVIRU - Wind onshore energy</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="Z35" t="s">
         <v>180</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AA35" t="s">
         <v>101</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AB35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B36" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREWON_PARNU00</v>
       </c>
       <c r="C36" s="21" t="str">
@@ -9025,51 +9148,55 @@
       <c r="J36" s="93">
         <v>1</v>
       </c>
-      <c r="K36" s="63">
+      <c r="K36" s="21">
+        <f t="shared" si="2"/>
+        <v>3.6</v>
+      </c>
+      <c r="L36" s="63">
         <v>0.3</v>
       </c>
-      <c r="L36" s="7">
+      <c r="M36" s="7">
         <v>1494.4630999999999</v>
       </c>
-      <c r="M36" s="83">
+      <c r="N36" s="83">
         <v>18.701711233400001</v>
       </c>
-      <c r="N36" s="83">
+      <c r="O36" s="83">
         <v>2.0036999999999998</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>27</v>
       </c>
-      <c r="P36" s="21">
+      <c r="Q36" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>0.4</v>
       </c>
-      <c r="U36" s="89" t="s">
+      <c r="V36" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W36" t="str">
+      <c r="X36" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$12,3)&amp;"_"&amp;Intra_areas!C11&amp;"00"</f>
         <v>ELCREWON_PARNU00</v>
       </c>
-      <c r="X36" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
+      <c r="Y36" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X36,2)&amp;" in "&amp;Intra_areas!C11&amp;" - "&amp;'EB1'!$R$3</f>
         <v>Power Plants Existing00 in PARNU - Wind onshore energy</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="Z36" t="s">
         <v>180</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AA36" t="s">
         <v>101</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ELCREMSW_IRU00</v>
       </c>
       <c r="C37" s="21" t="str">
@@ -9090,50 +9217,54 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="K37" s="21">
+        <f t="shared" si="2"/>
+        <v>2.0160000000000005</v>
+      </c>
+      <c r="L37" s="21">
         <v>0.9</v>
       </c>
-      <c r="L37" s="79">
+      <c r="M37" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="M37" s="79">
+      <c r="N37" s="79">
         <v>160.216352398</v>
       </c>
-      <c r="N37" s="79">
+      <c r="O37" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="O37" s="79">
+      <c r="P37" s="79">
         <v>53</v>
       </c>
-      <c r="P37" s="21">
+      <c r="Q37" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>1</v>
       </c>
-      <c r="U37" s="89" t="s">
+      <c r="V37" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W37" t="str">
+      <c r="X37" t="str">
         <f>$B$2&amp;$E$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!L15,3)&amp;"_IRU"&amp;"00"</f>
         <v>ELCREMSW_IRU00</v>
       </c>
-      <c r="X37" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W37,2)&amp;" Iru Power plant - Municipal waste"</f>
+      <c r="Y37" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X37,2)&amp;" Iru Power plant - Municipal waste"</f>
         <v>Power Plants Existing00 Iru Power plant - Municipal waste</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Z37" t="s">
         <v>180</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AA37" t="s">
         <v>101</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B38" s="21" t="str">
-        <f>W38</f>
+        <f>X38</f>
         <v>ELCTESHL_EESTI00</v>
       </c>
       <c r="C38" s="21" t="str">
@@ -9154,51 +9285,55 @@
         <v>0.33</v>
       </c>
       <c r="K38" s="21">
+        <f t="shared" si="2"/>
+        <v>1.1880000000000002</v>
+      </c>
+      <c r="L38" s="21">
         <v>0.95</v>
       </c>
-      <c r="L38" s="79">
+      <c r="M38" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="M38" s="79">
+      <c r="N38" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="N38" s="79">
+      <c r="O38" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="O38" s="79">
+      <c r="P38" s="79">
         <v>40</v>
       </c>
-      <c r="P38" s="21">
+      <c r="Q38" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q38" s="21">
+      <c r="R38" s="21">
         <v>1</v>
       </c>
-      <c r="U38" s="89" t="s">
+      <c r="V38" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V38" s="89"/>
-      <c r="W38" s="89" t="str">
+      <c r="W38" s="89"/>
+      <c r="X38" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_EESTI00"</f>
         <v>ELCTESHL_EESTI00</v>
       </c>
-      <c r="X38" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W38,2)&amp;" Eesti Power plant - Oil Shale"</f>
+      <c r="Y38" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X38,2)&amp;" Eesti Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Eesti Power plant - Oil Shale</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="Z38" t="s">
         <v>180</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>101</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B39" s="21" t="str">
-        <f>W39</f>
+        <f>X39</f>
         <v>ELCTESHL_AUVERE00</v>
       </c>
       <c r="C39" s="21" t="str">
@@ -9219,51 +9354,55 @@
         <v>0.33</v>
       </c>
       <c r="K39" s="21">
+        <f t="shared" si="2"/>
+        <v>1.1880000000000002</v>
+      </c>
+      <c r="L39" s="21">
         <v>0.95</v>
       </c>
-      <c r="L39" s="79">
+      <c r="M39" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="M39" s="79">
+      <c r="N39" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="N39" s="79">
+      <c r="O39" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="O39" s="21">
+      <c r="P39" s="21">
         <v>40</v>
       </c>
-      <c r="P39" s="21">
+      <c r="Q39" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q39" s="21">
+      <c r="R39" s="21">
         <v>1</v>
       </c>
-      <c r="U39" s="89" t="s">
+      <c r="V39" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V39" s="89"/>
-      <c r="W39" s="89" t="str">
+      <c r="W39" s="89"/>
+      <c r="X39" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_AUVERE00"</f>
         <v>ELCTESHL_AUVERE00</v>
       </c>
-      <c r="X39" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W39,2)&amp;" Auvere Power plant - Oil Shale"</f>
+      <c r="Y39" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X39,2)&amp;" Auvere Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Auvere Power plant - Oil Shale</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Z39" t="s">
         <v>180</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>101</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B40" s="21" t="str">
-        <f>W40</f>
+        <f>X40</f>
         <v>ELCTESHL_ENEFIT00</v>
       </c>
       <c r="C40" s="21" t="str">
@@ -9284,51 +9423,55 @@
         <v>0.33</v>
       </c>
       <c r="K40" s="21">
+        <f t="shared" si="2"/>
+        <v>1.1880000000000002</v>
+      </c>
+      <c r="L40" s="21">
         <v>0.95</v>
       </c>
-      <c r="L40" s="79">
+      <c r="M40" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="M40" s="79">
+      <c r="N40" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="N40" s="79">
+      <c r="O40" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="O40" s="21">
+      <c r="P40" s="21">
         <v>40</v>
       </c>
-      <c r="P40" s="21">
+      <c r="Q40" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q40" s="21">
+      <c r="R40" s="21">
         <v>1</v>
       </c>
-      <c r="U40" s="89" t="s">
+      <c r="V40" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V40" s="89"/>
-      <c r="W40" s="89" t="str">
+      <c r="W40" s="89"/>
+      <c r="X40" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_ENEFIT00"</f>
         <v>ELCTESHL_ENEFIT00</v>
       </c>
-      <c r="X40" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W40,2)&amp;" Eenefit Power plant - Oil Shale"</f>
+      <c r="Y40" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X40,2)&amp;" Eenefit Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Eenefit Power plant - Oil Shale</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Z40" t="s">
         <v>180</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AA40" t="s">
         <v>101</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B41" s="21" t="str">
-        <f>W41</f>
+        <f>X41</f>
         <v>ELCTESHL_BALTI00</v>
       </c>
       <c r="C41" s="21" t="str">
@@ -9349,51 +9492,55 @@
         <v>0.33</v>
       </c>
       <c r="K41" s="21">
+        <f t="shared" si="2"/>
+        <v>1.1880000000000002</v>
+      </c>
+      <c r="L41" s="21">
         <v>0.95</v>
       </c>
-      <c r="L41" s="79">
+      <c r="M41" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="M41" s="79">
+      <c r="N41" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="N41" s="79">
+      <c r="O41" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="O41" s="21">
+      <c r="P41" s="21">
         <v>40</v>
       </c>
-      <c r="P41" s="21">
+      <c r="Q41" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q41" s="21">
+      <c r="R41" s="21">
         <v>1</v>
       </c>
-      <c r="U41" s="89" t="s">
+      <c r="V41" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V41" s="89"/>
-      <c r="W41" s="89" t="str">
+      <c r="W41" s="89"/>
+      <c r="X41" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_BALTI00"</f>
         <v>ELCTESHL_BALTI00</v>
       </c>
-      <c r="X41" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W41,2)&amp;" Balti Power plant - Oil Shale"</f>
+      <c r="Y41" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X41,2)&amp;" Balti Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Balti Power plant - Oil Shale</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="Z41" t="s">
         <v>180</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AA41" t="s">
         <v>101</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B42" s="21" t="str">
-        <f>W42</f>
+        <f>X42</f>
         <v>ELCTESHL_SILLAMAE00</v>
       </c>
       <c r="C42" s="21" t="str">
@@ -9414,50 +9561,54 @@
         <v>0.33</v>
       </c>
       <c r="K42" s="21">
+        <f t="shared" si="2"/>
+        <v>1.1880000000000002</v>
+      </c>
+      <c r="L42" s="21">
         <v>0.95</v>
       </c>
-      <c r="L42" s="79">
+      <c r="M42" s="79">
         <v>4812.0244000000002</v>
       </c>
-      <c r="M42" s="79">
+      <c r="N42" s="79">
         <v>63.037519640000006</v>
       </c>
-      <c r="N42" s="79">
+      <c r="O42" s="79">
         <v>4.1005000000000003</v>
       </c>
-      <c r="O42" s="21">
+      <c r="P42" s="21">
         <v>40</v>
       </c>
-      <c r="P42" s="21">
+      <c r="Q42" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q42" s="21">
+      <c r="R42" s="21">
         <v>1</v>
       </c>
-      <c r="U42" s="89" t="s">
+      <c r="V42" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W42" s="89" t="str">
+      <c r="X42" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$16,3)&amp;"_SILLAMAE00"</f>
         <v>ELCTESHL_SILLAMAE00</v>
       </c>
-      <c r="X42" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W42,2)&amp;" Sillamae Power plant - Oil Shale"</f>
+      <c r="Y42" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X42,2)&amp;" Sillamae Power plant - Oil Shale"</f>
         <v>Power Plants Existing00 Sillamae Power plant - Oil Shale</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Z42" t="s">
         <v>180</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="AA42" t="s">
         <v>101</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AB42" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B43" s="21" t="str">
-        <f t="shared" ref="B43:B45" si="3">W43</f>
+        <f t="shared" ref="B43:B45" si="4">X43</f>
         <v>ELCTEGAS_POHJA00</v>
       </c>
       <c r="C43" s="21" t="str">
@@ -9478,51 +9629,55 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="K43" s="21">
+        <f t="shared" si="2"/>
+        <v>2.0160000000000005</v>
+      </c>
+      <c r="L43" s="21">
         <v>0.95</v>
       </c>
-      <c r="L43" s="79">
+      <c r="M43" s="79">
         <v>1175.5066999999999</v>
       </c>
-      <c r="M43" s="79">
+      <c r="N43" s="79">
         <v>39.138495576499992</v>
       </c>
-      <c r="N43" s="79">
+      <c r="O43" s="79">
         <v>5.8775000000000004</v>
       </c>
-      <c r="O43" s="79">
+      <c r="P43" s="79">
         <v>40</v>
       </c>
-      <c r="P43" s="21">
+      <c r="Q43" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q43" s="21">
+      <c r="R43" s="21">
         <v>1</v>
       </c>
-      <c r="U43" s="89" t="s">
+      <c r="V43" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="V43" s="89"/>
-      <c r="W43" s="89" t="str">
+      <c r="W43" s="89"/>
+      <c r="X43" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_POHJA00"</f>
         <v>ELCTEGAS_POHJA00</v>
       </c>
-      <c r="X43" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W43,2)&amp;" Pohja Power plant - "&amp;'EB1'!E3</f>
+      <c r="Y43" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X43,2)&amp;" Pohja Power plant - "&amp;'EB1'!E3</f>
         <v>Power Plants Existing00 Pohja Power plant - Natural Gas</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="Z43" t="s">
         <v>180</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AA43" t="s">
         <v>101</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B44" s="21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ELCTEBIO_TLNUTILITAS00</v>
       </c>
       <c r="C44" s="21" t="str">
@@ -9543,50 +9698,54 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="K44" s="21">
+        <f t="shared" si="2"/>
+        <v>1.6848000000000001</v>
+      </c>
+      <c r="L44" s="21">
         <v>0.95</v>
       </c>
-      <c r="L44" s="79">
+      <c r="M44" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="M44" s="79">
+      <c r="N44" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="N44" s="79">
+      <c r="O44" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="O44" s="79">
+      <c r="P44" s="79">
         <v>40</v>
       </c>
-      <c r="P44" s="21">
+      <c r="Q44" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q44" s="21">
+      <c r="R44" s="21">
         <v>1</v>
       </c>
-      <c r="U44" s="89" t="s">
+      <c r="V44" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W44" s="89" t="str">
+      <c r="X44" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TLNUTILITAS00"</f>
         <v>ELCTEBIO_TLNUTILITAS00</v>
       </c>
-      <c r="X44" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W44,2)&amp;" Tallinn Utilitas Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="Y44" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X44,2)&amp;" Tallinn Utilitas Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Tallinn Utilitas Power plant - Biomass</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="Z44" t="s">
         <v>180</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AA44" t="s">
         <v>101</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AB44" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B45" s="21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>ELCTEBIO_TARTU00</v>
       </c>
       <c r="C45" s="21" t="str">
@@ -9607,50 +9766,54 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="K45" s="21">
+        <f t="shared" si="2"/>
+        <v>1.6848000000000001</v>
+      </c>
+      <c r="L45" s="21">
         <v>0.95</v>
       </c>
-      <c r="L45" s="79">
+      <c r="M45" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="M45" s="79">
+      <c r="N45" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="N45" s="79">
+      <c r="O45" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="O45" s="79">
+      <c r="P45" s="79">
         <v>40</v>
       </c>
-      <c r="P45" s="21">
+      <c r="Q45" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q45" s="21">
+      <c r="R45" s="21">
         <v>1</v>
       </c>
-      <c r="U45" s="89" t="s">
+      <c r="V45" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W45" s="89" t="str">
+      <c r="X45" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_TARTU00"</f>
         <v>ELCTEBIO_TARTU00</v>
       </c>
-      <c r="X45" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W45,2)&amp;" Tartu Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="Y45" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X45,2)&amp;" Tartu Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Tartu Power plant - Biomass</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="Z45" t="s">
         <v>180</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AA45" t="s">
         <v>101</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AB45" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B46" s="21" t="str">
-        <f>W46</f>
+        <f>X46</f>
         <v>ELCTEBIO_PARNU00</v>
       </c>
       <c r="C46" s="21" t="str">
@@ -9671,50 +9834,54 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="K46" s="21">
+        <f t="shared" si="2"/>
+        <v>1.6848000000000001</v>
+      </c>
+      <c r="L46" s="21">
         <v>0.95</v>
       </c>
-      <c r="L46" s="79">
+      <c r="M46" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="M46" s="79">
+      <c r="N46" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="N46" s="79">
+      <c r="O46" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="O46" s="79">
+      <c r="P46" s="79">
         <v>40</v>
       </c>
-      <c r="P46" s="21">
+      <c r="Q46" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q46" s="21">
+      <c r="R46" s="21">
         <v>1</v>
       </c>
-      <c r="U46" s="89" t="s">
+      <c r="V46" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W46" s="89" t="str">
+      <c r="X46" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_PARNU00"</f>
         <v>ELCTEBIO_PARNU00</v>
       </c>
-      <c r="X46" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W46,2)&amp;" Parnu Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="Y46" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X46,2)&amp;" Parnu Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Parnu Power plant - Biomass</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="Z46" t="s">
         <v>180</v>
       </c>
-      <c r="Z46" t="s">
+      <c r="AA46" t="s">
         <v>101</v>
       </c>
-      <c r="AA46" t="s">
+      <c r="AB46" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B47" s="21" t="str">
-        <f>W47</f>
+        <f>X47</f>
         <v>ELCTEBIO_HORIZON00</v>
       </c>
       <c r="C47" s="21" t="str">
@@ -9735,50 +9902,54 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="K47" s="21">
+        <f t="shared" si="2"/>
+        <v>1.6848000000000001</v>
+      </c>
+      <c r="L47" s="21">
         <v>0.95</v>
       </c>
-      <c r="L47" s="79">
+      <c r="M47" s="79">
         <v>2950.7891</v>
       </c>
-      <c r="M47" s="79">
+      <c r="N47" s="79">
         <v>133.5792717679</v>
       </c>
-      <c r="N47" s="79">
+      <c r="O47" s="79">
         <v>2.8138000000000001</v>
       </c>
-      <c r="O47" s="79">
+      <c r="P47" s="79">
         <v>40</v>
       </c>
-      <c r="P47" s="21">
+      <c r="Q47" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q47" s="21">
+      <c r="R47" s="21">
         <v>1</v>
       </c>
-      <c r="U47" s="89" t="s">
+      <c r="V47" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W47" s="89" t="str">
+      <c r="X47" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$9,3)&amp;"_HORIZON00"</f>
         <v>ELCTEBIO_HORIZON00</v>
       </c>
-      <c r="X47" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W47,2)&amp;" Horizon Power plant - "&amp;'EB1'!$O$3</f>
+      <c r="Y47" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X47,2)&amp;" Horizon Power plant - "&amp;'EB1'!$O$3</f>
         <v>Power Plants Existing00 Horizon Power plant - Biomass</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="Z47" t="s">
         <v>180</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="AA47" t="s">
         <v>101</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AB47" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B48" s="21" t="str">
-        <f>W48</f>
+        <f>X48</f>
         <v>ELCTEGAS_GRUNE00</v>
       </c>
       <c r="C48" s="21" t="str">
@@ -9799,49 +9970,53 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="K48" s="21">
+        <f t="shared" si="2"/>
+        <v>2.0160000000000005</v>
+      </c>
+      <c r="L48" s="21">
         <v>0.95</v>
       </c>
-      <c r="L48" s="7">
+      <c r="M48" s="7">
         <v>1175.5066999999999</v>
       </c>
-      <c r="M48" s="83">
+      <c r="N48" s="83">
         <v>39.138495576499992</v>
       </c>
-      <c r="N48" s="83">
+      <c r="O48" s="83">
         <v>5.8775000000000004</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>40</v>
       </c>
-      <c r="P48" s="21">
+      <c r="Q48" s="21">
         <v>8.76</v>
       </c>
-      <c r="Q48" s="21">
+      <c r="R48" s="21">
         <v>1</v>
       </c>
-      <c r="U48" s="89" t="s">
+      <c r="V48" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="W48" s="89" t="str">
+      <c r="X48" s="89" t="str">
         <f>$B$2&amp;$C$5&amp;$H$2&amp;RIGHT(Sector_Fuels_ELC!$L$6,3)&amp;"_GRUNE00"</f>
         <v>ELCTEGAS_GRUNE00</v>
       </c>
-      <c r="X48" t="str">
-        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(W48,2)&amp;" GRUNE Power plant - "&amp;'EB1'!$E$3</f>
+      <c r="Y48" t="str">
+        <f>$D$2&amp;" "&amp;$H$1&amp;RIGHT(X48,2)&amp;" GRUNE Power plant - "&amp;'EB1'!$E$3</f>
         <v>Power Plants Existing00 GRUNE Power plant - Natural Gas</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="Z48" t="s">
         <v>180</v>
       </c>
-      <c r="Z48" t="s">
+      <c r="AA48" t="s">
         <v>101</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AB48" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="65529" spans="20:20" x14ac:dyDescent="0.2">
-      <c r="T65529" s="29"/>
+    <row r="65529" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U65529" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10254,7 +10429,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D12" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E12">
@@ -10322,7 +10497,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D13" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E13">
@@ -10390,7 +10565,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D14" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E14">
@@ -10458,7 +10633,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D15" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E15">
@@ -10526,7 +10701,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D16" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E16">
@@ -10594,7 +10769,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D17" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E17">
@@ -10662,7 +10837,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D18" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E18">
@@ -10730,7 +10905,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D19" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E19">
@@ -10794,7 +10969,7 @@
         <v>ELCGAS</v>
       </c>
       <c r="D20" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E20">
@@ -10858,7 +11033,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D21" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E21">
@@ -10922,7 +11097,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D22" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E22">
@@ -10986,7 +11161,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D23" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E23">
@@ -11050,7 +11225,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D24" s="92" t="str">
-        <f>ELC!$W$5</f>
+        <f>ELC!$X$5</f>
         <v>ELC</v>
       </c>
       <c r="E24">
@@ -11410,7 +11585,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="21" t="str">
-        <f>ELC!$W$6</f>
+        <f>ELC!$X$6</f>
         <v>ELCCO2</v>
       </c>
       <c r="C8" s="63">

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792619DC-794A-4EFD-87FE-9336FA30E4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08888B1-4F70-40C0-84D5-6BBB844D8B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2333,7 +2333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="211">
   <si>
     <t>CommName</t>
   </si>
@@ -2953,9 +2953,6 @@
     <t>NCAP_BND~0</t>
   </si>
   <si>
-    <t>PASTI~2025</t>
-  </si>
-  <si>
     <t>TWh2PJ</t>
   </si>
   <si>
@@ -2963,6 +2960,12 @@
   </si>
   <si>
     <t>EFF TWh</t>
+  </si>
+  <si>
+    <t>M€2025/TWh</t>
+  </si>
+  <si>
+    <t>PASTI</t>
   </si>
 </sst>
 </file>
@@ -6996,7 +6999,8 @@
     <col min="12" max="12" width="8.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="21" customWidth="1"/>
+    <col min="16" max="16" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15" style="21" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2" style="21" bestFit="1" customWidth="1"/>
@@ -7176,7 +7180,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="L5" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M5" s="9"/>
       <c r="V5" s="85" t="s">
@@ -7274,7 +7278,7 @@
         <v>160</v>
       </c>
       <c r="G9" s="67" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H9" s="67" t="s">
         <v>144</v>
@@ -7366,10 +7370,10 @@
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L10" s="73" t="s">
         <v>82</v>
@@ -7424,7 +7428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:30" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -7458,9 +7462,8 @@
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2025/GW</v>
       </c>
-      <c r="O11" s="13" t="str">
-        <f>$G$2&amp;"/"&amp;$E$2</f>
-        <v>M€2025/PJ</v>
+      <c r="O11" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="P11" s="13" t="s">
         <v>77</v>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08888B1-4F70-40C0-84D5-6BBB844D8B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569139BA-E0C6-4733-B24E-BDFDD7D95A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9236,7 +9236,7 @@
         <v>5.8775000000000004</v>
       </c>
       <c r="P37" s="79">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="Q37" s="21">
         <v>8.76</v>
@@ -9304,7 +9304,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="P38" s="79">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="21">
         <v>8.76</v>
@@ -9373,7 +9373,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="P39" s="21">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q39" s="21">
         <v>8.76</v>
@@ -9442,7 +9442,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="P40" s="21">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q40" s="21">
         <v>8.76</v>
@@ -9511,7 +9511,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="P41" s="21">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q41" s="21">
         <v>8.76</v>
@@ -9580,7 +9580,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="P42" s="21">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="21">
         <v>8.76</v>

--- a/VT_EE_ELC_V01.xlsx
+++ b/VT_EE_ELC_V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569139BA-E0C6-4733-B24E-BDFDD7D95A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ABDFE5-FEB1-4AAD-9D8D-E1F2E6BC29D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -6318,7 +6318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>37</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:30" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:30" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>37</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:30" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>76</v>
       </c>
@@ -11594,19 +11594,27 @@
       <c r="C8" s="63">
         <v>95</v>
       </c>
-      <c r="D8" s="63">
-        <v>56.1</v>
+      <c r="D8">
+        <v>515</v>
       </c>
       <c r="E8" s="63">
         <v>76.400000000000006</v>
       </c>
-      <c r="F8" s="63">
-        <v>100</v>
+      <c r="F8">
+        <v>900</v>
       </c>
       <c r="G8" s="63">
         <v>41.4</v>
       </c>
       <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D9" s="63">
+        <v>56.1</v>
+      </c>
+      <c r="F9" s="63">
+        <v>100</v>
+      </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="43"/>
